--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFCBAEA2-0C38-415F-8291-9720B28CD14B}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="rfKrMs4lDiuXVCdzkXtVU6oJ2skGT9O+eEH13pZMp4M="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="198">
   <si>
     <t>Signal Type</t>
   </si>
@@ -604,42 +613,50 @@
   </si>
   <si>
     <t>Pump 2 Current</t>
+  </si>
+  <si>
+    <t>SIG-26</t>
+  </si>
+  <si>
+    <t>Master Pump Switch Request</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
@@ -649,44 +666,50 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -876,31 +899,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1001"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.13"/>
-    <col customWidth="1" min="2" max="2" width="8.63"/>
-    <col customWidth="1" min="3" max="4" width="30.5"/>
-    <col customWidth="1" min="5" max="5" width="10.63"/>
-    <col customWidth="1" min="6" max="6" width="14.75"/>
-    <col customWidth="1" min="7" max="7" width="28.88"/>
-    <col customWidth="1" min="8" max="8" width="26.25"/>
-    <col customWidth="1" min="9" max="9" width="16.63"/>
-    <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="11" width="21.63"/>
-    <col customWidth="1" min="12" max="12" width="16.25"/>
-    <col customWidth="1" min="13" max="28" width="8.63"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" customWidth="1"/>
+    <col min="3" max="4" width="30.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" customWidth="1"/>
+    <col min="7" max="7" width="28.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.21875" customWidth="1"/>
+    <col min="13" max="28" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -938,7 +961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -961,7 +984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -984,7 +1007,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1007,7 +1030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -1030,7 +1053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1053,7 +1076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1076,7 +1099,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -1099,7 +1122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -1122,7 +1145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1145,7 +1168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
@@ -1168,7 +1191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
@@ -1191,7 +1214,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1214,7 +1237,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1237,7 +1260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
@@ -1260,7 +1283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
@@ -1283,7 +1306,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>45</v>
       </c>
@@ -1306,7 +1329,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>45</v>
       </c>
@@ -1329,7 +1352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>45</v>
       </c>
@@ -1352,7 +1375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>45</v>
       </c>
@@ -1375,7 +1398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>45</v>
       </c>
@@ -1398,7 +1421,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
@@ -1421,7 +1444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
@@ -1444,7 +1467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
@@ -1467,7 +1490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>45</v>
       </c>
@@ -1490,7 +1513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>45</v>
       </c>
@@ -1513,7 +1536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>45</v>
       </c>
@@ -1536,7 +1559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>45</v>
       </c>
@@ -1559,7 +1582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>45</v>
       </c>
@@ -1582,7 +1605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>45</v>
       </c>
@@ -1605,7 +1628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>45</v>
       </c>
@@ -1628,7 +1651,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>45</v>
       </c>
@@ -1651,7 +1674,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>45</v>
       </c>
@@ -1674,7 +1697,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>45</v>
       </c>
@@ -1697,7 +1720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>45</v>
       </c>
@@ -1720,7 +1743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>45</v>
       </c>
@@ -1743,7 +1766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>45</v>
       </c>
@@ -1766,7 +1789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>45</v>
       </c>
@@ -1789,7 +1812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>45</v>
       </c>
@@ -1812,7 +1835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>45</v>
       </c>
@@ -1823,38 +1846,29 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
+        <v>45</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>15</v>
@@ -1869,15 +1883,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>15</v>
@@ -1892,15 +1906,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>15</v>
@@ -1915,15 +1929,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>15</v>
@@ -1938,15 +1952,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>15</v>
@@ -1961,15 +1975,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>15</v>
@@ -1984,15 +1998,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>15</v>
@@ -2007,15 +2021,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>15</v>
@@ -2030,15 +2044,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>15</v>
@@ -2053,15 +2067,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>15</v>
@@ -2076,15 +2090,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>15</v>
@@ -2099,15 +2113,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>15</v>
@@ -2122,15 +2136,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>15</v>
@@ -2145,15 +2159,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>15</v>
@@ -2168,15 +2182,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>15</v>
@@ -2191,52 +2205,52 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C58" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="E58" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customHeight="1">
+    </row>
+    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>15</v>
@@ -2251,15 +2265,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" ht="14.25" customHeight="1">
+    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>15</v>
@@ -2274,15 +2288,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" ht="14.25" customHeight="1">
+    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>15</v>
@@ -2297,15 +2311,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
+    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>15</v>
@@ -2320,15 +2334,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" ht="14.25" customHeight="1">
+    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>15</v>
@@ -2343,15 +2357,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" ht="14.25" customHeight="1">
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>15</v>
@@ -2366,55 +2380,55 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" ht="14.25" customHeight="1">
+    <row r="65" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C66" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="E66" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="67" ht="14.25" customHeight="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>16</v>
@@ -2426,15 +2440,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>157</v>
@@ -2449,15 +2463,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>157</v>
@@ -2472,18 +2486,18 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" ht="14.25" customHeight="1">
+    <row r="70" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>16</v>
@@ -2495,15 +2509,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>152</v>
@@ -2517,17 +2531,16 @@
       <c r="J71" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="L71" s="5"/>
-    </row>
-    <row r="72" ht="14.25" customHeight="1">
+    </row>
+    <row r="72" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>152</v>
@@ -2541,19 +2554,20 @@
       <c r="J72" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="73" ht="14.25" customHeight="1">
+      <c r="L72" s="5"/>
+    </row>
+    <row r="73" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>16</v>
@@ -2565,15 +2579,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>15</v>
@@ -2588,15 +2602,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>15</v>
@@ -2611,15 +2625,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>15</v>
@@ -2634,15 +2648,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>15</v>
@@ -2651,21 +2665,21 @@
         <v>16</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>15</v>
@@ -2680,15 +2694,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>15</v>
@@ -2703,15 +2717,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>15</v>
@@ -2726,18 +2740,18 @@
         <v>154</v>
       </c>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>16</v>
@@ -2749,49 +2763,58 @@
         <v>154</v>
       </c>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>190</v>
+      <c r="B83" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" ht="14.25" customHeight="1">
+      <c r="I83" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>190</v>
@@ -2800,952 +2823,964 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
-    <row r="137" ht="14.25" customHeight="1"/>
-    <row r="138" ht="14.25" customHeight="1"/>
-    <row r="139" ht="14.25" customHeight="1"/>
-    <row r="140" ht="14.25" customHeight="1"/>
-    <row r="141" ht="14.25" customHeight="1"/>
-    <row r="142" ht="14.25" customHeight="1"/>
-    <row r="143" ht="14.25" customHeight="1"/>
-    <row r="144" ht="14.25" customHeight="1"/>
-    <row r="145" ht="14.25" customHeight="1"/>
-    <row r="146" ht="14.25" customHeight="1"/>
-    <row r="147" ht="14.25" customHeight="1"/>
-    <row r="148" ht="14.25" customHeight="1"/>
-    <row r="149" ht="14.25" customHeight="1"/>
-    <row r="150" ht="14.25" customHeight="1"/>
-    <row r="151" ht="14.25" customHeight="1"/>
-    <row r="152" ht="14.25" customHeight="1"/>
-    <row r="153" ht="14.25" customHeight="1"/>
-    <row r="154" ht="14.25" customHeight="1"/>
-    <row r="155" ht="14.25" customHeight="1"/>
-    <row r="156" ht="14.25" customHeight="1"/>
-    <row r="157" ht="14.25" customHeight="1"/>
-    <row r="158" ht="14.25" customHeight="1"/>
-    <row r="159" ht="14.25" customHeight="1"/>
-    <row r="160" ht="14.25" customHeight="1"/>
-    <row r="161" ht="14.25" customHeight="1"/>
-    <row r="162" ht="14.25" customHeight="1"/>
-    <row r="163" ht="14.25" customHeight="1"/>
-    <row r="164" ht="14.25" customHeight="1"/>
-    <row r="165" ht="14.25" customHeight="1"/>
-    <row r="166" ht="14.25" customHeight="1"/>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
+      <c r="F87" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFCBAEA2-0C38-415F-8291-9720B28CD14B}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0223417-4CEC-493D-9B82-66032F7A71B6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="201">
   <si>
     <t>Signal Type</t>
   </si>
@@ -619,6 +619,15 @@
   </si>
   <si>
     <t>Master Pump Switch Request</t>
+  </si>
+  <si>
+    <t>Deadman</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -906,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1001"/>
+  <dimension ref="A1:M1001"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
@@ -920,10 +929,11 @@
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="21.6640625" customWidth="1"/>
     <col min="12" max="12" width="16.21875" customWidth="1"/>
-    <col min="13" max="28" width="8.6640625" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="28" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -960,8 +970,11 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M1" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -983,8 +996,11 @@
       <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1006,8 +1022,11 @@
       <c r="J3" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1029,8 +1048,11 @@
       <c r="J4" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -1052,8 +1074,11 @@
       <c r="J5" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1100,11 @@
       <c r="J6" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1098,8 +1126,11 @@
       <c r="J7" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -1121,8 +1152,11 @@
       <c r="J8" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -1144,8 +1178,11 @@
       <c r="J9" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1167,8 +1204,11 @@
       <c r="J10" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
@@ -1190,8 +1230,11 @@
       <c r="J11" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
@@ -1213,8 +1256,11 @@
       <c r="J12" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1236,8 +1282,11 @@
       <c r="J13" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1259,8 +1308,11 @@
       <c r="J14" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M14" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
@@ -1282,8 +1334,11 @@
       <c r="J15" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
@@ -1305,8 +1360,11 @@
       <c r="J16" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>45</v>
       </c>
@@ -1328,8 +1386,11 @@
       <c r="J17" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M17" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>45</v>
       </c>
@@ -1351,8 +1412,11 @@
       <c r="J18" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M18" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>45</v>
       </c>
@@ -1374,8 +1438,11 @@
       <c r="J19" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>45</v>
       </c>
@@ -1397,8 +1464,11 @@
       <c r="J20" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>45</v>
       </c>
@@ -1420,8 +1490,11 @@
       <c r="J21" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M21" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
@@ -1443,8 +1516,11 @@
       <c r="J22" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M22" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
@@ -1466,8 +1542,11 @@
       <c r="J23" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
@@ -1489,8 +1568,11 @@
       <c r="J24" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>45</v>
       </c>
@@ -1512,8 +1594,11 @@
       <c r="J25" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M25" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>45</v>
       </c>
@@ -1535,8 +1620,11 @@
       <c r="J26" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>45</v>
       </c>
@@ -1558,8 +1646,11 @@
       <c r="J27" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M27" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>45</v>
       </c>
@@ -1581,8 +1672,11 @@
       <c r="J28" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M28" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>45</v>
       </c>
@@ -1604,8 +1698,11 @@
       <c r="J29" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M29" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>45</v>
       </c>
@@ -1627,8 +1724,11 @@
       <c r="J30" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M30" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>45</v>
       </c>
@@ -1650,8 +1750,11 @@
       <c r="J31" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M31" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>45</v>
       </c>
@@ -1673,8 +1776,11 @@
       <c r="J32" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M32" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>45</v>
       </c>
@@ -1696,8 +1802,11 @@
       <c r="J33" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M33" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>45</v>
       </c>
@@ -1719,8 +1828,11 @@
       <c r="J34" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>45</v>
       </c>
@@ -1742,8 +1854,11 @@
       <c r="J35" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>45</v>
       </c>
@@ -1765,8 +1880,11 @@
       <c r="J36" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>45</v>
       </c>
@@ -1788,8 +1906,11 @@
       <c r="J37" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M37" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>45</v>
       </c>
@@ -1811,8 +1932,11 @@
       <c r="J38" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M38" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>45</v>
       </c>
@@ -1834,8 +1958,11 @@
       <c r="J39" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M39" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>45</v>
       </c>
@@ -1846,7 +1973,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>45</v>
       </c>
@@ -1860,7 +1987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>97</v>
       </c>
@@ -1883,7 +2010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>97</v>
       </c>
@@ -1906,7 +2033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>97</v>
       </c>
@@ -1929,7 +2056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>97</v>
       </c>
@@ -1952,7 +2079,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>97</v>
       </c>
@@ -1975,7 +2102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>97</v>
       </c>
@@ -1998,7 +2125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>97</v>
       </c>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0223417-4CEC-493D-9B82-66032F7A71B6}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67B320DA-B2CA-404F-92C4-037A65440ADB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="rfKrMs4lDiuXVCdzkXtVU6oJ2skGT9O+eEH13pZMp4M="/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="219">
   <si>
     <t>Signal Type</t>
   </si>
@@ -628,13 +639,67 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>SIG-27</t>
+  </si>
+  <si>
+    <t>SIG-28</t>
+  </si>
+  <si>
+    <t>SIG-29</t>
+  </si>
+  <si>
+    <t>SIG-30</t>
+  </si>
+  <si>
+    <t>SIG-31</t>
+  </si>
+  <si>
+    <t>Manual Valve Open %</t>
+  </si>
+  <si>
+    <t>Output Pump 1 Voltage</t>
+  </si>
+  <si>
+    <t>Output Pump 1 Current</t>
+  </si>
+  <si>
+    <t>Output Pump 2 Voltage</t>
+  </si>
+  <si>
+    <t>Output Pump 2 Current</t>
+  </si>
+  <si>
+    <t>SIG-32</t>
+  </si>
+  <si>
+    <t>SIG-33</t>
+  </si>
+  <si>
+    <t>SIG-34</t>
+  </si>
+  <si>
+    <t>SIG-35</t>
+  </si>
+  <si>
+    <t>Measured Pump 1 Voltage</t>
+  </si>
+  <si>
+    <t>Measured Pump 1 Current</t>
+  </si>
+  <si>
+    <t>Measured Pump 2 Voltage</t>
+  </si>
+  <si>
+    <t>Measured Pump 2 Current</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -669,6 +734,11 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -690,7 +760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -699,7 +769,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -715,6 +784,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -915,7 +988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1001"/>
+  <dimension ref="A1:M1010"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
@@ -1977,10 +2050,10 @@
       <c r="A41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" t="s">
         <v>196</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" t="s">
         <v>197</v>
       </c>
       <c r="E41" t="s">
@@ -1989,209 +2062,101 @@
     </row>
     <row r="42" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B43" t="s">
+        <v>202</v>
+      </c>
+      <c r="C43" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>203</v>
+      </c>
+      <c r="C44" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>205</v>
+      </c>
+      <c r="C46" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>211</v>
+      </c>
+      <c r="C47" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B48" t="s">
+        <v>212</v>
+      </c>
+      <c r="C48" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B49" t="s">
+        <v>213</v>
+      </c>
+      <c r="C49" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B50" t="s">
+        <v>214</v>
+      </c>
+      <c r="C50" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2199,10 +2164,10 @@
         <v>97</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>15</v>
@@ -2222,10 +2187,10 @@
         <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>15</v>
@@ -2245,10 +2210,10 @@
         <v>97</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>15</v>
@@ -2268,10 +2233,10 @@
         <v>97</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>15</v>
@@ -2291,10 +2256,10 @@
         <v>97</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>15</v>
@@ -2314,10 +2279,10 @@
         <v>97</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>15</v>
@@ -2337,10 +2302,10 @@
         <v>97</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>15</v>
@@ -2360,24 +2325,33 @@
         <v>97</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>15</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>15</v>
@@ -2394,13 +2368,13 @@
     </row>
     <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>15</v>
@@ -2417,13 +2391,13 @@
     </row>
     <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>15</v>
@@ -2440,13 +2414,13 @@
     </row>
     <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>15</v>
@@ -2463,13 +2437,13 @@
     </row>
     <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>15</v>
@@ -2486,284 +2460,274 @@
     </row>
     <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B68" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C73" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="E73" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B74" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C74" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="E74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B75" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C75" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L72" s="5"/>
-    </row>
-    <row r="73" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="E75" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>16</v>
@@ -2775,18 +2739,18 @@
         <v>154</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>16</v>
@@ -2798,107 +2762,108 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L81" s="5"/>
+    </row>
+    <row r="82" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>152</v>
@@ -2907,21 +2872,21 @@
         <v>16</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>15</v>
@@ -2936,71 +2901,269 @@
         <v>154</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>190</v>
+      <c r="B84" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I84" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>190</v>
+      <c r="B85" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I85" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>193</v>
+      <c r="B86" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I86" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="F96" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3906,7 +4069,17 @@
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1003" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1004" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1007" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1008" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1009" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="683" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A11C8230-6EF5-4368-ABD4-FE67B0E09BA7}"/>
+  <xr:revisionPtr revIDLastSave="914" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD66D6AC-CE73-46A8-AA6B-49DA7A4F6855}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="357">
   <si>
     <t>Signal Type</t>
   </si>
@@ -1089,17 +1090,42 @@
   </si>
   <si>
     <t>wrRTD3</t>
+  </si>
+  <si>
+    <t>MOMENTARY</t>
+  </si>
+  <si>
+    <t>Proface  Type</t>
+  </si>
+  <si>
+    <t>BIT INVERT</t>
+  </si>
+  <si>
+    <t>LAMP</t>
+  </si>
+  <si>
+    <t>NUMERIC</t>
+  </si>
+  <si>
+    <t>Size (Bits)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1178,20 +1204,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1600,33 +1663,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}" name="Table1" displayName="Table1" ref="A1:R97" totalsRowShown="0" headerRowDxfId="18">
-  <autoFilter ref="A1:R97" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}">
-    <filterColumn colId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}" name="Table1" displayName="Table1" ref="A1:T97" totalsRowShown="0" headerRowDxfId="20">
+  <autoFilter ref="A1:T97" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}">
+    <filterColumn colId="0">
       <filters>
-        <filter val="IN-USE"/>
+        <filter val="Switch"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="BOOL"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{423FA6DC-9142-4672-A14E-553234A081EF}" name="Signal Type" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{56D9DA24-EF6A-4F6A-8733-677B62E46902}" name="Tag No" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{A96BC653-60FF-429B-B698-AD90C0B0B0D3}" name="Name" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{706A0F32-C352-4264-929A-BBE84E0336CD}" name="Status" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{C8D7F886-484A-4506-96D7-825482566CEA}" name="Data Type" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{BD2571AB-DE7E-4006-8157-4106695ACD69}" name="Memory Type" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{3B62562F-5D5D-4A72-AC30-A11E0297A3A2}" name="PDU Hexadecimal" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{8719FB6E-76D0-42CA-A6D4-A07F76F787FE}" name="Modbus Address" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{494772C3-DD22-48E6-87F4-54FAD05AA979}" name="Modicon Address" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{E8FE6B00-067F-43B4-AFBC-4B31DC0D3ACD}" name="PLC Memory Address" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{32B52740-581E-4139-B281-3664B4614465}" name="Position" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{E6944375-EF05-45BC-8ADD-793CB19A0ADA}" name="I/O Card Number" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{527E8B44-E1FF-4F80-A269-6A31B18D6394}" name="Channel" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{E82449CF-F378-4789-9FE2-B0D21BD261F7}" name="I/O" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{6CE76123-31FB-4788-B701-5DEA98A3B0AA}" name="Global Variable" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{E1175C2D-C54B-4E1D-8F34-46534F2CFC8A}" name="Program Variable Name" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{70FE0A90-A798-47C6-B87B-28B2D22A1365}" name="Operator Visiblity" dataDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{3FC319EF-8DF3-4168-B3CA-EF31C5FF6669}" name="Deadman" dataDxfId="0"/>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{423FA6DC-9142-4672-A14E-553234A081EF}" name="Signal Type" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{56D9DA24-EF6A-4F6A-8733-677B62E46902}" name="Tag No" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{A96BC653-60FF-429B-B698-AD90C0B0B0D3}" name="Name" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{706A0F32-C352-4264-929A-BBE84E0336CD}" name="Status" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{C8D7F886-484A-4506-96D7-825482566CEA}" name="Data Type" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{BD2571AB-DE7E-4006-8157-4106695ACD69}" name="Memory Type" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{3B62562F-5D5D-4A72-AC30-A11E0297A3A2}" name="PDU Hexadecimal" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{8719FB6E-76D0-42CA-A6D4-A07F76F787FE}" name="Modbus Address" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{494772C3-DD22-48E6-87F4-54FAD05AA979}" name="Modicon Address" dataDxfId="11"/>
+    <tableColumn id="19" xr3:uid="{2564375E-1543-4B77-A111-66D99BB1656A}" name="Proface  Type" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{753ED6D6-F73A-4E76-87DB-792F48C2C75C}" name="Size (Bits)" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{E8FE6B00-067F-43B4-AFBC-4B31DC0D3ACD}" name="PLC Memory Address" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{32B52740-581E-4139-B281-3664B4614465}" name="Position" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{E6944375-EF05-45BC-8ADD-793CB19A0ADA}" name="I/O Card Number" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{527E8B44-E1FF-4F80-A269-6A31B18D6394}" name="Channel" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{E82449CF-F378-4789-9FE2-B0D21BD261F7}" name="I/O" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{6CE76123-31FB-4788-B701-5DEA98A3B0AA}" name="Global Variable" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{E1175C2D-C54B-4E1D-8F34-46534F2CFC8A}" name="Program Variable Name" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{70FE0A90-A798-47C6-B87B-28B2D22A1365}" name="Operator Visiblity" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{3FC319EF-8DF3-4168-B3CA-EF31C5FF6669}" name="Deadman" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1830,7 +1900,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1011"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Z1011"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" customWidth="1"/>
@@ -1841,20 +1914,20 @@
     <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="18.33203125" customWidth="1"/>
     <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" customWidth="1"/>
-    <col min="10" max="10" width="24.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="19.33203125" customWidth="1"/>
-    <col min="13" max="13" width="11.21875" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="15.77734375" customWidth="1"/>
-    <col min="16" max="16" width="23" customWidth="1"/>
-    <col min="17" max="17" width="17.6640625" customWidth="1"/>
-    <col min="18" max="18" width="11.109375" customWidth="1"/>
-    <col min="19" max="33" width="8.6640625" customWidth="1"/>
+    <col min="9" max="11" width="17.33203125" customWidth="1"/>
+    <col min="12" max="12" width="24.5546875" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" customWidth="1"/>
+    <col min="15" max="15" width="11.21875" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="15.77734375" customWidth="1"/>
+    <col min="18" max="18" width="23" customWidth="1"/>
+    <col min="19" max="19" width="17.6640625" customWidth="1"/>
+    <col min="20" max="20" width="11.109375" customWidth="1"/>
+    <col min="21" max="35" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1882,38 +1955,44 @@
       <c r="I1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="X1">
+      <c r="Z1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -1941,10 +2020,10 @@
       <c r="I2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="5" t="s">
@@ -1960,20 +2039,26 @@
         <v>12</v>
       </c>
       <c r="P2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X2">
-        <f>X1+1</f>
+      <c r="T2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z2">
+        <f>Z1+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -2003,40 +2088,46 @@
         <f t="shared" ref="I3:I22" si="1">_xlfn.CONCAT(0,H3+1)</f>
         <v>012289</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K3" s="6">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" t="str">
-        <f>_xlfn.CONCAT("axSW[",X1, "]")</f>
+      <c r="N3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z1, "]")</f>
         <v>axSW[1]</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="S3" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X3">
-        <f t="shared" ref="X3:X66" si="2">X2+1</f>
+      <c r="T3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" ref="Z3:Z5" si="2">Z2+1</f>
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -2067,40 +2158,46 @@
         <f t="shared" si="1"/>
         <v>012290</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K4" s="6">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P4" t="str">
-        <f t="shared" ref="P4:P18" si="4">_xlfn.CONCAT("axSW[",X2, "]")</f>
+      <c r="N4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" t="str">
+        <f t="shared" ref="R4:R5" si="4">_xlfn.CONCAT("axSW[",Z2, "]")</f>
         <v>axSW[2]</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="S4" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X4">
+      <c r="T4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z4">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2131,40 +2228,46 @@
         <f t="shared" si="1"/>
         <v>012291</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K5" s="6">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P5" t="str">
+      <c r="N5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R5" t="str">
         <f t="shared" si="4"/>
         <v>axSW[3]</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="S5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X5">
+      <c r="T5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z5">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -2188,47 +2291,53 @@
         <v>0x3003</v>
       </c>
       <c r="H6" s="7">
-        <f t="shared" si="3"/>
+        <f>H5+1</f>
         <v>12291</v>
       </c>
       <c r="I6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>012292</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K6" s="6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P6" t="str">
-        <f t="shared" si="4"/>
+      <c r="N6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R6" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z4, "]")</f>
         <v>axSW[4]</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="S6" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X6">
-        <f t="shared" si="2"/>
+      <c r="T6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z6">
+        <f>Z5+1</f>
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -2259,40 +2368,46 @@
         <f t="shared" si="1"/>
         <v>012293</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P7" t="str">
-        <f t="shared" si="4"/>
+      <c r="N7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R7" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z5, "]")</f>
         <v>axSW[5]</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="S7" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R7" s="5" t="s">
+      <c r="T7" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="X7">
-        <f t="shared" si="2"/>
+      <c r="Z7">
+        <f>Z6+1</f>
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2323,40 +2438,46 @@
         <f t="shared" si="1"/>
         <v>012294</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P8" t="str">
-        <f t="shared" si="4"/>
+      <c r="N8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R8" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z6, "]")</f>
         <v>axSW[6]</v>
       </c>
-      <c r="Q8" s="6" t="s">
+      <c r="S8" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="T8" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="X8">
-        <f t="shared" si="2"/>
+      <c r="Z8">
+        <f>Z7+1</f>
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -2387,40 +2508,44 @@
         <f t="shared" si="1"/>
         <v>012295</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="6"/>
+      <c r="K9" s="6">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P9" t="str">
-        <f t="shared" si="4"/>
+      <c r="N9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R9" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z7, "]")</f>
         <v>axSW[7]</v>
       </c>
-      <c r="Q9" s="6" t="s">
+      <c r="S9" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X9">
-        <f t="shared" si="2"/>
+      <c r="T9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z9">
+        <f>Z8+1</f>
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -2451,40 +2576,46 @@
         <f t="shared" si="1"/>
         <v>012296</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="K10" s="6">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P10" t="str">
-        <f t="shared" si="4"/>
+      <c r="N10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R10" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z8, "]")</f>
         <v>axSW[8]</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="S10" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X10">
-        <f t="shared" si="2"/>
+      <c r="T10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z10">
+        <f>Z9+1</f>
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -2515,40 +2646,46 @@
         <f t="shared" si="1"/>
         <v>012297</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P11" t="str">
-        <f t="shared" si="4"/>
+      <c r="N11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R11" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z9, "]")</f>
         <v>axSW[9]</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="S11" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X11">
-        <f t="shared" si="2"/>
+      <c r="T11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z11">
+        <f>Z10+1</f>
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -2579,40 +2716,46 @@
         <f t="shared" si="1"/>
         <v>012298</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K12" s="6">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P12" t="str">
-        <f t="shared" si="4"/>
+      <c r="N12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R12" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z10, "]")</f>
         <v>axSW[10]</v>
       </c>
-      <c r="Q12" s="6" t="s">
+      <c r="S12" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X12">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z12">
+        <f>Z11+1</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -2643,40 +2786,46 @@
         <f t="shared" si="1"/>
         <v>012299</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K13" s="6">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P13" t="str">
-        <f t="shared" si="4"/>
+      <c r="N13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R13" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z11, "]")</f>
         <v>axSW[11]</v>
       </c>
-      <c r="Q13" s="6" t="s">
+      <c r="S13" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X13">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z13">
+        <f>Z12+1</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>8</v>
       </c>
@@ -2707,40 +2856,46 @@
         <f t="shared" si="1"/>
         <v>012300</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="K14" s="6">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P14" t="str">
-        <f t="shared" si="4"/>
+      <c r="N14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R14" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z12, "]")</f>
         <v>axSW[12]</v>
       </c>
-      <c r="Q14" s="6" t="s">
+      <c r="S14" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="2"/>
+      <c r="T14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z14">
+        <f>Z13+1</f>
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -2771,40 +2926,46 @@
         <f t="shared" si="1"/>
         <v>012301</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P15" t="str">
-        <f t="shared" si="4"/>
+      <c r="N15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R15" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z13, "]")</f>
         <v>axSW[13]</v>
       </c>
-      <c r="Q15" s="6" t="s">
+      <c r="S15" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="2"/>
+      <c r="T15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z15">
+        <f>Z14+1</f>
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>8</v>
       </c>
@@ -2835,40 +2996,46 @@
         <f t="shared" si="1"/>
         <v>012302</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K16" s="6">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P16" t="str">
-        <f t="shared" si="4"/>
+      <c r="N16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R16" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z14, "]")</f>
         <v>axSW[14]</v>
       </c>
-      <c r="Q16" s="6" t="s">
+      <c r="S16" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X16">
-        <f t="shared" si="2"/>
+      <c r="T16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z16">
+        <f>Z15+1</f>
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -2879,7 +3046,7 @@
         <v>220</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>11</v>
@@ -2899,15 +3066,13 @@
         <f t="shared" si="1"/>
         <v>012303</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="6"/>
+      <c r="K17" s="6">
+        <v>1</v>
+      </c>
+      <c r="L17" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M17" s="5" t="s">
         <v>12</v>
       </c>
@@ -2915,24 +3080,30 @@
         <v>12</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P17" t="str">
-        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R17" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z15, "]")</f>
         <v>axSW[15]</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="S17" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="2"/>
+      <c r="T17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z17">
+        <f>Z16+1</f>
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
@@ -2943,7 +3114,7 @@
         <v>221</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>11</v>
@@ -2956,22 +3127,20 @@
         <v>0x300F</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="3"/>
+        <f>H17+1</f>
         <v>12303</v>
       </c>
       <c r="I18" s="6" t="str">
         <f t="shared" si="1"/>
         <v>012304</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="6"/>
+      <c r="K18" s="6">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="K18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M18" s="5" t="s">
         <v>12</v>
       </c>
@@ -2979,24 +3148,30 @@
         <v>12</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P18" t="str">
-        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R18" t="str">
+        <f>_xlfn.CONCAT("axSW[",Z16, "]")</f>
         <v>axSW[16]</v>
       </c>
-      <c r="Q18" s="6" t="s">
+      <c r="S18" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X18">
-        <f t="shared" si="2"/>
+      <c r="T18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z18">
+        <f>Z17+1</f>
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
@@ -3020,47 +3195,53 @@
         <v>0x3010</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="3"/>
+        <f>H18+1</f>
         <v>12304</v>
       </c>
       <c r="I19" s="6" t="str">
         <f t="shared" si="1"/>
         <v>012305</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K19" s="6">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="K19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P19" t="str">
-        <f>_xlfn.CONCAT("axSIG[",X1,"]")</f>
+      <c r="N19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z1,"]")</f>
         <v>axSIG[1]</v>
       </c>
-      <c r="Q19" s="6" t="s">
+      <c r="S19" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X19">
-        <f t="shared" si="2"/>
+      <c r="T19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z19">
+        <f>Z18+1</f>
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -3091,40 +3272,46 @@
         <f t="shared" si="1"/>
         <v>012306</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K20" s="6">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P20" t="str">
-        <f t="shared" ref="P20:P22" si="5">_xlfn.CONCAT("axSIG[",X2,"]")</f>
+      <c r="N20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R20" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z2,"]")</f>
         <v>axSIG[2]</v>
       </c>
-      <c r="Q20" s="6" t="s">
+      <c r="S20" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="2"/>
+      <c r="T20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z20">
+        <f>Z19+1</f>
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
@@ -3155,40 +3342,46 @@
         <f t="shared" si="1"/>
         <v>012307</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K21" s="6">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="K21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P21" t="str">
-        <f t="shared" si="5"/>
+      <c r="N21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R21" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z3,"]")</f>
         <v>axSIG[3]</v>
       </c>
-      <c r="Q21" s="6" t="s">
+      <c r="S21" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X21">
-        <f t="shared" si="2"/>
+      <c r="T21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z21">
+        <f>Z20+1</f>
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>40</v>
       </c>
@@ -3219,40 +3412,46 @@
         <f t="shared" si="1"/>
         <v>012308</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K22" s="6">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P22" t="str">
-        <f t="shared" si="5"/>
+      <c r="N22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R22" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z4,"]")</f>
         <v>axSIG[4]</v>
       </c>
-      <c r="Q22" s="6" t="s">
+      <c r="S22" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="2"/>
+      <c r="T22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z22">
+        <f>Z21+1</f>
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>40</v>
       </c>
@@ -3280,43 +3479,49 @@
         <v>12548</v>
       </c>
       <c r="I23" s="6" t="str">
-        <f t="shared" ref="I23:I32" si="6">_xlfn.CONCAT(4,H23+1)</f>
+        <f t="shared" ref="I23:I32" si="5">_xlfn.CONCAT(4,H23+1)</f>
         <v>412549</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K23" s="6">
+        <v>32</v>
+      </c>
+      <c r="L23" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="K23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N23" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P23" t="str">
-        <f>_xlfn.CONCAT("arSW[",X1,"]")</f>
+      <c r="N23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R23" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z1,"]")</f>
         <v>arSW[1]</v>
       </c>
-      <c r="Q23" s="6" t="s">
+      <c r="S23" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X23">
-        <f t="shared" si="2"/>
+      <c r="T23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z23">
+        <f>Z22+1</f>
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
@@ -3340,47 +3545,53 @@
         <v>0x3106</v>
       </c>
       <c r="H24" s="7">
-        <f t="shared" ref="H24:H32" si="7">H23+2</f>
+        <f t="shared" ref="H24:H32" si="6">H23+2</f>
         <v>12550</v>
       </c>
       <c r="I24" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>412551</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K24" s="6">
+        <v>32</v>
+      </c>
+      <c r="L24" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="K24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N24" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P24" t="str">
-        <f t="shared" ref="P24:P32" si="8">_xlfn.CONCAT("arSW[",X2,"]")</f>
+      <c r="N24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R24" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z2,"]")</f>
         <v>arSW[2]</v>
       </c>
-      <c r="Q24" s="6" t="s">
+      <c r="S24" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X24">
-        <f t="shared" si="2"/>
+      <c r="T24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z24">
+        <f>Z23+1</f>
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
@@ -3404,47 +3615,53 @@
         <v>0x3108</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12552</v>
       </c>
       <c r="I25" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>412553</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K25" s="6">
+        <v>32</v>
+      </c>
+      <c r="L25" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="K25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P25" t="str">
-        <f t="shared" si="8"/>
+      <c r="N25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R25" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z3,"]")</f>
         <v>arSW[3]</v>
       </c>
-      <c r="Q25" s="6" t="s">
+      <c r="S25" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X25">
-        <f t="shared" si="2"/>
+      <c r="T25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z25">
+        <f>Z24+1</f>
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
@@ -3468,47 +3685,53 @@
         <v>0x310A</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12554</v>
       </c>
       <c r="I26" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>412555</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K26" s="6">
+        <v>32</v>
+      </c>
+      <c r="L26" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="K26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P26" t="str">
-        <f t="shared" si="8"/>
+      <c r="N26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R26" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z4,"]")</f>
         <v>arSW[4]</v>
       </c>
-      <c r="Q26" s="6" t="s">
+      <c r="S26" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X26">
-        <f t="shared" si="2"/>
+      <c r="T26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z26">
+        <f>Z25+1</f>
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>40</v>
       </c>
@@ -3532,47 +3755,53 @@
         <v>0x310C</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12556</v>
       </c>
       <c r="I27" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>412557</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="J27" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K27" s="6">
+        <v>32</v>
+      </c>
+      <c r="L27" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="K27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N27" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P27" t="str">
-        <f t="shared" si="8"/>
+      <c r="N27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R27" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z5,"]")</f>
         <v>arSW[5]</v>
       </c>
-      <c r="Q27" s="6" t="s">
+      <c r="S27" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X27">
-        <f t="shared" si="2"/>
+      <c r="T27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z27">
+        <f>Z26+1</f>
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
@@ -3596,47 +3825,53 @@
         <v>0x310E</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12558</v>
       </c>
       <c r="I28" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>412559</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" s="6">
+        <v>32</v>
+      </c>
+      <c r="L28" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="K28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N28" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P28" t="str">
-        <f t="shared" si="8"/>
+      <c r="N28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R28" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z6,"]")</f>
         <v>arSW[6]</v>
       </c>
-      <c r="Q28" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X28">
-        <f t="shared" si="2"/>
+      <c r="S28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z28">
+        <f>Z27+1</f>
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
@@ -3660,47 +3895,53 @@
         <v>0x3110</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12560</v>
       </c>
       <c r="I29" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>412561</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="J29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="6">
+        <v>32</v>
+      </c>
+      <c r="L29" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="K29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N29" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O29" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P29" t="str">
-        <f t="shared" si="8"/>
+      <c r="N29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R29" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z7,"]")</f>
         <v>arSW[7]</v>
       </c>
-      <c r="Q29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X29">
-        <f t="shared" si="2"/>
+      <c r="S29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z29">
+        <f>Z28+1</f>
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
@@ -3724,47 +3965,53 @@
         <v>0x3112</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12562</v>
       </c>
       <c r="I30" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>412563</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K30" s="6">
+        <v>32</v>
+      </c>
+      <c r="L30" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="K30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N30" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P30" t="str">
-        <f t="shared" si="8"/>
+      <c r="N30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P30" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R30" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z8,"]")</f>
         <v>arSW[8]</v>
       </c>
-      <c r="Q30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X30">
-        <f t="shared" si="2"/>
+      <c r="S30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z30">
+        <f>Z29+1</f>
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
@@ -3788,47 +4035,53 @@
         <v>0x3114</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12564</v>
       </c>
       <c r="I31" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>412565</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K31" s="6">
+        <v>32</v>
+      </c>
+      <c r="L31" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="K31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N31" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O31" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P31" t="str">
-        <f t="shared" si="8"/>
+      <c r="N31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q31" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R31" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z9,"]")</f>
         <v>arSW[9]</v>
       </c>
-      <c r="Q31" s="5" t="s">
+      <c r="S31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="R31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X31">
-        <f t="shared" si="2"/>
+      <c r="T31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z31">
+        <f>Z30+1</f>
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>40</v>
       </c>
@@ -3852,47 +4105,53 @@
         <v>0x3116</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12566</v>
       </c>
       <c r="I32" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>412567</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K32" s="6">
+        <v>32</v>
+      </c>
+      <c r="L32" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="K32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N32" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O32" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P32" t="str">
-        <f t="shared" si="8"/>
+      <c r="N32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q32" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R32" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z10,"]")</f>
         <v>arSW[10]</v>
       </c>
-      <c r="Q32" s="5" t="s">
+      <c r="S32" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="R32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X32">
-        <f t="shared" si="2"/>
+      <c r="T32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z32">
+        <f>Z31+1</f>
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>40</v>
       </c>
@@ -3920,43 +4179,49 @@
         <v>12308</v>
       </c>
       <c r="I33" s="6" t="str">
-        <f t="shared" ref="I33:I44" si="9">_xlfn.CONCAT(0,H33+1)</f>
+        <f t="shared" ref="I33:I44" si="7">_xlfn.CONCAT(0,H33+1)</f>
         <v>012309</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K33" s="6">
+        <v>1</v>
+      </c>
+      <c r="L33" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="K33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M33" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N33" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O33" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P33" t="str">
-        <f>_xlfn.CONCAT("axSIG[",X5,"]")</f>
+      <c r="N33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R33" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z5,"]")</f>
         <v>axSIG[5]</v>
       </c>
-      <c r="Q33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X33">
-        <f t="shared" si="2"/>
+      <c r="S33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z33">
+        <f>Z32+1</f>
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
@@ -3980,47 +4245,53 @@
         <v>0x3015</v>
       </c>
       <c r="H34" s="7">
-        <f t="shared" ref="H34:H42" si="10">H33+1</f>
+        <f t="shared" ref="H34:H42" si="8">H33+1</f>
         <v>12309</v>
       </c>
       <c r="I34" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012310</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K34" s="6">
+        <v>1</v>
+      </c>
+      <c r="L34" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="K34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M34" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N34" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O34" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P34" t="str">
-        <f t="shared" ref="P34:P42" si="11">_xlfn.CONCAT("axSIG[",X6,"]")</f>
+      <c r="N34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R34" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z6,"]")</f>
         <v>axSIG[6]</v>
       </c>
-      <c r="Q34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X34">
-        <f t="shared" si="2"/>
+      <c r="S34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z34">
+        <f>Z33+1</f>
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
@@ -4040,51 +4311,57 @@
         <v>214</v>
       </c>
       <c r="G35" s="5" t="str">
-        <f t="shared" ref="G35:G66" si="12">_xlfn.CONCAT("0x",DEC2HEX(H35))</f>
+        <f t="shared" ref="G35:G66" si="9">_xlfn.CONCAT("0x",DEC2HEX(H35))</f>
         <v>0x3016</v>
       </c>
       <c r="H35" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12310</v>
       </c>
       <c r="I35" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012311</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K35" s="6">
+        <v>1</v>
+      </c>
+      <c r="L35" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="K35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M35" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O35" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P35" t="str">
-        <f t="shared" si="11"/>
+      <c r="N35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R35" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z7,"]")</f>
         <v>axSIG[7]</v>
       </c>
-      <c r="Q35" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X35">
-        <f t="shared" si="2"/>
+      <c r="S35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z35">
+        <f>Z34+1</f>
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>40</v>
       </c>
@@ -4104,51 +4381,57 @@
         <v>214</v>
       </c>
       <c r="G36" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x3017</v>
       </c>
       <c r="H36" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12311</v>
       </c>
       <c r="I36" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012312</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K36" s="6">
+        <v>1</v>
+      </c>
+      <c r="L36" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="K36" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M36" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N36" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O36" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P36" t="str">
-        <f t="shared" si="11"/>
+      <c r="N36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R36" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z8,"]")</f>
         <v>axSIG[8]</v>
       </c>
-      <c r="Q36" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R36" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X36">
-        <f t="shared" si="2"/>
+      <c r="S36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z36">
+        <f>Z35+1</f>
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>40</v>
       </c>
@@ -4168,51 +4451,57 @@
         <v>214</v>
       </c>
       <c r="G37" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x3018</v>
       </c>
       <c r="H37" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12312</v>
       </c>
       <c r="I37" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012313</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K37" s="6">
+        <v>1</v>
+      </c>
+      <c r="L37" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="K37" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M37" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N37" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O37" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P37" t="str">
-        <f t="shared" si="11"/>
+      <c r="N37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R37" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z9,"]")</f>
         <v>axSIG[9]</v>
       </c>
-      <c r="Q37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R37" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X37">
-        <f t="shared" si="2"/>
+      <c r="S37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z37">
+        <f>Z36+1</f>
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
@@ -4232,51 +4521,57 @@
         <v>214</v>
       </c>
       <c r="G38" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x3019</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12313</v>
       </c>
       <c r="I38" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012314</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K38" s="6">
+        <v>1</v>
+      </c>
+      <c r="L38" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="K38" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L38" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M38" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O38" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P38" t="str">
-        <f t="shared" si="11"/>
+      <c r="N38" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P38" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R38" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z10,"]")</f>
         <v>axSIG[10]</v>
       </c>
-      <c r="Q38" s="5" t="s">
+      <c r="S38" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="R38" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X38">
-        <f t="shared" si="2"/>
+      <c r="T38" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z38">
+        <f>Z37+1</f>
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>40</v>
       </c>
@@ -4296,51 +4591,57 @@
         <v>214</v>
       </c>
       <c r="G39" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x301A</v>
       </c>
       <c r="H39" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12314</v>
       </c>
       <c r="I39" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012315</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J39" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K39" s="6">
+        <v>1</v>
+      </c>
+      <c r="L39" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="K39" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L39" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M39" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N39" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O39" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P39" t="str">
-        <f t="shared" si="11"/>
+      <c r="N39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P39" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q39" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R39" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z11,"]")</f>
         <v>axSIG[11]</v>
       </c>
-      <c r="Q39" s="5" t="s">
+      <c r="S39" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="R39" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X39">
-        <f t="shared" si="2"/>
+      <c r="T39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z39">
+        <f>Z38+1</f>
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -4360,51 +4661,57 @@
         <v>214</v>
       </c>
       <c r="G40" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x301B</v>
       </c>
       <c r="H40" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12315</v>
       </c>
       <c r="I40" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012316</v>
       </c>
-      <c r="J40" s="5" t="s">
+      <c r="J40" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K40" s="6">
+        <v>1</v>
+      </c>
+      <c r="L40" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="K40" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N40" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O40" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P40" t="str">
-        <f t="shared" si="11"/>
+      <c r="N40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P40" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R40" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z12,"]")</f>
         <v>axSIG[12]</v>
       </c>
-      <c r="Q40" s="5" t="s">
+      <c r="S40" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="R40" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X40">
-        <f t="shared" si="2"/>
+      <c r="T40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z40">
+        <f>Z39+1</f>
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>40</v>
       </c>
@@ -4424,51 +4731,57 @@
         <v>214</v>
       </c>
       <c r="G41" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x301C</v>
       </c>
       <c r="H41" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12316</v>
       </c>
       <c r="I41" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012317</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="J41" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K41" s="6">
+        <v>1</v>
+      </c>
+      <c r="L41" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="K41" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L41" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M41" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N41" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O41" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P41" t="str">
-        <f t="shared" si="11"/>
+      <c r="N41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R41" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z13,"]")</f>
         <v>axSIG[13]</v>
       </c>
-      <c r="Q41" s="5" t="s">
+      <c r="S41" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="R41" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X41">
-        <f t="shared" si="2"/>
+      <c r="T41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z41">
+        <f>Z40+1</f>
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
@@ -4488,51 +4801,57 @@
         <v>214</v>
       </c>
       <c r="G42" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x301D</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>12317</v>
       </c>
       <c r="I42" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012318</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K42" s="6">
+        <v>1</v>
+      </c>
+      <c r="L42" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="K42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M42" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N42" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O42" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P42" t="str">
-        <f t="shared" si="11"/>
+      <c r="N42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P42" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q42" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R42" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z14,"]")</f>
         <v>axSIG[14]</v>
       </c>
-      <c r="Q42" s="5" t="s">
+      <c r="S42" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="R42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X42">
-        <f t="shared" si="2"/>
+      <c r="T42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z42">
+        <f>Z41+1</f>
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>40</v>
       </c>
@@ -4552,7 +4871,7 @@
         <v>214</v>
       </c>
       <c r="G43" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x309C</v>
       </c>
       <c r="H43" s="5">
@@ -4560,43 +4879,49 @@
         <v>12444</v>
       </c>
       <c r="I43" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012445</v>
       </c>
-      <c r="J43" s="5" t="s">
+      <c r="J43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K43" s="6">
+        <v>32</v>
+      </c>
+      <c r="L43" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="K43" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M43" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N43" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O43" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P43" t="str">
-        <f>_xlfn.CONCAT("adiSW[",X1,"]")</f>
+      <c r="N43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P43" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R43" t="str">
+        <f>_xlfn.CONCAT("adiSW[",Z1,"]")</f>
         <v>adiSW[1]</v>
       </c>
-      <c r="Q43" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R43" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X43">
-        <f t="shared" si="2"/>
+      <c r="S43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z43">
+        <f>Z42+1</f>
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>40</v>
       </c>
@@ -4616,7 +4941,7 @@
         <v>214</v>
       </c>
       <c r="G44" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x301E</v>
       </c>
       <c r="H44">
@@ -4624,43 +4949,49 @@
         <v>12318</v>
       </c>
       <c r="I44" s="6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>012319</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K44" s="6">
+        <v>1</v>
+      </c>
+      <c r="L44" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="K44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M44" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N44" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O44" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P44" t="str">
-        <f>_xlfn.CONCAT("axSIG[",X15,"]")</f>
+      <c r="N44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P44" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q44" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R44" t="str">
+        <f>_xlfn.CONCAT("axSIG[",Z15,"]")</f>
         <v>axSIG[15]</v>
       </c>
-      <c r="Q44" t="s">
-        <v>13</v>
-      </c>
-      <c r="R44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X44">
-        <f t="shared" si="2"/>
+      <c r="S44" t="s">
+        <v>13</v>
+      </c>
+      <c r="T44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z44">
+        <f>Z43+1</f>
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
@@ -4680,7 +5011,7 @@
         <v>214</v>
       </c>
       <c r="G45" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x3118</v>
       </c>
       <c r="H45">
@@ -4688,43 +5019,49 @@
         <v>12568</v>
       </c>
       <c r="I45" s="6" t="str">
-        <f t="shared" ref="I45:I50" si="13">_xlfn.CONCAT(4,H45+1)</f>
+        <f t="shared" ref="I45:I50" si="10">_xlfn.CONCAT(4,H45+1)</f>
         <v>412569</v>
       </c>
-      <c r="J45" s="5" t="s">
+      <c r="J45" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K45" s="6">
+        <v>32</v>
+      </c>
+      <c r="L45" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="K45" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L45" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M45" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N45" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O45" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P45" t="str">
-        <f t="shared" ref="P45:P48" si="14">_xlfn.CONCAT("arSW[",X23,"]")</f>
+      <c r="N45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P45" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q45" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R45" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z23,"]")</f>
         <v>arSW[23]</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="S45" t="s">
         <v>145</v>
       </c>
-      <c r="R45" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X45">
-        <f t="shared" si="2"/>
+      <c r="T45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z45">
+        <f>Z44+1</f>
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
@@ -4744,7 +5081,7 @@
         <v>214</v>
       </c>
       <c r="G46" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x311A</v>
       </c>
       <c r="H46">
@@ -4752,43 +5089,49 @@
         <v>12570</v>
       </c>
       <c r="I46" s="6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>412571</v>
       </c>
-      <c r="J46" s="5" t="s">
+      <c r="J46" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K46" s="6">
+        <v>32</v>
+      </c>
+      <c r="L46" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L46" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M46" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N46" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O46" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P46" t="str">
-        <f t="shared" si="14"/>
+      <c r="N46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P46" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R46" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z24,"]")</f>
         <v>arSW[24]</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="S46" t="s">
         <v>145</v>
       </c>
-      <c r="R46" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X46">
-        <f t="shared" si="2"/>
+      <c r="T46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z46">
+        <f>Z45+1</f>
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
@@ -4808,7 +5151,7 @@
         <v>214</v>
       </c>
       <c r="G47" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x311C</v>
       </c>
       <c r="H47">
@@ -4816,43 +5159,49 @@
         <v>12572</v>
       </c>
       <c r="I47" s="6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>412573</v>
       </c>
-      <c r="J47" s="5" t="s">
+      <c r="J47" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K47" s="6">
+        <v>32</v>
+      </c>
+      <c r="L47" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="K47" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L47" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M47" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N47" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O47" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P47" t="str">
-        <f t="shared" si="14"/>
+      <c r="N47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P47" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q47" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R47" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z25,"]")</f>
         <v>arSW[25]</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="S47" t="s">
         <v>145</v>
       </c>
-      <c r="R47" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X47">
-        <f t="shared" si="2"/>
+      <c r="T47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z47">
+        <f>Z46+1</f>
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>40</v>
       </c>
@@ -4872,7 +5221,7 @@
         <v>214</v>
       </c>
       <c r="G48" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x311E</v>
       </c>
       <c r="H48">
@@ -4880,43 +5229,49 @@
         <v>12574</v>
       </c>
       <c r="I48" s="6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>412575</v>
       </c>
-      <c r="J48" s="5" t="s">
+      <c r="J48" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K48" s="6">
+        <v>32</v>
+      </c>
+      <c r="L48" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="K48" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L48" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M48" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N48" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O48" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P48" t="str">
-        <f t="shared" si="14"/>
+      <c r="N48" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P48" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R48" t="str">
+        <f>_xlfn.CONCAT("arSW[",Z26,"]")</f>
         <v>arSW[26]</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="S48" t="s">
         <v>145</v>
       </c>
-      <c r="R48" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X48">
-        <f t="shared" si="2"/>
+      <c r="T48" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z48">
+        <f>Z47+1</f>
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>40</v>
       </c>
@@ -4936,7 +5291,7 @@
         <v>214</v>
       </c>
       <c r="G49" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x309E</v>
       </c>
       <c r="H49">
@@ -4944,43 +5299,49 @@
         <v>12446</v>
       </c>
       <c r="I49" s="6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>412447</v>
       </c>
-      <c r="J49" s="5" t="s">
+      <c r="J49" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K49" s="6">
+        <v>32</v>
+      </c>
+      <c r="L49" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="K49" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L49" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M49" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N49" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O49" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P49" t="str">
-        <f>_xlfn.CONCAT("adiSW[",X2,"]")</f>
+      <c r="N49" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P49" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q49" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R49" t="str">
+        <f>_xlfn.CONCAT("adiSW[",Z2,"]")</f>
         <v>adiSW[2]</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="S49" t="s">
         <v>145</v>
       </c>
-      <c r="R49" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X49">
-        <f t="shared" si="2"/>
+      <c r="T49" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z49">
+        <f>Z48+1</f>
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>40</v>
       </c>
@@ -5000,7 +5361,7 @@
         <v>214</v>
       </c>
       <c r="G50" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x30A0</v>
       </c>
       <c r="H50">
@@ -5008,43 +5369,49 @@
         <v>12448</v>
       </c>
       <c r="I50" s="6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>412449</v>
       </c>
-      <c r="J50" s="5" t="s">
+      <c r="J50" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K50" s="6">
+        <v>32</v>
+      </c>
+      <c r="L50" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="K50" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L50" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M50" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N50" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O50" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P50" t="str">
-        <f>_xlfn.CONCAT("adiSW[",X3,"]")</f>
+      <c r="N50" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P50" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q50" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R50" t="str">
+        <f>_xlfn.CONCAT("adiSW[",Z3,"]")</f>
         <v>adiSW[3]</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="S50" t="s">
         <v>145</v>
       </c>
-      <c r="R50" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X50">
-        <f t="shared" si="2"/>
+      <c r="T50" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z50">
+        <f>Z49+1</f>
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>89</v>
       </c>
@@ -5064,7 +5431,7 @@
         <v>214</v>
       </c>
       <c r="G51" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x301F</v>
       </c>
       <c r="H51" s="7">
@@ -5072,43 +5439,49 @@
         <v>12319</v>
       </c>
       <c r="I51" s="6" t="str">
-        <f t="shared" ref="I51:I76" si="15">_xlfn.CONCAT(0,H51+1)</f>
+        <f t="shared" ref="I51:I76" si="11">_xlfn.CONCAT(0,H51+1)</f>
         <v>012320</v>
       </c>
-      <c r="J51" s="5" t="s">
+      <c r="J51" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K51" s="6">
+        <v>1</v>
+      </c>
+      <c r="L51" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="K51" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L51" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M51" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N51" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O51" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P51" t="str">
-        <f>_xlfn.CONCAT("axALM[",X1,"]")</f>
+      <c r="N51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P51" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q51" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R51" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z1,"]")</f>
         <v>axALM[1]</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="S51" t="s">
         <v>145</v>
       </c>
-      <c r="R51" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X51">
-        <f t="shared" si="2"/>
+      <c r="T51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z51">
+        <f>Z50+1</f>
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>89</v>
       </c>
@@ -5128,51 +5501,57 @@
         <v>214</v>
       </c>
       <c r="G52" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0x3020</v>
       </c>
       <c r="H52" s="7">
-        <f t="shared" ref="H52:H76" si="16">H51+1</f>
+        <f t="shared" ref="H52:H76" si="12">H51+1</f>
         <v>12320</v>
       </c>
       <c r="I52" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012321</v>
       </c>
-      <c r="J52" s="5" t="s">
+      <c r="J52" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K52" s="6">
+        <v>1</v>
+      </c>
+      <c r="L52" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="K52" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L52" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M52" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N52" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O52" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P52" t="str">
-        <f t="shared" ref="P52:P67" si="17">_xlfn.CONCAT("axALM[",X2,"]")</f>
+      <c r="N52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P52" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q52" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R52" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z2,"]")</f>
         <v>axALM[2]</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="S52" t="s">
         <v>145</v>
       </c>
-      <c r="R52" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X52">
-        <f t="shared" si="2"/>
+      <c r="T52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z52">
+        <f>Z51+1</f>
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>89</v>
       </c>
@@ -5192,51 +5571,57 @@
         <v>214</v>
       </c>
       <c r="G53" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x3021</v>
+      </c>
+      <c r="H53" s="7">
         <f t="shared" si="12"/>
-        <v>0x3021</v>
-      </c>
-      <c r="H53" s="7">
-        <f t="shared" si="16"/>
         <v>12321</v>
       </c>
       <c r="I53" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012322</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="J53" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K53" s="6">
+        <v>1</v>
+      </c>
+      <c r="L53" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K53" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L53" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M53" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N53" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O53" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P53" t="str">
-        <f t="shared" si="17"/>
+      <c r="N53" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P53" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q53" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R53" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z3,"]")</f>
         <v>axALM[3]</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="S53" t="s">
         <v>145</v>
       </c>
-      <c r="R53" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X53">
-        <f t="shared" si="2"/>
+      <c r="T53" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z53">
+        <f>Z52+1</f>
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>89</v>
       </c>
@@ -5256,51 +5641,57 @@
         <v>214</v>
       </c>
       <c r="G54" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x3022</v>
+      </c>
+      <c r="H54" s="7">
         <f t="shared" si="12"/>
-        <v>0x3022</v>
-      </c>
-      <c r="H54" s="7">
-        <f t="shared" si="16"/>
         <v>12322</v>
       </c>
       <c r="I54" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012323</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="J54" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K54" s="6">
+        <v>1</v>
+      </c>
+      <c r="L54" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="K54" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L54" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M54" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N54" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O54" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P54" t="str">
-        <f t="shared" si="17"/>
+      <c r="N54" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O54" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P54" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q54" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R54" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z4,"]")</f>
         <v>axALM[4]</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="S54" t="s">
         <v>145</v>
       </c>
-      <c r="R54" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X54">
-        <f t="shared" si="2"/>
+      <c r="T54" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z54">
+        <f>Z53+1</f>
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>89</v>
       </c>
@@ -5320,51 +5711,57 @@
         <v>214</v>
       </c>
       <c r="G55" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x3023</v>
+      </c>
+      <c r="H55" s="7">
         <f t="shared" si="12"/>
-        <v>0x3023</v>
-      </c>
-      <c r="H55" s="7">
-        <f t="shared" si="16"/>
         <v>12323</v>
       </c>
       <c r="I55" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012324</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="J55" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K55" s="6">
+        <v>1</v>
+      </c>
+      <c r="L55" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="K55" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L55" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M55" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N55" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O55" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P55" t="str">
-        <f t="shared" si="17"/>
+      <c r="N55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P55" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q55" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R55" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z5,"]")</f>
         <v>axALM[5]</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="S55" t="s">
         <v>145</v>
       </c>
-      <c r="R55" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X55">
-        <f t="shared" si="2"/>
+      <c r="T55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z55">
+        <f>Z54+1</f>
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>89</v>
       </c>
@@ -5384,51 +5781,57 @@
         <v>214</v>
       </c>
       <c r="G56" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x3024</v>
+      </c>
+      <c r="H56" s="7">
         <f t="shared" si="12"/>
-        <v>0x3024</v>
-      </c>
-      <c r="H56" s="7">
-        <f t="shared" si="16"/>
         <v>12324</v>
       </c>
       <c r="I56" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012325</v>
       </c>
-      <c r="J56" s="5" t="s">
+      <c r="J56" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K56" s="6">
+        <v>1</v>
+      </c>
+      <c r="L56" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="K56" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L56" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M56" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N56" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O56" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P56" t="str">
-        <f t="shared" si="17"/>
+      <c r="N56" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O56" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q56" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R56" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z6,"]")</f>
         <v>axALM[6]</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="S56" t="s">
         <v>145</v>
       </c>
-      <c r="R56" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X56">
-        <f t="shared" si="2"/>
+      <c r="T56" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z56">
+        <f>Z55+1</f>
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>89</v>
       </c>
@@ -5448,51 +5851,57 @@
         <v>214</v>
       </c>
       <c r="G57" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x3025</v>
+      </c>
+      <c r="H57" s="7">
         <f t="shared" si="12"/>
-        <v>0x3025</v>
-      </c>
-      <c r="H57" s="7">
-        <f t="shared" si="16"/>
         <v>12325</v>
       </c>
       <c r="I57" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012326</v>
       </c>
-      <c r="J57" s="5" t="s">
+      <c r="J57" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K57" s="6">
+        <v>1</v>
+      </c>
+      <c r="L57" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="K57" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L57" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M57" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N57" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O57" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P57" t="str">
-        <f t="shared" si="17"/>
+      <c r="N57" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O57" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P57" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q57" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R57" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z7,"]")</f>
         <v>axALM[7]</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="S57" t="s">
         <v>145</v>
       </c>
-      <c r="R57" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X57">
-        <f t="shared" si="2"/>
+      <c r="T57" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z57">
+        <f>Z56+1</f>
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>89</v>
       </c>
@@ -5512,51 +5921,57 @@
         <v>214</v>
       </c>
       <c r="G58" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x3026</v>
+      </c>
+      <c r="H58" s="7">
         <f t="shared" si="12"/>
-        <v>0x3026</v>
-      </c>
-      <c r="H58" s="7">
-        <f t="shared" si="16"/>
         <v>12326</v>
       </c>
       <c r="I58" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012327</v>
       </c>
-      <c r="J58" s="5" t="s">
+      <c r="J58" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K58" s="6">
+        <v>1</v>
+      </c>
+      <c r="L58" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="K58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L58" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M58" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N58" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O58" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P58" t="str">
-        <f t="shared" si="17"/>
+      <c r="N58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P58" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q58" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R58" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z8,"]")</f>
         <v>axALM[8]</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="S58" t="s">
         <v>145</v>
       </c>
-      <c r="R58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X58">
-        <f t="shared" si="2"/>
+      <c r="T58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z58">
+        <f>Z57+1</f>
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>89</v>
       </c>
@@ -5576,51 +5991,57 @@
         <v>214</v>
       </c>
       <c r="G59" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x3027</v>
+      </c>
+      <c r="H59" s="7">
         <f t="shared" si="12"/>
-        <v>0x3027</v>
-      </c>
-      <c r="H59" s="7">
-        <f t="shared" si="16"/>
         <v>12327</v>
       </c>
       <c r="I59" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012328</v>
       </c>
-      <c r="J59" s="5" t="s">
+      <c r="J59" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K59" s="6">
+        <v>1</v>
+      </c>
+      <c r="L59" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="K59" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L59" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M59" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N59" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O59" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P59" t="str">
-        <f t="shared" si="17"/>
+      <c r="N59" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O59" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P59" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q59" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R59" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z9,"]")</f>
         <v>axALM[9]</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="S59" t="s">
         <v>145</v>
       </c>
-      <c r="R59" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X59">
-        <f t="shared" si="2"/>
+      <c r="T59" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z59">
+        <f>Z58+1</f>
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>89</v>
       </c>
@@ -5640,51 +6061,57 @@
         <v>214</v>
       </c>
       <c r="G60" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x3028</v>
+      </c>
+      <c r="H60" s="7">
         <f t="shared" si="12"/>
-        <v>0x3028</v>
-      </c>
-      <c r="H60" s="7">
-        <f t="shared" si="16"/>
         <v>12328</v>
       </c>
       <c r="I60" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012329</v>
       </c>
-      <c r="J60" s="5" t="s">
+      <c r="J60" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K60" s="6">
+        <v>1</v>
+      </c>
+      <c r="L60" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="K60" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L60" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M60" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N60" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O60" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P60" t="str">
-        <f t="shared" si="17"/>
+      <c r="N60" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O60" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P60" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q60" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R60" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z10,"]")</f>
         <v>axALM[10]</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="S60" t="s">
         <v>145</v>
       </c>
-      <c r="R60" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X60">
-        <f t="shared" si="2"/>
+      <c r="T60" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z60">
+        <f>Z59+1</f>
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>89</v>
       </c>
@@ -5704,51 +6131,57 @@
         <v>214</v>
       </c>
       <c r="G61" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x3029</v>
+      </c>
+      <c r="H61" s="7">
         <f t="shared" si="12"/>
-        <v>0x3029</v>
-      </c>
-      <c r="H61" s="7">
-        <f t="shared" si="16"/>
         <v>12329</v>
       </c>
       <c r="I61" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012330</v>
       </c>
-      <c r="J61" s="5" t="s">
+      <c r="J61" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K61" s="6">
+        <v>1</v>
+      </c>
+      <c r="L61" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="K61" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M61" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N61" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O61" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P61" t="str">
-        <f t="shared" si="17"/>
+      <c r="N61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q61" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R61" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z11,"]")</f>
         <v>axALM[11]</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="S61" t="s">
         <v>145</v>
       </c>
-      <c r="R61" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X61">
-        <f t="shared" si="2"/>
+      <c r="T61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z61">
+        <f>Z60+1</f>
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>89</v>
       </c>
@@ -5768,51 +6201,57 @@
         <v>214</v>
       </c>
       <c r="G62" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x302A</v>
+      </c>
+      <c r="H62" s="7">
         <f t="shared" si="12"/>
-        <v>0x302A</v>
-      </c>
-      <c r="H62" s="7">
-        <f t="shared" si="16"/>
         <v>12330</v>
       </c>
       <c r="I62" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012331</v>
       </c>
-      <c r="J62" s="5" t="s">
+      <c r="J62" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K62" s="6">
+        <v>1</v>
+      </c>
+      <c r="L62" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="K62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L62" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M62" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N62" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O62" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P62" t="str">
-        <f t="shared" si="17"/>
+      <c r="N62" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O62" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P62" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q62" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R62" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z12,"]")</f>
         <v>axALM[12]</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="S62" t="s">
         <v>145</v>
       </c>
-      <c r="R62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X62">
-        <f t="shared" si="2"/>
+      <c r="T62" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z62">
+        <f>Z61+1</f>
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>89</v>
       </c>
@@ -5832,51 +6271,57 @@
         <v>214</v>
       </c>
       <c r="G63" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x302B</v>
+      </c>
+      <c r="H63" s="7">
         <f t="shared" si="12"/>
-        <v>0x302B</v>
-      </c>
-      <c r="H63" s="7">
-        <f t="shared" si="16"/>
         <v>12331</v>
       </c>
       <c r="I63" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012332</v>
       </c>
-      <c r="J63" s="5" t="s">
+      <c r="J63" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K63" s="6">
+        <v>1</v>
+      </c>
+      <c r="L63" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="K63" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L63" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M63" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N63" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O63" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P63" t="str">
-        <f t="shared" si="17"/>
+      <c r="N63" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O63" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P63" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q63" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R63" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z13,"]")</f>
         <v>axALM[13]</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="S63" t="s">
         <v>145</v>
       </c>
-      <c r="R63" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X63">
-        <f t="shared" si="2"/>
+      <c r="T63" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z63">
+        <f>Z62+1</f>
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>89</v>
       </c>
@@ -5896,51 +6341,57 @@
         <v>214</v>
       </c>
       <c r="G64" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x302C</v>
+      </c>
+      <c r="H64" s="7">
         <f t="shared" si="12"/>
-        <v>0x302C</v>
-      </c>
-      <c r="H64" s="7">
-        <f t="shared" si="16"/>
         <v>12332</v>
       </c>
       <c r="I64" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012333</v>
       </c>
-      <c r="J64" s="5" t="s">
+      <c r="J64" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K64" s="6">
+        <v>1</v>
+      </c>
+      <c r="L64" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="K64" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L64" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M64" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N64" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O64" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P64" t="str">
-        <f t="shared" si="17"/>
+      <c r="N64" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O64" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q64" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R64" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z14,"]")</f>
         <v>axALM[14]</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="S64" t="s">
         <v>145</v>
       </c>
-      <c r="R64" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X64">
-        <f t="shared" si="2"/>
+      <c r="T64" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z64">
+        <f>Z63+1</f>
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>89</v>
       </c>
@@ -5960,51 +6411,57 @@
         <v>214</v>
       </c>
       <c r="G65" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x302D</v>
+      </c>
+      <c r="H65" s="7">
         <f t="shared" si="12"/>
-        <v>0x302D</v>
-      </c>
-      <c r="H65" s="7">
-        <f t="shared" si="16"/>
         <v>12333</v>
       </c>
       <c r="I65" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012334</v>
       </c>
-      <c r="J65" s="5" t="s">
+      <c r="J65" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K65" s="6">
+        <v>1</v>
+      </c>
+      <c r="L65" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="K65" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L65" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M65" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N65" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O65" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P65" t="str">
-        <f t="shared" si="17"/>
+      <c r="N65" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O65" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P65" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q65" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R65" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z15,"]")</f>
         <v>axALM[15]</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="S65" t="s">
         <v>145</v>
       </c>
-      <c r="R65" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X65">
-        <f t="shared" si="2"/>
+      <c r="T65" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z65">
+        <f>Z64+1</f>
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>89</v>
       </c>
@@ -6024,51 +6481,57 @@
         <v>214</v>
       </c>
       <c r="G66" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>0x302E</v>
+      </c>
+      <c r="H66" s="7">
         <f t="shared" si="12"/>
-        <v>0x302E</v>
-      </c>
-      <c r="H66" s="7">
-        <f t="shared" si="16"/>
         <v>12334</v>
       </c>
       <c r="I66" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012335</v>
       </c>
-      <c r="J66" s="5" t="s">
+      <c r="J66" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K66" s="6">
+        <v>1</v>
+      </c>
+      <c r="L66" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="K66" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L66" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M66" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N66" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O66" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P66" t="str">
-        <f t="shared" si="17"/>
+      <c r="N66" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O66" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P66" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q66" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R66" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z16,"]")</f>
         <v>axALM[16]</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="S66" t="s">
         <v>145</v>
       </c>
-      <c r="R66" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X66">
-        <f t="shared" si="2"/>
+      <c r="T66" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z66">
+        <f>Z65+1</f>
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>89</v>
       </c>
@@ -6088,51 +6551,57 @@
         <v>214</v>
       </c>
       <c r="G67" s="5" t="str">
-        <f t="shared" ref="G67:G98" si="18">_xlfn.CONCAT("0x",DEC2HEX(H67))</f>
+        <f t="shared" ref="G67:G76" si="13">_xlfn.CONCAT("0x",DEC2HEX(H67))</f>
         <v>0x302F</v>
       </c>
       <c r="H67" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12335</v>
       </c>
       <c r="I67" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012336</v>
       </c>
-      <c r="J67" s="5" t="s">
+      <c r="J67" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K67" s="6">
+        <v>1</v>
+      </c>
+      <c r="L67" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="K67" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L67" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M67" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N67" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O67" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P67" t="str">
-        <f t="shared" si="17"/>
+      <c r="N67" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O67" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P67" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R67" t="str">
+        <f>_xlfn.CONCAT("axALM[",Z17,"]")</f>
         <v>axALM[17]</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="S67" t="s">
         <v>145</v>
       </c>
-      <c r="R67" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X67">
-        <f t="shared" ref="X67:X98" si="19">X66+1</f>
+      <c r="T67" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z67">
+        <f>Z66+1</f>
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>124</v>
       </c>
@@ -6152,51 +6621,57 @@
         <v>214</v>
       </c>
       <c r="G68" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0x3030</v>
       </c>
       <c r="H68" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12336</v>
       </c>
       <c r="I68" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012337</v>
       </c>
-      <c r="J68" s="5" t="s">
+      <c r="J68" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K68" s="6">
+        <v>1</v>
+      </c>
+      <c r="L68" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="K68" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L68" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M68" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N68" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O68" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P68" s="5" t="str">
-        <f>_xlfn.CONCAT("axFLT[",X1,"]")</f>
+      <c r="N68" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O68" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P68" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q68" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R68" s="5" t="str">
+        <f>_xlfn.CONCAT("axFLT[",Z1,"]")</f>
         <v>axFLT[1]</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="S68" t="s">
         <v>145</v>
       </c>
-      <c r="R68" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X68">
-        <f t="shared" si="19"/>
+      <c r="T68" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z68">
+        <f>Z67+1</f>
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>124</v>
       </c>
@@ -6216,51 +6691,57 @@
         <v>214</v>
       </c>
       <c r="G69" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0x3031</v>
       </c>
       <c r="H69" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12337</v>
       </c>
       <c r="I69" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012338</v>
       </c>
-      <c r="J69" s="5" t="s">
+      <c r="J69" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K69" s="6">
+        <v>1</v>
+      </c>
+      <c r="L69" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="K69" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L69" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M69" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N69" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O69" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P69" s="5" t="str">
-        <f t="shared" ref="P69:P76" si="20">_xlfn.CONCAT("axFLT[",X2,"]")</f>
+      <c r="N69" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P69" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R69" s="5" t="str">
+        <f>_xlfn.CONCAT("axFLT[",Z2,"]")</f>
         <v>axFLT[2]</v>
       </c>
-      <c r="Q69" t="s">
+      <c r="S69" t="s">
         <v>145</v>
       </c>
-      <c r="R69" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X69">
-        <f t="shared" si="19"/>
+      <c r="T69" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z69">
+        <f>Z68+1</f>
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>124</v>
       </c>
@@ -6280,51 +6761,57 @@
         <v>214</v>
       </c>
       <c r="G70" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0x3032</v>
       </c>
       <c r="H70" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12338</v>
       </c>
       <c r="I70" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012339</v>
       </c>
-      <c r="J70" s="5" t="s">
+      <c r="J70" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K70" s="6">
+        <v>1</v>
+      </c>
+      <c r="L70" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="K70" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L70" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M70" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N70" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O70" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P70" s="5" t="str">
-        <f t="shared" si="20"/>
+      <c r="N70" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O70" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P70" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q70" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R70" s="5" t="str">
+        <f>_xlfn.CONCAT("axFLT[",Z3,"]")</f>
         <v>axFLT[3]</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="S70" t="s">
         <v>145</v>
       </c>
-      <c r="R70" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X70">
-        <f t="shared" si="19"/>
+      <c r="T70" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z70">
+        <f>Z69+1</f>
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>124</v>
       </c>
@@ -6344,51 +6831,57 @@
         <v>214</v>
       </c>
       <c r="G71" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0x3033</v>
       </c>
       <c r="H71" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12339</v>
       </c>
       <c r="I71" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012340</v>
       </c>
-      <c r="J71" s="5" t="s">
+      <c r="J71" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K71" s="6">
+        <v>1</v>
+      </c>
+      <c r="L71" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="K71" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L71" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M71" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N71" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O71" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P71" s="5" t="str">
-        <f t="shared" si="20"/>
+      <c r="N71" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O71" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P71" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q71" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R71" s="5" t="str">
+        <f>_xlfn.CONCAT("axFLT[",Z4,"]")</f>
         <v>axFLT[4]</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="S71" t="s">
         <v>145</v>
       </c>
-      <c r="R71" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X71">
-        <f t="shared" si="19"/>
+      <c r="T71" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z71">
+        <f>Z70+1</f>
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>124</v>
       </c>
@@ -6408,51 +6901,57 @@
         <v>214</v>
       </c>
       <c r="G72" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0x3034</v>
       </c>
       <c r="H72" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12340</v>
       </c>
       <c r="I72" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012341</v>
       </c>
-      <c r="J72" s="5" t="s">
+      <c r="J72" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K72" s="6">
+        <v>1</v>
+      </c>
+      <c r="L72" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="K72" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L72" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M72" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N72" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O72" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P72" s="5" t="str">
-        <f t="shared" si="20"/>
+      <c r="N72" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O72" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P72" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q72" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R72" s="5" t="str">
+        <f>_xlfn.CONCAT("axFLT[",Z5,"]")</f>
         <v>axFLT[5]</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="S72" t="s">
         <v>145</v>
       </c>
-      <c r="R72" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X72">
-        <f t="shared" si="19"/>
+      <c r="T72" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z72">
+        <f>Z71+1</f>
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>124</v>
       </c>
@@ -6472,51 +6971,57 @@
         <v>214</v>
       </c>
       <c r="G73" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0x3035</v>
       </c>
       <c r="H73" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12341</v>
       </c>
       <c r="I73" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012342</v>
       </c>
-      <c r="J73" s="5" t="s">
+      <c r="J73" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K73" s="6">
+        <v>1</v>
+      </c>
+      <c r="L73" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="K73" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L73" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M73" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N73" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O73" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P73" s="5" t="str">
-        <f t="shared" si="20"/>
+      <c r="N73" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O73" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P73" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q73" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R73" s="5" t="str">
+        <f>_xlfn.CONCAT("axFLT[",Z6,"]")</f>
         <v>axFLT[6]</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="S73" t="s">
         <v>145</v>
       </c>
-      <c r="R73" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X73">
-        <f t="shared" si="19"/>
+      <c r="T73" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z73">
+        <f>Z72+1</f>
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>124</v>
       </c>
@@ -6536,51 +7041,57 @@
         <v>214</v>
       </c>
       <c r="G74" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0x3036</v>
       </c>
       <c r="H74" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12342</v>
       </c>
       <c r="I74" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012343</v>
       </c>
-      <c r="J74" s="5" t="s">
+      <c r="J74" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K74" s="6">
+        <v>1</v>
+      </c>
+      <c r="L74" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="K74" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L74" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M74" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N74" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O74" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P74" s="5" t="str">
-        <f t="shared" si="20"/>
+      <c r="N74" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O74" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P74" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q74" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R74" s="5" t="str">
+        <f>_xlfn.CONCAT("axFLT[",Z7,"]")</f>
         <v>axFLT[7]</v>
       </c>
-      <c r="Q74" t="s">
+      <c r="S74" t="s">
         <v>145</v>
       </c>
-      <c r="R74" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X74">
-        <f t="shared" si="19"/>
+      <c r="T74" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z74">
+        <f>Z73+1</f>
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>124</v>
       </c>
@@ -6600,26 +7111,26 @@
         <v>214</v>
       </c>
       <c r="G75" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0x3037</v>
       </c>
       <c r="H75" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12343</v>
       </c>
       <c r="I75" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012344</v>
       </c>
-      <c r="J75" s="5" t="s">
+      <c r="J75" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K75" s="6">
+        <v>1</v>
+      </c>
+      <c r="L75" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="K75" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L75" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M75" s="5" t="s">
         <v>12</v>
       </c>
@@ -6627,24 +7138,30 @@
         <v>12</v>
       </c>
       <c r="O75" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P75" s="5" t="str">
-        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="P75" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q75" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R75" s="5" t="str">
+        <f>_xlfn.CONCAT("axFLT[",Z8,"]")</f>
         <v>axFLT[8]</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="S75" t="s">
         <v>145</v>
       </c>
-      <c r="R75" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X75">
-        <f t="shared" si="19"/>
+      <c r="T75" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z75">
+        <f>Z74+1</f>
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>124</v>
       </c>
@@ -6664,26 +7181,26 @@
         <v>214</v>
       </c>
       <c r="G76" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0x3038</v>
       </c>
       <c r="H76" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>12344</v>
       </c>
       <c r="I76" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>012345</v>
       </c>
-      <c r="J76" s="5" t="s">
+      <c r="J76" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K76" s="6">
+        <v>1</v>
+      </c>
+      <c r="L76" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="K76" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L76" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="M76" s="5" t="s">
         <v>12</v>
       </c>
@@ -6691,24 +7208,30 @@
         <v>12</v>
       </c>
       <c r="O76" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P76" s="5" t="str">
-        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="P76" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q76" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R76" s="5" t="str">
+        <f>_xlfn.CONCAT("axFLT[",Z9,"]")</f>
         <v>axFLT[9]</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="S76" t="s">
         <v>145</v>
       </c>
-      <c r="R76" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X76">
-        <f t="shared" si="19"/>
+      <c r="T76" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z76">
+        <f>Z75+1</f>
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>141</v>
       </c>
@@ -6736,39 +7259,45 @@
       <c r="I77" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J77" s="5" t="s">
+      <c r="J77" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K77" s="5">
+        <v>16</v>
+      </c>
+      <c r="L77" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="K77">
+      <c r="M77">
         <v>8</v>
       </c>
-      <c r="L77" s="5" t="s">
+      <c r="N77" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="M77">
+      <c r="O77">
         <v>1</v>
       </c>
-      <c r="N77" s="5" t="s">
+      <c r="P77" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O77" s="7" t="s">
+      <c r="Q77" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P77" s="5" t="s">
+      <c r="R77" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="Q77" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R77" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X77">
-        <f t="shared" si="19"/>
+      <c r="S77" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T77" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z77">
+        <f>Z76+1</f>
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>141</v>
       </c>
@@ -6796,39 +7325,45 @@
       <c r="I78" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J78" s="5" t="s">
+      <c r="J78" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K78" s="5">
+        <v>16</v>
+      </c>
+      <c r="L78" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="K78" s="5">
+      <c r="M78" s="5">
         <v>9</v>
       </c>
-      <c r="L78" s="5" t="s">
+      <c r="N78" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="M78" s="5">
+      <c r="O78" s="5">
         <v>1</v>
       </c>
-      <c r="N78" s="5" t="s">
+      <c r="P78" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O78" s="7" t="s">
+      <c r="Q78" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P78" s="5" t="s">
+      <c r="R78" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="Q78" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R78" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X78">
-        <f t="shared" si="19"/>
+      <c r="S78" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T78" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z78">
+        <f>Z77+1</f>
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>141</v>
       </c>
@@ -6856,39 +7391,45 @@
       <c r="I79" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J79" s="5" t="s">
+      <c r="J79" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K79" s="5">
+        <v>16</v>
+      </c>
+      <c r="L79" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="K79" s="5">
+      <c r="M79" s="5">
         <v>9</v>
       </c>
-      <c r="L79" s="5" t="s">
+      <c r="N79" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="M79" s="5">
+      <c r="O79" s="5">
         <v>2</v>
       </c>
-      <c r="N79" s="5" t="s">
+      <c r="P79" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O79" s="7" t="s">
+      <c r="Q79" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P79" s="5" t="s">
+      <c r="R79" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="Q79" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R79" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X79">
-        <f t="shared" si="19"/>
+      <c r="S79" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T79" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z79">
+        <f>Z78+1</f>
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:24" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:26" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>141</v>
       </c>
@@ -6916,39 +7457,45 @@
       <c r="I80" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J80" s="5" t="s">
+      <c r="J80" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K80" s="5">
+        <v>16</v>
+      </c>
+      <c r="L80" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="K80">
+      <c r="M80">
         <v>10</v>
       </c>
-      <c r="L80" s="5" t="s">
+      <c r="N80" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="M80">
+      <c r="O80">
         <v>1</v>
       </c>
-      <c r="N80" s="5" t="s">
+      <c r="P80" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O80" s="7" t="s">
+      <c r="Q80" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P80" s="5" t="s">
+      <c r="R80" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="Q80" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R80" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X80">
-        <f t="shared" si="19"/>
+      <c r="S80" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T80" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z80">
+        <f>Z79+1</f>
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:26" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>141</v>
       </c>
@@ -6976,24 +7523,30 @@
       <c r="I81" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="N81" s="5" t="s">
+      <c r="J81" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K81" s="5">
+        <v>16</v>
+      </c>
+      <c r="P81" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O81" s="7" t="s">
+      <c r="Q81" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Q81" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R81" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X81">
-        <f t="shared" si="19"/>
+      <c r="S81" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T81" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z81">
+        <f>Z80+1</f>
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>141</v>
       </c>
@@ -7021,24 +7574,30 @@
       <c r="I82" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="N82" s="5" t="s">
+      <c r="J82" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K82" s="5">
+        <v>16</v>
+      </c>
+      <c r="P82" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O82" s="7" t="s">
+      <c r="Q82" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Q82" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R82" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X82">
-        <f t="shared" si="19"/>
+      <c r="S82" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T82" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z82">
+        <f>Z81+1</f>
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>141</v>
       </c>
@@ -7066,39 +7625,45 @@
       <c r="I83" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J83" s="5" t="s">
+      <c r="J83" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K83" s="5">
+        <v>16</v>
+      </c>
+      <c r="L83" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="K83">
+      <c r="M83">
         <v>8</v>
       </c>
-      <c r="L83" s="5" t="s">
+      <c r="N83" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="M83">
+      <c r="O83">
         <v>2</v>
       </c>
-      <c r="N83" s="5" t="s">
+      <c r="P83" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O83" s="7" t="s">
+      <c r="Q83" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P83" s="5" t="s">
+      <c r="R83" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="Q83" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R83" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X83">
-        <f t="shared" si="19"/>
+      <c r="S83" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T83" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z83">
+        <f>Z82+1</f>
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>141</v>
       </c>
@@ -7126,39 +7691,45 @@
       <c r="I84" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J84" s="5" t="s">
+      <c r="J84" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K84" s="6">
+        <v>1</v>
+      </c>
+      <c r="L84" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="K84">
+      <c r="M84">
         <v>2</v>
       </c>
-      <c r="L84" s="5" t="s">
+      <c r="N84" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="M84">
+      <c r="O84">
         <v>1</v>
       </c>
-      <c r="N84" s="5" t="s">
+      <c r="P84" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O84" s="7" t="s">
+      <c r="Q84" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P84" s="5" t="s">
+      <c r="R84" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="Q84" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R84" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X84">
-        <f t="shared" si="19"/>
+      <c r="S84" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T84" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z84">
+        <f>Z83+1</f>
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>141</v>
       </c>
@@ -7186,39 +7757,45 @@
       <c r="I85" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J85" s="5" t="s">
+      <c r="J85" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K85" s="6">
+        <v>1</v>
+      </c>
+      <c r="L85" s="5" t="s">
         <v>316</v>
-      </c>
-      <c r="K85">
-        <v>2</v>
-      </c>
-      <c r="L85" s="5" t="s">
-        <v>317</v>
       </c>
       <c r="M85">
         <v>2</v>
       </c>
       <c r="N85" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="O85">
+        <v>2</v>
+      </c>
+      <c r="P85" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O85" s="7" t="s">
+      <c r="Q85" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P85" s="5" t="s">
+      <c r="R85" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="Q85" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R85" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X85">
-        <f t="shared" si="19"/>
+      <c r="S85" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T85" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z85">
+        <f>Z84+1</f>
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>141</v>
       </c>
@@ -7246,39 +7823,45 @@
       <c r="I86" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J86" s="5" t="s">
+      <c r="J86" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K86" s="6">
+        <v>1</v>
+      </c>
+      <c r="L86" s="5" t="s">
         <v>318</v>
-      </c>
-      <c r="K86">
-        <v>1</v>
-      </c>
-      <c r="L86" s="5" t="s">
-        <v>321</v>
       </c>
       <c r="M86">
         <v>1</v>
       </c>
       <c r="N86" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="O86">
+        <v>1</v>
+      </c>
+      <c r="P86" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O86" s="7" t="s">
+      <c r="Q86" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P86" s="5" t="s">
+      <c r="R86" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="Q86" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R86" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X86">
-        <f t="shared" si="19"/>
+      <c r="S86" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T86" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z86">
+        <f>Z85+1</f>
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>141</v>
       </c>
@@ -7306,39 +7889,45 @@
       <c r="I87" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J87" s="5" t="s">
+      <c r="J87" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K87" s="6">
+        <v>1</v>
+      </c>
+      <c r="L87" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="K87">
+      <c r="M87">
         <v>1</v>
       </c>
-      <c r="L87" s="5" t="s">
+      <c r="N87" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="M87">
+      <c r="O87">
         <v>2</v>
       </c>
-      <c r="N87" s="5" t="s">
+      <c r="P87" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O87" s="7" t="s">
+      <c r="Q87" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P87" s="5" t="s">
+      <c r="R87" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="Q87" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R87" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X87">
-        <f t="shared" si="19"/>
+      <c r="S87" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T87" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z87">
+        <f>Z86+1</f>
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>141</v>
       </c>
@@ -7366,39 +7955,45 @@
       <c r="I88" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J88" s="5" t="s">
+      <c r="J88" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K88" s="6">
+        <v>1</v>
+      </c>
+      <c r="L88" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="K88">
+      <c r="M88">
         <v>5</v>
       </c>
-      <c r="L88" s="5" t="s">
+      <c r="N88" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="M88">
+      <c r="O88">
         <v>2</v>
       </c>
-      <c r="N88" s="5" t="s">
+      <c r="P88" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="O88" s="7" t="s">
+      <c r="Q88" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P88" s="5" t="s">
+      <c r="R88" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="Q88" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R88" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X88">
-        <f t="shared" si="19"/>
+      <c r="S88" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T88" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z88">
+        <f>Z87+1</f>
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>141</v>
       </c>
@@ -7426,39 +8021,45 @@
       <c r="I89" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J89" s="5" t="s">
+      <c r="J89" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K89" s="6">
+        <v>1</v>
+      </c>
+      <c r="L89" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="K89">
+      <c r="M89">
         <v>5</v>
       </c>
-      <c r="L89" s="5" t="s">
+      <c r="N89" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="M89">
+      <c r="O89">
         <v>4</v>
       </c>
-      <c r="N89" s="5" t="s">
+      <c r="P89" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="O89" s="7" t="s">
+      <c r="Q89" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P89" s="5" t="s">
+      <c r="R89" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="Q89" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R89" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X89">
-        <f t="shared" si="19"/>
+      <c r="S89" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T89" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z89">
+        <f>Z88+1</f>
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>141</v>
       </c>
@@ -7486,39 +8087,45 @@
       <c r="I90" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J90" s="5" t="s">
+      <c r="J90" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K90" s="6">
+        <v>1</v>
+      </c>
+      <c r="L90" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="K90">
+      <c r="M90">
         <v>5</v>
       </c>
-      <c r="L90" s="5" t="s">
+      <c r="N90" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="M90">
+      <c r="O90">
         <v>1</v>
       </c>
-      <c r="N90" s="5" t="s">
+      <c r="P90" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="O90" s="7" t="s">
+      <c r="Q90" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P90" s="5" t="s">
+      <c r="R90" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="Q90" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R90" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X90">
-        <f t="shared" si="19"/>
+      <c r="S90" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T90" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z90">
+        <f>Z89+1</f>
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>141</v>
       </c>
@@ -7546,39 +8153,45 @@
       <c r="I91" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J91" s="5" t="s">
+      <c r="J91" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K91" s="6">
+        <v>1</v>
+      </c>
+      <c r="L91" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="K91">
+      <c r="M91">
         <v>5</v>
       </c>
-      <c r="L91" s="5" t="s">
+      <c r="N91" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="M91">
+      <c r="O91">
         <v>3</v>
       </c>
-      <c r="N91" s="5" t="s">
+      <c r="P91" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="O91" s="7" t="s">
+      <c r="Q91" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P91" s="5" t="s">
+      <c r="R91" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="Q91" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R91" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X91">
-        <f t="shared" si="19"/>
+      <c r="S91" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T91" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z91">
+        <f>Z90+1</f>
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>141</v>
       </c>
@@ -7606,39 +8219,45 @@
       <c r="I92" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J92" s="5" t="s">
+      <c r="J92" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K92" s="5">
+        <v>16</v>
+      </c>
+      <c r="L92" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="K92">
-        <v>12</v>
-      </c>
-      <c r="L92" s="5" t="s">
+      <c r="M92">
+        <v>12</v>
+      </c>
+      <c r="N92" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="M92">
+      <c r="O92">
         <v>1</v>
       </c>
-      <c r="N92" s="5" t="s">
+      <c r="P92" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="O92" s="7" t="s">
+      <c r="Q92" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P92" s="5" t="s">
+      <c r="R92" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="Q92" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R92" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X92">
-        <f t="shared" si="19"/>
+      <c r="S92" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T92" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z92">
+        <f>Z91+1</f>
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>141</v>
       </c>
@@ -7666,39 +8285,45 @@
       <c r="I93" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J93" s="5" t="s">
+      <c r="J93" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K93" s="6">
+        <v>1</v>
+      </c>
+      <c r="L93" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="K93">
+      <c r="M93">
         <v>2</v>
       </c>
-      <c r="L93" s="5" t="s">
+      <c r="N93" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="M93">
+      <c r="O93">
         <v>3</v>
       </c>
-      <c r="N93" s="5" t="s">
+      <c r="P93" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O93" s="7" t="s">
+      <c r="Q93" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P93" s="5" t="s">
+      <c r="R93" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="Q93" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R93" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X93">
-        <f t="shared" si="19"/>
+      <c r="S93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T93" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z93">
+        <f>Z92+1</f>
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>141</v>
       </c>
@@ -7726,39 +8351,45 @@
       <c r="I94" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J94" s="5" t="s">
+      <c r="J94" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K94" s="5">
+        <v>16</v>
+      </c>
+      <c r="L94" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="K94">
+      <c r="M94">
         <v>11</v>
       </c>
-      <c r="L94" s="5" t="s">
+      <c r="N94" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="M94">
+      <c r="O94">
         <v>1</v>
       </c>
-      <c r="N94" s="5" t="s">
+      <c r="P94" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O94" s="7" t="s">
+      <c r="Q94" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P94" s="5" t="s">
+      <c r="R94" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="Q94" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R94" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X94">
-        <f t="shared" si="19"/>
+      <c r="S94" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T94" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z94">
+        <f>Z93+1</f>
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>141</v>
       </c>
@@ -7786,39 +8417,45 @@
       <c r="I95" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J95" s="5" t="s">
+      <c r="J95" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K95" s="5">
+        <v>16</v>
+      </c>
+      <c r="L95" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="K95">
+      <c r="M95">
         <v>11</v>
       </c>
-      <c r="L95" s="5" t="s">
+      <c r="N95" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="M95">
+      <c r="O95">
         <v>2</v>
       </c>
-      <c r="N95" s="5" t="s">
+      <c r="P95" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O95" s="7" t="s">
+      <c r="Q95" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P95" s="5" t="s">
+      <c r="R95" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="Q95" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R95" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X95">
-        <f t="shared" si="19"/>
+      <c r="S95" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T95" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z95">
+        <f>Z94+1</f>
         <v>95</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>141</v>
       </c>
@@ -7846,39 +8483,45 @@
       <c r="I96" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J96" s="5" t="s">
+      <c r="J96" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K96" s="5">
+        <v>16</v>
+      </c>
+      <c r="L96" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="K96">
+      <c r="M96">
         <v>11</v>
       </c>
-      <c r="L96" s="5" t="s">
+      <c r="N96" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="M96">
+      <c r="O96">
         <v>3</v>
       </c>
-      <c r="N96" s="5" t="s">
+      <c r="P96" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O96" s="7" t="s">
+      <c r="Q96" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P96" s="5" t="s">
+      <c r="R96" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="Q96" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R96" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X96">
-        <f t="shared" si="19"/>
+      <c r="S96" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T96" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z96">
+        <f>Z95+1</f>
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>141</v>
       </c>
@@ -7906,128 +8549,134 @@
       <c r="I97" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J97" s="5" t="s">
+      <c r="J97" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K97" s="5">
+        <v>16</v>
+      </c>
+      <c r="L97" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="K97">
+      <c r="M97">
         <v>11</v>
       </c>
-      <c r="L97" s="5" t="s">
+      <c r="N97" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="M97">
+      <c r="O97">
         <v>4</v>
       </c>
-      <c r="N97" s="5" t="s">
+      <c r="P97" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="O97" s="7" t="s">
+      <c r="Q97" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="P97" s="5" t="s">
+      <c r="R97" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="Q97" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R97" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X97">
-        <f t="shared" si="19"/>
+      <c r="S97" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T97" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z97">
+        <f>Z96+1</f>
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W98">
+    <row r="98" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y98">
         <v>1</v>
       </c>
-      <c r="X98">
-        <f t="shared" si="19"/>
+      <c r="Z98">
+        <f>Z97+1</f>
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W99">
-        <f>W98+1</f>
+    <row r="99" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y99">
+        <f>Y98+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W100">
-        <f t="shared" ref="W100:W112" si="21">W99+1</f>
+    <row r="100" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y100">
+        <f t="shared" ref="Y100:Y112" si="14">Y99+1</f>
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W101">
-        <f t="shared" si="21"/>
+    <row r="101" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y101">
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W102">
-        <f t="shared" si="21"/>
+    <row r="102" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y102">
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W103">
-        <f t="shared" si="21"/>
+    <row r="103" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y103">
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W104">
-        <f t="shared" si="21"/>
+    <row r="104" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y104">
+        <f t="shared" si="14"/>
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W105">
-        <f t="shared" si="21"/>
+    <row r="105" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y105">
+        <f t="shared" si="14"/>
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W106">
-        <f t="shared" si="21"/>
+    <row r="106" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y106">
+        <f t="shared" si="14"/>
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W107">
-        <f t="shared" si="21"/>
+    <row r="107" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y107">
+        <f t="shared" si="14"/>
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W108">
-        <f t="shared" si="21"/>
+    <row r="108" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y108">
+        <f t="shared" si="14"/>
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W109">
-        <f t="shared" si="21"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="110" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W110">
-        <f t="shared" si="21"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W111">
-        <f t="shared" si="21"/>
+    <row r="109" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y109">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y110">
+        <f t="shared" si="14"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y111">
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W112">
-        <f t="shared" si="21"/>
+    <row r="112" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y112">
+        <f t="shared" si="14"/>
         <v>15</v>
       </c>
     </row>
@@ -8931,11 +9580,1368 @@
     <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1011" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup scale="32" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D08089E4-07FF-4E11-BB0F-BCF5A936B571}">
+  <dimension ref="A1:D224"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="D1">
+        <f>12288</f>
+        <v>12288</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <f>A1+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f t="shared" ref="A3:A66" si="0">A2+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <f t="shared" ref="A67:A130" si="1">A66+1</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <f t="shared" ref="A131:A194" si="2">A130+1</f>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <f t="shared" si="2"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <f t="shared" si="2"/>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <f t="shared" si="2"/>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <f t="shared" si="2"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <f t="shared" si="2"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <f t="shared" si="2"/>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <f t="shared" si="2"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <f t="shared" si="2"/>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <f t="shared" si="2"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <f t="shared" si="2"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <f t="shared" si="2"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <f t="shared" si="2"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <f t="shared" si="2"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <f t="shared" si="2"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <f t="shared" si="2"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <f t="shared" si="2"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <f t="shared" si="2"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <f t="shared" si="2"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <f t="shared" si="2"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <f t="shared" si="2"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <f t="shared" si="2"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <f t="shared" si="2"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <f t="shared" si="2"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <f t="shared" si="2"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <f t="shared" si="2"/>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <f t="shared" si="2"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <f t="shared" si="2"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <f t="shared" si="2"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <f t="shared" si="2"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <f t="shared" si="2"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <f t="shared" si="2"/>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <f t="shared" si="2"/>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <f t="shared" si="2"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <f t="shared" si="2"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <f t="shared" ref="A195:A224" si="3">A194+1</f>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <f t="shared" si="3"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <f t="shared" si="3"/>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <f t="shared" si="3"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <f t="shared" si="3"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <f t="shared" si="3"/>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <f t="shared" si="3"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <f t="shared" si="3"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <f t="shared" si="3"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <f t="shared" si="3"/>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <f t="shared" si="3"/>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <f t="shared" si="3"/>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <f t="shared" si="3"/>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <f t="shared" si="3"/>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <f t="shared" si="3"/>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <f t="shared" si="3"/>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <f t="shared" si="3"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <f t="shared" si="3"/>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <f t="shared" si="3"/>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <f t="shared" si="3"/>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <f t="shared" si="3"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <f t="shared" si="3"/>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <f t="shared" si="3"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <f t="shared" si="3"/>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <f t="shared" si="3"/>
+        <v>224</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1360" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A76EF951-0BDE-471D-90C0-BEEA5C8EE1F3}"/>
+  <xr:revisionPtr revIDLastSave="1385" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAC1873A-B054-405F-9D44-E2C388A82159}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="287">
   <si>
     <t>Signal Type</t>
   </si>
@@ -134,9 +134,6 @@
   </si>
   <si>
     <t>SW-7</t>
-  </si>
-  <si>
-    <t>Force Valve Open/Close</t>
   </si>
   <si>
     <t>SW-8</t>
@@ -472,9 +469,6 @@
     <t>FLT-8</t>
   </si>
   <si>
-    <t xml:space="preserve">Overflow/EOTW </t>
-  </si>
-  <si>
     <t>Physical</t>
   </si>
   <si>
@@ -514,13 +508,7 @@
     <t>PHY-5</t>
   </si>
   <si>
-    <t xml:space="preserve">Pump 1 Power </t>
-  </si>
-  <si>
     <t>PHY-6</t>
-  </si>
-  <si>
-    <t>Pump 2 Power</t>
   </si>
   <si>
     <t>PHY-7</t>
@@ -598,9 +586,6 @@
     <t>PHY-20</t>
   </si>
   <si>
-    <t>Pump 2 Voltage</t>
-  </si>
-  <si>
     <t>PHY-21</t>
   </si>
   <si>
@@ -626,9 +611,6 @@
   </si>
   <si>
     <t>SIG-32</t>
-  </si>
-  <si>
-    <t>Measured Pump 2 Current</t>
   </si>
   <si>
     <t>SW-0</t>
@@ -686,12 +668,6 @@
   </si>
   <si>
     <t>SW-16</t>
-  </si>
-  <si>
-    <t>Pump 1 EOL Ack</t>
-  </si>
-  <si>
-    <t>Pump 2 EOL Ack</t>
   </si>
   <si>
     <t>INTERNAL I/O</t>
@@ -901,9 +877,6 @@
     <t>Valve Position Signal</t>
   </si>
   <si>
-    <t>Active Pump Power Signal</t>
-  </si>
-  <si>
     <t>Bingo Pumps</t>
   </si>
   <si>
@@ -941,6 +914,12 @@
   </si>
   <si>
     <t>NUMRIC</t>
+  </si>
+  <si>
+    <t>AVAILABLE</t>
+  </si>
+  <si>
+    <t>Bad Valve Pos</t>
   </si>
 </sst>
 </file>
@@ -1521,19 +1500,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}" name="Table1" displayName="Table1" ref="A1:T102" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:T102" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Internal"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="DINT"/>
-        <filter val="REAL"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T102" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{423FA6DC-9142-4672-A14E-553234A081EF}" name="Signal Type" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{56D9DA24-EF6A-4F6A-8733-677B62E46902}" name="Tag No" dataDxfId="19"/>
@@ -1796,40 +1763,40 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>4</v>
@@ -1844,21 +1811,21 @@
         <v>7</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>12</v>
@@ -1900,16 +1867,16 @@
         <v>12</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -1920,13 +1887,13 @@
         <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G3" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H3))</f>
@@ -1941,7 +1908,7 @@
         <v>012289</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K3" s="6">
         <v>1</v>
@@ -1970,13 +1937,13 @@
         <v>axSW[]</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -1987,13 +1954,13 @@
         <v>15</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G4" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H4))</f>
@@ -2008,7 +1975,7 @@
         <v>012290</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K4" s="6">
         <v>1</v>
@@ -2037,13 +2004,13 @@
         <v>axSW[]</v>
       </c>
       <c r="S4" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T4" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2054,13 +2021,13 @@
         <v>17</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G5" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H5))</f>
@@ -2075,7 +2042,7 @@
         <v>012291</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K5" s="6">
         <v>1</v>
@@ -2104,13 +2071,13 @@
         <v>axSW[]</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -2121,13 +2088,13 @@
         <v>19</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G6" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H6))</f>
@@ -2142,7 +2109,7 @@
         <v>012292</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
@@ -2171,13 +2138,13 @@
         <v>axSW[]</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -2188,13 +2155,13 @@
         <v>21</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G7" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H7))</f>
@@ -2209,7 +2176,7 @@
         <v>012293</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K7" s="6">
         <v>1</v>
@@ -2238,13 +2205,13 @@
         <v>axSW[]</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2255,13 +2222,13 @@
         <v>23</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G8" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H8))</f>
@@ -2276,7 +2243,7 @@
         <v>012294</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K8" s="6">
         <v>1</v>
@@ -2305,13 +2272,13 @@
         <v>axSW[]</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -2319,16 +2286,16 @@
         <v>24</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>25</v>
+        <v>285</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G9" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H9))</f>
@@ -2372,30 +2339,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>27</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G10" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H10))</f>
@@ -2410,7 +2377,7 @@
         <v>012296</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K10" s="6">
         <v>1</v>
@@ -2439,30 +2406,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="D11" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G11" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H11))</f>
@@ -2477,7 +2444,7 @@
         <v>012297</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K11" s="6">
         <v>1</v>
@@ -2506,30 +2473,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T11" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="D12" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G12" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H12))</f>
@@ -2544,7 +2511,7 @@
         <v>012298</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
@@ -2573,30 +2540,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T12" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="D13" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G13" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H13))</f>
@@ -2611,7 +2578,7 @@
         <v>012299</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K13" s="6">
         <v>1</v>
@@ -2640,30 +2607,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T13" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>35</v>
-      </c>
       <c r="D14" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G14" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H14))</f>
@@ -2678,7 +2645,7 @@
         <v>012300</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K14" s="6">
         <v>1</v>
@@ -2707,30 +2674,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T14" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="D15" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G15" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H15))</f>
@@ -2745,7 +2712,7 @@
         <v>012301</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K15" s="6">
         <v>1</v>
@@ -2774,30 +2741,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T15" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="D16" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G16" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H16))</f>
@@ -2812,7 +2779,7 @@
         <v>012302</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K16" s="6">
         <v>1</v>
@@ -2841,30 +2808,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T16" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>209</v>
+        <v>285</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G17" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H17))</f>
@@ -2908,30 +2875,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G18" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H18))</f>
@@ -2975,30 +2942,30 @@
         <v>axSW[]</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T18" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G19" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H19))</f>
@@ -3013,7 +2980,7 @@
         <v>012305</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K19" s="6">
         <v>1</v>
@@ -3042,30 +3009,30 @@
         <v>axSIG[]</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T19" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="D20" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G20" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H20))</f>
@@ -3080,7 +3047,7 @@
         <v>012306</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K20" s="6">
         <v>1</v>
@@ -3109,30 +3076,30 @@
         <v>axSIG[]</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T20" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G21" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H21))</f>
@@ -3147,7 +3114,7 @@
         <v>012307</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K21" s="6">
         <v>1</v>
@@ -3176,30 +3143,30 @@
         <v>axSIG[]</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T21" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G22" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H22))</f>
@@ -3214,7 +3181,7 @@
         <v>012308</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K22" s="6">
         <v>1</v>
@@ -3243,7 +3210,7 @@
         <v>axSIG[]</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>12</v>
@@ -3251,22 +3218,22 @@
     </row>
     <row r="23" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="D23" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G23" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H23))</f>
@@ -3281,7 +3248,7 @@
         <v>412555</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K23" s="6">
         <v>32</v>
@@ -3310,7 +3277,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T23" s="5" t="s">
         <v>12</v>
@@ -3318,22 +3285,22 @@
     </row>
     <row r="24" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="D24" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="F24" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G24" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H24))</f>
@@ -3348,7 +3315,7 @@
         <v>412557</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K24" s="6">
         <v>32</v>
@@ -3377,7 +3344,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S24" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T24" s="5" t="s">
         <v>12</v>
@@ -3385,22 +3352,22 @@
     </row>
     <row r="25" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="D25" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G25" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H25))</f>
@@ -3415,7 +3382,7 @@
         <v>412559</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K25" s="6">
         <v>32</v>
@@ -3444,7 +3411,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T25" s="5" t="s">
         <v>12</v>
@@ -3452,22 +3419,22 @@
     </row>
     <row r="26" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="D26" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G26" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H26))</f>
@@ -3482,7 +3449,7 @@
         <v>412561</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K26" s="6">
         <v>32</v>
@@ -3511,7 +3478,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T26" s="5" t="s">
         <v>12</v>
@@ -3519,22 +3486,22 @@
     </row>
     <row r="27" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="D27" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G27" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H27))</f>
@@ -3549,7 +3516,7 @@
         <v>412563</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K27" s="6">
         <v>32</v>
@@ -3578,7 +3545,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T27" s="5" t="s">
         <v>12</v>
@@ -3586,22 +3553,22 @@
     </row>
     <row r="28" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G28" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H28))</f>
@@ -3616,7 +3583,7 @@
         <v>412565</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K28" s="6">
         <v>32</v>
@@ -3653,22 +3620,22 @@
     </row>
     <row r="29" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="D29" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G29" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H29))</f>
@@ -3683,7 +3650,7 @@
         <v>412567</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K29" s="6">
         <v>32</v>
@@ -3720,22 +3687,22 @@
     </row>
     <row r="30" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="D30" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G30" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H30))</f>
@@ -3750,7 +3717,7 @@
         <v>412569</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="K30" s="6">
         <v>32</v>
@@ -3787,22 +3754,22 @@
     </row>
     <row r="31" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G31" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H31))</f>
@@ -3817,7 +3784,7 @@
         <v>412571</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K31" s="6">
         <v>32</v>
@@ -3846,7 +3813,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T31" s="5" t="s">
         <v>12</v>
@@ -3854,22 +3821,22 @@
     </row>
     <row r="32" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>279</v>
+        <v>66</v>
+      </c>
+      <c r="C32" t="s">
+        <v>266</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G32" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H32))</f>
@@ -3884,7 +3851,7 @@
         <v>412573</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K32" s="6">
         <v>32</v>
@@ -3913,30 +3880,30 @@
         <v>arSW[]</v>
       </c>
       <c r="S32" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T32" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="D33" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G33" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H33))</f>
@@ -3986,24 +3953,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="D34" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G34" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H34))</f>
@@ -4053,24 +4020,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="D35" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G35" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H35))</f>
@@ -4120,24 +4087,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="D36" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G36" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H36))</f>
@@ -4187,24 +4154,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>77</v>
-      </c>
       <c r="D37" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G37" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H37))</f>
@@ -4254,24 +4221,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="D38" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G38" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H38))</f>
@@ -4286,7 +4253,7 @@
         <v>012314</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K38" s="6">
         <v>1</v>
@@ -4315,30 +4282,30 @@
         <v>axSIG[]</v>
       </c>
       <c r="S38" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T38" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>81</v>
-      </c>
       <c r="D39" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G39" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H39))</f>
@@ -4353,7 +4320,7 @@
         <v>012315</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K39" s="6">
         <v>1</v>
@@ -4382,30 +4349,30 @@
         <v>axSIG[]</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T39" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>83</v>
-      </c>
       <c r="D40" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G40" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H40))</f>
@@ -4420,7 +4387,7 @@
         <v>012316</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K40" s="6">
         <v>1</v>
@@ -4449,30 +4416,30 @@
         <v>axSIG[]</v>
       </c>
       <c r="S40" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T40" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="D41" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G41" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H41))</f>
@@ -4487,7 +4454,7 @@
         <v>012317</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K41" s="6">
         <v>1</v>
@@ -4516,30 +4483,30 @@
         <v>axSIG[]</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T41" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>87</v>
-      </c>
       <c r="D42" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G42" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H42))</f>
@@ -4554,7 +4521,7 @@
         <v>012318</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K42" s="6">
         <v>1</v>
@@ -4583,7 +4550,7 @@
         <v>axSIG[]</v>
       </c>
       <c r="S42" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T42" s="5" t="s">
         <v>12</v>
@@ -4591,22 +4558,22 @@
     </row>
     <row r="43" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G43" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H43))</f>
@@ -4656,24 +4623,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E44" t="s">
         <v>11</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G44" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H44))</f>
@@ -4725,22 +4692,22 @@
     </row>
     <row r="45" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C45" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G45" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H45))</f>
@@ -4755,7 +4722,7 @@
         <v>412575</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K45" s="6">
         <v>32</v>
@@ -4784,7 +4751,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T45" s="5" t="s">
         <v>12</v>
@@ -4792,22 +4759,22 @@
     </row>
     <row r="46" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C46" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G46" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H46))</f>
@@ -4822,7 +4789,7 @@
         <v>412577</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K46" s="6">
         <v>32</v>
@@ -4851,7 +4818,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T46" s="5" t="s">
         <v>12</v>
@@ -4859,22 +4826,22 @@
     </row>
     <row r="47" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C47" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G47" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H47))</f>
@@ -4889,7 +4856,7 @@
         <v>412579</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K47" s="6">
         <v>32</v>
@@ -4918,7 +4885,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T47" s="5" t="s">
         <v>12</v>
@@ -4926,22 +4893,22 @@
     </row>
     <row r="48" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C48" t="s">
-        <v>189</v>
+        <v>285</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G48" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H48))</f>
@@ -4985,7 +4952,7 @@
         <v>arSW[]</v>
       </c>
       <c r="S48" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T48" s="5" t="s">
         <v>12</v>
@@ -4993,22 +4960,22 @@
     </row>
     <row r="49" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G49" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H49))</f>
@@ -5023,7 +4990,7 @@
         <v>412453</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K49" s="6">
         <v>32</v>
@@ -5052,7 +5019,7 @@
         <v>adiSW[]</v>
       </c>
       <c r="S49" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T49" s="5" t="s">
         <v>12</v>
@@ -5060,22 +5027,22 @@
     </row>
     <row r="50" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>194</v>
-      </c>
       <c r="F50" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G50" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H50))</f>
@@ -5090,7 +5057,7 @@
         <v>412455</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K50" s="6">
         <v>32</v>
@@ -5119,30 +5086,30 @@
         <v>adiSW[]</v>
       </c>
       <c r="S50" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T50" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="D51" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G51" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H51))</f>
@@ -5157,7 +5124,7 @@
         <v>012320</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K51" s="6">
         <v>1</v>
@@ -5186,30 +5153,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S51" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T51" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B52" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C52" s="7" t="s">
-        <v>93</v>
-      </c>
       <c r="D52" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G52" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H52))</f>
@@ -5224,7 +5191,7 @@
         <v>012321</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K52" s="6">
         <v>1</v>
@@ -5253,30 +5220,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S52" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T52" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C53" s="7" t="s">
-        <v>95</v>
-      </c>
       <c r="D53" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G53" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H53))</f>
@@ -5291,7 +5258,7 @@
         <v>012322</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K53" s="6">
         <v>1</v>
@@ -5320,30 +5287,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S53" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T53" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B54" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>97</v>
-      </c>
       <c r="D54" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G54" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H54))</f>
@@ -5358,7 +5325,7 @@
         <v>012323</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K54" s="6">
         <v>1</v>
@@ -5387,30 +5354,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S54" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T54" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="D55" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G55" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H55))</f>
@@ -5425,7 +5392,7 @@
         <v>012324</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K55" s="6">
         <v>1</v>
@@ -5454,30 +5421,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S55" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T55" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="D56" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G56" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H56))</f>
@@ -5492,7 +5459,7 @@
         <v>012325</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K56" s="6">
         <v>1</v>
@@ -5521,30 +5488,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S56" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T56" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G57" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H57))</f>
@@ -5559,7 +5526,7 @@
         <v>012326</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K57" s="6">
         <v>1</v>
@@ -5588,30 +5555,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S57" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T57" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G58" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H58))</f>
@@ -5626,7 +5593,7 @@
         <v>012327</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K58" s="6">
         <v>1</v>
@@ -5655,30 +5622,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S58" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T58" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C59" s="7" t="s">
-        <v>105</v>
-      </c>
       <c r="D59" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G59" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H59))</f>
@@ -5693,7 +5660,7 @@
         <v>012328</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K59" s="6">
         <v>1</v>
@@ -5722,30 +5689,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S59" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T59" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>107</v>
-      </c>
       <c r="D60" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G60" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H60))</f>
@@ -5760,7 +5727,7 @@
         <v>012329</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K60" s="6">
         <v>1</v>
@@ -5789,30 +5756,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S60" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T60" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C61" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="7" t="s">
-        <v>109</v>
-      </c>
       <c r="D61" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G61" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H61))</f>
@@ -5827,7 +5794,7 @@
         <v>012330</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K61" s="6">
         <v>1</v>
@@ -5856,30 +5823,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S61" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T61" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B62" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="D62" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G62" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H62))</f>
@@ -5894,7 +5861,7 @@
         <v>012331</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K62" s="6">
         <v>1</v>
@@ -5923,30 +5890,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S62" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T62" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B63" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>113</v>
-      </c>
       <c r="D63" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G63" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H63))</f>
@@ -5961,7 +5928,7 @@
         <v>012332</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K63" s="6">
         <v>1</v>
@@ -5990,30 +5957,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S63" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T63" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B64" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C64" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C64" s="7" t="s">
-        <v>115</v>
-      </c>
       <c r="D64" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G64" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H64))</f>
@@ -6028,7 +5995,7 @@
         <v>012333</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K64" s="6">
         <v>1</v>
@@ -6057,30 +6024,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T64" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B65" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C65" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C65" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="D65" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G65" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H65))</f>
@@ -6095,7 +6062,7 @@
         <v>012334</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K65" s="6">
         <v>1</v>
@@ -6124,30 +6091,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T65" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B66" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C66" s="7" t="s">
-        <v>119</v>
-      </c>
       <c r="D66" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G66" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H66))</f>
@@ -6162,7 +6129,7 @@
         <v>012335</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K66" s="6">
         <v>1</v>
@@ -6191,30 +6158,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S66" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T66" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B67" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C67" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C67" s="11" t="s">
-        <v>121</v>
-      </c>
       <c r="D67" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G67" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H67))</f>
@@ -6229,7 +6196,7 @@
         <v>012336</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K67" s="6">
         <v>1</v>
@@ -6258,30 +6225,30 @@
         <v>axALM[]</v>
       </c>
       <c r="S67" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T67" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>124</v>
-      </c>
       <c r="D68" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G68" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H68))</f>
@@ -6296,7 +6263,7 @@
         <v>012337</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K68" s="6">
         <v>1</v>
@@ -6325,30 +6292,30 @@
         <v>axFLT[]</v>
       </c>
       <c r="S68" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T68" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B69" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C69" s="7" t="s">
-        <v>126</v>
-      </c>
       <c r="D69" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G69" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H69))</f>
@@ -6363,7 +6330,7 @@
         <v>012338</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K69" s="6">
         <v>1</v>
@@ -6392,30 +6359,30 @@
         <v>axFLT[]</v>
       </c>
       <c r="S69" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T69" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B70" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="D70" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G70" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H70))</f>
@@ -6430,7 +6397,7 @@
         <v>012339</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K70" s="6">
         <v>1</v>
@@ -6459,30 +6426,30 @@
         <v>axFLT[]</v>
       </c>
       <c r="S70" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T70" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B71" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C71" s="7" t="s">
-        <v>130</v>
-      </c>
       <c r="D71" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G71" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H71))</f>
@@ -6497,7 +6464,7 @@
         <v>012340</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K71" s="6">
         <v>1</v>
@@ -6526,30 +6493,30 @@
         <v>axFLT[]</v>
       </c>
       <c r="S71" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T71" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B72" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C72" s="7" t="s">
-        <v>132</v>
-      </c>
       <c r="D72" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G72" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H72))</f>
@@ -6564,7 +6531,7 @@
         <v>012341</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K72" s="6">
         <v>1</v>
@@ -6593,30 +6560,30 @@
         <v>axFLT[]</v>
       </c>
       <c r="S72" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T72" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G73" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H73))</f>
@@ -6631,7 +6598,7 @@
         <v>012342</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K73" s="6">
         <v>1</v>
@@ -6660,30 +6627,30 @@
         <v>axFLT[]</v>
       </c>
       <c r="S73" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T73" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B74" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C74" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C74" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="D74" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G74" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H74))</f>
@@ -6698,7 +6665,7 @@
         <v>012343</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K74" s="6">
         <v>1</v>
@@ -6727,30 +6694,30 @@
         <v>axFLT[]</v>
       </c>
       <c r="S74" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T74" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>286</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G75" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H75))</f>
@@ -6765,7 +6732,7 @@
         <v>012344</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K75" s="6">
         <v>1</v>
@@ -6794,30 +6761,30 @@
         <v>axFLT[]</v>
       </c>
       <c r="S75" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T75" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G76" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H76))</f>
@@ -6832,7 +6799,7 @@
         <v>012345</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K76" s="6">
         <v>1</v>
@@ -6861,39 +6828,39 @@
         <v>axFLT[]</v>
       </c>
       <c r="S76" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T76" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C77" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="D77" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E77" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C77" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>141</v>
-      </c>
       <c r="F77" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>12</v>
@@ -6902,25 +6869,25 @@
         <v>16</v>
       </c>
       <c r="L77" s="5" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="M77">
         <v>8</v>
       </c>
       <c r="N77" s="5" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="O77">
         <v>1</v>
       </c>
       <c r="P77" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R77" s="5" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="S77" s="5" t="s">
         <v>13</v>
@@ -6929,33 +6896,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B78" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E78" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C78" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="F78" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J78" s="8" t="s">
         <v>12</v>
@@ -6964,25 +6931,25 @@
         <v>16</v>
       </c>
       <c r="L78" s="5" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="M78" s="5">
         <v>9</v>
       </c>
       <c r="N78" s="5" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="O78" s="5">
         <v>1</v>
       </c>
       <c r="P78" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R78" s="5" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="S78" s="5" t="s">
         <v>13</v>
@@ -6991,33 +6958,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>12</v>
@@ -7026,25 +6993,25 @@
         <v>16</v>
       </c>
       <c r="L79" s="5" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="M79" s="5">
         <v>9</v>
       </c>
       <c r="N79" s="5" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="O79" s="5">
         <v>2</v>
       </c>
       <c r="P79" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R79" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="S79" s="5" t="s">
         <v>13</v>
@@ -7053,33 +7020,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>12</v>
@@ -7088,25 +7055,25 @@
         <v>16</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="M80">
         <v>10</v>
       </c>
       <c r="N80" s="5" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R80" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="S80" s="5" t="s">
         <v>13</v>
@@ -7115,33 +7082,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>151</v>
+        <v>285</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>12</v>
@@ -7150,10 +7117,10 @@
         <v>16</v>
       </c>
       <c r="P81" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="S81" s="5" t="s">
         <v>13</v>
@@ -7162,33 +7129,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>153</v>
+        <v>285</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>12</v>
@@ -7197,10 +7164,10 @@
         <v>16</v>
       </c>
       <c r="P82" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="S82" s="5" t="s">
         <v>13</v>
@@ -7209,33 +7176,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>12</v>
@@ -7244,25 +7211,25 @@
         <v>16</v>
       </c>
       <c r="L83" s="5" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M83">
         <v>8</v>
       </c>
       <c r="N83" s="5" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="O83">
         <v>2</v>
       </c>
       <c r="P83" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R83" s="5" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="S83" s="5" t="s">
         <v>13</v>
@@ -7271,33 +7238,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J84" s="8" t="s">
         <v>12</v>
@@ -7306,25 +7273,25 @@
         <v>1</v>
       </c>
       <c r="L84" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M84">
         <v>2</v>
       </c>
       <c r="N84" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="O84">
         <v>1</v>
       </c>
       <c r="P84" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R84" s="5" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="S84" s="5" t="s">
         <v>13</v>
@@ -7333,33 +7300,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J85" s="8" t="s">
         <v>12</v>
@@ -7368,25 +7335,25 @@
         <v>1</v>
       </c>
       <c r="L85" s="5" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="M85">
         <v>2</v>
       </c>
       <c r="N85" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="O85">
         <v>2</v>
       </c>
       <c r="P85" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R85" s="5" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="S85" s="5" t="s">
         <v>13</v>
@@ -7395,33 +7362,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J86" s="8" t="s">
         <v>12</v>
@@ -7430,25 +7397,25 @@
         <v>1</v>
       </c>
       <c r="L86" s="5" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="M86">
         <v>1</v>
       </c>
       <c r="N86" s="5" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R86" s="5" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="S86" s="5" t="s">
         <v>13</v>
@@ -7457,33 +7424,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>12</v>
@@ -7492,25 +7459,25 @@
         <v>1</v>
       </c>
       <c r="L87" s="5" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87" s="5" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="O87">
         <v>2</v>
       </c>
       <c r="P87" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R87" s="5" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="S87" s="5" t="s">
         <v>13</v>
@@ -7519,33 +7486,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J88" s="8" t="s">
         <v>12</v>
@@ -7554,25 +7521,25 @@
         <v>1</v>
       </c>
       <c r="L88" s="5" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M88">
         <v>5</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="O88">
         <v>2</v>
       </c>
       <c r="P88" s="5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R88" s="5" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="S88" s="5" t="s">
         <v>13</v>
@@ -7581,33 +7548,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J89" s="8" t="s">
         <v>12</v>
@@ -7616,25 +7583,25 @@
         <v>1</v>
       </c>
       <c r="L89" s="5" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="M89">
         <v>5</v>
       </c>
       <c r="N89" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="O89">
         <v>4</v>
       </c>
       <c r="P89" s="5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R89" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="S89" s="5" t="s">
         <v>13</v>
@@ -7643,33 +7610,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J90" s="8" t="s">
         <v>12</v>
@@ -7678,25 +7645,25 @@
         <v>1</v>
       </c>
       <c r="L90" s="5" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M90">
         <v>5</v>
       </c>
       <c r="N90" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" s="5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R90" s="5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="S90" s="5" t="s">
         <v>13</v>
@@ -7705,33 +7672,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J91" s="8" t="s">
         <v>12</v>
@@ -7740,25 +7707,25 @@
         <v>1</v>
       </c>
       <c r="L91" s="5" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="M91">
         <v>5</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="O91">
         <v>3</v>
       </c>
       <c r="P91" s="5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R91" s="5" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="S91" s="5" t="s">
         <v>13</v>
@@ -7767,33 +7734,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J92" s="8" t="s">
         <v>12</v>
@@ -7802,25 +7769,25 @@
         <v>16</v>
       </c>
       <c r="L92" s="5" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M92">
         <v>12</v>
       </c>
       <c r="N92" s="5" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" s="5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R92" s="5" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="S92" s="5" t="s">
         <v>13</v>
@@ -7829,33 +7796,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>11</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J93" s="8" t="s">
         <v>12</v>
@@ -7864,25 +7831,25 @@
         <v>1</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="M93">
         <v>2</v>
       </c>
       <c r="N93" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="O93">
         <v>3</v>
       </c>
       <c r="P93" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R93" s="5" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="S93" s="5" t="s">
         <v>13</v>
@@ -7891,33 +7858,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J94" s="8" t="s">
         <v>12</v>
@@ -7926,25 +7893,25 @@
         <v>16</v>
       </c>
       <c r="L94" s="5" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="M94">
         <v>11</v>
       </c>
       <c r="N94" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R94" s="5" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="S94" s="5" t="s">
         <v>13</v>
@@ -7953,33 +7920,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J95" s="8" t="s">
         <v>12</v>
@@ -7988,25 +7955,25 @@
         <v>16</v>
       </c>
       <c r="L95" s="5" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="M95">
         <v>11</v>
       </c>
       <c r="N95" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O95">
         <v>2</v>
       </c>
       <c r="P95" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R95" s="5" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="S95" s="5" t="s">
         <v>13</v>
@@ -8015,33 +7982,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J96" s="8" t="s">
         <v>12</v>
@@ -8050,25 +8017,25 @@
         <v>16</v>
       </c>
       <c r="L96" s="5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="M96">
         <v>11</v>
       </c>
       <c r="N96" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O96">
         <v>3</v>
       </c>
       <c r="P96" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R96" s="5" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="S96" s="5" t="s">
         <v>13</v>
@@ -8077,33 +8044,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J97" s="8" t="s">
         <v>12</v>
@@ -8112,25 +8079,25 @@
         <v>16</v>
       </c>
       <c r="L97" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="M97">
         <v>11</v>
       </c>
       <c r="N97" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O97">
         <v>4</v>
       </c>
       <c r="P97" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R97" s="5" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="S97" s="5" t="s">
         <v>13</v>
@@ -8139,24 +8106,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G98" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H98))</f>
@@ -8171,7 +8138,7 @@
         <v>012346</v>
       </c>
       <c r="J98" s="11" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K98" s="11">
         <v>1</v>
@@ -8197,30 +8164,30 @@
       </c>
       <c r="R98" s="12"/>
       <c r="S98" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T98" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G99" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H99))</f>
@@ -8235,7 +8202,7 @@
         <v>012347</v>
       </c>
       <c r="J99" s="11" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K99" s="11">
         <v>1</v>
@@ -8261,30 +8228,30 @@
       </c>
       <c r="R99" s="12"/>
       <c r="S99" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T99" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G100" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H100))</f>
@@ -8299,7 +8266,7 @@
         <v>012348</v>
       </c>
       <c r="J100" s="11" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K100" s="11">
         <v>1</v>
@@ -8318,37 +8285,37 @@
         <v>12</v>
       </c>
       <c r="P100" s="9" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="Q100" s="13" t="s">
         <v>13</v>
       </c>
       <c r="R100" s="12"/>
       <c r="S100" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T100" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G101" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H101))</f>
@@ -8363,7 +8330,7 @@
         <v>012349</v>
       </c>
       <c r="J101" s="11" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K101" s="11">
         <v>1</v>
@@ -8389,30 +8356,30 @@
       </c>
       <c r="R101" s="12"/>
       <c r="S101" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T101" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G102" s="5" t="str">
         <f>_xlfn.CONCAT("0x",DEC2HEX(H102))</f>
@@ -8427,7 +8394,7 @@
         <v>012350</v>
       </c>
       <c r="J102" s="11" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K102" s="11">
         <v>1</v>
@@ -8453,7 +8420,7 @@
       </c>
       <c r="R102" s="12"/>
       <c r="S102" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T102" s="9" t="s">
         <v>12</v>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1714" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06227EB4-F7E3-4296-8346-23666AEFA310}"/>
+  <xr:revisionPtr revIDLastSave="1734" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A426E290-5ED2-4342-8F05-30B6726B666F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point List" sheetId="1" r:id="rId1"/>
     <sheet name="Symbol Table" sheetId="3" r:id="rId2"/>
     <sheet name="Mapping Sheet" sheetId="2" r:id="rId3"/>
+    <sheet name="SymbolTableCSV" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="315">
   <si>
     <t>Signal Type</t>
   </si>
@@ -1178,42 +1179,6 @@
   </cellStyles>
   <dxfs count="24">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="0"/>
@@ -1424,6 +1389,24 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1568,6 +1551,24 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1692,26 +1693,26 @@
     <tableColumn id="1" xr3:uid="{423FA6DC-9142-4672-A14E-553234A081EF}" name="Signal Type" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{56D9DA24-EF6A-4F6A-8733-677B62E46902}" name="Tag No" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{A96BC653-60FF-429B-B698-AD90C0B0B0D3}" name="Name" dataDxfId="20"/>
-    <tableColumn id="20" xr3:uid="{18691D5F-606F-4A16-B04B-74830D1D8BC1}" name="Instrument" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{706A0F32-C352-4264-929A-BBE84E0336CD}" name="Status" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{C8D7F886-484A-4506-96D7-825482566CEA}" name="Data Type" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{BD2571AB-DE7E-4006-8157-4106695ACD69}" name="Memory Type" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{3B62562F-5D5D-4A72-AC30-A11E0297A3A2}" name="PDU Hexadecimal" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{8719FB6E-76D0-42CA-A6D4-A07F76F787FE}" name="Modbus Address" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{494772C3-DD22-48E6-87F4-54FAD05AA979}" name="Modicon Address" dataDxfId="14"/>
-    <tableColumn id="19" xr3:uid="{2564375E-1543-4B77-A111-66D99BB1656A}" name="Proface  Type" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{810DD2FA-32AC-4AC6-9BCB-5E8AE7516595}" name="Proface Data Type" dataDxfId="0"/>
-    <tableColumn id="21" xr3:uid="{753ED6D6-F73A-4E76-87DB-792F48C2C75C}" name="Size (Bits)" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{E8FE6B00-067F-43B4-AFBC-4B31DC0D3ACD}" name="PLC Memory Address" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{32B52740-581E-4139-B281-3664B4614465}" name="Position" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{E6944375-EF05-45BC-8ADD-793CB19A0ADA}" name="I/O Card Number" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{527E8B44-E1FF-4F80-A269-6A31B18D6394}" name="Channel" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{E82449CF-F378-4789-9FE2-B0D21BD261F7}" name="I/O" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{6CE76123-31FB-4788-B701-5DEA98A3B0AA}" name="Global Variable" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{E1175C2D-C54B-4E1D-8F34-46534F2CFC8A}" name="Program Variable Name" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{70FE0A90-A798-47C6-B87B-28B2D22A1365}" name="Operator Visiblity" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{3FC319EF-8DF3-4168-B3CA-EF31C5FF6669}" name="Deadman" dataDxfId="3"/>
-    <tableColumn id="22" xr3:uid="{8E66A915-FC7F-450B-81CE-EE2C726AB2C6}" name="Validated" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{18691D5F-606F-4A16-B04B-74830D1D8BC1}" name="Instrument" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{706A0F32-C352-4264-929A-BBE84E0336CD}" name="Status" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{C8D7F886-484A-4506-96D7-825482566CEA}" name="Data Type" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{BD2571AB-DE7E-4006-8157-4106695ACD69}" name="Memory Type" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{3B62562F-5D5D-4A72-AC30-A11E0297A3A2}" name="PDU Hexadecimal" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{8719FB6E-76D0-42CA-A6D4-A07F76F787FE}" name="Modbus Address" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{494772C3-DD22-48E6-87F4-54FAD05AA979}" name="Modicon Address" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{2564375E-1543-4B77-A111-66D99BB1656A}" name="Proface  Type" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{810DD2FA-32AC-4AC6-9BCB-5E8AE7516595}" name="Proface Data Type" dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{753ED6D6-F73A-4E76-87DB-792F48C2C75C}" name="Size (Bits)" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{E8FE6B00-067F-43B4-AFBC-4B31DC0D3ACD}" name="PLC Memory Address" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{32B52740-581E-4139-B281-3664B4614465}" name="Position" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{E6944375-EF05-45BC-8ADD-793CB19A0ADA}" name="I/O Card Number" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{527E8B44-E1FF-4F80-A269-6A31B18D6394}" name="Channel" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{E82449CF-F378-4789-9FE2-B0D21BD261F7}" name="I/O" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{6CE76123-31FB-4788-B701-5DEA98A3B0AA}" name="Global Variable" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{E1175C2D-C54B-4E1D-8F34-46534F2CFC8A}" name="Program Variable Name" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{70FE0A90-A798-47C6-B87B-28B2D22A1365}" name="Operator Visiblity" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{3FC319EF-8DF3-4168-B3CA-EF31C5FF6669}" name="Deadman" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{8E66A915-FC7F-450B-81CE-EE2C726AB2C6}" name="Validated" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10508,28 +10509,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EBECA59-5A01-4BF3-8401-1EE4D98726D4}">
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:K194"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1" t="str">
+        <f>A1</f>
+        <v>GP-Pro EX</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>302</v>
       </c>
       <c r="B2" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K2" t="str">
+        <f>_xlfn.CONCAT(A2,",",B2)</f>
+        <v>File Type,SymbolVariable</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>303</v>
       </c>
@@ -10539,8 +10550,12 @@
       <c r="C3">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3" t="str">
+        <f>_xlfn.CONCAT(A3,",",B3,",",C3)</f>
+        <v>File Version,3,0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -10562,8 +10577,12 @@
       <c r="G5" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K5" t="str">
+        <f>_xlfn.CONCAT(A5,",",B5,",",C5,",",D5,",",E5,",",F5,",",G5)</f>
+        <v>Name,Index,Type,External/Internal,Address,Keep,Comment</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>'Point List'!C3</f>
         <v>System Start</v>
@@ -10579,8 +10598,12 @@
         <f>'Point List'!J3</f>
         <v>012289</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K6" t="str">
+        <f>_xlfn.CONCAT(A6,",",B6,",",C6,",",D6,",",E6,",",F6,",",G6)</f>
+        <v>System Start,,BitAddress,PLC1,012289,,</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>'Point List'!C4</f>
         <v>System Shutdown</v>
@@ -10596,8 +10619,12 @@
         <f>'Point List'!J4</f>
         <v>012290</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K7" t="str">
+        <f t="shared" ref="K7:K70" si="0">_xlfn.CONCAT(A7,",",B7,",",C7,",",D7,",",E7,",",F7,",",G7)</f>
+        <v>System Shutdown,,BitAddress,PLC1,012290,,</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>'Point List'!C5</f>
         <v>Simplex Mode</v>
@@ -10613,8 +10640,12 @@
         <f>'Point List'!J5</f>
         <v>012291</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K8" t="str">
+        <f t="shared" si="0"/>
+        <v>Simplex Mode,,BitAddress,PLC1,012291,,</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>'Point List'!C6</f>
         <v>Manual Turnover</v>
@@ -10630,8 +10661,12 @@
         <f>'Point List'!J6</f>
         <v>012292</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K9" t="str">
+        <f t="shared" si="0"/>
+        <v>Manual Turnover,,BitAddress,PLC1,012292,,</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>'Point List'!C7</f>
         <v>Enable Manual Valve Control</v>
@@ -10647,8 +10682,12 @@
         <f>'Point List'!J7</f>
         <v>012293</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K10" t="str">
+        <f t="shared" si="0"/>
+        <v>Enable Manual Valve Control,,BitAddress,PLC1,012293,,</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>'Point List'!C8</f>
         <v>Enable Manual Fan Control</v>
@@ -10664,8 +10703,12 @@
         <f>'Point List'!J8</f>
         <v>012294</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K11" t="str">
+        <f t="shared" si="0"/>
+        <v>Enable Manual Fan Control,,BitAddress,PLC1,012294,,</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>'Point List'!C9</f>
         <v>AVAILABLE</v>
@@ -10681,8 +10724,12 @@
         <f>'Point List'!J9</f>
         <v>012295</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K12" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,BitAddress,PLC1,012295,,</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>'Point List'!C10</f>
         <v>Force Fan 1 On/Off</v>
@@ -10698,8 +10745,12 @@
         <f>'Point List'!J10</f>
         <v>012296</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K13" t="str">
+        <f t="shared" si="0"/>
+        <v>Force Fan 1 On/Off,,BitAddress,PLC1,012296,,</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>'Point List'!C11</f>
         <v>Force Fan 2 On/Off</v>
@@ -10715,8 +10766,12 @@
         <f>'Point List'!J11</f>
         <v>012297</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K14" t="str">
+        <f t="shared" si="0"/>
+        <v>Force Fan 2 On/Off,,BitAddress,PLC1,012297,,</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>'Point List'!C12</f>
         <v>Primary Hydraulic Fault ACK</v>
@@ -10732,8 +10787,12 @@
         <f>'Point List'!J12</f>
         <v>012298</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K15" t="str">
+        <f t="shared" si="0"/>
+        <v>Primary Hydraulic Fault ACK,,BitAddress,PLC1,012298,,</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>'Point List'!C13</f>
         <v>Secondary Hydraulic Fault ACK</v>
@@ -10749,8 +10808,12 @@
         <f>'Point List'!J13</f>
         <v>012299</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K16" t="str">
+        <f t="shared" si="0"/>
+        <v>Secondary Hydraulic Fault ACK,,BitAddress,PLC1,012299,,</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>'Point List'!C14</f>
         <v>Enable Pump Cycling</v>
@@ -10766,8 +10829,12 @@
         <f>'Point List'!J14</f>
         <v>012300</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K17" t="str">
+        <f t="shared" si="0"/>
+        <v>Enable Pump Cycling,,BitAddress,PLC1,012300,,</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>'Point List'!C15</f>
         <v>Reset Pump Differential Signal</v>
@@ -10783,8 +10850,12 @@
         <f>'Point List'!J15</f>
         <v>012301</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K18" t="str">
+        <f t="shared" si="0"/>
+        <v>Reset Pump Differential Signal,,BitAddress,PLC1,012301,,</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>'Point List'!C16</f>
         <v>Fault ACK</v>
@@ -10800,8 +10871,12 @@
         <f>'Point List'!J16</f>
         <v>012302</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K19" t="str">
+        <f t="shared" si="0"/>
+        <v>Fault ACK,,BitAddress,PLC1,012302,,</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>'Point List'!C17</f>
         <v>AVAILABLE</v>
@@ -10817,8 +10892,12 @@
         <f>'Point List'!J17</f>
         <v>012303</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K20" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,0,PLC1,012303,,</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>'Point List'!C18</f>
         <v>AVAILABLE</v>
@@ -10834,8 +10913,12 @@
         <f>'Point List'!J18</f>
         <v>012304</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K21" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,0,PLC1,012304,,</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>'Point List'!C19</f>
         <v>System On</v>
@@ -10851,8 +10934,12 @@
         <f>'Point List'!J19</f>
         <v>012305</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K22" t="str">
+        <f t="shared" si="0"/>
+        <v>System On,,BitAddress,PLC1,012305,,</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>'Point List'!C20</f>
         <v>System Shutting Down</v>
@@ -10868,8 +10955,12 @@
         <f>'Point List'!J20</f>
         <v>012306</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K23" t="str">
+        <f t="shared" si="0"/>
+        <v>System Shutting Down,,BitAddress,PLC1,012306,,</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>'Point List'!C21</f>
         <v>System Initializing</v>
@@ -10885,8 +10976,12 @@
         <f>'Point List'!J21</f>
         <v>012307</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K24" t="str">
+        <f t="shared" si="0"/>
+        <v>System Initializing,,BitAddress,PLC1,012307,,</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>'Point List'!C22</f>
         <v>System Calibrating</v>
@@ -10902,8 +10997,12 @@
         <f>'Point List'!J22</f>
         <v>012308</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K25" t="str">
+        <f t="shared" si="0"/>
+        <v>System Calibrating,,BitAddress,PLC1,012308,,</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>'Point List'!C23</f>
         <v>Measured Pump Power</v>
@@ -10919,8 +11018,12 @@
         <f>'Point List'!J23</f>
         <v>412557</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K26" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Pump Power,,WordAddress,PLC1,412557,,</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>'Point List'!C24</f>
         <v>Measured Inlet Coolant Temperature</v>
@@ -10936,8 +11039,12 @@
         <f>'Point List'!J24</f>
         <v>412559</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K27" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Inlet Coolant Temperature,,WordAddress,PLC1,412559,,</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>'Point List'!C25</f>
         <v>Measured Conductivity</v>
@@ -10953,8 +11060,12 @@
         <f>'Point List'!J25</f>
         <v>412561</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K28" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Conductivity,,WordAddress,PLC1,412561,,</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>'Point List'!C26</f>
         <v>Measured Flow</v>
@@ -10970,8 +11081,12 @@
         <f>'Point List'!J26</f>
         <v>412563</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K29" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Flow,,WordAddress,PLC1,412563,,</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>'Point List'!C27</f>
         <v>Valve Open Percentage</v>
@@ -10987,8 +11102,12 @@
         <f>'Point List'!J27</f>
         <v>412565</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K30" t="str">
+        <f t="shared" si="0"/>
+        <v>Valve Open Percentage,,WordAddress,PLC1,412565,,</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>'Point List'!C28</f>
         <v>Real RTD 1 Signal</v>
@@ -11004,8 +11123,12 @@
         <f>'Point List'!J28</f>
         <v>412567</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K31" t="str">
+        <f t="shared" si="0"/>
+        <v>Real RTD 1 Signal,,WordAddress,PLC1,412567,,</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>'Point List'!C29</f>
         <v>Real RTD 2 Signal</v>
@@ -11021,8 +11144,12 @@
         <f>'Point List'!J29</f>
         <v>412569</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K32" t="str">
+        <f t="shared" si="0"/>
+        <v>Real RTD 2 Signal,,WordAddress,PLC1,412569,,</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>'Point List'!C30</f>
         <v>Real RTD 3 Signal</v>
@@ -11038,8 +11165,12 @@
         <f>'Point List'!J30</f>
         <v>412571</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K33" t="str">
+        <f t="shared" si="0"/>
+        <v>Real RTD 3 Signal,,WordAddress,PLC1,412571,,</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>'Point List'!C31</f>
         <v>AVAILABLE</v>
@@ -11055,8 +11186,12 @@
         <f>'Point List'!J31</f>
         <v>412573</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K34" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,WordAddress,PLC1,412573,,</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f>'Point List'!C32</f>
         <v xml:space="preserve">Measured Valve Position </v>
@@ -11072,8 +11207,12 @@
         <f>'Point List'!J32</f>
         <v>412575</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K35" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Valve Position ,,WordAddress,PLC1,412575,,</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f>'Point List'!C33</f>
         <v>Debounced Water Level Low Signal</v>
@@ -11089,8 +11228,12 @@
         <f>'Point List'!J33</f>
         <v>012309</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K36" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Water Level Low Signal,,WordAddress,PLC1,012309,,</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f>'Point List'!C34</f>
         <v>Debounced Water Level Low Low Signal</v>
@@ -11106,8 +11249,12 @@
         <f>'Point List'!J34</f>
         <v>012310</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K37" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Water Level Low Low Signal,,0,PLC1,012310,,</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f>'Point List'!C35</f>
         <v>Debounced Pressure Signal</v>
@@ -11123,8 +11270,12 @@
         <f>'Point List'!J35</f>
         <v>012311</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K38" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Pressure Signal,,0,PLC1,012311,,</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f>'Point List'!C36</f>
         <v>Debounced Conductivity Alarm Signal</v>
@@ -11140,8 +11291,12 @@
         <f>'Point List'!J36</f>
         <v>012312</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K39" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Conductivity Alarm Signal,,0,PLC1,012312,,</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f>'Point List'!C37</f>
         <v>Debounced Conductivity Fault Signal</v>
@@ -11157,8 +11312,12 @@
         <f>'Point List'!J37</f>
         <v>012313</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K40" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Conductivity Fault Signal,,0,PLC1,012313,,</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <f>'Point List'!C38</f>
         <v>Output Water Level Low Signal</v>
@@ -11174,8 +11333,12 @@
         <f>'Point List'!J38</f>
         <v>012314</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K41" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Water Level Low Signal,,BitAddress,PLC1,012314,,</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f>'Point List'!C39</f>
         <v>Output Water Level Low Low Signal</v>
@@ -11191,8 +11354,12 @@
         <f>'Point List'!J39</f>
         <v>012315</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K42" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Water Level Low Low Signal,,BitAddress,PLC1,012315,,</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f>'Point List'!C40</f>
         <v>Output Pressure Signal</v>
@@ -11208,8 +11375,12 @@
         <f>'Point List'!J40</f>
         <v>012316</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K43" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Pressure Signal,,BitAddress,PLC1,012316,,</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
         <f>'Point List'!C41</f>
         <v>Output Conductivity Alarm Signal</v>
@@ -11225,8 +11396,12 @@
         <f>'Point List'!J41</f>
         <v>012317</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K44" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Conductivity Alarm Signal,,BitAddress,PLC1,012317,,</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f>'Point List'!C42</f>
         <v>Output Conductivity Fault Signal</v>
@@ -11242,8 +11417,12 @@
         <f>'Point List'!J42</f>
         <v>012318</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K45" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Conductivity Fault Signal,,BitAddress,PLC1,012318,,</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f>'Point List'!C43</f>
         <v>Differential Pump Hours</v>
@@ -11259,8 +11438,12 @@
         <f>'Point List'!J43</f>
         <v>012453</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K46" t="str">
+        <f t="shared" si="0"/>
+        <v>Differential Pump Hours,,0,PLC1,012453,,</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f>'Point List'!C44</f>
         <v>System Pulse</v>
@@ -11276,8 +11459,12 @@
         <f>'Point List'!J44</f>
         <v>012319</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K47" t="str">
+        <f t="shared" si="0"/>
+        <v>System Pulse,,0,PLC1,012319,,</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
         <f>'Point List'!C45</f>
         <v>Measured Active Pump  Voltage</v>
@@ -11293,8 +11480,12 @@
         <f>'Point List'!J45</f>
         <v>412577</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K48" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Active Pump  Voltage,,WordAddress,PLC1,412577,,</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
         <f>'Point List'!C46</f>
         <v>Measured Active Pump  Current</v>
@@ -11310,8 +11501,12 @@
         <f>'Point List'!J46</f>
         <v>412579</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K49" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Active Pump  Current,,WordAddress,PLC1,412579,,</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
         <f>'Point List'!C47</f>
         <v>AVAILABLE</v>
@@ -11327,8 +11522,12 @@
         <f>'Point List'!J47</f>
         <v>412581</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K50" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,WordAddress,PLC1,412581,,</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
         <f>'Point List'!C48</f>
         <v>AVAILABLE</v>
@@ -11344,8 +11543,12 @@
         <f>'Point List'!J48</f>
         <v>412583</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K51" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,0,PLC1,412583,,</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f>'Point List'!C49</f>
         <v>Pump 1 Total Hours</v>
@@ -11361,8 +11564,12 @@
         <f>'Point List'!J49</f>
         <v>412455</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K52" t="str">
+        <f t="shared" si="0"/>
+        <v>Pump 1 Total Hours,,WordAddress,PLC1,412455,,</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
         <f>'Point List'!C50</f>
         <v>Pump 2 Total Hours</v>
@@ -11378,8 +11585,12 @@
         <f>'Point List'!J50</f>
         <v>412457</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K53" t="str">
+        <f t="shared" si="0"/>
+        <v>Pump 2 Total Hours,,WordAddress,PLC1,412457,,</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
         <f>'Point List'!C51</f>
         <v xml:space="preserve">High Coolant Temperature </v>
@@ -11395,8 +11606,12 @@
         <f>'Point List'!J51</f>
         <v>012320</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K54" t="str">
+        <f t="shared" si="0"/>
+        <v>High Coolant Temperature ,,BitAddress,PLC1,012320,,</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
         <f>'Point List'!C52</f>
         <v>Low Coolant Level in Vessel</v>
@@ -11412,8 +11627,12 @@
         <f>'Point List'!J52</f>
         <v>012321</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K55" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Coolant Level in Vessel,,BitAddress,PLC1,012321,,</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f>'Point List'!C53</f>
         <v xml:space="preserve">High Coolant Conductivity </v>
@@ -11429,8 +11648,12 @@
         <f>'Point List'!J53</f>
         <v>012322</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K56" t="str">
+        <f t="shared" si="0"/>
+        <v>High Coolant Conductivity ,,BitAddress,PLC1,012322,,</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <f>'Point List'!C54</f>
         <v>Low Hydraulic Power</v>
@@ -11446,8 +11669,12 @@
         <f>'Point List'!J54</f>
         <v>012323</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K57" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Hydraulic Power,,BitAddress,PLC1,012323,,</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f>'Point List'!C55</f>
         <v>Low Hydraulic Flow</v>
@@ -11463,8 +11690,12 @@
         <f>'Point List'!J55</f>
         <v>012324</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K58" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Hydraulic Flow,,BitAddress,PLC1,012324,,</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <f>'Point List'!C56</f>
         <v>Low Hydraulic Pressure</v>
@@ -11480,8 +11711,12 @@
         <f>'Point List'!J56</f>
         <v>012325</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K59" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Hydraulic Pressure,,BitAddress,PLC1,012325,,</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <f>'Point List'!C57</f>
         <v>Voltage Signal Malfunction</v>
@@ -11497,8 +11732,12 @@
         <f>'Point List'!J57</f>
         <v>012326</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K60" t="str">
+        <f t="shared" si="0"/>
+        <v>Voltage Signal Malfunction,,BitAddress,PLC1,012326,,</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <f>'Point List'!C58</f>
         <v>Current Signal Malfunction</v>
@@ -11514,8 +11753,12 @@
         <f>'Point List'!J58</f>
         <v>012327</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K61" t="str">
+        <f t="shared" si="0"/>
+        <v>Current Signal Malfunction,,BitAddress,PLC1,012327,,</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
         <f>'Point List'!C59</f>
         <v>Primary Hydraulic Failure</v>
@@ -11531,8 +11774,12 @@
         <f>'Point List'!J59</f>
         <v>012328</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K62" t="str">
+        <f t="shared" si="0"/>
+        <v>Primary Hydraulic Failure,,BitAddress,PLC1,012328,,</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
         <f>'Point List'!C60</f>
         <v>Secondary Hydraulic Failure</v>
@@ -11548,8 +11795,12 @@
         <f>'Point List'!J60</f>
         <v>012329</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K63" t="str">
+        <f t="shared" si="0"/>
+        <v>Secondary Hydraulic Failure,,BitAddress,PLC1,012329,,</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <f>'Point List'!C61</f>
         <v>Automatic Valve Control Disabled</v>
@@ -11565,8 +11816,12 @@
         <f>'Point List'!J61</f>
         <v>012330</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K64" t="str">
+        <f t="shared" si="0"/>
+        <v>Automatic Valve Control Disabled,,BitAddress,PLC1,012330,,</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
         <f>'Point List'!C62</f>
         <v>Automatic Fan Control Disabled</v>
@@ -11582,8 +11837,12 @@
         <f>'Point List'!J62</f>
         <v>012331</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K65" t="str">
+        <f t="shared" si="0"/>
+        <v>Automatic Fan Control Disabled,,BitAddress,PLC1,012331,,</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
         <f>'Point List'!C63</f>
         <v>Flow Signal Malfunction</v>
@@ -11599,8 +11858,12 @@
         <f>'Point List'!J63</f>
         <v>012332</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K66" t="str">
+        <f t="shared" si="0"/>
+        <v>Flow Signal Malfunction,,BitAddress,PLC1,012332,,</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
         <f>'Point List'!C64</f>
         <v>Bad RTD 1 Signal</v>
@@ -11616,8 +11879,12 @@
         <f>'Point List'!J64</f>
         <v>012333</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K67" t="str">
+        <f t="shared" si="0"/>
+        <v>Bad RTD 1 Signal,,BitAddress,PLC1,012333,,</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <f>'Point List'!C65</f>
         <v>Bad RTD 2 Signal</v>
@@ -11633,8 +11900,12 @@
         <f>'Point List'!J65</f>
         <v>012334</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K68" t="str">
+        <f t="shared" si="0"/>
+        <v>Bad RTD 2 Signal,,BitAddress,PLC1,012334,,</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <f>'Point List'!C66</f>
         <v>Bad RTD 3 Signal</v>
@@ -11650,8 +11921,12 @@
         <f>'Point List'!J66</f>
         <v>012335</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K69" t="str">
+        <f t="shared" si="0"/>
+        <v>Bad RTD 3 Signal,,BitAddress,PLC1,012335,,</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
         <f>'Point List'!C67</f>
         <v>Pump Cycle Alarm</v>
@@ -11667,8 +11942,12 @@
         <f>'Point List'!J67</f>
         <v>012336</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K70" t="str">
+        <f t="shared" si="0"/>
+        <v>Pump Cycle Alarm,,BitAddress,PLC1,012336,,</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <f>'Point List'!C68</f>
         <v>Critical Temperature</v>
@@ -11684,8 +11963,12 @@
         <f>'Point List'!J68</f>
         <v>012337</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K71" t="str">
+        <f t="shared" ref="K71:K107" si="1">_xlfn.CONCAT(A71,",",B71,",",C71,",",D71,",",E71,",",F71,",",G71)</f>
+        <v>Critical Temperature,,BitAddress,PLC1,012337,,</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
         <f>'Point List'!C69</f>
         <v>Critical Vessel Level</v>
@@ -11701,8 +11984,12 @@
         <f>'Point List'!J69</f>
         <v>012338</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K72" t="str">
+        <f t="shared" si="1"/>
+        <v>Critical Vessel Level,,BitAddress,PLC1,012338,,</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="str">
         <f>'Point List'!C70</f>
         <v>Critical Conductivity</v>
@@ -11718,8 +12005,12 @@
         <f>'Point List'!J70</f>
         <v>012339</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K73" t="str">
+        <f t="shared" si="1"/>
+        <v>Critical Conductivity,,BitAddress,PLC1,012339,,</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
         <f>'Point List'!C71</f>
         <v>Level Sensor Malfunction</v>
@@ -11735,8 +12026,12 @@
         <f>'Point List'!J71</f>
         <v>012340</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K74" t="str">
+        <f t="shared" si="1"/>
+        <v>Level Sensor Malfunction,,BitAddress,PLC1,012340,,</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
         <f>'Point List'!C72</f>
         <v>Conductivity Sensor Malfunction</v>
@@ -11752,8 +12047,12 @@
         <f>'Point List'!J72</f>
         <v>012341</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K75" t="str">
+        <f t="shared" si="1"/>
+        <v>Conductivity Sensor Malfunction,,BitAddress,PLC1,012341,,</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
         <f>'Point List'!C73</f>
         <v>Bingo Pumps</v>
@@ -11769,8 +12068,12 @@
         <f>'Point List'!J73</f>
         <v>012342</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K76" t="str">
+        <f t="shared" si="1"/>
+        <v>Bingo Pumps,,BitAddress,PLC1,012342,,</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
         <f>'Point List'!C74</f>
         <v>Temperature Sensor Malfunction</v>
@@ -11786,8 +12089,12 @@
         <f>'Point List'!J74</f>
         <v>012343</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K77" t="str">
+        <f t="shared" si="1"/>
+        <v>Temperature Sensor Malfunction,,BitAddress,PLC1,012343,,</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
         <f>'Point List'!C75</f>
         <v>Bad Valve Pos</v>
@@ -11803,8 +12110,12 @@
         <f>'Point List'!J75</f>
         <v>012344</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K78" t="str">
+        <f t="shared" si="1"/>
+        <v>Bad Valve Pos,,BitAddress,PLC1,012344,,</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <f>'Point List'!C76</f>
         <v>Master Fault Signal</v>
@@ -11820,8 +12131,12 @@
         <f>'Point List'!J76</f>
         <v>012345</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K79" t="str">
+        <f t="shared" si="1"/>
+        <v>Master Fault Signal,,BitAddress,PLC1,012345,,</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
         <f>'Point List'!C77</f>
         <v>Conductivity Analog</v>
@@ -11837,8 +12152,12 @@
         <f>'Point List'!J77</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K80" t="str">
+        <f t="shared" si="1"/>
+        <v>Conductivity Analog,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
         <f>'Point List'!C78</f>
         <v>RTD 1</v>
@@ -11854,8 +12173,12 @@
         <f>'Point List'!J78</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K81" t="str">
+        <f t="shared" si="1"/>
+        <v>RTD 1,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
         <f>'Point List'!C79</f>
         <v>RTD 2</v>
@@ -11871,8 +12194,12 @@
         <f>'Point List'!J79</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K82" t="str">
+        <f t="shared" si="1"/>
+        <v>RTD 2,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
         <f>'Point List'!C80</f>
         <v>RTD 3</v>
@@ -11888,8 +12215,12 @@
         <f>'Point List'!J80</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K83" t="str">
+        <f t="shared" si="1"/>
+        <v>RTD 3,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
         <f>'Point List'!C81</f>
         <v>AVAILABLE</v>
@@ -11905,8 +12236,12 @@
         <f>'Point List'!J81</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K84" t="str">
+        <f t="shared" si="1"/>
+        <v>AVAILABLE,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
         <f>'Point List'!C82</f>
         <v>AVAILABLE</v>
@@ -11922,8 +12257,12 @@
         <f>'Point List'!J82</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K85" t="str">
+        <f t="shared" si="1"/>
+        <v>AVAILABLE,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f>'Point List'!C83</f>
         <v>Flow Analog</v>
@@ -11939,8 +12278,12 @@
         <f>'Point List'!J83</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K86" t="str">
+        <f t="shared" si="1"/>
+        <v>Flow Analog,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
         <f>'Point List'!C84</f>
         <v>Conductivity Alarm</v>
@@ -11956,8 +12299,12 @@
         <f>'Point List'!J84</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K87" t="str">
+        <f t="shared" si="1"/>
+        <v>Conductivity Alarm,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="str">
         <f>'Point List'!C85</f>
         <v>Conductivity Fault</v>
@@ -11973,8 +12320,12 @@
         <f>'Point List'!J85</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K88" t="str">
+        <f t="shared" si="1"/>
+        <v>Conductivity Fault,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="str">
         <f>'Point List'!C86</f>
         <v>Level Low Switch</v>
@@ -11990,8 +12341,12 @@
         <f>'Point List'!J86</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K89" t="str">
+        <f t="shared" si="1"/>
+        <v>Level Low Switch,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
         <f>'Point List'!C87</f>
         <v>Level Low Low Switch</v>
@@ -12007,8 +12362,12 @@
         <f>'Point List'!J87</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K90" t="str">
+        <f t="shared" si="1"/>
+        <v>Level Low Low Switch,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="str">
         <f>'Point List'!C88</f>
         <v>Fan 1 Enable</v>
@@ -12024,8 +12383,12 @@
         <f>'Point List'!J88</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K91" t="str">
+        <f t="shared" si="1"/>
+        <v>Fan 1 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="str">
         <f>'Point List'!C89</f>
         <v>Fan 2 Enable</v>
@@ -12041,8 +12404,12 @@
         <f>'Point List'!J89</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K92" t="str">
+        <f t="shared" si="1"/>
+        <v>Fan 2 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="str">
         <f>'Point List'!C90</f>
         <v>Pump 1 Enable</v>
@@ -12058,8 +12425,12 @@
         <f>'Point List'!J90</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K93" t="str">
+        <f t="shared" si="1"/>
+        <v>Pump 1 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="str">
         <f>'Point List'!C91</f>
         <v>Pump 2 Enable</v>
@@ -12075,8 +12446,12 @@
         <f>'Point List'!J91</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K94" t="str">
+        <f t="shared" si="1"/>
+        <v>Pump 2 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="str">
         <f>'Point List'!C92</f>
         <v>Valve Actuation Signal</v>
@@ -12092,8 +12467,12 @@
         <f>'Point List'!J92</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K95" t="str">
+        <f t="shared" si="1"/>
+        <v>Valve Actuation Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="str">
         <f>'Point List'!C93</f>
         <v>Pressure Switch Signal</v>
@@ -12109,8 +12488,12 @@
         <f>'Point List'!J93</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K96" t="str">
+        <f t="shared" si="1"/>
+        <v>Pressure Switch Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
         <f>'Point List'!C94</f>
         <v>Active Pump  Current</v>
@@ -12126,8 +12509,12 @@
         <f>'Point List'!J94</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K97" t="str">
+        <f t="shared" si="1"/>
+        <v>Active Pump  Current,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="str">
         <f>'Point List'!C95</f>
         <v>Active Pump  Voltage</v>
@@ -12143,8 +12530,12 @@
         <f>'Point List'!J95</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K98" t="str">
+        <f t="shared" si="1"/>
+        <v>Active Pump  Voltage,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="str">
         <f>'Point List'!C96</f>
         <v>Valve Position Signal</v>
@@ -12160,8 +12551,12 @@
         <f>'Point List'!J96</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K99" t="str">
+        <f t="shared" si="1"/>
+        <v>Valve Position Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="str">
         <f>'Point List'!C97</f>
         <v>AVAILABLE</v>
@@ -12177,8 +12572,12 @@
         <f>'Point List'!J97</f>
         <v>NOT ACCESSIBLE</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K100" t="str">
+        <f t="shared" si="1"/>
+        <v>AVAILABLE,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="str">
         <f>'Point List'!C98</f>
         <v>Primary Pump Active</v>
@@ -12194,8 +12593,12 @@
         <f>'Point List'!J98</f>
         <v>012346</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K101" t="str">
+        <f t="shared" si="1"/>
+        <v>Primary Pump Active,,BitAddress,PLC1,012346,,</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="str">
         <f>'Point List'!C99</f>
         <v>Secondary Pump  Active</v>
@@ -12211,8 +12614,12 @@
         <f>'Point List'!J99</f>
         <v>012347</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K102" t="str">
+        <f t="shared" si="1"/>
+        <v>Secondary Pump  Active,,BitAddress,PLC1,012347,,</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="str">
         <f>'Point List'!C100</f>
         <v>Simplex Mode Active</v>
@@ -12228,8 +12635,12 @@
         <f>'Point List'!J100</f>
         <v>012348</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K103" t="str">
+        <f t="shared" si="1"/>
+        <v>Simplex Mode Active,,BitAddress,PLC1,012348,,</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" t="str">
         <f>'Point List'!C101</f>
         <v>Fan 1 Active</v>
@@ -12245,8 +12656,12 @@
         <f>'Point List'!J101</f>
         <v>012349</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K104" t="str">
+        <f t="shared" si="1"/>
+        <v>Fan 1 Active,,BitAddress,PLC1,012349,,</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="str">
         <f>'Point List'!C102</f>
         <v>Fan 2 Active</v>
@@ -12262,8 +12677,12 @@
         <f>'Point List'!J102</f>
         <v>012350</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K105" t="str">
+        <f t="shared" si="1"/>
+        <v>Fan 2 Active,,BitAddress,PLC1,012350,,</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" t="str">
         <f>'Point List'!C103</f>
         <v>Enable Pump Cycling</v>
@@ -12279,8 +12698,12 @@
         <f>'Point List'!J103</f>
         <v>012351</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K106" t="str">
+        <f t="shared" si="1"/>
+        <v>Enable Pump Cycling,,BitAddress,PLC1,012351,,</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="str">
         <f>'Point List'!C104</f>
         <v>System Diagnostics</v>
@@ -12296,8 +12719,12 @@
         <f>'Point List'!J104</f>
         <v>012352</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="K107" t="str">
+        <f t="shared" si="1"/>
+        <v>System Diagnostics,,BitAddress,PLC1,012352,,</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
         <f>'Point List'!C105</f>
         <v>0</v>
@@ -12314,7 +12741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
         <f>'Point List'!C106</f>
         <v>0</v>
@@ -12331,7 +12758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <f>'Point List'!C107</f>
         <v>0</v>
@@ -12348,7 +12775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111">
         <f>'Point List'!C108</f>
         <v>0</v>
@@ -12365,7 +12792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112">
         <f>'Point List'!C109</f>
         <v>0</v>
@@ -74043,4 +74470,3705 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B9609-D38B-45A0-9E25-0F7CEDBD1FA5}">
+  <dimension ref="A1:K194"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K1" t="str">
+        <f>A1</f>
+        <v>GP-Pro EX</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" t="s">
+        <v>304</v>
+      </c>
+      <c r="K2" t="str">
+        <f>_xlfn.CONCAT(A2,",",B2)</f>
+        <v>File Type,SymbolVariable</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="str">
+        <f>_xlfn.CONCAT(A3,",",B3,",",C3)</f>
+        <v>File Version,3,0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G5" t="s">
+        <v>310</v>
+      </c>
+      <c r="K5" t="str">
+        <f>_xlfn.CONCAT(A5,",",B5,",",C5,",",D5,",",E5,",",F5,",",G5)</f>
+        <v>Name,Index,Type,External/Internal,Address,Keep,Comment</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <f>'Point List'!C3</f>
+        <v>System Start</v>
+      </c>
+      <c r="C6" t="str">
+        <f>'Point List'!L3</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E6" t="str">
+        <f>'Point List'!J3</f>
+        <v>012289</v>
+      </c>
+      <c r="K6" t="str">
+        <f>_xlfn.CONCAT(A6,",",B6,",",C6,",",D6,",",E6,",",F6,",",G6)</f>
+        <v>System Start,,BitAddress,PLC1,012289,,</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f>'Point List'!C4</f>
+        <v>System Shutdown</v>
+      </c>
+      <c r="C7" t="str">
+        <f>'Point List'!L4</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E7" t="str">
+        <f>'Point List'!J4</f>
+        <v>012290</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" ref="K7:K70" si="0">_xlfn.CONCAT(A7,",",B7,",",C7,",",D7,",",E7,",",F7,",",G7)</f>
+        <v>System Shutdown,,BitAddress,PLC1,012290,,</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <f>'Point List'!C5</f>
+        <v>Simplex Mode</v>
+      </c>
+      <c r="C8" t="str">
+        <f>'Point List'!L5</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E8" t="str">
+        <f>'Point List'!J5</f>
+        <v>012291</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="0"/>
+        <v>Simplex Mode,,BitAddress,PLC1,012291,,</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f>'Point List'!C6</f>
+        <v>Manual Turnover</v>
+      </c>
+      <c r="C9" t="str">
+        <f>'Point List'!L6</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D9" t="s">
+        <v>313</v>
+      </c>
+      <c r="E9" t="str">
+        <f>'Point List'!J6</f>
+        <v>012292</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="0"/>
+        <v>Manual Turnover,,BitAddress,PLC1,012292,,</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <f>'Point List'!C7</f>
+        <v>Enable Manual Valve Control</v>
+      </c>
+      <c r="C10" t="str">
+        <f>'Point List'!L7</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D10" t="s">
+        <v>313</v>
+      </c>
+      <c r="E10" t="str">
+        <f>'Point List'!J7</f>
+        <v>012293</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="0"/>
+        <v>Enable Manual Valve Control,,BitAddress,PLC1,012293,,</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <f>'Point List'!C8</f>
+        <v>Enable Manual Fan Control</v>
+      </c>
+      <c r="C11" t="str">
+        <f>'Point List'!L8</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D11" t="s">
+        <v>313</v>
+      </c>
+      <c r="E11" t="str">
+        <f>'Point List'!J8</f>
+        <v>012294</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="0"/>
+        <v>Enable Manual Fan Control,,BitAddress,PLC1,012294,,</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="str">
+        <f>'Point List'!C9</f>
+        <v>AVAILABLE</v>
+      </c>
+      <c r="C12" t="str">
+        <f>'Point List'!L9</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E12" t="str">
+        <f>'Point List'!J9</f>
+        <v>012295</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,BitAddress,PLC1,012295,,</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="str">
+        <f>'Point List'!C10</f>
+        <v>Force Fan 1 On/Off</v>
+      </c>
+      <c r="C13" t="str">
+        <f>'Point List'!L10</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" t="str">
+        <f>'Point List'!J10</f>
+        <v>012296</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="0"/>
+        <v>Force Fan 1 On/Off,,BitAddress,PLC1,012296,,</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="str">
+        <f>'Point List'!C11</f>
+        <v>Force Fan 2 On/Off</v>
+      </c>
+      <c r="C14" t="str">
+        <f>'Point List'!L11</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D14" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" t="str">
+        <f>'Point List'!J11</f>
+        <v>012297</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="0"/>
+        <v>Force Fan 2 On/Off,,BitAddress,PLC1,012297,,</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="str">
+        <f>'Point List'!C12</f>
+        <v>Primary Hydraulic Fault ACK</v>
+      </c>
+      <c r="C15" t="str">
+        <f>'Point List'!L12</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D15" t="s">
+        <v>313</v>
+      </c>
+      <c r="E15" t="str">
+        <f>'Point List'!J12</f>
+        <v>012298</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="0"/>
+        <v>Primary Hydraulic Fault ACK,,BitAddress,PLC1,012298,,</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
+        <f>'Point List'!C13</f>
+        <v>Secondary Hydraulic Fault ACK</v>
+      </c>
+      <c r="C16" t="str">
+        <f>'Point List'!L13</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D16" t="s">
+        <v>313</v>
+      </c>
+      <c r="E16" t="str">
+        <f>'Point List'!J13</f>
+        <v>012299</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="0"/>
+        <v>Secondary Hydraulic Fault ACK,,BitAddress,PLC1,012299,,</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="str">
+        <f>'Point List'!C14</f>
+        <v>Enable Pump Cycling</v>
+      </c>
+      <c r="C17" t="str">
+        <f>'Point List'!L14</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D17" t="s">
+        <v>313</v>
+      </c>
+      <c r="E17" t="str">
+        <f>'Point List'!J14</f>
+        <v>012300</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="0"/>
+        <v>Enable Pump Cycling,,BitAddress,PLC1,012300,,</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="str">
+        <f>'Point List'!C15</f>
+        <v>Reset Pump Differential Signal</v>
+      </c>
+      <c r="C18" t="str">
+        <f>'Point List'!L15</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D18" t="s">
+        <v>313</v>
+      </c>
+      <c r="E18" t="str">
+        <f>'Point List'!J15</f>
+        <v>012301</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="0"/>
+        <v>Reset Pump Differential Signal,,BitAddress,PLC1,012301,,</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="str">
+        <f>'Point List'!C16</f>
+        <v>Fault ACK</v>
+      </c>
+      <c r="C19" t="str">
+        <f>'Point List'!L16</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D19" t="s">
+        <v>313</v>
+      </c>
+      <c r="E19" t="str">
+        <f>'Point List'!J16</f>
+        <v>012302</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="0"/>
+        <v>Fault ACK,,BitAddress,PLC1,012302,,</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="str">
+        <f>'Point List'!C17</f>
+        <v>AVAILABLE</v>
+      </c>
+      <c r="C20">
+        <f>'Point List'!L17</f>
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>313</v>
+      </c>
+      <c r="E20" t="str">
+        <f>'Point List'!J17</f>
+        <v>012303</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,0,PLC1,012303,,</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="str">
+        <f>'Point List'!C18</f>
+        <v>AVAILABLE</v>
+      </c>
+      <c r="C21">
+        <f>'Point List'!L18</f>
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E21" t="str">
+        <f>'Point List'!J18</f>
+        <v>012304</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,0,PLC1,012304,,</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="str">
+        <f>'Point List'!C19</f>
+        <v>System On</v>
+      </c>
+      <c r="C22" t="str">
+        <f>'Point List'!L19</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D22" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" t="str">
+        <f>'Point List'!J19</f>
+        <v>012305</v>
+      </c>
+      <c r="K22" t="str">
+        <f t="shared" si="0"/>
+        <v>System On,,BitAddress,PLC1,012305,,</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="str">
+        <f>'Point List'!C20</f>
+        <v>System Shutting Down</v>
+      </c>
+      <c r="C23" t="str">
+        <f>'Point List'!L20</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D23" t="s">
+        <v>313</v>
+      </c>
+      <c r="E23" t="str">
+        <f>'Point List'!J20</f>
+        <v>012306</v>
+      </c>
+      <c r="K23" t="str">
+        <f t="shared" si="0"/>
+        <v>System Shutting Down,,BitAddress,PLC1,012306,,</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="str">
+        <f>'Point List'!C21</f>
+        <v>System Initializing</v>
+      </c>
+      <c r="C24" t="str">
+        <f>'Point List'!L21</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D24" t="s">
+        <v>313</v>
+      </c>
+      <c r="E24" t="str">
+        <f>'Point List'!J21</f>
+        <v>012307</v>
+      </c>
+      <c r="K24" t="str">
+        <f t="shared" si="0"/>
+        <v>System Initializing,,BitAddress,PLC1,012307,,</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="str">
+        <f>'Point List'!C22</f>
+        <v>System Calibrating</v>
+      </c>
+      <c r="C25" t="str">
+        <f>'Point List'!L22</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D25" t="s">
+        <v>313</v>
+      </c>
+      <c r="E25" t="str">
+        <f>'Point List'!J22</f>
+        <v>012308</v>
+      </c>
+      <c r="K25" t="str">
+        <f t="shared" si="0"/>
+        <v>System Calibrating,,BitAddress,PLC1,012308,,</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="str">
+        <f>'Point List'!C23</f>
+        <v>Measured Pump Power</v>
+      </c>
+      <c r="C26" t="str">
+        <f>'Point List'!L23</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D26" t="s">
+        <v>313</v>
+      </c>
+      <c r="E26" t="str">
+        <f>'Point List'!J23</f>
+        <v>412557</v>
+      </c>
+      <c r="K26" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Pump Power,,WordAddress,PLC1,412557,,</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="str">
+        <f>'Point List'!C24</f>
+        <v>Measured Inlet Coolant Temperature</v>
+      </c>
+      <c r="C27" t="str">
+        <f>'Point List'!L24</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D27" t="s">
+        <v>313</v>
+      </c>
+      <c r="E27" t="str">
+        <f>'Point List'!J24</f>
+        <v>412559</v>
+      </c>
+      <c r="K27" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Inlet Coolant Temperature,,WordAddress,PLC1,412559,,</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="str">
+        <f>'Point List'!C25</f>
+        <v>Measured Conductivity</v>
+      </c>
+      <c r="C28" t="str">
+        <f>'Point List'!L25</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D28" t="s">
+        <v>313</v>
+      </c>
+      <c r="E28" t="str">
+        <f>'Point List'!J25</f>
+        <v>412561</v>
+      </c>
+      <c r="K28" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Conductivity,,WordAddress,PLC1,412561,,</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="str">
+        <f>'Point List'!C26</f>
+        <v>Measured Flow</v>
+      </c>
+      <c r="C29" t="str">
+        <f>'Point List'!L26</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D29" t="s">
+        <v>313</v>
+      </c>
+      <c r="E29" t="str">
+        <f>'Point List'!J26</f>
+        <v>412563</v>
+      </c>
+      <c r="K29" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Flow,,WordAddress,PLC1,412563,,</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="str">
+        <f>'Point List'!C27</f>
+        <v>Valve Open Percentage</v>
+      </c>
+      <c r="C30" t="str">
+        <f>'Point List'!L27</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D30" t="s">
+        <v>313</v>
+      </c>
+      <c r="E30" t="str">
+        <f>'Point List'!J27</f>
+        <v>412565</v>
+      </c>
+      <c r="K30" t="str">
+        <f t="shared" si="0"/>
+        <v>Valve Open Percentage,,WordAddress,PLC1,412565,,</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="str">
+        <f>'Point List'!C28</f>
+        <v>Real RTD 1 Signal</v>
+      </c>
+      <c r="C31" t="str">
+        <f>'Point List'!L28</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D31" t="s">
+        <v>313</v>
+      </c>
+      <c r="E31" t="str">
+        <f>'Point List'!J28</f>
+        <v>412567</v>
+      </c>
+      <c r="K31" t="str">
+        <f t="shared" si="0"/>
+        <v>Real RTD 1 Signal,,WordAddress,PLC1,412567,,</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="str">
+        <f>'Point List'!C29</f>
+        <v>Real RTD 2 Signal</v>
+      </c>
+      <c r="C32" t="str">
+        <f>'Point List'!L29</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D32" t="s">
+        <v>313</v>
+      </c>
+      <c r="E32" t="str">
+        <f>'Point List'!J29</f>
+        <v>412569</v>
+      </c>
+      <c r="K32" t="str">
+        <f t="shared" si="0"/>
+        <v>Real RTD 2 Signal,,WordAddress,PLC1,412569,,</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="str">
+        <f>'Point List'!C30</f>
+        <v>Real RTD 3 Signal</v>
+      </c>
+      <c r="C33" t="str">
+        <f>'Point List'!L30</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E33" t="str">
+        <f>'Point List'!J30</f>
+        <v>412571</v>
+      </c>
+      <c r="K33" t="str">
+        <f t="shared" si="0"/>
+        <v>Real RTD 3 Signal,,WordAddress,PLC1,412571,,</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="str">
+        <f>'Point List'!C31</f>
+        <v>AVAILABLE</v>
+      </c>
+      <c r="C34" t="str">
+        <f>'Point List'!L31</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D34" t="s">
+        <v>313</v>
+      </c>
+      <c r="E34" t="str">
+        <f>'Point List'!J31</f>
+        <v>412573</v>
+      </c>
+      <c r="K34" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,WordAddress,PLC1,412573,,</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="str">
+        <f>'Point List'!C32</f>
+        <v xml:space="preserve">Measured Valve Position </v>
+      </c>
+      <c r="C35" t="str">
+        <f>'Point List'!L32</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D35" t="s">
+        <v>313</v>
+      </c>
+      <c r="E35" t="str">
+        <f>'Point List'!J32</f>
+        <v>412575</v>
+      </c>
+      <c r="K35" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Valve Position ,,WordAddress,PLC1,412575,,</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="str">
+        <f>'Point List'!C33</f>
+        <v>Debounced Water Level Low Signal</v>
+      </c>
+      <c r="C36" t="str">
+        <f>'Point List'!L33</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D36" t="s">
+        <v>313</v>
+      </c>
+      <c r="E36" t="str">
+        <f>'Point List'!J33</f>
+        <v>012309</v>
+      </c>
+      <c r="K36" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Water Level Low Signal,,WordAddress,PLC1,012309,,</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="str">
+        <f>'Point List'!C34</f>
+        <v>Debounced Water Level Low Low Signal</v>
+      </c>
+      <c r="C37">
+        <f>'Point List'!L34</f>
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>313</v>
+      </c>
+      <c r="E37" t="str">
+        <f>'Point List'!J34</f>
+        <v>012310</v>
+      </c>
+      <c r="K37" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Water Level Low Low Signal,,0,PLC1,012310,,</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="str">
+        <f>'Point List'!C35</f>
+        <v>Debounced Pressure Signal</v>
+      </c>
+      <c r="C38">
+        <f>'Point List'!L35</f>
+        <v>0</v>
+      </c>
+      <c r="D38" t="s">
+        <v>313</v>
+      </c>
+      <c r="E38" t="str">
+        <f>'Point List'!J35</f>
+        <v>012311</v>
+      </c>
+      <c r="K38" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Pressure Signal,,0,PLC1,012311,,</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="str">
+        <f>'Point List'!C36</f>
+        <v>Debounced Conductivity Alarm Signal</v>
+      </c>
+      <c r="C39">
+        <f>'Point List'!L36</f>
+        <v>0</v>
+      </c>
+      <c r="D39" t="s">
+        <v>313</v>
+      </c>
+      <c r="E39" t="str">
+        <f>'Point List'!J36</f>
+        <v>012312</v>
+      </c>
+      <c r="K39" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Conductivity Alarm Signal,,0,PLC1,012312,,</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="str">
+        <f>'Point List'!C37</f>
+        <v>Debounced Conductivity Fault Signal</v>
+      </c>
+      <c r="C40">
+        <f>'Point List'!L37</f>
+        <v>0</v>
+      </c>
+      <c r="D40" t="s">
+        <v>313</v>
+      </c>
+      <c r="E40" t="str">
+        <f>'Point List'!J37</f>
+        <v>012313</v>
+      </c>
+      <c r="K40" t="str">
+        <f t="shared" si="0"/>
+        <v>Debounced Conductivity Fault Signal,,0,PLC1,012313,,</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="str">
+        <f>'Point List'!C38</f>
+        <v>Output Water Level Low Signal</v>
+      </c>
+      <c r="C41" t="str">
+        <f>'Point List'!L38</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D41" t="s">
+        <v>313</v>
+      </c>
+      <c r="E41" t="str">
+        <f>'Point List'!J38</f>
+        <v>012314</v>
+      </c>
+      <c r="K41" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Water Level Low Signal,,BitAddress,PLC1,012314,,</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="str">
+        <f>'Point List'!C39</f>
+        <v>Output Water Level Low Low Signal</v>
+      </c>
+      <c r="C42" t="str">
+        <f>'Point List'!L39</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D42" t="s">
+        <v>313</v>
+      </c>
+      <c r="E42" t="str">
+        <f>'Point List'!J39</f>
+        <v>012315</v>
+      </c>
+      <c r="K42" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Water Level Low Low Signal,,BitAddress,PLC1,012315,,</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="str">
+        <f>'Point List'!C40</f>
+        <v>Output Pressure Signal</v>
+      </c>
+      <c r="C43" t="str">
+        <f>'Point List'!L40</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D43" t="s">
+        <v>313</v>
+      </c>
+      <c r="E43" t="str">
+        <f>'Point List'!J40</f>
+        <v>012316</v>
+      </c>
+      <c r="K43" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Pressure Signal,,BitAddress,PLC1,012316,,</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="str">
+        <f>'Point List'!C41</f>
+        <v>Output Conductivity Alarm Signal</v>
+      </c>
+      <c r="C44" t="str">
+        <f>'Point List'!L41</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D44" t="s">
+        <v>313</v>
+      </c>
+      <c r="E44" t="str">
+        <f>'Point List'!J41</f>
+        <v>012317</v>
+      </c>
+      <c r="K44" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Conductivity Alarm Signal,,BitAddress,PLC1,012317,,</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="str">
+        <f>'Point List'!C42</f>
+        <v>Output Conductivity Fault Signal</v>
+      </c>
+      <c r="C45" t="str">
+        <f>'Point List'!L42</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D45" t="s">
+        <v>313</v>
+      </c>
+      <c r="E45" t="str">
+        <f>'Point List'!J42</f>
+        <v>012318</v>
+      </c>
+      <c r="K45" t="str">
+        <f t="shared" si="0"/>
+        <v>Output Conductivity Fault Signal,,BitAddress,PLC1,012318,,</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="str">
+        <f>'Point List'!C43</f>
+        <v>Differential Pump Hours</v>
+      </c>
+      <c r="C46">
+        <f>'Point List'!L43</f>
+        <v>0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>313</v>
+      </c>
+      <c r="E46" t="str">
+        <f>'Point List'!J43</f>
+        <v>012453</v>
+      </c>
+      <c r="K46" t="str">
+        <f t="shared" si="0"/>
+        <v>Differential Pump Hours,,0,PLC1,012453,,</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="str">
+        <f>'Point List'!C44</f>
+        <v>System Pulse</v>
+      </c>
+      <c r="C47">
+        <f>'Point List'!L44</f>
+        <v>0</v>
+      </c>
+      <c r="D47" t="s">
+        <v>313</v>
+      </c>
+      <c r="E47" t="str">
+        <f>'Point List'!J44</f>
+        <v>012319</v>
+      </c>
+      <c r="K47" t="str">
+        <f t="shared" si="0"/>
+        <v>System Pulse,,0,PLC1,012319,,</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="str">
+        <f>'Point List'!C45</f>
+        <v>Measured Active Pump  Voltage</v>
+      </c>
+      <c r="C48" t="str">
+        <f>'Point List'!L45</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D48" t="s">
+        <v>313</v>
+      </c>
+      <c r="E48" t="str">
+        <f>'Point List'!J45</f>
+        <v>412577</v>
+      </c>
+      <c r="K48" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Active Pump  Voltage,,WordAddress,PLC1,412577,,</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="str">
+        <f>'Point List'!C46</f>
+        <v>Measured Active Pump  Current</v>
+      </c>
+      <c r="C49" t="str">
+        <f>'Point List'!L46</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D49" t="s">
+        <v>313</v>
+      </c>
+      <c r="E49" t="str">
+        <f>'Point List'!J46</f>
+        <v>412579</v>
+      </c>
+      <c r="K49" t="str">
+        <f t="shared" si="0"/>
+        <v>Measured Active Pump  Current,,WordAddress,PLC1,412579,,</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="str">
+        <f>'Point List'!C47</f>
+        <v>AVAILABLE</v>
+      </c>
+      <c r="C50" t="str">
+        <f>'Point List'!L47</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D50" t="s">
+        <v>313</v>
+      </c>
+      <c r="E50" t="str">
+        <f>'Point List'!J47</f>
+        <v>412581</v>
+      </c>
+      <c r="K50" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,WordAddress,PLC1,412581,,</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" t="str">
+        <f>'Point List'!C48</f>
+        <v>AVAILABLE</v>
+      </c>
+      <c r="C51">
+        <f>'Point List'!L48</f>
+        <v>0</v>
+      </c>
+      <c r="D51" t="s">
+        <v>313</v>
+      </c>
+      <c r="E51" t="str">
+        <f>'Point List'!J48</f>
+        <v>412583</v>
+      </c>
+      <c r="K51" t="str">
+        <f t="shared" si="0"/>
+        <v>AVAILABLE,,0,PLC1,412583,,</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" t="str">
+        <f>'Point List'!C49</f>
+        <v>Pump 1 Total Hours</v>
+      </c>
+      <c r="C52" t="str">
+        <f>'Point List'!L49</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D52" t="s">
+        <v>313</v>
+      </c>
+      <c r="E52" t="str">
+        <f>'Point List'!J49</f>
+        <v>412455</v>
+      </c>
+      <c r="K52" t="str">
+        <f t="shared" si="0"/>
+        <v>Pump 1 Total Hours,,WordAddress,PLC1,412455,,</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" t="str">
+        <f>'Point List'!C50</f>
+        <v>Pump 2 Total Hours</v>
+      </c>
+      <c r="C53" t="str">
+        <f>'Point List'!L50</f>
+        <v>WordAddress</v>
+      </c>
+      <c r="D53" t="s">
+        <v>313</v>
+      </c>
+      <c r="E53" t="str">
+        <f>'Point List'!J50</f>
+        <v>412457</v>
+      </c>
+      <c r="K53" t="str">
+        <f t="shared" si="0"/>
+        <v>Pump 2 Total Hours,,WordAddress,PLC1,412457,,</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" t="str">
+        <f>'Point List'!C51</f>
+        <v xml:space="preserve">High Coolant Temperature </v>
+      </c>
+      <c r="C54" t="str">
+        <f>'Point List'!L51</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D54" t="s">
+        <v>313</v>
+      </c>
+      <c r="E54" t="str">
+        <f>'Point List'!J51</f>
+        <v>012320</v>
+      </c>
+      <c r="K54" t="str">
+        <f t="shared" si="0"/>
+        <v>High Coolant Temperature ,,BitAddress,PLC1,012320,,</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" t="str">
+        <f>'Point List'!C52</f>
+        <v>Low Coolant Level in Vessel</v>
+      </c>
+      <c r="C55" t="str">
+        <f>'Point List'!L52</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D55" t="s">
+        <v>313</v>
+      </c>
+      <c r="E55" t="str">
+        <f>'Point List'!J52</f>
+        <v>012321</v>
+      </c>
+      <c r="K55" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Coolant Level in Vessel,,BitAddress,PLC1,012321,,</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" t="str">
+        <f>'Point List'!C53</f>
+        <v xml:space="preserve">High Coolant Conductivity </v>
+      </c>
+      <c r="C56" t="str">
+        <f>'Point List'!L53</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D56" t="s">
+        <v>313</v>
+      </c>
+      <c r="E56" t="str">
+        <f>'Point List'!J53</f>
+        <v>012322</v>
+      </c>
+      <c r="K56" t="str">
+        <f t="shared" si="0"/>
+        <v>High Coolant Conductivity ,,BitAddress,PLC1,012322,,</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" t="str">
+        <f>'Point List'!C54</f>
+        <v>Low Hydraulic Power</v>
+      </c>
+      <c r="C57" t="str">
+        <f>'Point List'!L54</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D57" t="s">
+        <v>313</v>
+      </c>
+      <c r="E57" t="str">
+        <f>'Point List'!J54</f>
+        <v>012323</v>
+      </c>
+      <c r="K57" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Hydraulic Power,,BitAddress,PLC1,012323,,</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" t="str">
+        <f>'Point List'!C55</f>
+        <v>Low Hydraulic Flow</v>
+      </c>
+      <c r="C58" t="str">
+        <f>'Point List'!L55</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D58" t="s">
+        <v>313</v>
+      </c>
+      <c r="E58" t="str">
+        <f>'Point List'!J55</f>
+        <v>012324</v>
+      </c>
+      <c r="K58" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Hydraulic Flow,,BitAddress,PLC1,012324,,</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" t="str">
+        <f>'Point List'!C56</f>
+        <v>Low Hydraulic Pressure</v>
+      </c>
+      <c r="C59" t="str">
+        <f>'Point List'!L56</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D59" t="s">
+        <v>313</v>
+      </c>
+      <c r="E59" t="str">
+        <f>'Point List'!J56</f>
+        <v>012325</v>
+      </c>
+      <c r="K59" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Hydraulic Pressure,,BitAddress,PLC1,012325,,</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" t="str">
+        <f>'Point List'!C57</f>
+        <v>Voltage Signal Malfunction</v>
+      </c>
+      <c r="C60" t="str">
+        <f>'Point List'!L57</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D60" t="s">
+        <v>313</v>
+      </c>
+      <c r="E60" t="str">
+        <f>'Point List'!J57</f>
+        <v>012326</v>
+      </c>
+      <c r="K60" t="str">
+        <f t="shared" si="0"/>
+        <v>Voltage Signal Malfunction,,BitAddress,PLC1,012326,,</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" t="str">
+        <f>'Point List'!C58</f>
+        <v>Current Signal Malfunction</v>
+      </c>
+      <c r="C61" t="str">
+        <f>'Point List'!L58</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D61" t="s">
+        <v>313</v>
+      </c>
+      <c r="E61" t="str">
+        <f>'Point List'!J58</f>
+        <v>012327</v>
+      </c>
+      <c r="K61" t="str">
+        <f t="shared" si="0"/>
+        <v>Current Signal Malfunction,,BitAddress,PLC1,012327,,</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" t="str">
+        <f>'Point List'!C59</f>
+        <v>Primary Hydraulic Failure</v>
+      </c>
+      <c r="C62" t="str">
+        <f>'Point List'!L59</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D62" t="s">
+        <v>313</v>
+      </c>
+      <c r="E62" t="str">
+        <f>'Point List'!J59</f>
+        <v>012328</v>
+      </c>
+      <c r="K62" t="str">
+        <f t="shared" si="0"/>
+        <v>Primary Hydraulic Failure,,BitAddress,PLC1,012328,,</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" t="str">
+        <f>'Point List'!C60</f>
+        <v>Secondary Hydraulic Failure</v>
+      </c>
+      <c r="C63" t="str">
+        <f>'Point List'!L60</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D63" t="s">
+        <v>313</v>
+      </c>
+      <c r="E63" t="str">
+        <f>'Point List'!J60</f>
+        <v>012329</v>
+      </c>
+      <c r="K63" t="str">
+        <f t="shared" si="0"/>
+        <v>Secondary Hydraulic Failure,,BitAddress,PLC1,012329,,</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" t="str">
+        <f>'Point List'!C61</f>
+        <v>Automatic Valve Control Disabled</v>
+      </c>
+      <c r="C64" t="str">
+        <f>'Point List'!L61</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D64" t="s">
+        <v>313</v>
+      </c>
+      <c r="E64" t="str">
+        <f>'Point List'!J61</f>
+        <v>012330</v>
+      </c>
+      <c r="K64" t="str">
+        <f t="shared" si="0"/>
+        <v>Automatic Valve Control Disabled,,BitAddress,PLC1,012330,,</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" t="str">
+        <f>'Point List'!C62</f>
+        <v>Automatic Fan Control Disabled</v>
+      </c>
+      <c r="C65" t="str">
+        <f>'Point List'!L62</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D65" t="s">
+        <v>313</v>
+      </c>
+      <c r="E65" t="str">
+        <f>'Point List'!J62</f>
+        <v>012331</v>
+      </c>
+      <c r="K65" t="str">
+        <f t="shared" si="0"/>
+        <v>Automatic Fan Control Disabled,,BitAddress,PLC1,012331,,</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" t="str">
+        <f>'Point List'!C63</f>
+        <v>Flow Signal Malfunction</v>
+      </c>
+      <c r="C66" t="str">
+        <f>'Point List'!L63</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D66" t="s">
+        <v>313</v>
+      </c>
+      <c r="E66" t="str">
+        <f>'Point List'!J63</f>
+        <v>012332</v>
+      </c>
+      <c r="K66" t="str">
+        <f t="shared" si="0"/>
+        <v>Flow Signal Malfunction,,BitAddress,PLC1,012332,,</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" t="str">
+        <f>'Point List'!C64</f>
+        <v>Bad RTD 1 Signal</v>
+      </c>
+      <c r="C67" t="str">
+        <f>'Point List'!L64</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D67" t="s">
+        <v>313</v>
+      </c>
+      <c r="E67" t="str">
+        <f>'Point List'!J64</f>
+        <v>012333</v>
+      </c>
+      <c r="K67" t="str">
+        <f t="shared" si="0"/>
+        <v>Bad RTD 1 Signal,,BitAddress,PLC1,012333,,</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" t="str">
+        <f>'Point List'!C65</f>
+        <v>Bad RTD 2 Signal</v>
+      </c>
+      <c r="C68" t="str">
+        <f>'Point List'!L65</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D68" t="s">
+        <v>313</v>
+      </c>
+      <c r="E68" t="str">
+        <f>'Point List'!J65</f>
+        <v>012334</v>
+      </c>
+      <c r="K68" t="str">
+        <f t="shared" si="0"/>
+        <v>Bad RTD 2 Signal,,BitAddress,PLC1,012334,,</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" t="str">
+        <f>'Point List'!C66</f>
+        <v>Bad RTD 3 Signal</v>
+      </c>
+      <c r="C69" t="str">
+        <f>'Point List'!L66</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D69" t="s">
+        <v>313</v>
+      </c>
+      <c r="E69" t="str">
+        <f>'Point List'!J66</f>
+        <v>012335</v>
+      </c>
+      <c r="K69" t="str">
+        <f t="shared" si="0"/>
+        <v>Bad RTD 3 Signal,,BitAddress,PLC1,012335,,</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" t="str">
+        <f>'Point List'!C67</f>
+        <v>Pump Cycle Alarm</v>
+      </c>
+      <c r="C70" t="str">
+        <f>'Point List'!L67</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D70" t="s">
+        <v>313</v>
+      </c>
+      <c r="E70" t="str">
+        <f>'Point List'!J67</f>
+        <v>012336</v>
+      </c>
+      <c r="K70" t="str">
+        <f t="shared" si="0"/>
+        <v>Pump Cycle Alarm,,BitAddress,PLC1,012336,,</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" t="str">
+        <f>'Point List'!C68</f>
+        <v>Critical Temperature</v>
+      </c>
+      <c r="C71" t="str">
+        <f>'Point List'!L68</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D71" t="s">
+        <v>313</v>
+      </c>
+      <c r="E71" t="str">
+        <f>'Point List'!J68</f>
+        <v>012337</v>
+      </c>
+      <c r="K71" t="str">
+        <f t="shared" ref="K71:K107" si="1">_xlfn.CONCAT(A71,",",B71,",",C71,",",D71,",",E71,",",F71,",",G71)</f>
+        <v>Critical Temperature,,BitAddress,PLC1,012337,,</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" t="str">
+        <f>'Point List'!C69</f>
+        <v>Critical Vessel Level</v>
+      </c>
+      <c r="C72" t="str">
+        <f>'Point List'!L69</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D72" t="s">
+        <v>313</v>
+      </c>
+      <c r="E72" t="str">
+        <f>'Point List'!J69</f>
+        <v>012338</v>
+      </c>
+      <c r="K72" t="str">
+        <f t="shared" si="1"/>
+        <v>Critical Vessel Level,,BitAddress,PLC1,012338,,</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" t="str">
+        <f>'Point List'!C70</f>
+        <v>Critical Conductivity</v>
+      </c>
+      <c r="C73" t="str">
+        <f>'Point List'!L70</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D73" t="s">
+        <v>313</v>
+      </c>
+      <c r="E73" t="str">
+        <f>'Point List'!J70</f>
+        <v>012339</v>
+      </c>
+      <c r="K73" t="str">
+        <f t="shared" si="1"/>
+        <v>Critical Conductivity,,BitAddress,PLC1,012339,,</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" t="str">
+        <f>'Point List'!C71</f>
+        <v>Level Sensor Malfunction</v>
+      </c>
+      <c r="C74" t="str">
+        <f>'Point List'!L71</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D74" t="s">
+        <v>313</v>
+      </c>
+      <c r="E74" t="str">
+        <f>'Point List'!J71</f>
+        <v>012340</v>
+      </c>
+      <c r="K74" t="str">
+        <f t="shared" si="1"/>
+        <v>Level Sensor Malfunction,,BitAddress,PLC1,012340,,</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" t="str">
+        <f>'Point List'!C72</f>
+        <v>Conductivity Sensor Malfunction</v>
+      </c>
+      <c r="C75" t="str">
+        <f>'Point List'!L72</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D75" t="s">
+        <v>313</v>
+      </c>
+      <c r="E75" t="str">
+        <f>'Point List'!J72</f>
+        <v>012341</v>
+      </c>
+      <c r="K75" t="str">
+        <f t="shared" si="1"/>
+        <v>Conductivity Sensor Malfunction,,BitAddress,PLC1,012341,,</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" t="str">
+        <f>'Point List'!C73</f>
+        <v>Bingo Pumps</v>
+      </c>
+      <c r="C76" t="str">
+        <f>'Point List'!L73</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D76" t="s">
+        <v>313</v>
+      </c>
+      <c r="E76" t="str">
+        <f>'Point List'!J73</f>
+        <v>012342</v>
+      </c>
+      <c r="K76" t="str">
+        <f t="shared" si="1"/>
+        <v>Bingo Pumps,,BitAddress,PLC1,012342,,</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" t="str">
+        <f>'Point List'!C74</f>
+        <v>Temperature Sensor Malfunction</v>
+      </c>
+      <c r="C77" t="str">
+        <f>'Point List'!L74</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D77" t="s">
+        <v>313</v>
+      </c>
+      <c r="E77" t="str">
+        <f>'Point List'!J74</f>
+        <v>012343</v>
+      </c>
+      <c r="K77" t="str">
+        <f t="shared" si="1"/>
+        <v>Temperature Sensor Malfunction,,BitAddress,PLC1,012343,,</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" t="str">
+        <f>'Point List'!C75</f>
+        <v>Bad Valve Pos</v>
+      </c>
+      <c r="C78" t="str">
+        <f>'Point List'!L75</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D78" t="s">
+        <v>313</v>
+      </c>
+      <c r="E78" t="str">
+        <f>'Point List'!J75</f>
+        <v>012344</v>
+      </c>
+      <c r="K78" t="str">
+        <f t="shared" si="1"/>
+        <v>Bad Valve Pos,,BitAddress,PLC1,012344,,</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" t="str">
+        <f>'Point List'!C76</f>
+        <v>Master Fault Signal</v>
+      </c>
+      <c r="C79" t="str">
+        <f>'Point List'!L76</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D79" t="s">
+        <v>313</v>
+      </c>
+      <c r="E79" t="str">
+        <f>'Point List'!J76</f>
+        <v>012345</v>
+      </c>
+      <c r="K79" t="str">
+        <f t="shared" si="1"/>
+        <v>Master Fault Signal,,BitAddress,PLC1,012345,,</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" t="str">
+        <f>'Point List'!C77</f>
+        <v>Conductivity Analog</v>
+      </c>
+      <c r="C80">
+        <f>'Point List'!L77</f>
+        <v>0</v>
+      </c>
+      <c r="D80" t="s">
+        <v>313</v>
+      </c>
+      <c r="E80" t="str">
+        <f>'Point List'!J77</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K80" t="str">
+        <f t="shared" si="1"/>
+        <v>Conductivity Analog,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" t="str">
+        <f>'Point List'!C78</f>
+        <v>RTD 1</v>
+      </c>
+      <c r="C81">
+        <f>'Point List'!L78</f>
+        <v>0</v>
+      </c>
+      <c r="D81" t="s">
+        <v>313</v>
+      </c>
+      <c r="E81" t="str">
+        <f>'Point List'!J78</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K81" t="str">
+        <f t="shared" si="1"/>
+        <v>RTD 1,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" t="str">
+        <f>'Point List'!C79</f>
+        <v>RTD 2</v>
+      </c>
+      <c r="C82">
+        <f>'Point List'!L79</f>
+        <v>0</v>
+      </c>
+      <c r="D82" t="s">
+        <v>313</v>
+      </c>
+      <c r="E82" t="str">
+        <f>'Point List'!J79</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K82" t="str">
+        <f t="shared" si="1"/>
+        <v>RTD 2,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" t="str">
+        <f>'Point List'!C80</f>
+        <v>RTD 3</v>
+      </c>
+      <c r="C83">
+        <f>'Point List'!L80</f>
+        <v>0</v>
+      </c>
+      <c r="D83" t="s">
+        <v>313</v>
+      </c>
+      <c r="E83" t="str">
+        <f>'Point List'!J80</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K83" t="str">
+        <f t="shared" si="1"/>
+        <v>RTD 3,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" t="str">
+        <f>'Point List'!C81</f>
+        <v>AVAILABLE</v>
+      </c>
+      <c r="C84">
+        <f>'Point List'!L81</f>
+        <v>0</v>
+      </c>
+      <c r="D84" t="s">
+        <v>313</v>
+      </c>
+      <c r="E84" t="str">
+        <f>'Point List'!J81</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K84" t="str">
+        <f t="shared" si="1"/>
+        <v>AVAILABLE,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" t="str">
+        <f>'Point List'!C82</f>
+        <v>AVAILABLE</v>
+      </c>
+      <c r="C85">
+        <f>'Point List'!L82</f>
+        <v>0</v>
+      </c>
+      <c r="D85" t="s">
+        <v>313</v>
+      </c>
+      <c r="E85" t="str">
+        <f>'Point List'!J82</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K85" t="str">
+        <f t="shared" si="1"/>
+        <v>AVAILABLE,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" t="str">
+        <f>'Point List'!C83</f>
+        <v>Flow Analog</v>
+      </c>
+      <c r="C86">
+        <f>'Point List'!L83</f>
+        <v>0</v>
+      </c>
+      <c r="D86" t="s">
+        <v>313</v>
+      </c>
+      <c r="E86" t="str">
+        <f>'Point List'!J83</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K86" t="str">
+        <f t="shared" si="1"/>
+        <v>Flow Analog,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" t="str">
+        <f>'Point List'!C84</f>
+        <v>Conductivity Alarm</v>
+      </c>
+      <c r="C87">
+        <f>'Point List'!L84</f>
+        <v>0</v>
+      </c>
+      <c r="D87" t="s">
+        <v>313</v>
+      </c>
+      <c r="E87" t="str">
+        <f>'Point List'!J84</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K87" t="str">
+        <f t="shared" si="1"/>
+        <v>Conductivity Alarm,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" t="str">
+        <f>'Point List'!C85</f>
+        <v>Conductivity Fault</v>
+      </c>
+      <c r="C88">
+        <f>'Point List'!L85</f>
+        <v>0</v>
+      </c>
+      <c r="D88" t="s">
+        <v>313</v>
+      </c>
+      <c r="E88" t="str">
+        <f>'Point List'!J85</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K88" t="str">
+        <f t="shared" si="1"/>
+        <v>Conductivity Fault,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89" t="str">
+        <f>'Point List'!C86</f>
+        <v>Level Low Switch</v>
+      </c>
+      <c r="C89">
+        <f>'Point List'!L86</f>
+        <v>0</v>
+      </c>
+      <c r="D89" t="s">
+        <v>313</v>
+      </c>
+      <c r="E89" t="str">
+        <f>'Point List'!J86</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K89" t="str">
+        <f t="shared" si="1"/>
+        <v>Level Low Switch,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" t="str">
+        <f>'Point List'!C87</f>
+        <v>Level Low Low Switch</v>
+      </c>
+      <c r="C90">
+        <f>'Point List'!L87</f>
+        <v>0</v>
+      </c>
+      <c r="D90" t="s">
+        <v>313</v>
+      </c>
+      <c r="E90" t="str">
+        <f>'Point List'!J87</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K90" t="str">
+        <f t="shared" si="1"/>
+        <v>Level Low Low Switch,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91" t="str">
+        <f>'Point List'!C88</f>
+        <v>Fan 1 Enable</v>
+      </c>
+      <c r="C91">
+        <f>'Point List'!L88</f>
+        <v>0</v>
+      </c>
+      <c r="D91" t="s">
+        <v>313</v>
+      </c>
+      <c r="E91" t="str">
+        <f>'Point List'!J88</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K91" t="str">
+        <f t="shared" si="1"/>
+        <v>Fan 1 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92" t="str">
+        <f>'Point List'!C89</f>
+        <v>Fan 2 Enable</v>
+      </c>
+      <c r="C92">
+        <f>'Point List'!L89</f>
+        <v>0</v>
+      </c>
+      <c r="D92" t="s">
+        <v>313</v>
+      </c>
+      <c r="E92" t="str">
+        <f>'Point List'!J89</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K92" t="str">
+        <f t="shared" si="1"/>
+        <v>Fan 2 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" t="str">
+        <f>'Point List'!C90</f>
+        <v>Pump 1 Enable</v>
+      </c>
+      <c r="C93">
+        <f>'Point List'!L90</f>
+        <v>0</v>
+      </c>
+      <c r="D93" t="s">
+        <v>313</v>
+      </c>
+      <c r="E93" t="str">
+        <f>'Point List'!J90</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K93" t="str">
+        <f t="shared" si="1"/>
+        <v>Pump 1 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" t="str">
+        <f>'Point List'!C91</f>
+        <v>Pump 2 Enable</v>
+      </c>
+      <c r="C94">
+        <f>'Point List'!L91</f>
+        <v>0</v>
+      </c>
+      <c r="D94" t="s">
+        <v>313</v>
+      </c>
+      <c r="E94" t="str">
+        <f>'Point List'!J91</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K94" t="str">
+        <f t="shared" si="1"/>
+        <v>Pump 2 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" t="str">
+        <f>'Point List'!C92</f>
+        <v>Valve Actuation Signal</v>
+      </c>
+      <c r="C95">
+        <f>'Point List'!L92</f>
+        <v>0</v>
+      </c>
+      <c r="D95" t="s">
+        <v>313</v>
+      </c>
+      <c r="E95" t="str">
+        <f>'Point List'!J92</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K95" t="str">
+        <f t="shared" si="1"/>
+        <v>Valve Actuation Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" t="str">
+        <f>'Point List'!C93</f>
+        <v>Pressure Switch Signal</v>
+      </c>
+      <c r="C96">
+        <f>'Point List'!L93</f>
+        <v>0</v>
+      </c>
+      <c r="D96" t="s">
+        <v>313</v>
+      </c>
+      <c r="E96" t="str">
+        <f>'Point List'!J93</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K96" t="str">
+        <f t="shared" si="1"/>
+        <v>Pressure Switch Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" t="str">
+        <f>'Point List'!C94</f>
+        <v>Active Pump  Current</v>
+      </c>
+      <c r="C97">
+        <f>'Point List'!L94</f>
+        <v>0</v>
+      </c>
+      <c r="D97" t="s">
+        <v>313</v>
+      </c>
+      <c r="E97" t="str">
+        <f>'Point List'!J94</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K97" t="str">
+        <f t="shared" si="1"/>
+        <v>Active Pump  Current,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" t="str">
+        <f>'Point List'!C95</f>
+        <v>Active Pump  Voltage</v>
+      </c>
+      <c r="C98">
+        <f>'Point List'!L95</f>
+        <v>0</v>
+      </c>
+      <c r="D98" t="s">
+        <v>313</v>
+      </c>
+      <c r="E98" t="str">
+        <f>'Point List'!J95</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K98" t="str">
+        <f t="shared" si="1"/>
+        <v>Active Pump  Voltage,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" t="str">
+        <f>'Point List'!C96</f>
+        <v>Valve Position Signal</v>
+      </c>
+      <c r="C99">
+        <f>'Point List'!L96</f>
+        <v>0</v>
+      </c>
+      <c r="D99" t="s">
+        <v>313</v>
+      </c>
+      <c r="E99" t="str">
+        <f>'Point List'!J96</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K99" t="str">
+        <f t="shared" si="1"/>
+        <v>Valve Position Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" t="str">
+        <f>'Point List'!C97</f>
+        <v>AVAILABLE</v>
+      </c>
+      <c r="C100">
+        <f>'Point List'!L97</f>
+        <v>0</v>
+      </c>
+      <c r="D100" t="s">
+        <v>313</v>
+      </c>
+      <c r="E100" t="str">
+        <f>'Point List'!J97</f>
+        <v>NOT ACCESSIBLE</v>
+      </c>
+      <c r="K100" t="str">
+        <f t="shared" si="1"/>
+        <v>AVAILABLE,,0,PLC1,NOT ACCESSIBLE,,</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" t="str">
+        <f>'Point List'!C98</f>
+        <v>Primary Pump Active</v>
+      </c>
+      <c r="C101" t="str">
+        <f>'Point List'!L98</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D101" t="s">
+        <v>313</v>
+      </c>
+      <c r="E101" t="str">
+        <f>'Point List'!J98</f>
+        <v>012346</v>
+      </c>
+      <c r="K101" t="str">
+        <f t="shared" si="1"/>
+        <v>Primary Pump Active,,BitAddress,PLC1,012346,,</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" t="str">
+        <f>'Point List'!C99</f>
+        <v>Secondary Pump  Active</v>
+      </c>
+      <c r="C102" t="str">
+        <f>'Point List'!L99</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D102" t="s">
+        <v>313</v>
+      </c>
+      <c r="E102" t="str">
+        <f>'Point List'!J99</f>
+        <v>012347</v>
+      </c>
+      <c r="K102" t="str">
+        <f t="shared" si="1"/>
+        <v>Secondary Pump  Active,,BitAddress,PLC1,012347,,</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" t="str">
+        <f>'Point List'!C100</f>
+        <v>Simplex Mode Active</v>
+      </c>
+      <c r="C103" t="str">
+        <f>'Point List'!L100</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D103" t="s">
+        <v>313</v>
+      </c>
+      <c r="E103" t="str">
+        <f>'Point List'!J100</f>
+        <v>012348</v>
+      </c>
+      <c r="K103" t="str">
+        <f t="shared" si="1"/>
+        <v>Simplex Mode Active,,BitAddress,PLC1,012348,,</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" t="str">
+        <f>'Point List'!C101</f>
+        <v>Fan 1 Active</v>
+      </c>
+      <c r="C104" t="str">
+        <f>'Point List'!L101</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D104" t="s">
+        <v>313</v>
+      </c>
+      <c r="E104" t="str">
+        <f>'Point List'!J101</f>
+        <v>012349</v>
+      </c>
+      <c r="K104" t="str">
+        <f t="shared" si="1"/>
+        <v>Fan 1 Active,,BitAddress,PLC1,012349,,</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" t="str">
+        <f>'Point List'!C102</f>
+        <v>Fan 2 Active</v>
+      </c>
+      <c r="C105" t="str">
+        <f>'Point List'!L102</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D105" t="s">
+        <v>313</v>
+      </c>
+      <c r="E105" t="str">
+        <f>'Point List'!J102</f>
+        <v>012350</v>
+      </c>
+      <c r="K105" t="str">
+        <f t="shared" si="1"/>
+        <v>Fan 2 Active,,BitAddress,PLC1,012350,,</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" t="str">
+        <f>'Point List'!C103</f>
+        <v>Enable Pump Cycling</v>
+      </c>
+      <c r="C106" t="str">
+        <f>'Point List'!L103</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D106" t="s">
+        <v>313</v>
+      </c>
+      <c r="E106" t="str">
+        <f>'Point List'!J103</f>
+        <v>012351</v>
+      </c>
+      <c r="K106" t="str">
+        <f t="shared" si="1"/>
+        <v>Enable Pump Cycling,,BitAddress,PLC1,012351,,</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" t="str">
+        <f>'Point List'!C104</f>
+        <v>System Diagnostics</v>
+      </c>
+      <c r="C107" t="str">
+        <f>'Point List'!L104</f>
+        <v>BitAddress</v>
+      </c>
+      <c r="D107" t="s">
+        <v>313</v>
+      </c>
+      <c r="E107" t="str">
+        <f>'Point List'!J104</f>
+        <v>012352</v>
+      </c>
+      <c r="K107" t="str">
+        <f t="shared" si="1"/>
+        <v>System Diagnostics,,BitAddress,PLC1,012352,,</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <f>'Point List'!C105</f>
+        <v>0</v>
+      </c>
+      <c r="C108">
+        <f>'Point List'!L105</f>
+        <v>0</v>
+      </c>
+      <c r="D108" t="s">
+        <v>313</v>
+      </c>
+      <c r="E108">
+        <f>'Point List'!J105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <f>'Point List'!C106</f>
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <f>'Point List'!L106</f>
+        <v>0</v>
+      </c>
+      <c r="D109" t="s">
+        <v>313</v>
+      </c>
+      <c r="E109">
+        <f>'Point List'!J106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <f>'Point List'!C107</f>
+        <v>0</v>
+      </c>
+      <c r="C110">
+        <f>'Point List'!L107</f>
+        <v>0</v>
+      </c>
+      <c r="D110" t="s">
+        <v>313</v>
+      </c>
+      <c r="E110">
+        <f>'Point List'!J107</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <f>'Point List'!C108</f>
+        <v>0</v>
+      </c>
+      <c r="C111">
+        <f>'Point List'!L108</f>
+        <v>0</v>
+      </c>
+      <c r="D111" t="s">
+        <v>313</v>
+      </c>
+      <c r="E111">
+        <f>'Point List'!J108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <f>'Point List'!C109</f>
+        <v>0</v>
+      </c>
+      <c r="C112">
+        <f>'Point List'!L109</f>
+        <v>0</v>
+      </c>
+      <c r="D112" t="s">
+        <v>313</v>
+      </c>
+      <c r="E112">
+        <f>'Point List'!J109</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <f>'Point List'!C110</f>
+        <v>0</v>
+      </c>
+      <c r="C113">
+        <f>'Point List'!L110</f>
+        <v>0</v>
+      </c>
+      <c r="D113" t="s">
+        <v>313</v>
+      </c>
+      <c r="E113">
+        <f>'Point List'!J110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <f>'Point List'!C111</f>
+        <v>0</v>
+      </c>
+      <c r="C114">
+        <f>'Point List'!L111</f>
+        <v>0</v>
+      </c>
+      <c r="D114" t="s">
+        <v>313</v>
+      </c>
+      <c r="E114">
+        <f>'Point List'!J111</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <f>'Point List'!C112</f>
+        <v>0</v>
+      </c>
+      <c r="C115">
+        <f>'Point List'!L112</f>
+        <v>0</v>
+      </c>
+      <c r="D115" t="s">
+        <v>313</v>
+      </c>
+      <c r="E115">
+        <f>'Point List'!J112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <f>'Point List'!C113</f>
+        <v>0</v>
+      </c>
+      <c r="C116">
+        <f>'Point List'!L113</f>
+        <v>0</v>
+      </c>
+      <c r="D116" t="s">
+        <v>313</v>
+      </c>
+      <c r="E116">
+        <f>'Point List'!J113</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <f>'Point List'!C114</f>
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <f>'Point List'!L114</f>
+        <v>0</v>
+      </c>
+      <c r="D117" t="s">
+        <v>313</v>
+      </c>
+      <c r="E117">
+        <f>'Point List'!J114</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <f>'Point List'!C115</f>
+        <v>0</v>
+      </c>
+      <c r="C118">
+        <f>'Point List'!L115</f>
+        <v>0</v>
+      </c>
+      <c r="D118" t="s">
+        <v>313</v>
+      </c>
+      <c r="E118">
+        <f>'Point List'!J115</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <f>'Point List'!C116</f>
+        <v>0</v>
+      </c>
+      <c r="C119">
+        <f>'Point List'!L116</f>
+        <v>0</v>
+      </c>
+      <c r="D119" t="s">
+        <v>313</v>
+      </c>
+      <c r="E119">
+        <f>'Point List'!J116</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <f>'Point List'!C117</f>
+        <v>0</v>
+      </c>
+      <c r="C120">
+        <f>'Point List'!L117</f>
+        <v>0</v>
+      </c>
+      <c r="D120" t="s">
+        <v>313</v>
+      </c>
+      <c r="E120">
+        <f>'Point List'!J117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <f>'Point List'!C118</f>
+        <v>0</v>
+      </c>
+      <c r="C121">
+        <f>'Point List'!L118</f>
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>313</v>
+      </c>
+      <c r="E121">
+        <f>'Point List'!J118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <f>'Point List'!C119</f>
+        <v>0</v>
+      </c>
+      <c r="C122">
+        <f>'Point List'!L119</f>
+        <v>0</v>
+      </c>
+      <c r="D122" t="s">
+        <v>313</v>
+      </c>
+      <c r="E122">
+        <f>'Point List'!J119</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <f>'Point List'!C120</f>
+        <v>0</v>
+      </c>
+      <c r="C123">
+        <f>'Point List'!L120</f>
+        <v>0</v>
+      </c>
+      <c r="D123" t="s">
+        <v>313</v>
+      </c>
+      <c r="E123">
+        <f>'Point List'!J120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <f>'Point List'!C121</f>
+        <v>0</v>
+      </c>
+      <c r="C124">
+        <f>'Point List'!L121</f>
+        <v>0</v>
+      </c>
+      <c r="D124" t="s">
+        <v>313</v>
+      </c>
+      <c r="E124">
+        <f>'Point List'!J121</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <f>'Point List'!C122</f>
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <f>'Point List'!L122</f>
+        <v>0</v>
+      </c>
+      <c r="D125" t="s">
+        <v>313</v>
+      </c>
+      <c r="E125">
+        <f>'Point List'!J122</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <f>'Point List'!C123</f>
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <f>'Point List'!L123</f>
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>313</v>
+      </c>
+      <c r="E126">
+        <f>'Point List'!J123</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <f>'Point List'!C124</f>
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <f>'Point List'!L124</f>
+        <v>0</v>
+      </c>
+      <c r="D127" t="s">
+        <v>313</v>
+      </c>
+      <c r="E127">
+        <f>'Point List'!J124</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <f>'Point List'!C125</f>
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <f>'Point List'!L125</f>
+        <v>0</v>
+      </c>
+      <c r="D128" t="s">
+        <v>313</v>
+      </c>
+      <c r="E128">
+        <f>'Point List'!J125</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <f>'Point List'!C126</f>
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <f>'Point List'!L126</f>
+        <v>0</v>
+      </c>
+      <c r="D129" t="s">
+        <v>313</v>
+      </c>
+      <c r="E129">
+        <f>'Point List'!J126</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <f>'Point List'!C127</f>
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <f>'Point List'!L127</f>
+        <v>0</v>
+      </c>
+      <c r="D130" t="s">
+        <v>313</v>
+      </c>
+      <c r="E130">
+        <f>'Point List'!J127</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <f>'Point List'!C128</f>
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <f>'Point List'!L128</f>
+        <v>0</v>
+      </c>
+      <c r="D131" t="s">
+        <v>313</v>
+      </c>
+      <c r="E131">
+        <f>'Point List'!J128</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <f>'Point List'!C129</f>
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <f>'Point List'!L129</f>
+        <v>0</v>
+      </c>
+      <c r="D132" t="s">
+        <v>313</v>
+      </c>
+      <c r="E132">
+        <f>'Point List'!J129</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <f>'Point List'!C130</f>
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <f>'Point List'!L130</f>
+        <v>0</v>
+      </c>
+      <c r="D133" t="s">
+        <v>313</v>
+      </c>
+      <c r="E133">
+        <f>'Point List'!J130</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <f>'Point List'!C131</f>
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <f>'Point List'!L131</f>
+        <v>0</v>
+      </c>
+      <c r="D134" t="s">
+        <v>313</v>
+      </c>
+      <c r="E134">
+        <f>'Point List'!J131</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <f>'Point List'!C132</f>
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <f>'Point List'!L132</f>
+        <v>0</v>
+      </c>
+      <c r="D135" t="s">
+        <v>313</v>
+      </c>
+      <c r="E135">
+        <f>'Point List'!J132</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <f>'Point List'!C133</f>
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <f>'Point List'!L133</f>
+        <v>0</v>
+      </c>
+      <c r="D136" t="s">
+        <v>313</v>
+      </c>
+      <c r="E136">
+        <f>'Point List'!J133</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <f>'Point List'!C134</f>
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <f>'Point List'!L134</f>
+        <v>0</v>
+      </c>
+      <c r="D137" t="s">
+        <v>313</v>
+      </c>
+      <c r="E137">
+        <f>'Point List'!J134</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <f>'Point List'!C135</f>
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <f>'Point List'!L135</f>
+        <v>0</v>
+      </c>
+      <c r="D138" t="s">
+        <v>313</v>
+      </c>
+      <c r="E138">
+        <f>'Point List'!J135</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <f>'Point List'!C136</f>
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <f>'Point List'!L136</f>
+        <v>0</v>
+      </c>
+      <c r="D139" t="s">
+        <v>313</v>
+      </c>
+      <c r="E139">
+        <f>'Point List'!J136</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <f>'Point List'!C137</f>
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <f>'Point List'!L137</f>
+        <v>0</v>
+      </c>
+      <c r="D140" t="s">
+        <v>313</v>
+      </c>
+      <c r="E140">
+        <f>'Point List'!J137</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <f>'Point List'!C138</f>
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <f>'Point List'!L138</f>
+        <v>0</v>
+      </c>
+      <c r="D141" t="s">
+        <v>313</v>
+      </c>
+      <c r="E141">
+        <f>'Point List'!J138</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <f>'Point List'!C139</f>
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <f>'Point List'!L139</f>
+        <v>0</v>
+      </c>
+      <c r="D142" t="s">
+        <v>313</v>
+      </c>
+      <c r="E142">
+        <f>'Point List'!J139</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <f>'Point List'!C140</f>
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <f>'Point List'!L140</f>
+        <v>0</v>
+      </c>
+      <c r="D143" t="s">
+        <v>313</v>
+      </c>
+      <c r="E143">
+        <f>'Point List'!J140</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <f>'Point List'!C141</f>
+        <v>0</v>
+      </c>
+      <c r="C144">
+        <f>'Point List'!L141</f>
+        <v>0</v>
+      </c>
+      <c r="D144" t="s">
+        <v>313</v>
+      </c>
+      <c r="E144">
+        <f>'Point List'!J141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <f>'Point List'!C142</f>
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <f>'Point List'!L142</f>
+        <v>0</v>
+      </c>
+      <c r="D145" t="s">
+        <v>313</v>
+      </c>
+      <c r="E145">
+        <f>'Point List'!J142</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <f>'Point List'!C143</f>
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <f>'Point List'!L143</f>
+        <v>0</v>
+      </c>
+      <c r="D146" t="s">
+        <v>313</v>
+      </c>
+      <c r="E146">
+        <f>'Point List'!J143</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <f>'Point List'!C144</f>
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <f>'Point List'!L144</f>
+        <v>0</v>
+      </c>
+      <c r="D147" t="s">
+        <v>313</v>
+      </c>
+      <c r="E147">
+        <f>'Point List'!J144</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <f>'Point List'!C145</f>
+        <v>0</v>
+      </c>
+      <c r="C148">
+        <f>'Point List'!L145</f>
+        <v>0</v>
+      </c>
+      <c r="D148" t="s">
+        <v>313</v>
+      </c>
+      <c r="E148">
+        <f>'Point List'!J145</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <f>'Point List'!C146</f>
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <f>'Point List'!L146</f>
+        <v>0</v>
+      </c>
+      <c r="D149" t="s">
+        <v>313</v>
+      </c>
+      <c r="E149">
+        <f>'Point List'!J146</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <f>'Point List'!C147</f>
+        <v>0</v>
+      </c>
+      <c r="C150">
+        <f>'Point List'!L147</f>
+        <v>0</v>
+      </c>
+      <c r="D150" t="s">
+        <v>313</v>
+      </c>
+      <c r="E150">
+        <f>'Point List'!J147</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <f>'Point List'!C148</f>
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <f>'Point List'!L148</f>
+        <v>0</v>
+      </c>
+      <c r="D151" t="s">
+        <v>313</v>
+      </c>
+      <c r="E151">
+        <f>'Point List'!J148</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <f>'Point List'!C149</f>
+        <v>0</v>
+      </c>
+      <c r="C152">
+        <f>'Point List'!L149</f>
+        <v>0</v>
+      </c>
+      <c r="D152" t="s">
+        <v>313</v>
+      </c>
+      <c r="E152">
+        <f>'Point List'!J149</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <f>'Point List'!C150</f>
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <f>'Point List'!L150</f>
+        <v>0</v>
+      </c>
+      <c r="D153" t="s">
+        <v>313</v>
+      </c>
+      <c r="E153">
+        <f>'Point List'!J150</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <f>'Point List'!C151</f>
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <f>'Point List'!L151</f>
+        <v>0</v>
+      </c>
+      <c r="D154" t="s">
+        <v>313</v>
+      </c>
+      <c r="E154">
+        <f>'Point List'!J151</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <f>'Point List'!C152</f>
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <f>'Point List'!L152</f>
+        <v>0</v>
+      </c>
+      <c r="D155" t="s">
+        <v>313</v>
+      </c>
+      <c r="E155">
+        <f>'Point List'!J152</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <f>'Point List'!C153</f>
+        <v>0</v>
+      </c>
+      <c r="C156">
+        <f>'Point List'!L153</f>
+        <v>0</v>
+      </c>
+      <c r="D156" t="s">
+        <v>313</v>
+      </c>
+      <c r="E156">
+        <f>'Point List'!J153</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <f>'Point List'!C154</f>
+        <v>0</v>
+      </c>
+      <c r="C157">
+        <f>'Point List'!L154</f>
+        <v>0</v>
+      </c>
+      <c r="D157" t="s">
+        <v>313</v>
+      </c>
+      <c r="E157">
+        <f>'Point List'!J154</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <f>'Point List'!C155</f>
+        <v>0</v>
+      </c>
+      <c r="C158">
+        <f>'Point List'!L155</f>
+        <v>0</v>
+      </c>
+      <c r="D158" t="s">
+        <v>313</v>
+      </c>
+      <c r="E158">
+        <f>'Point List'!J155</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <f>'Point List'!C156</f>
+        <v>0</v>
+      </c>
+      <c r="C159">
+        <f>'Point List'!L156</f>
+        <v>0</v>
+      </c>
+      <c r="D159" t="s">
+        <v>313</v>
+      </c>
+      <c r="E159">
+        <f>'Point List'!J156</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <f>'Point List'!C157</f>
+        <v>0</v>
+      </c>
+      <c r="C160">
+        <f>'Point List'!L157</f>
+        <v>0</v>
+      </c>
+      <c r="D160" t="s">
+        <v>313</v>
+      </c>
+      <c r="E160">
+        <f>'Point List'!J157</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <f>'Point List'!C158</f>
+        <v>0</v>
+      </c>
+      <c r="C161">
+        <f>'Point List'!L158</f>
+        <v>0</v>
+      </c>
+      <c r="D161" t="s">
+        <v>313</v>
+      </c>
+      <c r="E161">
+        <f>'Point List'!J158</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <f>'Point List'!C159</f>
+        <v>0</v>
+      </c>
+      <c r="C162">
+        <f>'Point List'!L159</f>
+        <v>0</v>
+      </c>
+      <c r="D162" t="s">
+        <v>313</v>
+      </c>
+      <c r="E162">
+        <f>'Point List'!J159</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <f>'Point List'!C160</f>
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <f>'Point List'!L160</f>
+        <v>0</v>
+      </c>
+      <c r="D163" t="s">
+        <v>313</v>
+      </c>
+      <c r="E163">
+        <f>'Point List'!J160</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <f>'Point List'!C161</f>
+        <v>0</v>
+      </c>
+      <c r="C164">
+        <f>'Point List'!L161</f>
+        <v>0</v>
+      </c>
+      <c r="D164" t="s">
+        <v>313</v>
+      </c>
+      <c r="E164">
+        <f>'Point List'!J161</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <f>'Point List'!C162</f>
+        <v>0</v>
+      </c>
+      <c r="C165">
+        <f>'Point List'!L162</f>
+        <v>0</v>
+      </c>
+      <c r="D165" t="s">
+        <v>313</v>
+      </c>
+      <c r="E165">
+        <f>'Point List'!J162</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <f>'Point List'!C163</f>
+        <v>0</v>
+      </c>
+      <c r="C166">
+        <f>'Point List'!L163</f>
+        <v>0</v>
+      </c>
+      <c r="D166" t="s">
+        <v>313</v>
+      </c>
+      <c r="E166">
+        <f>'Point List'!J163</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <f>'Point List'!C164</f>
+        <v>0</v>
+      </c>
+      <c r="C167">
+        <f>'Point List'!L164</f>
+        <v>0</v>
+      </c>
+      <c r="D167" t="s">
+        <v>313</v>
+      </c>
+      <c r="E167">
+        <f>'Point List'!J164</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <f>'Point List'!C165</f>
+        <v>0</v>
+      </c>
+      <c r="C168">
+        <f>'Point List'!L165</f>
+        <v>0</v>
+      </c>
+      <c r="D168" t="s">
+        <v>313</v>
+      </c>
+      <c r="E168">
+        <f>'Point List'!J165</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <f>'Point List'!C166</f>
+        <v>0</v>
+      </c>
+      <c r="C169">
+        <f>'Point List'!L166</f>
+        <v>0</v>
+      </c>
+      <c r="D169" t="s">
+        <v>313</v>
+      </c>
+      <c r="E169">
+        <f>'Point List'!J166</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <f>'Point List'!C167</f>
+        <v>0</v>
+      </c>
+      <c r="C170">
+        <f>'Point List'!L167</f>
+        <v>0</v>
+      </c>
+      <c r="D170" t="s">
+        <v>313</v>
+      </c>
+      <c r="E170">
+        <f>'Point List'!J167</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <f>'Point List'!C168</f>
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <f>'Point List'!L168</f>
+        <v>0</v>
+      </c>
+      <c r="D171" t="s">
+        <v>313</v>
+      </c>
+      <c r="E171">
+        <f>'Point List'!J168</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <f>'Point List'!C169</f>
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <f>'Point List'!L169</f>
+        <v>0</v>
+      </c>
+      <c r="D172" t="s">
+        <v>313</v>
+      </c>
+      <c r="E172">
+        <f>'Point List'!J169</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <f>'Point List'!C170</f>
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <f>'Point List'!L170</f>
+        <v>0</v>
+      </c>
+      <c r="D173" t="s">
+        <v>313</v>
+      </c>
+      <c r="E173">
+        <f>'Point List'!J170</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <f>'Point List'!C171</f>
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <f>'Point List'!L171</f>
+        <v>0</v>
+      </c>
+      <c r="D174" t="s">
+        <v>313</v>
+      </c>
+      <c r="E174">
+        <f>'Point List'!J171</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <f>'Point List'!C172</f>
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <f>'Point List'!L172</f>
+        <v>0</v>
+      </c>
+      <c r="D175" t="s">
+        <v>313</v>
+      </c>
+      <c r="E175">
+        <f>'Point List'!J172</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <f>'Point List'!C173</f>
+        <v>0</v>
+      </c>
+      <c r="C176">
+        <f>'Point List'!L173</f>
+        <v>0</v>
+      </c>
+      <c r="D176" t="s">
+        <v>313</v>
+      </c>
+      <c r="E176">
+        <f>'Point List'!J173</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <f>'Point List'!C174</f>
+        <v>0</v>
+      </c>
+      <c r="C177">
+        <f>'Point List'!L174</f>
+        <v>0</v>
+      </c>
+      <c r="D177" t="s">
+        <v>313</v>
+      </c>
+      <c r="E177">
+        <f>'Point List'!J174</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <f>'Point List'!C175</f>
+        <v>0</v>
+      </c>
+      <c r="C178">
+        <f>'Point List'!L175</f>
+        <v>0</v>
+      </c>
+      <c r="D178" t="s">
+        <v>313</v>
+      </c>
+      <c r="E178">
+        <f>'Point List'!J175</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <f>'Point List'!C176</f>
+        <v>0</v>
+      </c>
+      <c r="C179">
+        <f>'Point List'!L176</f>
+        <v>0</v>
+      </c>
+      <c r="D179" t="s">
+        <v>313</v>
+      </c>
+      <c r="E179">
+        <f>'Point List'!J176</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <f>'Point List'!C177</f>
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <f>'Point List'!L177</f>
+        <v>0</v>
+      </c>
+      <c r="D180" t="s">
+        <v>313</v>
+      </c>
+      <c r="E180">
+        <f>'Point List'!J177</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <f>'Point List'!C178</f>
+        <v>0</v>
+      </c>
+      <c r="C181">
+        <f>'Point List'!L178</f>
+        <v>0</v>
+      </c>
+      <c r="D181" t="s">
+        <v>313</v>
+      </c>
+      <c r="E181">
+        <f>'Point List'!J178</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <f>'Point List'!C179</f>
+        <v>0</v>
+      </c>
+      <c r="C182">
+        <f>'Point List'!L179</f>
+        <v>0</v>
+      </c>
+      <c r="D182" t="s">
+        <v>313</v>
+      </c>
+      <c r="E182">
+        <f>'Point List'!J179</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <f>'Point List'!C180</f>
+        <v>0</v>
+      </c>
+      <c r="C183">
+        <f>'Point List'!L180</f>
+        <v>0</v>
+      </c>
+      <c r="D183" t="s">
+        <v>313</v>
+      </c>
+      <c r="E183">
+        <f>'Point List'!J180</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <f>'Point List'!C181</f>
+        <v>0</v>
+      </c>
+      <c r="C184">
+        <f>'Point List'!L181</f>
+        <v>0</v>
+      </c>
+      <c r="D184" t="s">
+        <v>313</v>
+      </c>
+      <c r="E184">
+        <f>'Point List'!J181</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <f>'Point List'!C182</f>
+        <v>0</v>
+      </c>
+      <c r="C185">
+        <f>'Point List'!L182</f>
+        <v>0</v>
+      </c>
+      <c r="D185" t="s">
+        <v>313</v>
+      </c>
+      <c r="E185">
+        <f>'Point List'!J182</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <f>'Point List'!C183</f>
+        <v>0</v>
+      </c>
+      <c r="C186">
+        <f>'Point List'!L183</f>
+        <v>0</v>
+      </c>
+      <c r="D186" t="s">
+        <v>313</v>
+      </c>
+      <c r="E186">
+        <f>'Point List'!J183</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <f>'Point List'!C184</f>
+        <v>0</v>
+      </c>
+      <c r="C187">
+        <f>'Point List'!L184</f>
+        <v>0</v>
+      </c>
+      <c r="D187" t="s">
+        <v>313</v>
+      </c>
+      <c r="E187">
+        <f>'Point List'!J184</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <f>'Point List'!C185</f>
+        <v>0</v>
+      </c>
+      <c r="C188">
+        <f>'Point List'!L185</f>
+        <v>0</v>
+      </c>
+      <c r="D188" t="s">
+        <v>313</v>
+      </c>
+      <c r="E188">
+        <f>'Point List'!J185</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <f>'Point List'!C186</f>
+        <v>0</v>
+      </c>
+      <c r="C189">
+        <f>'Point List'!L186</f>
+        <v>0</v>
+      </c>
+      <c r="D189" t="s">
+        <v>313</v>
+      </c>
+      <c r="E189">
+        <f>'Point List'!J186</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <f>'Point List'!C187</f>
+        <v>0</v>
+      </c>
+      <c r="C190">
+        <f>'Point List'!L187</f>
+        <v>0</v>
+      </c>
+      <c r="D190" t="s">
+        <v>313</v>
+      </c>
+      <c r="E190">
+        <f>'Point List'!J187</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <f>'Point List'!C188</f>
+        <v>0</v>
+      </c>
+      <c r="C191">
+        <f>'Point List'!L188</f>
+        <v>0</v>
+      </c>
+      <c r="D191" t="s">
+        <v>313</v>
+      </c>
+      <c r="E191">
+        <f>'Point List'!J188</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <f>'Point List'!C189</f>
+        <v>0</v>
+      </c>
+      <c r="C192">
+        <f>'Point List'!L189</f>
+        <v>0</v>
+      </c>
+      <c r="D192" t="s">
+        <v>313</v>
+      </c>
+      <c r="E192">
+        <f>'Point List'!J189</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <f>'Point List'!C190</f>
+        <v>0</v>
+      </c>
+      <c r="C193">
+        <f>'Point List'!L190</f>
+        <v>0</v>
+      </c>
+      <c r="D193" t="s">
+        <v>313</v>
+      </c>
+      <c r="E193">
+        <f>'Point List'!J190</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <f>'Point List'!C191</f>
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <f>'Point List'!L191</f>
+        <v>0</v>
+      </c>
+      <c r="D194" t="s">
+        <v>313</v>
+      </c>
+      <c r="E194">
+        <f>'Point List'!J191</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1734" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A426E290-5ED2-4342-8F05-30B6726B666F}"/>
+  <xr:revisionPtr revIDLastSave="1765" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56D085A7-0B10-4616-A2FD-419F36CBB186}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point List" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="320">
   <si>
     <t>Signal Type</t>
   </si>
@@ -867,9 +867,6 @@
     <t>Active Pump  Voltage</t>
   </si>
   <si>
-    <t>Valve Position Signal</t>
-  </si>
-  <si>
     <t>Bingo Pumps</t>
   </si>
   <si>
@@ -1007,16 +1004,41 @@
   <si>
     <t>BitAddress</t>
   </si>
+  <si>
+    <t>Valve Feedback Signal</t>
+  </si>
+  <si>
+    <t>SIG-40</t>
+  </si>
+  <si>
+    <t>Status Indicator Text</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>sStatus</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1145,19 +1167,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
@@ -1171,8 +1193,13 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1687,8 +1714,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}" name="Table1" displayName="Table1" ref="A1:W104" totalsRowShown="0" headerRowDxfId="23">
-  <autoFilter ref="A1:W104" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}" name="Table1" displayName="Table1" ref="A1:W106" totalsRowShown="0" headerRowDxfId="23">
+  <autoFilter ref="A1:W106" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{423FA6DC-9142-4672-A14E-553234A081EF}" name="Signal Type" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{56D9DA24-EF6A-4F6A-8733-677B62E46902}" name="Tag No" dataDxfId="21"/>
@@ -1954,7 +1981,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>213</v>
@@ -1978,7 +2005,7 @@
         <v>256</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>260</v>
@@ -2011,7 +2038,7 @@
         <v>174</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2025,7 +2052,7 @@
         <v>182</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>214</v>
@@ -2094,7 +2121,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>214</v>
@@ -2121,7 +2148,7 @@
         <v>255</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M3" s="6">
         <v>1</v>
@@ -2170,7 +2197,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>214</v>
@@ -2197,7 +2224,7 @@
         <v>255</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M4" s="6">
         <v>1</v>
@@ -2246,7 +2273,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>214</v>
@@ -2273,7 +2300,7 @@
         <v>255</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M5" s="6">
         <v>1</v>
@@ -2322,7 +2349,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>214</v>
@@ -2349,7 +2376,7 @@
         <v>255</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M6" s="6">
         <v>1</v>
@@ -2398,7 +2425,7 @@
         <v>21</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>214</v>
@@ -2425,7 +2452,7 @@
         <v>257</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M7" s="6">
         <v>1</v>
@@ -2474,7 +2501,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>214</v>
@@ -2501,7 +2528,7 @@
         <v>257</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M8" s="6">
         <v>1</v>
@@ -2547,7 +2574,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>12</v>
@@ -2577,7 +2604,7 @@
         <v>12</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M9" s="6">
         <v>1</v>
@@ -2626,7 +2653,7 @@
         <v>26</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>214</v>
@@ -2653,7 +2680,7 @@
         <v>257</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M10" s="6">
         <v>1</v>
@@ -2702,7 +2729,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>214</v>
@@ -2729,7 +2756,7 @@
         <v>257</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M11" s="6">
         <v>1</v>
@@ -2778,7 +2805,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>214</v>
@@ -2805,7 +2832,7 @@
         <v>255</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M12" s="6">
         <v>1</v>
@@ -2854,7 +2881,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>214</v>
@@ -2881,7 +2908,7 @@
         <v>255</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M13" s="6">
         <v>1</v>
@@ -2930,7 +2957,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>214</v>
@@ -2957,7 +2984,7 @@
         <v>255</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M14" s="6">
         <v>1</v>
@@ -3006,7 +3033,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>214</v>
@@ -3033,7 +3060,7 @@
         <v>255</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M15" s="6">
         <v>1</v>
@@ -3082,7 +3109,7 @@
         <v>38</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>214</v>
@@ -3109,7 +3136,7 @@
         <v>255</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M16" s="6">
         <v>1</v>
@@ -3155,7 +3182,7 @@
         <v>198</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="6" t="s">
@@ -3227,7 +3254,7 @@
         <v>199</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="6" t="s">
@@ -3302,7 +3329,7 @@
         <v>41</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>214</v>
@@ -3329,7 +3356,7 @@
         <v>258</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M19" s="6">
         <v>1</v>
@@ -3378,7 +3405,7 @@
         <v>43</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>214</v>
@@ -3405,7 +3432,7 @@
         <v>258</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M20" s="6">
         <v>1</v>
@@ -3454,7 +3481,7 @@
         <v>45</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>214</v>
@@ -3481,7 +3508,7 @@
         <v>258</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M21" s="6">
         <v>1</v>
@@ -3530,7 +3557,7 @@
         <v>47</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>214</v>
@@ -3557,7 +3584,7 @@
         <v>258</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M22" s="6">
         <v>1</v>
@@ -3606,7 +3633,7 @@
         <v>49</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>214</v>
@@ -3633,7 +3660,7 @@
         <v>259</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M23" s="6">
         <v>32</v>
@@ -3682,7 +3709,7 @@
         <v>51</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>214</v>
@@ -3709,7 +3736,7 @@
         <v>259</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M24" s="6">
         <v>32</v>
@@ -3758,7 +3785,7 @@
         <v>54</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>214</v>
@@ -3785,7 +3812,7 @@
         <v>259</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M25" s="6">
         <v>32</v>
@@ -3834,7 +3861,7 @@
         <v>56</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>214</v>
@@ -3861,7 +3888,7 @@
         <v>259</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M26" s="6">
         <v>32</v>
@@ -3910,7 +3937,7 @@
         <v>58</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>214</v>
@@ -3937,7 +3964,7 @@
         <v>259</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M27" s="6">
         <v>32</v>
@@ -3986,7 +4013,7 @@
         <v>60</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>214</v>
@@ -4013,7 +4040,7 @@
         <v>259</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M28" s="6">
         <v>32</v>
@@ -4062,7 +4089,7 @@
         <v>62</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>214</v>
@@ -4089,7 +4116,7 @@
         <v>259</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M29" s="6">
         <v>32</v>
@@ -4138,7 +4165,7 @@
         <v>64</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>214</v>
@@ -4165,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M30" s="6">
         <v>32</v>
@@ -4211,7 +4238,7 @@
         <v>65</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="6" t="s">
@@ -4239,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M31" s="6">
         <v>32</v>
@@ -4288,7 +4315,7 @@
         <v>263</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>214</v>
@@ -4315,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M32" s="6">
         <v>32</v>
@@ -4364,7 +4391,7 @@
         <v>68</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>234</v>
@@ -4391,7 +4418,7 @@
         <v>12</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M33" s="6">
         <v>1</v>
@@ -4440,7 +4467,7 @@
         <v>70</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>234</v>
@@ -4514,7 +4541,7 @@
         <v>72</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>234</v>
@@ -4588,7 +4615,7 @@
         <v>74</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>234</v>
@@ -4662,7 +4689,7 @@
         <v>76</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>234</v>
@@ -4736,7 +4763,7 @@
         <v>78</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>234</v>
@@ -4763,7 +4790,7 @@
         <v>258</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M38" s="6">
         <v>1</v>
@@ -4812,7 +4839,7 @@
         <v>80</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>234</v>
@@ -4839,7 +4866,7 @@
         <v>258</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M39" s="6">
         <v>1</v>
@@ -4888,7 +4915,7 @@
         <v>82</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>234</v>
@@ -4915,7 +4942,7 @@
         <v>258</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M40" s="6">
         <v>1</v>
@@ -4964,7 +4991,7 @@
         <v>84</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>234</v>
@@ -4991,7 +5018,7 @@
         <v>258</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M41" s="6">
         <v>1</v>
@@ -5040,7 +5067,7 @@
         <v>86</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>234</v>
@@ -5067,7 +5094,7 @@
         <v>258</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M42" s="6">
         <v>1</v>
@@ -5116,7 +5143,7 @@
         <v>197</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>234</v>
@@ -5190,7 +5217,7 @@
         <v>201</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>234</v>
@@ -5264,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>214</v>
@@ -5291,7 +5318,7 @@
         <v>259</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M45" s="6">
         <v>32</v>
@@ -5340,7 +5367,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>214</v>
@@ -5367,7 +5394,7 @@
         <v>259</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M46" s="6">
         <v>32</v>
@@ -5413,7 +5440,7 @@
         <v>177</v>
       </c>
       <c r="C47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>215</v>
@@ -5440,7 +5467,7 @@
         <v>259</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M47" s="6">
         <v>32</v>
@@ -5486,7 +5513,7 @@
         <v>178</v>
       </c>
       <c r="C48" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>215</v>
@@ -5560,7 +5587,7 @@
         <v>195</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>214</v>
@@ -5587,7 +5614,7 @@
         <v>259</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M49" s="6">
         <v>32</v>
@@ -5636,7 +5663,7 @@
         <v>196</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>214</v>
@@ -5663,7 +5690,7 @@
         <v>259</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M50" s="6">
         <v>32</v>
@@ -5712,7 +5739,7 @@
         <v>90</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>214</v>
@@ -5739,7 +5766,7 @@
         <v>258</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M51" s="6">
         <v>1</v>
@@ -5788,7 +5815,7 @@
         <v>92</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>214</v>
@@ -5815,7 +5842,7 @@
         <v>258</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M52" s="6">
         <v>1</v>
@@ -5864,7 +5891,7 @@
         <v>94</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>214</v>
@@ -5891,7 +5918,7 @@
         <v>258</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M53" s="6">
         <v>1</v>
@@ -5940,7 +5967,7 @@
         <v>96</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>214</v>
@@ -5967,7 +5994,7 @@
         <v>258</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M54" s="6">
         <v>1</v>
@@ -6016,7 +6043,7 @@
         <v>98</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>214</v>
@@ -6043,7 +6070,7 @@
         <v>258</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M55" s="6">
         <v>1</v>
@@ -6092,7 +6119,7 @@
         <v>100</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>214</v>
@@ -6119,7 +6146,7 @@
         <v>258</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M56" s="6">
         <v>1</v>
@@ -6165,10 +6192,10 @@
         <v>101</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>214</v>
@@ -6195,7 +6222,7 @@
         <v>258</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M57" s="6">
         <v>1</v>
@@ -6241,10 +6268,10 @@
         <v>102</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -6271,7 +6298,7 @@
         <v>258</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M58" s="6">
         <v>1</v>
@@ -6320,7 +6347,7 @@
         <v>104</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>214</v>
@@ -6347,7 +6374,7 @@
         <v>258</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M59" s="6">
         <v>1</v>
@@ -6396,7 +6423,7 @@
         <v>106</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>214</v>
@@ -6423,7 +6450,7 @@
         <v>258</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M60" s="6">
         <v>1</v>
@@ -6472,7 +6499,7 @@
         <v>108</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>214</v>
@@ -6499,7 +6526,7 @@
         <v>258</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M61" s="6">
         <v>1</v>
@@ -6548,7 +6575,7 @@
         <v>110</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>214</v>
@@ -6575,7 +6602,7 @@
         <v>258</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M62" s="6">
         <v>1</v>
@@ -6624,7 +6651,7 @@
         <v>112</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>214</v>
@@ -6651,7 +6678,7 @@
         <v>258</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M63" s="6">
         <v>1</v>
@@ -6700,7 +6727,7 @@
         <v>114</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>214</v>
@@ -6727,7 +6754,7 @@
         <v>258</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M64" s="6">
         <v>1</v>
@@ -6776,7 +6803,7 @@
         <v>116</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>214</v>
@@ -6803,7 +6830,7 @@
         <v>258</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M65" s="6">
         <v>1</v>
@@ -6852,7 +6879,7 @@
         <v>118</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>214</v>
@@ -6879,7 +6906,7 @@
         <v>258</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M66" s="6">
         <v>1</v>
@@ -6928,7 +6955,7 @@
         <v>120</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>214</v>
@@ -6955,7 +6982,7 @@
         <v>258</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M67" s="6">
         <v>1</v>
@@ -7004,7 +7031,7 @@
         <v>123</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>214</v>
@@ -7031,7 +7058,7 @@
         <v>258</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M68" s="6">
         <v>1</v>
@@ -7080,7 +7107,7 @@
         <v>125</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>214</v>
@@ -7107,7 +7134,7 @@
         <v>258</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M69" s="6">
         <v>1</v>
@@ -7156,7 +7183,7 @@
         <v>127</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>214</v>
@@ -7183,7 +7210,7 @@
         <v>258</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M70" s="6">
         <v>1</v>
@@ -7232,7 +7259,7 @@
         <v>129</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>214</v>
@@ -7259,7 +7286,7 @@
         <v>258</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M71" s="6">
         <v>1</v>
@@ -7308,7 +7335,7 @@
         <v>131</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>214</v>
@@ -7335,7 +7362,7 @@
         <v>258</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M72" s="6">
         <v>1</v>
@@ -7381,10 +7408,10 @@
         <v>132</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>214</v>
@@ -7411,7 +7438,7 @@
         <v>258</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M73" s="6">
         <v>1</v>
@@ -7457,10 +7484,10 @@
         <v>133</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>214</v>
@@ -7487,7 +7514,7 @@
         <v>258</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M74" s="6">
         <v>1</v>
@@ -7533,10 +7560,10 @@
         <v>134</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>214</v>
@@ -7563,7 +7590,7 @@
         <v>258</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M75" s="6">
         <v>1</v>
@@ -7612,7 +7639,7 @@
         <v>193</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>214</v>
@@ -7639,7 +7666,7 @@
         <v>258</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M76" s="6">
         <v>1</v>
@@ -7685,10 +7712,10 @@
         <v>136</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>214</v>
@@ -7757,7 +7784,7 @@
         <v>140</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>214</v>
@@ -7826,7 +7853,7 @@
         <v>143</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>214</v>
@@ -7895,7 +7922,7 @@
         <v>145</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>214</v>
@@ -7961,7 +7988,7 @@
         <v>146</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="5" t="s">
@@ -8013,7 +8040,7 @@
         <v>147</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D82" s="7"/>
       <c r="E82" s="5" t="s">
@@ -8065,10 +8092,10 @@
         <v>148</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>214</v>
@@ -8137,7 +8164,7 @@
         <v>150</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>214</v>
@@ -8206,7 +8233,7 @@
         <v>152</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>214</v>
@@ -8275,7 +8302,7 @@
         <v>154</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>214</v>
@@ -8344,7 +8371,7 @@
         <v>156</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>214</v>
@@ -8413,7 +8440,7 @@
         <v>158</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>214</v>
@@ -8482,7 +8509,7 @@
         <v>160</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>214</v>
@@ -8551,7 +8578,7 @@
         <v>162</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>214</v>
@@ -8620,7 +8647,7 @@
         <v>164</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>214</v>
@@ -8685,11 +8712,11 @@
       <c r="B92" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="15" t="s">
         <v>166</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>214</v>
@@ -8744,7 +8771,7 @@
         <v>12</v>
       </c>
       <c r="W92" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8758,7 +8785,7 @@
         <v>168</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>214</v>
@@ -8827,7 +8854,7 @@
         <v>266</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>214</v>
@@ -8896,7 +8923,7 @@
         <v>267</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>214</v>
@@ -8961,11 +8988,11 @@
       <c r="B96" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C96" s="9" t="s">
-        <v>268</v>
+      <c r="C96" s="15" t="s">
+        <v>314</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>214</v>
@@ -9031,7 +9058,7 @@
         <v>172</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="6" t="s">
@@ -9098,10 +9125,10 @@
         <v>264</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>214</v>
@@ -9113,7 +9140,7 @@
         <v>194</v>
       </c>
       <c r="H98" s="5" t="str">
-        <f t="shared" ref="H98:H104" si="17">_xlfn.CONCAT("0x",DEC2HEX(I98))</f>
+        <f t="shared" ref="H98:H105" si="17">_xlfn.CONCAT("0x",DEC2HEX(I98))</f>
         <v>0x3039</v>
       </c>
       <c r="I98" s="7">
@@ -9121,14 +9148,14 @@
         <v>12345</v>
       </c>
       <c r="J98" s="6" t="str">
-        <f t="shared" ref="J98:J104" si="18">_xlfn.CONCAT(0,I98+1)</f>
+        <f t="shared" ref="J98:J105" si="18">_xlfn.CONCAT(0,I98+1)</f>
         <v>012346</v>
       </c>
       <c r="K98" s="9" t="s">
         <v>258</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M98" s="9">
         <v>1</v>
@@ -9170,10 +9197,10 @@
         <v>265</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>214</v>
@@ -9200,7 +9227,7 @@
         <v>258</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M99" s="9">
         <v>1</v>
@@ -9239,13 +9266,13 @@
         <v>39</v>
       </c>
       <c r="B100" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C100" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="C100" s="9" t="s">
-        <v>271</v>
-      </c>
       <c r="D100" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>214</v>
@@ -9272,7 +9299,7 @@
         <v>258</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M100" s="9">
         <v>1</v>
@@ -9291,7 +9318,7 @@
         <v>12</v>
       </c>
       <c r="R100" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S100" t="s">
         <v>13</v>
@@ -9311,13 +9338,13 @@
         <v>39</v>
       </c>
       <c r="B101" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C101" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C101" s="9" t="s">
-        <v>276</v>
-      </c>
       <c r="D101" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>214</v>
@@ -9344,7 +9371,7 @@
         <v>258</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M101" s="9">
         <v>1</v>
@@ -9383,13 +9410,13 @@
         <v>39</v>
       </c>
       <c r="B102" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C102" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="C102" s="9" t="s">
-        <v>278</v>
-      </c>
       <c r="D102" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>214</v>
@@ -9416,7 +9443,7 @@
         <v>258</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M102" s="9">
         <v>1</v>
@@ -9455,13 +9482,13 @@
         <v>39</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C103" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>214</v>
@@ -9488,7 +9515,7 @@
         <v>258</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M103" s="9">
         <v>1</v>
@@ -9525,13 +9552,13 @@
         <v>39</v>
       </c>
       <c r="B104" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C104" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="C104" s="9" t="s">
-        <v>288</v>
-      </c>
       <c r="D104" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>214</v>
@@ -9558,7 +9585,7 @@
         <v>258</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M104" s="9">
         <v>1</v>
@@ -9590,8 +9617,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B105" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="E105" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="G105" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="H105" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>0x318A</v>
+      </c>
+      <c r="I105" s="16">
+        <f>I48+100</f>
+        <v>12682</v>
+      </c>
+      <c r="J105" s="6" t="str">
+        <f t="shared" si="18"/>
+        <v>012683</v>
+      </c>
+      <c r="K105" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="L105" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="M105" s="15">
+        <v>32</v>
+      </c>
+      <c r="N105" s="16" t="str">
+        <f>_xlfn.CONCAT("%MD",INDEX('Mapping Sheet'!G:G,Table1[[#This Row],[Modbus Address]]-12287,1))</f>
+        <v>%MD197</v>
+      </c>
+      <c r="O105" t="s">
+        <v>12</v>
+      </c>
+      <c r="P105" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>12</v>
+      </c>
+      <c r="R105" t="s">
+        <v>12</v>
+      </c>
+      <c r="S105" t="s">
+        <v>13</v>
+      </c>
+      <c r="T105" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="U105" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="V105" s="16"/>
+      <c r="W105" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="16"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="17"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="16"/>
+      <c r="H106" s="16"/>
+      <c r="I106" s="16"/>
+      <c r="J106" s="16"/>
+      <c r="K106" s="15"/>
+      <c r="L106" s="15"/>
+      <c r="M106" s="15"/>
+      <c r="N106" s="16"/>
+      <c r="O106" s="18"/>
+      <c r="P106" s="16"/>
+      <c r="Q106" s="18"/>
+      <c r="R106" s="16"/>
+      <c r="S106" s="19"/>
+      <c r="T106" s="18"/>
+      <c r="U106" s="18"/>
+      <c r="V106" s="16"/>
+      <c r="W106" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
     <row r="107" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -10498,7 +10623,7 @@
     <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1011" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="32" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
@@ -10521,7 +10646,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K1" t="str">
         <f>A1</f>
@@ -10530,10 +10655,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K2" t="str">
         <f>_xlfn.CONCAT(A2,",",B2)</f>
@@ -10542,7 +10667,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -10560,22 +10685,22 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" t="s">
         <v>305</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>306</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>307</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>308</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>309</v>
-      </c>
-      <c r="G5" t="s">
-        <v>310</v>
       </c>
       <c r="K5" t="str">
         <f>_xlfn.CONCAT(A5,",",B5,",",C5,",",D5,",",E5,",",F5,",",G5)</f>
@@ -10592,7 +10717,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E6" t="str">
         <f>'Point List'!J3</f>
@@ -10613,7 +10738,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E7" t="str">
         <f>'Point List'!J4</f>
@@ -10634,7 +10759,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E8" t="str">
         <f>'Point List'!J5</f>
@@ -10655,7 +10780,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E9" t="str">
         <f>'Point List'!J6</f>
@@ -10676,7 +10801,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E10" t="str">
         <f>'Point List'!J7</f>
@@ -10697,7 +10822,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E11" t="str">
         <f>'Point List'!J8</f>
@@ -10718,7 +10843,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E12" t="str">
         <f>'Point List'!J9</f>
@@ -10739,7 +10864,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E13" t="str">
         <f>'Point List'!J10</f>
@@ -10760,7 +10885,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E14" t="str">
         <f>'Point List'!J11</f>
@@ -10781,7 +10906,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E15" t="str">
         <f>'Point List'!J12</f>
@@ -10802,7 +10927,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E16" t="str">
         <f>'Point List'!J13</f>
@@ -10823,7 +10948,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E17" t="str">
         <f>'Point List'!J14</f>
@@ -10844,7 +10969,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E18" t="str">
         <f>'Point List'!J15</f>
@@ -10865,7 +10990,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E19" t="str">
         <f>'Point List'!J16</f>
@@ -10886,7 +11011,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E20" t="str">
         <f>'Point List'!J17</f>
@@ -10907,7 +11032,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E21" t="str">
         <f>'Point List'!J18</f>
@@ -10928,7 +11053,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E22" t="str">
         <f>'Point List'!J19</f>
@@ -10949,7 +11074,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E23" t="str">
         <f>'Point List'!J20</f>
@@ -10970,7 +11095,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E24" t="str">
         <f>'Point List'!J21</f>
@@ -10991,7 +11116,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E25" t="str">
         <f>'Point List'!J22</f>
@@ -11012,7 +11137,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E26" t="str">
         <f>'Point List'!J23</f>
@@ -11033,7 +11158,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E27" t="str">
         <f>'Point List'!J24</f>
@@ -11054,7 +11179,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E28" t="str">
         <f>'Point List'!J25</f>
@@ -11075,7 +11200,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E29" t="str">
         <f>'Point List'!J26</f>
@@ -11096,7 +11221,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E30" t="str">
         <f>'Point List'!J27</f>
@@ -11117,7 +11242,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E31" t="str">
         <f>'Point List'!J28</f>
@@ -11138,7 +11263,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E32" t="str">
         <f>'Point List'!J29</f>
@@ -11159,7 +11284,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E33" t="str">
         <f>'Point List'!J30</f>
@@ -11180,7 +11305,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E34" t="str">
         <f>'Point List'!J31</f>
@@ -11201,7 +11326,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E35" t="str">
         <f>'Point List'!J32</f>
@@ -11222,7 +11347,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D36" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E36" t="str">
         <f>'Point List'!J33</f>
@@ -11243,7 +11368,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E37" t="str">
         <f>'Point List'!J34</f>
@@ -11264,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E38" t="str">
         <f>'Point List'!J35</f>
@@ -11285,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E39" t="str">
         <f>'Point List'!J36</f>
@@ -11306,7 +11431,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E40" t="str">
         <f>'Point List'!J37</f>
@@ -11327,7 +11452,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E41" t="str">
         <f>'Point List'!J38</f>
@@ -11348,7 +11473,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E42" t="str">
         <f>'Point List'!J39</f>
@@ -11369,7 +11494,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E43" t="str">
         <f>'Point List'!J40</f>
@@ -11390,7 +11515,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E44" t="str">
         <f>'Point List'!J41</f>
@@ -11411,7 +11536,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E45" t="str">
         <f>'Point List'!J42</f>
@@ -11432,7 +11557,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E46" t="str">
         <f>'Point List'!J43</f>
@@ -11453,7 +11578,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E47" t="str">
         <f>'Point List'!J44</f>
@@ -11474,7 +11599,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E48" t="str">
         <f>'Point List'!J45</f>
@@ -11495,7 +11620,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E49" t="str">
         <f>'Point List'!J46</f>
@@ -11516,7 +11641,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E50" t="str">
         <f>'Point List'!J47</f>
@@ -11537,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E51" t="str">
         <f>'Point List'!J48</f>
@@ -11558,7 +11683,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E52" t="str">
         <f>'Point List'!J49</f>
@@ -11579,7 +11704,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E53" t="str">
         <f>'Point List'!J50</f>
@@ -11600,7 +11725,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E54" t="str">
         <f>'Point List'!J51</f>
@@ -11621,7 +11746,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E55" t="str">
         <f>'Point List'!J52</f>
@@ -11642,7 +11767,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D56" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E56" t="str">
         <f>'Point List'!J53</f>
@@ -11663,7 +11788,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D57" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E57" t="str">
         <f>'Point List'!J54</f>
@@ -11684,7 +11809,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D58" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E58" t="str">
         <f>'Point List'!J55</f>
@@ -11705,7 +11830,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D59" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E59" t="str">
         <f>'Point List'!J56</f>
@@ -11726,7 +11851,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D60" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E60" t="str">
         <f>'Point List'!J57</f>
@@ -11747,7 +11872,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D61" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E61" t="str">
         <f>'Point List'!J58</f>
@@ -11768,7 +11893,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D62" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E62" t="str">
         <f>'Point List'!J59</f>
@@ -11789,7 +11914,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E63" t="str">
         <f>'Point List'!J60</f>
@@ -11810,7 +11935,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D64" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E64" t="str">
         <f>'Point List'!J61</f>
@@ -11831,7 +11956,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D65" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E65" t="str">
         <f>'Point List'!J62</f>
@@ -11852,7 +11977,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D66" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E66" t="str">
         <f>'Point List'!J63</f>
@@ -11873,7 +11998,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D67" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E67" t="str">
         <f>'Point List'!J64</f>
@@ -11894,7 +12019,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D68" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E68" t="str">
         <f>'Point List'!J65</f>
@@ -11915,7 +12040,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D69" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E69" t="str">
         <f>'Point List'!J66</f>
@@ -11936,7 +12061,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D70" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E70" t="str">
         <f>'Point List'!J67</f>
@@ -11957,7 +12082,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D71" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E71" t="str">
         <f>'Point List'!J68</f>
@@ -11978,7 +12103,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D72" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E72" t="str">
         <f>'Point List'!J69</f>
@@ -11999,7 +12124,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D73" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E73" t="str">
         <f>'Point List'!J70</f>
@@ -12020,7 +12145,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D74" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E74" t="str">
         <f>'Point List'!J71</f>
@@ -12041,7 +12166,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D75" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E75" t="str">
         <f>'Point List'!J72</f>
@@ -12062,7 +12187,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D76" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E76" t="str">
         <f>'Point List'!J73</f>
@@ -12083,7 +12208,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D77" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E77" t="str">
         <f>'Point List'!J74</f>
@@ -12104,7 +12229,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D78" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E78" t="str">
         <f>'Point List'!J75</f>
@@ -12125,7 +12250,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D79" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E79" t="str">
         <f>'Point List'!J76</f>
@@ -12146,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E80" t="str">
         <f>'Point List'!J77</f>
@@ -12167,7 +12292,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E81" t="str">
         <f>'Point List'!J78</f>
@@ -12188,7 +12313,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E82" t="str">
         <f>'Point List'!J79</f>
@@ -12209,7 +12334,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E83" t="str">
         <f>'Point List'!J80</f>
@@ -12230,7 +12355,7 @@
         <v>0</v>
       </c>
       <c r="D84" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E84" t="str">
         <f>'Point List'!J81</f>
@@ -12251,7 +12376,7 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E85" t="str">
         <f>'Point List'!J82</f>
@@ -12272,7 +12397,7 @@
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E86" t="str">
         <f>'Point List'!J83</f>
@@ -12293,7 +12418,7 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E87" t="str">
         <f>'Point List'!J84</f>
@@ -12314,7 +12439,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E88" t="str">
         <f>'Point List'!J85</f>
@@ -12335,7 +12460,7 @@
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E89" t="str">
         <f>'Point List'!J86</f>
@@ -12356,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E90" t="str">
         <f>'Point List'!J87</f>
@@ -12377,7 +12502,7 @@
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E91" t="str">
         <f>'Point List'!J88</f>
@@ -12398,7 +12523,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E92" t="str">
         <f>'Point List'!J89</f>
@@ -12419,7 +12544,7 @@
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E93" t="str">
         <f>'Point List'!J90</f>
@@ -12440,7 +12565,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E94" t="str">
         <f>'Point List'!J91</f>
@@ -12461,7 +12586,7 @@
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E95" t="str">
         <f>'Point List'!J92</f>
@@ -12482,7 +12607,7 @@
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E96" t="str">
         <f>'Point List'!J93</f>
@@ -12503,7 +12628,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E97" t="str">
         <f>'Point List'!J94</f>
@@ -12524,7 +12649,7 @@
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E98" t="str">
         <f>'Point List'!J95</f>
@@ -12538,14 +12663,14 @@
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="str">
         <f>'Point List'!C96</f>
-        <v>Valve Position Signal</v>
+        <v>Valve Feedback Signal</v>
       </c>
       <c r="C99">
         <f>'Point List'!L96</f>
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E99" t="str">
         <f>'Point List'!J96</f>
@@ -12553,7 +12678,7 @@
       </c>
       <c r="K99" t="str">
         <f t="shared" si="1"/>
-        <v>Valve Position Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <v>Valve Feedback Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
@@ -12566,7 +12691,7 @@
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E100" t="str">
         <f>'Point List'!J97</f>
@@ -12587,7 +12712,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D101" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E101" t="str">
         <f>'Point List'!J98</f>
@@ -12608,7 +12733,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D102" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E102" t="str">
         <f>'Point List'!J99</f>
@@ -12629,7 +12754,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D103" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E103" t="str">
         <f>'Point List'!J100</f>
@@ -12650,7 +12775,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D104" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E104" t="str">
         <f>'Point List'!J101</f>
@@ -12671,7 +12796,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D105" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E105" t="str">
         <f>'Point List'!J102</f>
@@ -12692,7 +12817,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D106" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E106" t="str">
         <f>'Point List'!J103</f>
@@ -12713,7 +12838,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D107" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E107" t="str">
         <f>'Point List'!J104</f>
@@ -12725,20 +12850,20 @@
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A108">
+      <c r="A108" t="str">
         <f>'Point List'!C105</f>
-        <v>0</v>
-      </c>
-      <c r="C108">
+        <v>Status Indicator Text</v>
+      </c>
+      <c r="C108" t="str">
         <f>'Point List'!L105</f>
-        <v>0</v>
+        <v>WordAddress</v>
       </c>
       <c r="D108" t="s">
-        <v>313</v>
-      </c>
-      <c r="E108">
+        <v>312</v>
+      </c>
+      <c r="E108" t="str">
         <f>'Point List'!J105</f>
-        <v>0</v>
+        <v>012683</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
@@ -12751,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E109">
         <f>'Point List'!J106</f>
@@ -12768,7 +12893,7 @@
         <v>0</v>
       </c>
       <c r="D110" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E110">
         <f>'Point List'!J107</f>
@@ -12785,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E111">
         <f>'Point List'!J108</f>
@@ -12802,7 +12927,7 @@
         <v>0</v>
       </c>
       <c r="D112" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E112">
         <f>'Point List'!J109</f>
@@ -12819,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E113">
         <f>'Point List'!J110</f>
@@ -12836,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E114">
         <f>'Point List'!J111</f>
@@ -12853,7 +12978,7 @@
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E115">
         <f>'Point List'!J112</f>
@@ -12870,7 +12995,7 @@
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E116">
         <f>'Point List'!J113</f>
@@ -12887,7 +13012,7 @@
         <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E117">
         <f>'Point List'!J114</f>
@@ -12904,7 +13029,7 @@
         <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E118">
         <f>'Point List'!J115</f>
@@ -12921,7 +13046,7 @@
         <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E119">
         <f>'Point List'!J116</f>
@@ -12938,7 +13063,7 @@
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E120">
         <f>'Point List'!J117</f>
@@ -12955,7 +13080,7 @@
         <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E121">
         <f>'Point List'!J118</f>
@@ -12972,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="D122" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E122">
         <f>'Point List'!J119</f>
@@ -12989,7 +13114,7 @@
         <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E123">
         <f>'Point List'!J120</f>
@@ -13006,7 +13131,7 @@
         <v>0</v>
       </c>
       <c r="D124" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E124">
         <f>'Point List'!J121</f>
@@ -13023,7 +13148,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E125">
         <f>'Point List'!J122</f>
@@ -13040,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E126">
         <f>'Point List'!J123</f>
@@ -13057,7 +13182,7 @@
         <v>0</v>
       </c>
       <c r="D127" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E127">
         <f>'Point List'!J124</f>
@@ -13074,7 +13199,7 @@
         <v>0</v>
       </c>
       <c r="D128" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E128">
         <f>'Point List'!J125</f>
@@ -13091,7 +13216,7 @@
         <v>0</v>
       </c>
       <c r="D129" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E129">
         <f>'Point List'!J126</f>
@@ -13108,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="D130" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E130">
         <f>'Point List'!J127</f>
@@ -13125,7 +13250,7 @@
         <v>0</v>
       </c>
       <c r="D131" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E131">
         <f>'Point List'!J128</f>
@@ -13142,7 +13267,7 @@
         <v>0</v>
       </c>
       <c r="D132" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E132">
         <f>'Point List'!J129</f>
@@ -13159,7 +13284,7 @@
         <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E133">
         <f>'Point List'!J130</f>
@@ -13176,7 +13301,7 @@
         <v>0</v>
       </c>
       <c r="D134" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E134">
         <f>'Point List'!J131</f>
@@ -13193,7 +13318,7 @@
         <v>0</v>
       </c>
       <c r="D135" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E135">
         <f>'Point List'!J132</f>
@@ -13210,7 +13335,7 @@
         <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E136">
         <f>'Point List'!J133</f>
@@ -13227,7 +13352,7 @@
         <v>0</v>
       </c>
       <c r="D137" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E137">
         <f>'Point List'!J134</f>
@@ -13244,7 +13369,7 @@
         <v>0</v>
       </c>
       <c r="D138" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E138">
         <f>'Point List'!J135</f>
@@ -13261,7 +13386,7 @@
         <v>0</v>
       </c>
       <c r="D139" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E139">
         <f>'Point List'!J136</f>
@@ -13278,7 +13403,7 @@
         <v>0</v>
       </c>
       <c r="D140" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E140">
         <f>'Point List'!J137</f>
@@ -13295,7 +13420,7 @@
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E141">
         <f>'Point List'!J138</f>
@@ -13312,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E142">
         <f>'Point List'!J139</f>
@@ -13329,7 +13454,7 @@
         <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E143">
         <f>'Point List'!J140</f>
@@ -13346,7 +13471,7 @@
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E144">
         <f>'Point List'!J141</f>
@@ -13363,7 +13488,7 @@
         <v>0</v>
       </c>
       <c r="D145" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E145">
         <f>'Point List'!J142</f>
@@ -13380,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E146">
         <f>'Point List'!J143</f>
@@ -13397,7 +13522,7 @@
         <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E147">
         <f>'Point List'!J144</f>
@@ -13414,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E148">
         <f>'Point List'!J145</f>
@@ -13431,7 +13556,7 @@
         <v>0</v>
       </c>
       <c r="D149" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E149">
         <f>'Point List'!J146</f>
@@ -13448,7 +13573,7 @@
         <v>0</v>
       </c>
       <c r="D150" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E150">
         <f>'Point List'!J147</f>
@@ -13465,7 +13590,7 @@
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E151">
         <f>'Point List'!J148</f>
@@ -13482,7 +13607,7 @@
         <v>0</v>
       </c>
       <c r="D152" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E152">
         <f>'Point List'!J149</f>
@@ -13499,7 +13624,7 @@
         <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E153">
         <f>'Point List'!J150</f>
@@ -13516,7 +13641,7 @@
         <v>0</v>
       </c>
       <c r="D154" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E154">
         <f>'Point List'!J151</f>
@@ -13533,7 +13658,7 @@
         <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E155">
         <f>'Point List'!J152</f>
@@ -13550,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="D156" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E156">
         <f>'Point List'!J153</f>
@@ -13567,7 +13692,7 @@
         <v>0</v>
       </c>
       <c r="D157" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E157">
         <f>'Point List'!J154</f>
@@ -13584,7 +13709,7 @@
         <v>0</v>
       </c>
       <c r="D158" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E158">
         <f>'Point List'!J155</f>
@@ -13601,7 +13726,7 @@
         <v>0</v>
       </c>
       <c r="D159" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E159">
         <f>'Point List'!J156</f>
@@ -13618,7 +13743,7 @@
         <v>0</v>
       </c>
       <c r="D160" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E160">
         <f>'Point List'!J157</f>
@@ -13635,7 +13760,7 @@
         <v>0</v>
       </c>
       <c r="D161" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E161">
         <f>'Point List'!J158</f>
@@ -13652,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="D162" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E162">
         <f>'Point List'!J159</f>
@@ -13669,7 +13794,7 @@
         <v>0</v>
       </c>
       <c r="D163" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E163">
         <f>'Point List'!J160</f>
@@ -13686,7 +13811,7 @@
         <v>0</v>
       </c>
       <c r="D164" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E164">
         <f>'Point List'!J161</f>
@@ -13703,7 +13828,7 @@
         <v>0</v>
       </c>
       <c r="D165" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E165">
         <f>'Point List'!J162</f>
@@ -13720,7 +13845,7 @@
         <v>0</v>
       </c>
       <c r="D166" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E166">
         <f>'Point List'!J163</f>
@@ -13737,7 +13862,7 @@
         <v>0</v>
       </c>
       <c r="D167" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E167">
         <f>'Point List'!J164</f>
@@ -13754,7 +13879,7 @@
         <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E168">
         <f>'Point List'!J165</f>
@@ -13771,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="D169" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E169">
         <f>'Point List'!J166</f>
@@ -13788,7 +13913,7 @@
         <v>0</v>
       </c>
       <c r="D170" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E170">
         <f>'Point List'!J167</f>
@@ -13805,7 +13930,7 @@
         <v>0</v>
       </c>
       <c r="D171" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E171">
         <f>'Point List'!J168</f>
@@ -13822,7 +13947,7 @@
         <v>0</v>
       </c>
       <c r="D172" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E172">
         <f>'Point List'!J169</f>
@@ -13839,7 +13964,7 @@
         <v>0</v>
       </c>
       <c r="D173" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E173">
         <f>'Point List'!J170</f>
@@ -13856,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="D174" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E174">
         <f>'Point List'!J171</f>
@@ -13873,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="D175" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E175">
         <f>'Point List'!J172</f>
@@ -13890,7 +14015,7 @@
         <v>0</v>
       </c>
       <c r="D176" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E176">
         <f>'Point List'!J173</f>
@@ -13907,7 +14032,7 @@
         <v>0</v>
       </c>
       <c r="D177" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E177">
         <f>'Point List'!J174</f>
@@ -13924,7 +14049,7 @@
         <v>0</v>
       </c>
       <c r="D178" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E178">
         <f>'Point List'!J175</f>
@@ -13941,7 +14066,7 @@
         <v>0</v>
       </c>
       <c r="D179" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E179">
         <f>'Point List'!J176</f>
@@ -13958,7 +14083,7 @@
         <v>0</v>
       </c>
       <c r="D180" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E180">
         <f>'Point List'!J177</f>
@@ -13975,7 +14100,7 @@
         <v>0</v>
       </c>
       <c r="D181" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E181">
         <f>'Point List'!J178</f>
@@ -13992,7 +14117,7 @@
         <v>0</v>
       </c>
       <c r="D182" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E182">
         <f>'Point List'!J179</f>
@@ -14009,7 +14134,7 @@
         <v>0</v>
       </c>
       <c r="D183" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E183">
         <f>'Point List'!J180</f>
@@ -14026,7 +14151,7 @@
         <v>0</v>
       </c>
       <c r="D184" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E184">
         <f>'Point List'!J181</f>
@@ -14043,7 +14168,7 @@
         <v>0</v>
       </c>
       <c r="D185" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E185">
         <f>'Point List'!J182</f>
@@ -14060,7 +14185,7 @@
         <v>0</v>
       </c>
       <c r="D186" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E186">
         <f>'Point List'!J183</f>
@@ -14077,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="D187" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E187">
         <f>'Point List'!J184</f>
@@ -14094,7 +14219,7 @@
         <v>0</v>
       </c>
       <c r="D188" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E188">
         <f>'Point List'!J185</f>
@@ -14111,7 +14236,7 @@
         <v>0</v>
       </c>
       <c r="D189" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E189">
         <f>'Point List'!J186</f>
@@ -14128,7 +14253,7 @@
         <v>0</v>
       </c>
       <c r="D190" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E190">
         <f>'Point List'!J187</f>
@@ -14145,7 +14270,7 @@
         <v>0</v>
       </c>
       <c r="D191" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E191">
         <f>'Point List'!J188</f>
@@ -14162,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="D192" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E192">
         <f>'Point List'!J189</f>
@@ -14179,7 +14304,7 @@
         <v>0</v>
       </c>
       <c r="D193" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E193">
         <f>'Point List'!J190</f>
@@ -14196,7 +14321,7 @@
         <v>0</v>
       </c>
       <c r="D194" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E194">
         <f>'Point List'!J191</f>
@@ -14204,7 +14329,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -74474,7 +74599,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B9609-D38B-45A0-9E25-0F7CEDBD1FA5}">
-  <dimension ref="A1:K194"/>
+  <dimension ref="A1:K173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
@@ -74486,7 +74611,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K1" t="str">
         <f>A1</f>
@@ -74495,10 +74620,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K2" t="str">
         <f>_xlfn.CONCAT(A2,",",B2)</f>
@@ -74507,7 +74632,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -74525,22 +74650,22 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" t="s">
         <v>305</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>306</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>307</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>308</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>309</v>
-      </c>
-      <c r="G5" t="s">
-        <v>310</v>
       </c>
       <c r="K5" t="str">
         <f>_xlfn.CONCAT(A5,",",B5,",",C5,",",D5,",",E5,",",F5,",",G5)</f>
@@ -74557,7 +74682,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E6" t="str">
         <f>'Point List'!J3</f>
@@ -74578,7 +74703,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E7" t="str">
         <f>'Point List'!J4</f>
@@ -74599,7 +74724,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E8" t="str">
         <f>'Point List'!J5</f>
@@ -74620,7 +74745,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E9" t="str">
         <f>'Point List'!J6</f>
@@ -74641,7 +74766,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E10" t="str">
         <f>'Point List'!J7</f>
@@ -74662,7 +74787,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E11" t="str">
         <f>'Point List'!J8</f>
@@ -74683,7 +74808,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E12" t="str">
         <f>'Point List'!J9</f>
@@ -74704,7 +74829,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E13" t="str">
         <f>'Point List'!J10</f>
@@ -74725,7 +74850,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E14" t="str">
         <f>'Point List'!J11</f>
@@ -74746,7 +74871,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E15" t="str">
         <f>'Point List'!J12</f>
@@ -74767,7 +74892,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E16" t="str">
         <f>'Point List'!J13</f>
@@ -74788,7 +74913,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E17" t="str">
         <f>'Point List'!J14</f>
@@ -74809,7 +74934,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E18" t="str">
         <f>'Point List'!J15</f>
@@ -74830,7 +74955,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E19" t="str">
         <f>'Point List'!J16</f>
@@ -74851,7 +74976,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E20" t="str">
         <f>'Point List'!J17</f>
@@ -74872,7 +74997,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E21" t="str">
         <f>'Point List'!J18</f>
@@ -74893,7 +75018,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E22" t="str">
         <f>'Point List'!J19</f>
@@ -74914,7 +75039,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E23" t="str">
         <f>'Point List'!J20</f>
@@ -74935,7 +75060,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E24" t="str">
         <f>'Point List'!J21</f>
@@ -74956,7 +75081,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E25" t="str">
         <f>'Point List'!J22</f>
@@ -74977,7 +75102,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E26" t="str">
         <f>'Point List'!J23</f>
@@ -74998,7 +75123,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E27" t="str">
         <f>'Point List'!J24</f>
@@ -75019,7 +75144,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E28" t="str">
         <f>'Point List'!J25</f>
@@ -75040,7 +75165,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E29" t="str">
         <f>'Point List'!J26</f>
@@ -75061,7 +75186,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E30" t="str">
         <f>'Point List'!J27</f>
@@ -75082,7 +75207,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E31" t="str">
         <f>'Point List'!J28</f>
@@ -75103,7 +75228,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E32" t="str">
         <f>'Point List'!J29</f>
@@ -75124,7 +75249,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E33" t="str">
         <f>'Point List'!J30</f>
@@ -75145,7 +75270,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E34" t="str">
         <f>'Point List'!J31</f>
@@ -75166,7 +75291,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E35" t="str">
         <f>'Point List'!J32</f>
@@ -75187,7 +75312,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D36" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E36" t="str">
         <f>'Point List'!J33</f>
@@ -75208,7 +75333,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E37" t="str">
         <f>'Point List'!J34</f>
@@ -75229,7 +75354,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E38" t="str">
         <f>'Point List'!J35</f>
@@ -75250,7 +75375,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E39" t="str">
         <f>'Point List'!J36</f>
@@ -75271,7 +75396,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E40" t="str">
         <f>'Point List'!J37</f>
@@ -75292,7 +75417,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E41" t="str">
         <f>'Point List'!J38</f>
@@ -75313,7 +75438,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E42" t="str">
         <f>'Point List'!J39</f>
@@ -75334,7 +75459,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E43" t="str">
         <f>'Point List'!J40</f>
@@ -75355,7 +75480,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E44" t="str">
         <f>'Point List'!J41</f>
@@ -75376,7 +75501,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E45" t="str">
         <f>'Point List'!J42</f>
@@ -75397,7 +75522,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E46" t="str">
         <f>'Point List'!J43</f>
@@ -75418,7 +75543,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E47" t="str">
         <f>'Point List'!J44</f>
@@ -75439,7 +75564,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E48" t="str">
         <f>'Point List'!J45</f>
@@ -75460,7 +75585,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E49" t="str">
         <f>'Point List'!J46</f>
@@ -75481,7 +75606,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E50" t="str">
         <f>'Point List'!J47</f>
@@ -75502,7 +75627,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E51" t="str">
         <f>'Point List'!J48</f>
@@ -75523,7 +75648,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E52" t="str">
         <f>'Point List'!J49</f>
@@ -75544,7 +75669,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E53" t="str">
         <f>'Point List'!J50</f>
@@ -75565,7 +75690,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E54" t="str">
         <f>'Point List'!J51</f>
@@ -75586,7 +75711,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E55" t="str">
         <f>'Point List'!J52</f>
@@ -75607,7 +75732,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D56" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E56" t="str">
         <f>'Point List'!J53</f>
@@ -75628,7 +75753,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D57" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E57" t="str">
         <f>'Point List'!J54</f>
@@ -75649,7 +75774,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D58" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E58" t="str">
         <f>'Point List'!J55</f>
@@ -75670,7 +75795,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D59" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E59" t="str">
         <f>'Point List'!J56</f>
@@ -75691,7 +75816,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D60" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E60" t="str">
         <f>'Point List'!J57</f>
@@ -75712,7 +75837,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D61" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E61" t="str">
         <f>'Point List'!J58</f>
@@ -75733,7 +75858,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D62" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E62" t="str">
         <f>'Point List'!J59</f>
@@ -75754,7 +75879,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E63" t="str">
         <f>'Point List'!J60</f>
@@ -75775,7 +75900,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D64" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E64" t="str">
         <f>'Point List'!J61</f>
@@ -75796,7 +75921,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D65" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E65" t="str">
         <f>'Point List'!J62</f>
@@ -75817,7 +75942,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D66" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E66" t="str">
         <f>'Point List'!J63</f>
@@ -75838,7 +75963,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D67" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E67" t="str">
         <f>'Point List'!J64</f>
@@ -75859,7 +75984,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D68" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E68" t="str">
         <f>'Point List'!J65</f>
@@ -75880,7 +76005,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D69" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E69" t="str">
         <f>'Point List'!J66</f>
@@ -75901,7 +76026,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D70" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E70" t="str">
         <f>'Point List'!J67</f>
@@ -75922,14 +76047,14 @@
         <v>BitAddress</v>
       </c>
       <c r="D71" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E71" t="str">
         <f>'Point List'!J68</f>
         <v>012337</v>
       </c>
       <c r="K71" t="str">
-        <f t="shared" ref="K71:K107" si="1">_xlfn.CONCAT(A71,",",B71,",",C71,",",D71,",",E71,",",F71,",",G71)</f>
+        <f t="shared" ref="K71:K79" si="1">_xlfn.CONCAT(A71,",",B71,",",C71,",",D71,",",E71,",",F71,",",G71)</f>
         <v>Critical Temperature,,BitAddress,PLC1,012337,,</v>
       </c>
     </row>
@@ -75943,7 +76068,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D72" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E72" t="str">
         <f>'Point List'!J69</f>
@@ -75964,7 +76089,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D73" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E73" t="str">
         <f>'Point List'!J70</f>
@@ -75985,7 +76110,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D74" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E74" t="str">
         <f>'Point List'!J71</f>
@@ -76006,7 +76131,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D75" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E75" t="str">
         <f>'Point List'!J72</f>
@@ -76027,7 +76152,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D76" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E76" t="str">
         <f>'Point List'!J73</f>
@@ -76048,7 +76173,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D77" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E77" t="str">
         <f>'Point List'!J74</f>
@@ -76069,7 +76194,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D78" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E78" t="str">
         <f>'Point List'!J75</f>
@@ -76090,7 +76215,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D79" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E79" t="str">
         <f>'Point List'!J76</f>
@@ -76103,2067 +76228,1630 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
-        <f>'Point List'!C77</f>
-        <v>Conductivity Analog</v>
-      </c>
-      <c r="C80">
-        <f>'Point List'!L77</f>
-        <v>0</v>
+        <f>'Point List'!C98</f>
+        <v>Primary Pump Active</v>
+      </c>
+      <c r="C80" t="str">
+        <f>'Point List'!L98</f>
+        <v>BitAddress</v>
       </c>
       <c r="D80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E80" t="str">
-        <f>'Point List'!J77</f>
-        <v>NOT ACCESSIBLE</v>
+        <f>'Point List'!J98</f>
+        <v>012346</v>
       </c>
       <c r="K80" t="str">
-        <f t="shared" si="1"/>
-        <v>Conductivity Analog,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <f>_xlfn.CONCAT(A80,",",B80,",",C80,",",D80,",",E80,",",F80,",",G80)</f>
+        <v>Primary Pump Active,,BitAddress,PLC1,012346,,</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
-        <f>'Point List'!C78</f>
-        <v>RTD 1</v>
-      </c>
-      <c r="C81">
-        <f>'Point List'!L78</f>
-        <v>0</v>
+        <f>'Point List'!C99</f>
+        <v>Secondary Pump  Active</v>
+      </c>
+      <c r="C81" t="str">
+        <f>'Point List'!L99</f>
+        <v>BitAddress</v>
       </c>
       <c r="D81" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E81" t="str">
-        <f>'Point List'!J78</f>
-        <v>NOT ACCESSIBLE</v>
+        <f>'Point List'!J99</f>
+        <v>012347</v>
       </c>
       <c r="K81" t="str">
-        <f t="shared" si="1"/>
-        <v>RTD 1,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <f>_xlfn.CONCAT(A81,",",B81,",",C81,",",D81,",",E81,",",F81,",",G81)</f>
+        <v>Secondary Pump  Active,,BitAddress,PLC1,012347,,</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
-        <f>'Point List'!C79</f>
-        <v>RTD 2</v>
-      </c>
-      <c r="C82">
-        <f>'Point List'!L79</f>
-        <v>0</v>
+        <f>'Point List'!C100</f>
+        <v>Simplex Mode Active</v>
+      </c>
+      <c r="C82" t="str">
+        <f>'Point List'!L100</f>
+        <v>BitAddress</v>
       </c>
       <c r="D82" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E82" t="str">
-        <f>'Point List'!J79</f>
-        <v>NOT ACCESSIBLE</v>
+        <f>'Point List'!J100</f>
+        <v>012348</v>
       </c>
       <c r="K82" t="str">
-        <f t="shared" si="1"/>
-        <v>RTD 2,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <f>_xlfn.CONCAT(A82,",",B82,",",C82,",",D82,",",E82,",",F82,",",G82)</f>
+        <v>Simplex Mode Active,,BitAddress,PLC1,012348,,</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
-        <f>'Point List'!C80</f>
-        <v>RTD 3</v>
-      </c>
-      <c r="C83">
-        <f>'Point List'!L80</f>
-        <v>0</v>
+        <f>'Point List'!C101</f>
+        <v>Fan 1 Active</v>
+      </c>
+      <c r="C83" t="str">
+        <f>'Point List'!L101</f>
+        <v>BitAddress</v>
       </c>
       <c r="D83" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E83" t="str">
-        <f>'Point List'!J80</f>
-        <v>NOT ACCESSIBLE</v>
+        <f>'Point List'!J101</f>
+        <v>012349</v>
       </c>
       <c r="K83" t="str">
-        <f t="shared" si="1"/>
-        <v>RTD 3,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <f>_xlfn.CONCAT(A83,",",B83,",",C83,",",D83,",",E83,",",F83,",",G83)</f>
+        <v>Fan 1 Active,,BitAddress,PLC1,012349,,</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
-        <f>'Point List'!C81</f>
-        <v>AVAILABLE</v>
-      </c>
-      <c r="C84">
-        <f>'Point List'!L81</f>
-        <v>0</v>
+        <f>'Point List'!C102</f>
+        <v>Fan 2 Active</v>
+      </c>
+      <c r="C84" t="str">
+        <f>'Point List'!L102</f>
+        <v>BitAddress</v>
       </c>
       <c r="D84" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E84" t="str">
-        <f>'Point List'!J81</f>
-        <v>NOT ACCESSIBLE</v>
+        <f>'Point List'!J102</f>
+        <v>012350</v>
       </c>
       <c r="K84" t="str">
-        <f t="shared" si="1"/>
-        <v>AVAILABLE,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <f>_xlfn.CONCAT(A84,",",B84,",",C84,",",D84,",",E84,",",F84,",",G84)</f>
+        <v>Fan 2 Active,,BitAddress,PLC1,012350,,</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
-        <f>'Point List'!C82</f>
-        <v>AVAILABLE</v>
-      </c>
-      <c r="C85">
-        <f>'Point List'!L82</f>
-        <v>0</v>
+        <f>'Point List'!C103</f>
+        <v>Enable Pump Cycling</v>
+      </c>
+      <c r="C85" t="str">
+        <f>'Point List'!L103</f>
+        <v>BitAddress</v>
       </c>
       <c r="D85" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E85" t="str">
-        <f>'Point List'!J82</f>
-        <v>NOT ACCESSIBLE</v>
+        <f>'Point List'!J103</f>
+        <v>012351</v>
       </c>
       <c r="K85" t="str">
-        <f t="shared" si="1"/>
-        <v>AVAILABLE,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <f>_xlfn.CONCAT(A85,",",B85,",",C85,",",D85,",",E85,",",F85,",",G85)</f>
+        <v>Enable Pump Cycling,,BitAddress,PLC1,012351,,</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
-        <f>'Point List'!C83</f>
-        <v>Flow Analog</v>
-      </c>
-      <c r="C86">
-        <f>'Point List'!L83</f>
-        <v>0</v>
+        <f>'Point List'!C104</f>
+        <v>System Diagnostics</v>
+      </c>
+      <c r="C86" t="str">
+        <f>'Point List'!L104</f>
+        <v>BitAddress</v>
       </c>
       <c r="D86" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E86" t="str">
-        <f>'Point List'!J83</f>
-        <v>NOT ACCESSIBLE</v>
+        <f>'Point List'!J104</f>
+        <v>012352</v>
       </c>
       <c r="K86" t="str">
-        <f t="shared" si="1"/>
-        <v>Flow Analog,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <f>_xlfn.CONCAT(A86,",",B86,",",C86,",",D86,",",E86,",",F86,",",G86)</f>
+        <v>System Diagnostics,,BitAddress,PLC1,012352,,</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
-        <f>'Point List'!C84</f>
-        <v>Conductivity Alarm</v>
-      </c>
-      <c r="C87">
-        <f>'Point List'!L84</f>
-        <v>0</v>
+        <f>'Point List'!C105</f>
+        <v>Status Indicator Text</v>
+      </c>
+      <c r="C87" t="str">
+        <f>'Point List'!L105</f>
+        <v>WordAddress</v>
       </c>
       <c r="D87" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E87" t="str">
-        <f>'Point List'!J84</f>
-        <v>NOT ACCESSIBLE</v>
+        <f>'Point List'!J105</f>
+        <v>012683</v>
       </c>
       <c r="K87" t="str">
-        <f t="shared" si="1"/>
-        <v>Conductivity Alarm,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <f>_xlfn.CONCAT(A87,",",B87,",",C87,",",D87,",",E87,",",F87,",",G87)</f>
+        <v>Status Indicator Text,,WordAddress,PLC1,012683,,</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A88" t="str">
-        <f>'Point List'!C85</f>
-        <v>Conductivity Fault</v>
+      <c r="A88">
+        <f>'Point List'!C106</f>
+        <v>0</v>
       </c>
       <c r="C88">
-        <f>'Point List'!L85</f>
+        <f>'Point List'!L106</f>
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>313</v>
-      </c>
-      <c r="E88" t="str">
-        <f>'Point List'!J85</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K88" t="str">
-        <f t="shared" si="1"/>
-        <v>Conductivity Fault,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <v>312</v>
+      </c>
+      <c r="E88">
+        <f>'Point List'!J106</f>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A89" t="str">
-        <f>'Point List'!C86</f>
-        <v>Level Low Switch</v>
+      <c r="A89">
+        <f>'Point List'!C107</f>
+        <v>0</v>
       </c>
       <c r="C89">
-        <f>'Point List'!L86</f>
+        <f>'Point List'!L107</f>
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>313</v>
-      </c>
-      <c r="E89" t="str">
-        <f>'Point List'!J86</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K89" t="str">
-        <f t="shared" si="1"/>
-        <v>Level Low Switch,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <v>312</v>
+      </c>
+      <c r="E89">
+        <f>'Point List'!J107</f>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" t="str">
-        <f>'Point List'!C87</f>
-        <v>Level Low Low Switch</v>
+      <c r="A90">
+        <f>'Point List'!C108</f>
+        <v>0</v>
       </c>
       <c r="C90">
-        <f>'Point List'!L87</f>
+        <f>'Point List'!L108</f>
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>313</v>
-      </c>
-      <c r="E90" t="str">
-        <f>'Point List'!J87</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K90" t="str">
-        <f t="shared" si="1"/>
-        <v>Level Low Low Switch,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <v>312</v>
+      </c>
+      <c r="E90">
+        <f>'Point List'!J108</f>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" t="str">
-        <f>'Point List'!C88</f>
-        <v>Fan 1 Enable</v>
+      <c r="A91">
+        <f>'Point List'!C109</f>
+        <v>0</v>
       </c>
       <c r="C91">
-        <f>'Point List'!L88</f>
+        <f>'Point List'!L109</f>
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>313</v>
-      </c>
-      <c r="E91" t="str">
-        <f>'Point List'!J88</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K91" t="str">
-        <f t="shared" si="1"/>
-        <v>Fan 1 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <v>312</v>
+      </c>
+      <c r="E91">
+        <f>'Point List'!J109</f>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92" t="str">
-        <f>'Point List'!C89</f>
-        <v>Fan 2 Enable</v>
+      <c r="A92">
+        <f>'Point List'!C110</f>
+        <v>0</v>
       </c>
       <c r="C92">
-        <f>'Point List'!L89</f>
+        <f>'Point List'!L110</f>
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>313</v>
-      </c>
-      <c r="E92" t="str">
-        <f>'Point List'!J89</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K92" t="str">
-        <f t="shared" si="1"/>
-        <v>Fan 2 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <v>312</v>
+      </c>
+      <c r="E92">
+        <f>'Point List'!J110</f>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A93" t="str">
-        <f>'Point List'!C90</f>
-        <v>Pump 1 Enable</v>
+      <c r="A93">
+        <f>'Point List'!C111</f>
+        <v>0</v>
       </c>
       <c r="C93">
-        <f>'Point List'!L90</f>
+        <f>'Point List'!L111</f>
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>313</v>
-      </c>
-      <c r="E93" t="str">
-        <f>'Point List'!J90</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K93" t="str">
-        <f t="shared" si="1"/>
-        <v>Pump 1 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <v>312</v>
+      </c>
+      <c r="E93">
+        <f>'Point List'!J111</f>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A94" t="str">
-        <f>'Point List'!C91</f>
-        <v>Pump 2 Enable</v>
+      <c r="A94">
+        <f>'Point List'!C112</f>
+        <v>0</v>
       </c>
       <c r="C94">
-        <f>'Point List'!L91</f>
+        <f>'Point List'!L112</f>
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>313</v>
-      </c>
-      <c r="E94" t="str">
-        <f>'Point List'!J91</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K94" t="str">
-        <f t="shared" si="1"/>
-        <v>Pump 2 Enable,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <v>312</v>
+      </c>
+      <c r="E94">
+        <f>'Point List'!J112</f>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A95" t="str">
-        <f>'Point List'!C92</f>
-        <v>Valve Actuation Signal</v>
+      <c r="A95">
+        <f>'Point List'!C113</f>
+        <v>0</v>
       </c>
       <c r="C95">
-        <f>'Point List'!L92</f>
+        <f>'Point List'!L113</f>
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>313</v>
-      </c>
-      <c r="E95" t="str">
-        <f>'Point List'!J92</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K95" t="str">
-        <f t="shared" si="1"/>
-        <v>Valve Actuation Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
+        <v>312</v>
+      </c>
+      <c r="E95">
+        <f>'Point List'!J113</f>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A96" t="str">
-        <f>'Point List'!C93</f>
-        <v>Pressure Switch Signal</v>
+      <c r="A96">
+        <f>'Point List'!C114</f>
+        <v>0</v>
       </c>
       <c r="C96">
-        <f>'Point List'!L93</f>
+        <f>'Point List'!L114</f>
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>313</v>
-      </c>
-      <c r="E96" t="str">
-        <f>'Point List'!J93</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K96" t="str">
-        <f t="shared" si="1"/>
-        <v>Pressure Switch Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A97" t="str">
-        <f>'Point List'!C94</f>
-        <v>Active Pump  Current</v>
+        <v>312</v>
+      </c>
+      <c r="E96">
+        <f>'Point List'!J114</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <f>'Point List'!C115</f>
+        <v>0</v>
       </c>
       <c r="C97">
-        <f>'Point List'!L94</f>
+        <f>'Point List'!L115</f>
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>313</v>
-      </c>
-      <c r="E97" t="str">
-        <f>'Point List'!J94</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K97" t="str">
-        <f t="shared" si="1"/>
-        <v>Active Pump  Current,,0,PLC1,NOT ACCESSIBLE,,</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A98" t="str">
-        <f>'Point List'!C95</f>
-        <v>Active Pump  Voltage</v>
+        <v>312</v>
+      </c>
+      <c r="E97">
+        <f>'Point List'!J115</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <f>'Point List'!C116</f>
+        <v>0</v>
       </c>
       <c r="C98">
-        <f>'Point List'!L95</f>
+        <f>'Point List'!L116</f>
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>313</v>
-      </c>
-      <c r="E98" t="str">
-        <f>'Point List'!J95</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K98" t="str">
-        <f t="shared" si="1"/>
-        <v>Active Pump  Voltage,,0,PLC1,NOT ACCESSIBLE,,</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A99" t="str">
-        <f>'Point List'!C96</f>
-        <v>Valve Position Signal</v>
+        <v>312</v>
+      </c>
+      <c r="E98">
+        <f>'Point List'!J116</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <f>'Point List'!C117</f>
+        <v>0</v>
       </c>
       <c r="C99">
-        <f>'Point List'!L96</f>
+        <f>'Point List'!L117</f>
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>313</v>
-      </c>
-      <c r="E99" t="str">
-        <f>'Point List'!J96</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K99" t="str">
-        <f t="shared" si="1"/>
-        <v>Valve Position Signal,,0,PLC1,NOT ACCESSIBLE,,</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A100" t="str">
-        <f>'Point List'!C97</f>
-        <v>AVAILABLE</v>
+        <v>312</v>
+      </c>
+      <c r="E99">
+        <f>'Point List'!J117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <f>'Point List'!C118</f>
+        <v>0</v>
       </c>
       <c r="C100">
-        <f>'Point List'!L97</f>
+        <f>'Point List'!L118</f>
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>313</v>
-      </c>
-      <c r="E100" t="str">
-        <f>'Point List'!J97</f>
-        <v>NOT ACCESSIBLE</v>
-      </c>
-      <c r="K100" t="str">
-        <f t="shared" si="1"/>
-        <v>AVAILABLE,,0,PLC1,NOT ACCESSIBLE,,</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A101" t="str">
-        <f>'Point List'!C98</f>
-        <v>Primary Pump Active</v>
-      </c>
-      <c r="C101" t="str">
-        <f>'Point List'!L98</f>
-        <v>BitAddress</v>
+        <v>312</v>
+      </c>
+      <c r="E100">
+        <f>'Point List'!J118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <f>'Point List'!C119</f>
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <f>'Point List'!L119</f>
+        <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>313</v>
-      </c>
-      <c r="E101" t="str">
-        <f>'Point List'!J98</f>
-        <v>012346</v>
-      </c>
-      <c r="K101" t="str">
-        <f t="shared" si="1"/>
-        <v>Primary Pump Active,,BitAddress,PLC1,012346,,</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A102" t="str">
-        <f>'Point List'!C99</f>
-        <v>Secondary Pump  Active</v>
-      </c>
-      <c r="C102" t="str">
-        <f>'Point List'!L99</f>
-        <v>BitAddress</v>
+        <v>312</v>
+      </c>
+      <c r="E101">
+        <f>'Point List'!J119</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <f>'Point List'!C120</f>
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <f>'Point List'!L120</f>
+        <v>0</v>
       </c>
       <c r="D102" t="s">
-        <v>313</v>
-      </c>
-      <c r="E102" t="str">
-        <f>'Point List'!J99</f>
-        <v>012347</v>
-      </c>
-      <c r="K102" t="str">
-        <f t="shared" si="1"/>
-        <v>Secondary Pump  Active,,BitAddress,PLC1,012347,,</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A103" t="str">
-        <f>'Point List'!C100</f>
-        <v>Simplex Mode Active</v>
-      </c>
-      <c r="C103" t="str">
-        <f>'Point List'!L100</f>
-        <v>BitAddress</v>
+        <v>312</v>
+      </c>
+      <c r="E102">
+        <f>'Point List'!J120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <f>'Point List'!C121</f>
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <f>'Point List'!L121</f>
+        <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>313</v>
-      </c>
-      <c r="E103" t="str">
-        <f>'Point List'!J100</f>
-        <v>012348</v>
-      </c>
-      <c r="K103" t="str">
-        <f t="shared" si="1"/>
-        <v>Simplex Mode Active,,BitAddress,PLC1,012348,,</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A104" t="str">
-        <f>'Point List'!C101</f>
-        <v>Fan 1 Active</v>
-      </c>
-      <c r="C104" t="str">
-        <f>'Point List'!L101</f>
-        <v>BitAddress</v>
+        <v>312</v>
+      </c>
+      <c r="E103">
+        <f>'Point List'!J121</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <f>'Point List'!C122</f>
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <f>'Point List'!L122</f>
+        <v>0</v>
       </c>
       <c r="D104" t="s">
-        <v>313</v>
-      </c>
-      <c r="E104" t="str">
-        <f>'Point List'!J101</f>
-        <v>012349</v>
-      </c>
-      <c r="K104" t="str">
-        <f t="shared" si="1"/>
-        <v>Fan 1 Active,,BitAddress,PLC1,012349,,</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A105" t="str">
-        <f>'Point List'!C102</f>
-        <v>Fan 2 Active</v>
-      </c>
-      <c r="C105" t="str">
-        <f>'Point List'!L102</f>
-        <v>BitAddress</v>
+        <v>312</v>
+      </c>
+      <c r="E104">
+        <f>'Point List'!J122</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <f>'Point List'!C123</f>
+        <v>0</v>
+      </c>
+      <c r="C105">
+        <f>'Point List'!L123</f>
+        <v>0</v>
       </c>
       <c r="D105" t="s">
-        <v>313</v>
-      </c>
-      <c r="E105" t="str">
-        <f>'Point List'!J102</f>
-        <v>012350</v>
-      </c>
-      <c r="K105" t="str">
-        <f t="shared" si="1"/>
-        <v>Fan 2 Active,,BitAddress,PLC1,012350,,</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A106" t="str">
-        <f>'Point List'!C103</f>
-        <v>Enable Pump Cycling</v>
-      </c>
-      <c r="C106" t="str">
-        <f>'Point List'!L103</f>
-        <v>BitAddress</v>
+        <v>312</v>
+      </c>
+      <c r="E105">
+        <f>'Point List'!J123</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <f>'Point List'!C124</f>
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <f>'Point List'!L124</f>
+        <v>0</v>
       </c>
       <c r="D106" t="s">
-        <v>313</v>
-      </c>
-      <c r="E106" t="str">
-        <f>'Point List'!J103</f>
-        <v>012351</v>
-      </c>
-      <c r="K106" t="str">
-        <f t="shared" si="1"/>
-        <v>Enable Pump Cycling,,BitAddress,PLC1,012351,,</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A107" t="str">
-        <f>'Point List'!C104</f>
-        <v>System Diagnostics</v>
-      </c>
-      <c r="C107" t="str">
-        <f>'Point List'!L104</f>
-        <v>BitAddress</v>
+        <v>312</v>
+      </c>
+      <c r="E106">
+        <f>'Point List'!J124</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <f>'Point List'!C125</f>
+        <v>0</v>
+      </c>
+      <c r="C107">
+        <f>'Point List'!L125</f>
+        <v>0</v>
       </c>
       <c r="D107" t="s">
-        <v>313</v>
-      </c>
-      <c r="E107" t="str">
-        <f>'Point List'!J104</f>
-        <v>012352</v>
-      </c>
-      <c r="K107" t="str">
-        <f t="shared" si="1"/>
-        <v>System Diagnostics,,BitAddress,PLC1,012352,,</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+      <c r="E107">
+        <f>'Point List'!J125</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
-        <f>'Point List'!C105</f>
+        <f>'Point List'!C126</f>
         <v>0</v>
       </c>
       <c r="C108">
-        <f>'Point List'!L105</f>
+        <f>'Point List'!L126</f>
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E108">
-        <f>'Point List'!J105</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+        <f>'Point List'!J126</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
-        <f>'Point List'!C106</f>
+        <f>'Point List'!C127</f>
         <v>0</v>
       </c>
       <c r="C109">
-        <f>'Point List'!L106</f>
+        <f>'Point List'!L127</f>
         <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E109">
-        <f>'Point List'!J106</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+        <f>'Point List'!J127</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
-        <f>'Point List'!C107</f>
+        <f>'Point List'!C128</f>
         <v>0</v>
       </c>
       <c r="C110">
-        <f>'Point List'!L107</f>
+        <f>'Point List'!L128</f>
         <v>0</v>
       </c>
       <c r="D110" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E110">
-        <f>'Point List'!J107</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+        <f>'Point List'!J128</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
-        <f>'Point List'!C108</f>
+        <f>'Point List'!C129</f>
         <v>0</v>
       </c>
       <c r="C111">
-        <f>'Point List'!L108</f>
+        <f>'Point List'!L129</f>
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E111">
-        <f>'Point List'!J108</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+        <f>'Point List'!J129</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
-        <f>'Point List'!C109</f>
+        <f>'Point List'!C130</f>
         <v>0</v>
       </c>
       <c r="C112">
-        <f>'Point List'!L109</f>
+        <f>'Point List'!L130</f>
         <v>0</v>
       </c>
       <c r="D112" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E112">
-        <f>'Point List'!J109</f>
+        <f>'Point List'!J130</f>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
-        <f>'Point List'!C110</f>
+        <f>'Point List'!C131</f>
         <v>0</v>
       </c>
       <c r="C113">
-        <f>'Point List'!L110</f>
+        <f>'Point List'!L131</f>
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E113">
-        <f>'Point List'!J110</f>
+        <f>'Point List'!J131</f>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
-        <f>'Point List'!C111</f>
+        <f>'Point List'!C132</f>
         <v>0</v>
       </c>
       <c r="C114">
-        <f>'Point List'!L111</f>
+        <f>'Point List'!L132</f>
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E114">
-        <f>'Point List'!J111</f>
+        <f>'Point List'!J132</f>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
-        <f>'Point List'!C112</f>
+        <f>'Point List'!C133</f>
         <v>0</v>
       </c>
       <c r="C115">
-        <f>'Point List'!L112</f>
+        <f>'Point List'!L133</f>
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E115">
-        <f>'Point List'!J112</f>
+        <f>'Point List'!J133</f>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
-        <f>'Point List'!C113</f>
+        <f>'Point List'!C134</f>
         <v>0</v>
       </c>
       <c r="C116">
-        <f>'Point List'!L113</f>
+        <f>'Point List'!L134</f>
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E116">
-        <f>'Point List'!J113</f>
+        <f>'Point List'!J134</f>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
-        <f>'Point List'!C114</f>
+        <f>'Point List'!C135</f>
         <v>0</v>
       </c>
       <c r="C117">
-        <f>'Point List'!L114</f>
+        <f>'Point List'!L135</f>
         <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E117">
-        <f>'Point List'!J114</f>
+        <f>'Point List'!J135</f>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
-        <f>'Point List'!C115</f>
+        <f>'Point List'!C136</f>
         <v>0</v>
       </c>
       <c r="C118">
-        <f>'Point List'!L115</f>
+        <f>'Point List'!L136</f>
         <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E118">
-        <f>'Point List'!J115</f>
+        <f>'Point List'!J136</f>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
-        <f>'Point List'!C116</f>
+        <f>'Point List'!C137</f>
         <v>0</v>
       </c>
       <c r="C119">
-        <f>'Point List'!L116</f>
+        <f>'Point List'!L137</f>
         <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E119">
-        <f>'Point List'!J116</f>
+        <f>'Point List'!J137</f>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
-        <f>'Point List'!C117</f>
+        <f>'Point List'!C138</f>
         <v>0</v>
       </c>
       <c r="C120">
-        <f>'Point List'!L117</f>
+        <f>'Point List'!L138</f>
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E120">
-        <f>'Point List'!J117</f>
+        <f>'Point List'!J138</f>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
-        <f>'Point List'!C118</f>
+        <f>'Point List'!C139</f>
         <v>0</v>
       </c>
       <c r="C121">
-        <f>'Point List'!L118</f>
+        <f>'Point List'!L139</f>
         <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E121">
-        <f>'Point List'!J118</f>
+        <f>'Point List'!J139</f>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
-        <f>'Point List'!C119</f>
+        <f>'Point List'!C140</f>
         <v>0</v>
       </c>
       <c r="C122">
-        <f>'Point List'!L119</f>
+        <f>'Point List'!L140</f>
         <v>0</v>
       </c>
       <c r="D122" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E122">
-        <f>'Point List'!J119</f>
+        <f>'Point List'!J140</f>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
-        <f>'Point List'!C120</f>
+        <f>'Point List'!C141</f>
         <v>0</v>
       </c>
       <c r="C123">
-        <f>'Point List'!L120</f>
+        <f>'Point List'!L141</f>
         <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E123">
-        <f>'Point List'!J120</f>
+        <f>'Point List'!J141</f>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
-        <f>'Point List'!C121</f>
+        <f>'Point List'!C142</f>
         <v>0</v>
       </c>
       <c r="C124">
-        <f>'Point List'!L121</f>
+        <f>'Point List'!L142</f>
         <v>0</v>
       </c>
       <c r="D124" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E124">
-        <f>'Point List'!J121</f>
+        <f>'Point List'!J142</f>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
-        <f>'Point List'!C122</f>
+        <f>'Point List'!C143</f>
         <v>0</v>
       </c>
       <c r="C125">
-        <f>'Point List'!L122</f>
+        <f>'Point List'!L143</f>
         <v>0</v>
       </c>
       <c r="D125" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E125">
-        <f>'Point List'!J122</f>
+        <f>'Point List'!J143</f>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
-        <f>'Point List'!C123</f>
+        <f>'Point List'!C144</f>
         <v>0</v>
       </c>
       <c r="C126">
-        <f>'Point List'!L123</f>
+        <f>'Point List'!L144</f>
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E126">
-        <f>'Point List'!J123</f>
+        <f>'Point List'!J144</f>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
-        <f>'Point List'!C124</f>
+        <f>'Point List'!C145</f>
         <v>0</v>
       </c>
       <c r="C127">
-        <f>'Point List'!L124</f>
+        <f>'Point List'!L145</f>
         <v>0</v>
       </c>
       <c r="D127" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E127">
-        <f>'Point List'!J124</f>
+        <f>'Point List'!J145</f>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
-        <f>'Point List'!C125</f>
+        <f>'Point List'!C146</f>
         <v>0</v>
       </c>
       <c r="C128">
-        <f>'Point List'!L125</f>
+        <f>'Point List'!L146</f>
         <v>0</v>
       </c>
       <c r="D128" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E128">
-        <f>'Point List'!J125</f>
+        <f>'Point List'!J146</f>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
-        <f>'Point List'!C126</f>
+        <f>'Point List'!C147</f>
         <v>0</v>
       </c>
       <c r="C129">
-        <f>'Point List'!L126</f>
+        <f>'Point List'!L147</f>
         <v>0</v>
       </c>
       <c r="D129" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E129">
-        <f>'Point List'!J126</f>
+        <f>'Point List'!J147</f>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
-        <f>'Point List'!C127</f>
+        <f>'Point List'!C148</f>
         <v>0</v>
       </c>
       <c r="C130">
-        <f>'Point List'!L127</f>
+        <f>'Point List'!L148</f>
         <v>0</v>
       </c>
       <c r="D130" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E130">
-        <f>'Point List'!J127</f>
+        <f>'Point List'!J148</f>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
-        <f>'Point List'!C128</f>
+        <f>'Point List'!C149</f>
         <v>0</v>
       </c>
       <c r="C131">
-        <f>'Point List'!L128</f>
+        <f>'Point List'!L149</f>
         <v>0</v>
       </c>
       <c r="D131" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E131">
-        <f>'Point List'!J128</f>
+        <f>'Point List'!J149</f>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
-        <f>'Point List'!C129</f>
+        <f>'Point List'!C150</f>
         <v>0</v>
       </c>
       <c r="C132">
-        <f>'Point List'!L129</f>
+        <f>'Point List'!L150</f>
         <v>0</v>
       </c>
       <c r="D132" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E132">
-        <f>'Point List'!J129</f>
+        <f>'Point List'!J150</f>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
-        <f>'Point List'!C130</f>
+        <f>'Point List'!C151</f>
         <v>0</v>
       </c>
       <c r="C133">
-        <f>'Point List'!L130</f>
+        <f>'Point List'!L151</f>
         <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E133">
-        <f>'Point List'!J130</f>
+        <f>'Point List'!J151</f>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
-        <f>'Point List'!C131</f>
+        <f>'Point List'!C152</f>
         <v>0</v>
       </c>
       <c r="C134">
-        <f>'Point List'!L131</f>
+        <f>'Point List'!L152</f>
         <v>0</v>
       </c>
       <c r="D134" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E134">
-        <f>'Point List'!J131</f>
+        <f>'Point List'!J152</f>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
-        <f>'Point List'!C132</f>
+        <f>'Point List'!C153</f>
         <v>0</v>
       </c>
       <c r="C135">
-        <f>'Point List'!L132</f>
+        <f>'Point List'!L153</f>
         <v>0</v>
       </c>
       <c r="D135" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E135">
-        <f>'Point List'!J132</f>
+        <f>'Point List'!J153</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
-        <f>'Point List'!C133</f>
+        <f>'Point List'!C154</f>
         <v>0</v>
       </c>
       <c r="C136">
-        <f>'Point List'!L133</f>
+        <f>'Point List'!L154</f>
         <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E136">
-        <f>'Point List'!J133</f>
+        <f>'Point List'!J154</f>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
-        <f>'Point List'!C134</f>
+        <f>'Point List'!C155</f>
         <v>0</v>
       </c>
       <c r="C137">
-        <f>'Point List'!L134</f>
+        <f>'Point List'!L155</f>
         <v>0</v>
       </c>
       <c r="D137" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E137">
-        <f>'Point List'!J134</f>
+        <f>'Point List'!J155</f>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
-        <f>'Point List'!C135</f>
+        <f>'Point List'!C156</f>
         <v>0</v>
       </c>
       <c r="C138">
-        <f>'Point List'!L135</f>
+        <f>'Point List'!L156</f>
         <v>0</v>
       </c>
       <c r="D138" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E138">
-        <f>'Point List'!J135</f>
+        <f>'Point List'!J156</f>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
-        <f>'Point List'!C136</f>
+        <f>'Point List'!C157</f>
         <v>0</v>
       </c>
       <c r="C139">
-        <f>'Point List'!L136</f>
+        <f>'Point List'!L157</f>
         <v>0</v>
       </c>
       <c r="D139" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E139">
-        <f>'Point List'!J136</f>
+        <f>'Point List'!J157</f>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
-        <f>'Point List'!C137</f>
+        <f>'Point List'!C158</f>
         <v>0</v>
       </c>
       <c r="C140">
-        <f>'Point List'!L137</f>
+        <f>'Point List'!L158</f>
         <v>0</v>
       </c>
       <c r="D140" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E140">
-        <f>'Point List'!J137</f>
+        <f>'Point List'!J158</f>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
-        <f>'Point List'!C138</f>
+        <f>'Point List'!C159</f>
         <v>0</v>
       </c>
       <c r="C141">
-        <f>'Point List'!L138</f>
+        <f>'Point List'!L159</f>
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E141">
-        <f>'Point List'!J138</f>
+        <f>'Point List'!J159</f>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
-        <f>'Point List'!C139</f>
+        <f>'Point List'!C160</f>
         <v>0</v>
       </c>
       <c r="C142">
-        <f>'Point List'!L139</f>
+        <f>'Point List'!L160</f>
         <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E142">
-        <f>'Point List'!J139</f>
+        <f>'Point List'!J160</f>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
-        <f>'Point List'!C140</f>
+        <f>'Point List'!C161</f>
         <v>0</v>
       </c>
       <c r="C143">
-        <f>'Point List'!L140</f>
+        <f>'Point List'!L161</f>
         <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E143">
-        <f>'Point List'!J140</f>
+        <f>'Point List'!J161</f>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
-        <f>'Point List'!C141</f>
+        <f>'Point List'!C162</f>
         <v>0</v>
       </c>
       <c r="C144">
-        <f>'Point List'!L141</f>
+        <f>'Point List'!L162</f>
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E144">
-        <f>'Point List'!J141</f>
+        <f>'Point List'!J162</f>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
-        <f>'Point List'!C142</f>
+        <f>'Point List'!C163</f>
         <v>0</v>
       </c>
       <c r="C145">
-        <f>'Point List'!L142</f>
+        <f>'Point List'!L163</f>
         <v>0</v>
       </c>
       <c r="D145" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E145">
-        <f>'Point List'!J142</f>
+        <f>'Point List'!J163</f>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
-        <f>'Point List'!C143</f>
+        <f>'Point List'!C164</f>
         <v>0</v>
       </c>
       <c r="C146">
-        <f>'Point List'!L143</f>
+        <f>'Point List'!L164</f>
         <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E146">
-        <f>'Point List'!J143</f>
+        <f>'Point List'!J164</f>
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
-        <f>'Point List'!C144</f>
+        <f>'Point List'!C165</f>
         <v>0</v>
       </c>
       <c r="C147">
-        <f>'Point List'!L144</f>
+        <f>'Point List'!L165</f>
         <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E147">
-        <f>'Point List'!J144</f>
+        <f>'Point List'!J165</f>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
-        <f>'Point List'!C145</f>
+        <f>'Point List'!C166</f>
         <v>0</v>
       </c>
       <c r="C148">
-        <f>'Point List'!L145</f>
+        <f>'Point List'!L166</f>
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E148">
-        <f>'Point List'!J145</f>
+        <f>'Point List'!J166</f>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
-        <f>'Point List'!C146</f>
+        <f>'Point List'!C167</f>
         <v>0</v>
       </c>
       <c r="C149">
-        <f>'Point List'!L146</f>
+        <f>'Point List'!L167</f>
         <v>0</v>
       </c>
       <c r="D149" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E149">
-        <f>'Point List'!J146</f>
+        <f>'Point List'!J167</f>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
-        <f>'Point List'!C147</f>
+        <f>'Point List'!C168</f>
         <v>0</v>
       </c>
       <c r="C150">
-        <f>'Point List'!L147</f>
+        <f>'Point List'!L168</f>
         <v>0</v>
       </c>
       <c r="D150" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E150">
-        <f>'Point List'!J147</f>
+        <f>'Point List'!J168</f>
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
-        <f>'Point List'!C148</f>
+        <f>'Point List'!C169</f>
         <v>0</v>
       </c>
       <c r="C151">
-        <f>'Point List'!L148</f>
+        <f>'Point List'!L169</f>
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E151">
-        <f>'Point List'!J148</f>
+        <f>'Point List'!J169</f>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
-        <f>'Point List'!C149</f>
+        <f>'Point List'!C170</f>
         <v>0</v>
       </c>
       <c r="C152">
-        <f>'Point List'!L149</f>
+        <f>'Point List'!L170</f>
         <v>0</v>
       </c>
       <c r="D152" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E152">
-        <f>'Point List'!J149</f>
+        <f>'Point List'!J170</f>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
-        <f>'Point List'!C150</f>
+        <f>'Point List'!C171</f>
         <v>0</v>
       </c>
       <c r="C153">
-        <f>'Point List'!L150</f>
+        <f>'Point List'!L171</f>
         <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E153">
-        <f>'Point List'!J150</f>
+        <f>'Point List'!J171</f>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
-        <f>'Point List'!C151</f>
+        <f>'Point List'!C172</f>
         <v>0</v>
       </c>
       <c r="C154">
-        <f>'Point List'!L151</f>
+        <f>'Point List'!L172</f>
         <v>0</v>
       </c>
       <c r="D154" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E154">
-        <f>'Point List'!J151</f>
+        <f>'Point List'!J172</f>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
-        <f>'Point List'!C152</f>
+        <f>'Point List'!C173</f>
         <v>0</v>
       </c>
       <c r="C155">
-        <f>'Point List'!L152</f>
+        <f>'Point List'!L173</f>
         <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E155">
-        <f>'Point List'!J152</f>
+        <f>'Point List'!J173</f>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
-        <f>'Point List'!C153</f>
+        <f>'Point List'!C174</f>
         <v>0</v>
       </c>
       <c r="C156">
-        <f>'Point List'!L153</f>
+        <f>'Point List'!L174</f>
         <v>0</v>
       </c>
       <c r="D156" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E156">
-        <f>'Point List'!J153</f>
+        <f>'Point List'!J174</f>
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
-        <f>'Point List'!C154</f>
+        <f>'Point List'!C175</f>
         <v>0</v>
       </c>
       <c r="C157">
-        <f>'Point List'!L154</f>
+        <f>'Point List'!L175</f>
         <v>0</v>
       </c>
       <c r="D157" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E157">
-        <f>'Point List'!J154</f>
+        <f>'Point List'!J175</f>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
-        <f>'Point List'!C155</f>
+        <f>'Point List'!C176</f>
         <v>0</v>
       </c>
       <c r="C158">
-        <f>'Point List'!L155</f>
+        <f>'Point List'!L176</f>
         <v>0</v>
       </c>
       <c r="D158" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E158">
-        <f>'Point List'!J155</f>
+        <f>'Point List'!J176</f>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
-        <f>'Point List'!C156</f>
+        <f>'Point List'!C177</f>
         <v>0</v>
       </c>
       <c r="C159">
-        <f>'Point List'!L156</f>
+        <f>'Point List'!L177</f>
         <v>0</v>
       </c>
       <c r="D159" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E159">
-        <f>'Point List'!J156</f>
+        <f>'Point List'!J177</f>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
-        <f>'Point List'!C157</f>
+        <f>'Point List'!C178</f>
         <v>0</v>
       </c>
       <c r="C160">
-        <f>'Point List'!L157</f>
+        <f>'Point List'!L178</f>
         <v>0</v>
       </c>
       <c r="D160" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E160">
-        <f>'Point List'!J157</f>
+        <f>'Point List'!J178</f>
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
-        <f>'Point List'!C158</f>
+        <f>'Point List'!C179</f>
         <v>0</v>
       </c>
       <c r="C161">
-        <f>'Point List'!L158</f>
+        <f>'Point List'!L179</f>
         <v>0</v>
       </c>
       <c r="D161" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E161">
-        <f>'Point List'!J158</f>
+        <f>'Point List'!J179</f>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
-        <f>'Point List'!C159</f>
+        <f>'Point List'!C180</f>
         <v>0</v>
       </c>
       <c r="C162">
-        <f>'Point List'!L159</f>
+        <f>'Point List'!L180</f>
         <v>0</v>
       </c>
       <c r="D162" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E162">
-        <f>'Point List'!J159</f>
+        <f>'Point List'!J180</f>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
-        <f>'Point List'!C160</f>
+        <f>'Point List'!C181</f>
         <v>0</v>
       </c>
       <c r="C163">
-        <f>'Point List'!L160</f>
+        <f>'Point List'!L181</f>
         <v>0</v>
       </c>
       <c r="D163" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E163">
-        <f>'Point List'!J160</f>
+        <f>'Point List'!J181</f>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164">
-        <f>'Point List'!C161</f>
+        <f>'Point List'!C182</f>
         <v>0</v>
       </c>
       <c r="C164">
-        <f>'Point List'!L161</f>
+        <f>'Point List'!L182</f>
         <v>0</v>
       </c>
       <c r="D164" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E164">
-        <f>'Point List'!J161</f>
+        <f>'Point List'!J182</f>
         <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165">
-        <f>'Point List'!C162</f>
+        <f>'Point List'!C183</f>
         <v>0</v>
       </c>
       <c r="C165">
-        <f>'Point List'!L162</f>
+        <f>'Point List'!L183</f>
         <v>0</v>
       </c>
       <c r="D165" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E165">
-        <f>'Point List'!J162</f>
+        <f>'Point List'!J183</f>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166">
-        <f>'Point List'!C163</f>
+        <f>'Point List'!C184</f>
         <v>0</v>
       </c>
       <c r="C166">
-        <f>'Point List'!L163</f>
+        <f>'Point List'!L184</f>
         <v>0</v>
       </c>
       <c r="D166" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E166">
-        <f>'Point List'!J163</f>
+        <f>'Point List'!J184</f>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167">
-        <f>'Point List'!C164</f>
+        <f>'Point List'!C185</f>
         <v>0</v>
       </c>
       <c r="C167">
-        <f>'Point List'!L164</f>
+        <f>'Point List'!L185</f>
         <v>0</v>
       </c>
       <c r="D167" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E167">
-        <f>'Point List'!J164</f>
+        <f>'Point List'!J185</f>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168">
-        <f>'Point List'!C165</f>
+        <f>'Point List'!C186</f>
         <v>0</v>
       </c>
       <c r="C168">
-        <f>'Point List'!L165</f>
+        <f>'Point List'!L186</f>
         <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E168">
-        <f>'Point List'!J165</f>
+        <f>'Point List'!J186</f>
         <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169">
-        <f>'Point List'!C166</f>
+        <f>'Point List'!C187</f>
         <v>0</v>
       </c>
       <c r="C169">
-        <f>'Point List'!L166</f>
+        <f>'Point List'!L187</f>
         <v>0</v>
       </c>
       <c r="D169" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E169">
-        <f>'Point List'!J166</f>
+        <f>'Point List'!J187</f>
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170">
-        <f>'Point List'!C167</f>
+        <f>'Point List'!C188</f>
         <v>0</v>
       </c>
       <c r="C170">
-        <f>'Point List'!L167</f>
+        <f>'Point List'!L188</f>
         <v>0</v>
       </c>
       <c r="D170" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E170">
-        <f>'Point List'!J167</f>
+        <f>'Point List'!J188</f>
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171">
-        <f>'Point List'!C168</f>
+        <f>'Point List'!C189</f>
         <v>0</v>
       </c>
       <c r="C171">
-        <f>'Point List'!L168</f>
+        <f>'Point List'!L189</f>
         <v>0</v>
       </c>
       <c r="D171" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E171">
-        <f>'Point List'!J168</f>
+        <f>'Point List'!J189</f>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172">
-        <f>'Point List'!C169</f>
+        <f>'Point List'!C190</f>
         <v>0</v>
       </c>
       <c r="C172">
-        <f>'Point List'!L169</f>
+        <f>'Point List'!L190</f>
         <v>0</v>
       </c>
       <c r="D172" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E172">
-        <f>'Point List'!J169</f>
+        <f>'Point List'!J190</f>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173">
-        <f>'Point List'!C170</f>
+        <f>'Point List'!C191</f>
         <v>0</v>
       </c>
       <c r="C173">
-        <f>'Point List'!L170</f>
+        <f>'Point List'!L191</f>
         <v>0</v>
       </c>
       <c r="D173" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E173">
-        <f>'Point List'!J170</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174">
-        <f>'Point List'!C171</f>
-        <v>0</v>
-      </c>
-      <c r="C174">
-        <f>'Point List'!L171</f>
-        <v>0</v>
-      </c>
-      <c r="D174" t="s">
-        <v>313</v>
-      </c>
-      <c r="E174">
-        <f>'Point List'!J171</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175">
-        <f>'Point List'!C172</f>
-        <v>0</v>
-      </c>
-      <c r="C175">
-        <f>'Point List'!L172</f>
-        <v>0</v>
-      </c>
-      <c r="D175" t="s">
-        <v>313</v>
-      </c>
-      <c r="E175">
-        <f>'Point List'!J172</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176">
-        <f>'Point List'!C173</f>
-        <v>0</v>
-      </c>
-      <c r="C176">
-        <f>'Point List'!L173</f>
-        <v>0</v>
-      </c>
-      <c r="D176" t="s">
-        <v>313</v>
-      </c>
-      <c r="E176">
-        <f>'Point List'!J173</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177">
-        <f>'Point List'!C174</f>
-        <v>0</v>
-      </c>
-      <c r="C177">
-        <f>'Point List'!L174</f>
-        <v>0</v>
-      </c>
-      <c r="D177" t="s">
-        <v>313</v>
-      </c>
-      <c r="E177">
-        <f>'Point List'!J174</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178">
-        <f>'Point List'!C175</f>
-        <v>0</v>
-      </c>
-      <c r="C178">
-        <f>'Point List'!L175</f>
-        <v>0</v>
-      </c>
-      <c r="D178" t="s">
-        <v>313</v>
-      </c>
-      <c r="E178">
-        <f>'Point List'!J175</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179">
-        <f>'Point List'!C176</f>
-        <v>0</v>
-      </c>
-      <c r="C179">
-        <f>'Point List'!L176</f>
-        <v>0</v>
-      </c>
-      <c r="D179" t="s">
-        <v>313</v>
-      </c>
-      <c r="E179">
-        <f>'Point List'!J176</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180">
-        <f>'Point List'!C177</f>
-        <v>0</v>
-      </c>
-      <c r="C180">
-        <f>'Point List'!L177</f>
-        <v>0</v>
-      </c>
-      <c r="D180" t="s">
-        <v>313</v>
-      </c>
-      <c r="E180">
-        <f>'Point List'!J177</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181">
-        <f>'Point List'!C178</f>
-        <v>0</v>
-      </c>
-      <c r="C181">
-        <f>'Point List'!L178</f>
-        <v>0</v>
-      </c>
-      <c r="D181" t="s">
-        <v>313</v>
-      </c>
-      <c r="E181">
-        <f>'Point List'!J178</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182">
-        <f>'Point List'!C179</f>
-        <v>0</v>
-      </c>
-      <c r="C182">
-        <f>'Point List'!L179</f>
-        <v>0</v>
-      </c>
-      <c r="D182" t="s">
-        <v>313</v>
-      </c>
-      <c r="E182">
-        <f>'Point List'!J179</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183">
-        <f>'Point List'!C180</f>
-        <v>0</v>
-      </c>
-      <c r="C183">
-        <f>'Point List'!L180</f>
-        <v>0</v>
-      </c>
-      <c r="D183" t="s">
-        <v>313</v>
-      </c>
-      <c r="E183">
-        <f>'Point List'!J180</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184">
-        <f>'Point List'!C181</f>
-        <v>0</v>
-      </c>
-      <c r="C184">
-        <f>'Point List'!L181</f>
-        <v>0</v>
-      </c>
-      <c r="D184" t="s">
-        <v>313</v>
-      </c>
-      <c r="E184">
-        <f>'Point List'!J181</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185">
-        <f>'Point List'!C182</f>
-        <v>0</v>
-      </c>
-      <c r="C185">
-        <f>'Point List'!L182</f>
-        <v>0</v>
-      </c>
-      <c r="D185" t="s">
-        <v>313</v>
-      </c>
-      <c r="E185">
-        <f>'Point List'!J182</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186">
-        <f>'Point List'!C183</f>
-        <v>0</v>
-      </c>
-      <c r="C186">
-        <f>'Point List'!L183</f>
-        <v>0</v>
-      </c>
-      <c r="D186" t="s">
-        <v>313</v>
-      </c>
-      <c r="E186">
-        <f>'Point List'!J183</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187">
-        <f>'Point List'!C184</f>
-        <v>0</v>
-      </c>
-      <c r="C187">
-        <f>'Point List'!L184</f>
-        <v>0</v>
-      </c>
-      <c r="D187" t="s">
-        <v>313</v>
-      </c>
-      <c r="E187">
-        <f>'Point List'!J184</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188">
-        <f>'Point List'!C185</f>
-        <v>0</v>
-      </c>
-      <c r="C188">
-        <f>'Point List'!L185</f>
-        <v>0</v>
-      </c>
-      <c r="D188" t="s">
-        <v>313</v>
-      </c>
-      <c r="E188">
-        <f>'Point List'!J185</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189">
-        <f>'Point List'!C186</f>
-        <v>0</v>
-      </c>
-      <c r="C189">
-        <f>'Point List'!L186</f>
-        <v>0</v>
-      </c>
-      <c r="D189" t="s">
-        <v>313</v>
-      </c>
-      <c r="E189">
-        <f>'Point List'!J186</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190">
-        <f>'Point List'!C187</f>
-        <v>0</v>
-      </c>
-      <c r="C190">
-        <f>'Point List'!L187</f>
-        <v>0</v>
-      </c>
-      <c r="D190" t="s">
-        <v>313</v>
-      </c>
-      <c r="E190">
-        <f>'Point List'!J187</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191">
-        <f>'Point List'!C188</f>
-        <v>0</v>
-      </c>
-      <c r="C191">
-        <f>'Point List'!L188</f>
-        <v>0</v>
-      </c>
-      <c r="D191" t="s">
-        <v>313</v>
-      </c>
-      <c r="E191">
-        <f>'Point List'!J188</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A192">
-        <f>'Point List'!C189</f>
-        <v>0</v>
-      </c>
-      <c r="C192">
-        <f>'Point List'!L189</f>
-        <v>0</v>
-      </c>
-      <c r="D192" t="s">
-        <v>313</v>
-      </c>
-      <c r="E192">
-        <f>'Point List'!J189</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A193">
-        <f>'Point List'!C190</f>
-        <v>0</v>
-      </c>
-      <c r="C193">
-        <f>'Point List'!L190</f>
-        <v>0</v>
-      </c>
-      <c r="D193" t="s">
-        <v>313</v>
-      </c>
-      <c r="E193">
-        <f>'Point List'!J190</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A194">
-        <f>'Point List'!C191</f>
-        <v>0</v>
-      </c>
-      <c r="C194">
-        <f>'Point List'!L191</f>
-        <v>0</v>
-      </c>
-      <c r="D194" t="s">
-        <v>313</v>
-      </c>
-      <c r="E194">
         <f>'Point List'!J191</f>
         <v>0</v>
       </c>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1765" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56D085A7-0B10-4616-A2FD-419F36CBB186}"/>
+  <xr:revisionPtr revIDLastSave="1784" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{746369A5-A800-4BE3-9E47-E1A1FA71BBA2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point List" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="320">
   <si>
     <t>Signal Type</t>
   </si>
@@ -74599,14 +74599,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B9609-D38B-45A0-9E25-0F7CEDBD1FA5}">
-  <dimension ref="A1:K173"/>
+  <dimension ref="A1:K168"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="59.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -74614,8 +74614,8 @@
         <v>300</v>
       </c>
       <c r="K1" t="str">
-        <f>A1</f>
-        <v>GP-Pro EX</v>
+        <f>"""" &amp; A1 &amp; """"</f>
+        <v>"GP-Pro EX"</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -74626,8 +74626,8 @@
         <v>303</v>
       </c>
       <c r="K2" t="str">
-        <f>_xlfn.CONCAT(A2,",",B2)</f>
-        <v>File Type,SymbolVariable</v>
+        <f>_xlfn.CONCAT(""""&amp;A2&amp;"""",",",""""&amp;B2&amp;"""")</f>
+        <v>"File Type","SymbolVariable"</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -74641,8 +74641,8 @@
         <v>0</v>
       </c>
       <c r="K3" t="str">
-        <f>_xlfn.CONCAT(A3,",",B3,",",C3)</f>
-        <v>File Version,3,0</v>
+        <f>_xlfn.CONCAT(""""&amp;A3&amp;"""",",",""""&amp;B3&amp;"""",",",""""&amp;C3&amp;"""")</f>
+        <v>"File Version","3","0"</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -74668,8 +74668,8 @@
         <v>309</v>
       </c>
       <c r="K5" t="str">
-        <f>_xlfn.CONCAT(A5,",",B5,",",C5,",",D5,",",E5,",",F5,",",G5)</f>
-        <v>Name,Index,Type,External/Internal,Address,Keep,Comment</v>
+        <f>_xlfn.CONCAT(""""&amp;A5&amp;"""",",",""""&amp;B5&amp;"""",",",""""&amp;C5&amp;"""",",",""""&amp;D5&amp;"""",",",""""&amp;E5&amp;"""",",",""""&amp;F5&amp;"""",",",""""&amp;G5&amp;"""")</f>
+        <v>"Name","Index","Type","External/Internal","Address","Keep","Comment"</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -74710,7 +74710,7 @@
         <v>012290</v>
       </c>
       <c r="K7" t="str">
-        <f t="shared" ref="K7:K70" si="0">_xlfn.CONCAT(A7,",",B7,",",C7,",",D7,",",E7,",",F7,",",G7)</f>
+        <f t="shared" ref="K7:K65" si="0">_xlfn.CONCAT(A7,",",B7,",",C7,",",D7,",",E7,",",F7,",",G7)</f>
         <v>System Shutdown,,BitAddress,PLC1,012290,,</v>
       </c>
     </row>
@@ -74968,2890 +74968,2785 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f>'Point List'!C17</f>
-        <v>AVAILABLE</v>
-      </c>
-      <c r="C20">
-        <f>'Point List'!L17</f>
-        <v>0</v>
+        <f>'Point List'!C19</f>
+        <v>System On</v>
+      </c>
+      <c r="C20" t="str">
+        <f>'Point List'!L19</f>
+        <v>BitAddress</v>
       </c>
       <c r="D20" t="s">
         <v>312</v>
       </c>
       <c r="E20" t="str">
-        <f>'Point List'!J17</f>
-        <v>012303</v>
+        <f>'Point List'!J19</f>
+        <v>012305</v>
       </c>
       <c r="K20" t="str">
         <f t="shared" si="0"/>
-        <v>AVAILABLE,,0,PLC1,012303,,</v>
+        <v>System On,,BitAddress,PLC1,012305,,</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
-        <f>'Point List'!C18</f>
-        <v>AVAILABLE</v>
-      </c>
-      <c r="C21">
-        <f>'Point List'!L18</f>
-        <v>0</v>
+        <f>'Point List'!C20</f>
+        <v>System Shutting Down</v>
+      </c>
+      <c r="C21" t="str">
+        <f>'Point List'!L20</f>
+        <v>BitAddress</v>
       </c>
       <c r="D21" t="s">
         <v>312</v>
       </c>
       <c r="E21" t="str">
-        <f>'Point List'!J18</f>
-        <v>012304</v>
+        <f>'Point List'!J20</f>
+        <v>012306</v>
       </c>
       <c r="K21" t="str">
         <f t="shared" si="0"/>
-        <v>AVAILABLE,,0,PLC1,012304,,</v>
+        <v>System Shutting Down,,BitAddress,PLC1,012306,,</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
-        <f>'Point List'!C19</f>
-        <v>System On</v>
+        <f>'Point List'!C21</f>
+        <v>System Initializing</v>
       </c>
       <c r="C22" t="str">
-        <f>'Point List'!L19</f>
+        <f>'Point List'!L21</f>
         <v>BitAddress</v>
       </c>
       <c r="D22" t="s">
         <v>312</v>
       </c>
       <c r="E22" t="str">
-        <f>'Point List'!J19</f>
-        <v>012305</v>
+        <f>'Point List'!J21</f>
+        <v>012307</v>
       </c>
       <c r="K22" t="str">
         <f t="shared" si="0"/>
-        <v>System On,,BitAddress,PLC1,012305,,</v>
+        <v>System Initializing,,BitAddress,PLC1,012307,,</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
-        <f>'Point List'!C20</f>
-        <v>System Shutting Down</v>
+        <f>'Point List'!C22</f>
+        <v>System Calibrating</v>
       </c>
       <c r="C23" t="str">
-        <f>'Point List'!L20</f>
+        <f>'Point List'!L22</f>
         <v>BitAddress</v>
       </c>
       <c r="D23" t="s">
         <v>312</v>
       </c>
       <c r="E23" t="str">
-        <f>'Point List'!J20</f>
-        <v>012306</v>
+        <f>'Point List'!J22</f>
+        <v>012308</v>
       </c>
       <c r="K23" t="str">
         <f t="shared" si="0"/>
-        <v>System Shutting Down,,BitAddress,PLC1,012306,,</v>
+        <v>System Calibrating,,BitAddress,PLC1,012308,,</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
-        <f>'Point List'!C21</f>
-        <v>System Initializing</v>
+        <f>'Point List'!C23</f>
+        <v>Measured Pump Power</v>
       </c>
       <c r="C24" t="str">
-        <f>'Point List'!L21</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L23</f>
+        <v>WordAddress</v>
       </c>
       <c r="D24" t="s">
         <v>312</v>
       </c>
       <c r="E24" t="str">
-        <f>'Point List'!J21</f>
-        <v>012307</v>
+        <f>'Point List'!J23</f>
+        <v>412557</v>
       </c>
       <c r="K24" t="str">
         <f t="shared" si="0"/>
-        <v>System Initializing,,BitAddress,PLC1,012307,,</v>
+        <v>Measured Pump Power,,WordAddress,PLC1,412557,,</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
-        <f>'Point List'!C22</f>
-        <v>System Calibrating</v>
+        <f>'Point List'!C24</f>
+        <v>Measured Inlet Coolant Temperature</v>
       </c>
       <c r="C25" t="str">
-        <f>'Point List'!L22</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L24</f>
+        <v>WordAddress</v>
       </c>
       <c r="D25" t="s">
         <v>312</v>
       </c>
       <c r="E25" t="str">
-        <f>'Point List'!J22</f>
-        <v>012308</v>
+        <f>'Point List'!J24</f>
+        <v>412559</v>
       </c>
       <c r="K25" t="str">
         <f t="shared" si="0"/>
-        <v>System Calibrating,,BitAddress,PLC1,012308,,</v>
+        <v>Measured Inlet Coolant Temperature,,WordAddress,PLC1,412559,,</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
-        <f>'Point List'!C23</f>
-        <v>Measured Pump Power</v>
+        <f>'Point List'!C25</f>
+        <v>Measured Conductivity</v>
       </c>
       <c r="C26" t="str">
-        <f>'Point List'!L23</f>
+        <f>'Point List'!L25</f>
         <v>WordAddress</v>
       </c>
       <c r="D26" t="s">
         <v>312</v>
       </c>
       <c r="E26" t="str">
-        <f>'Point List'!J23</f>
-        <v>412557</v>
+        <f>'Point List'!J25</f>
+        <v>412561</v>
       </c>
       <c r="K26" t="str">
         <f t="shared" si="0"/>
-        <v>Measured Pump Power,,WordAddress,PLC1,412557,,</v>
+        <v>Measured Conductivity,,WordAddress,PLC1,412561,,</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
-        <f>'Point List'!C24</f>
-        <v>Measured Inlet Coolant Temperature</v>
+        <f>'Point List'!C26</f>
+        <v>Measured Flow</v>
       </c>
       <c r="C27" t="str">
-        <f>'Point List'!L24</f>
+        <f>'Point List'!L26</f>
         <v>WordAddress</v>
       </c>
       <c r="D27" t="s">
         <v>312</v>
       </c>
       <c r="E27" t="str">
-        <f>'Point List'!J24</f>
-        <v>412559</v>
+        <f>'Point List'!J26</f>
+        <v>412563</v>
       </c>
       <c r="K27" t="str">
         <f t="shared" si="0"/>
-        <v>Measured Inlet Coolant Temperature,,WordAddress,PLC1,412559,,</v>
+        <v>Measured Flow,,WordAddress,PLC1,412563,,</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
-        <f>'Point List'!C25</f>
-        <v>Measured Conductivity</v>
+        <f>'Point List'!C27</f>
+        <v>Valve Open Percentage</v>
       </c>
       <c r="C28" t="str">
-        <f>'Point List'!L25</f>
+        <f>'Point List'!L27</f>
         <v>WordAddress</v>
       </c>
       <c r="D28" t="s">
         <v>312</v>
       </c>
       <c r="E28" t="str">
-        <f>'Point List'!J25</f>
-        <v>412561</v>
+        <f>'Point List'!J27</f>
+        <v>412565</v>
       </c>
       <c r="K28" t="str">
         <f t="shared" si="0"/>
-        <v>Measured Conductivity,,WordAddress,PLC1,412561,,</v>
+        <v>Valve Open Percentage,,WordAddress,PLC1,412565,,</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
-        <f>'Point List'!C26</f>
-        <v>Measured Flow</v>
+        <f>'Point List'!C28</f>
+        <v>Real RTD 1 Signal</v>
       </c>
       <c r="C29" t="str">
-        <f>'Point List'!L26</f>
+        <f>'Point List'!L28</f>
         <v>WordAddress</v>
       </c>
       <c r="D29" t="s">
         <v>312</v>
       </c>
       <c r="E29" t="str">
-        <f>'Point List'!J26</f>
-        <v>412563</v>
+        <f>'Point List'!J28</f>
+        <v>412567</v>
       </c>
       <c r="K29" t="str">
         <f t="shared" si="0"/>
-        <v>Measured Flow,,WordAddress,PLC1,412563,,</v>
+        <v>Real RTD 1 Signal,,WordAddress,PLC1,412567,,</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
-        <f>'Point List'!C27</f>
-        <v>Valve Open Percentage</v>
+        <f>'Point List'!C29</f>
+        <v>Real RTD 2 Signal</v>
       </c>
       <c r="C30" t="str">
-        <f>'Point List'!L27</f>
+        <f>'Point List'!L29</f>
         <v>WordAddress</v>
       </c>
       <c r="D30" t="s">
         <v>312</v>
       </c>
       <c r="E30" t="str">
-        <f>'Point List'!J27</f>
-        <v>412565</v>
+        <f>'Point List'!J29</f>
+        <v>412569</v>
       </c>
       <c r="K30" t="str">
         <f t="shared" si="0"/>
-        <v>Valve Open Percentage,,WordAddress,PLC1,412565,,</v>
+        <v>Real RTD 2 Signal,,WordAddress,PLC1,412569,,</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
-        <f>'Point List'!C28</f>
-        <v>Real RTD 1 Signal</v>
+        <f>'Point List'!C30</f>
+        <v>Real RTD 3 Signal</v>
       </c>
       <c r="C31" t="str">
-        <f>'Point List'!L28</f>
+        <f>'Point List'!L30</f>
         <v>WordAddress</v>
       </c>
       <c r="D31" t="s">
         <v>312</v>
       </c>
       <c r="E31" t="str">
-        <f>'Point List'!J28</f>
-        <v>412567</v>
+        <f>'Point List'!J30</f>
+        <v>412571</v>
       </c>
       <c r="K31" t="str">
         <f t="shared" si="0"/>
-        <v>Real RTD 1 Signal,,WordAddress,PLC1,412567,,</v>
+        <v>Real RTD 3 Signal,,WordAddress,PLC1,412571,,</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
-        <f>'Point List'!C29</f>
-        <v>Real RTD 2 Signal</v>
+        <f>'Point List'!C32</f>
+        <v xml:space="preserve">Measured Valve Position </v>
       </c>
       <c r="C32" t="str">
-        <f>'Point List'!L29</f>
+        <f>'Point List'!L32</f>
         <v>WordAddress</v>
       </c>
       <c r="D32" t="s">
         <v>312</v>
       </c>
       <c r="E32" t="str">
-        <f>'Point List'!J29</f>
-        <v>412569</v>
+        <f>'Point List'!J32</f>
+        <v>412575</v>
       </c>
       <c r="K32" t="str">
         <f t="shared" si="0"/>
-        <v>Real RTD 2 Signal,,WordAddress,PLC1,412569,,</v>
+        <v>Measured Valve Position ,,WordAddress,PLC1,412575,,</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
-        <f>'Point List'!C30</f>
-        <v>Real RTD 3 Signal</v>
+        <f>'Point List'!C33</f>
+        <v>Debounced Water Level Low Signal</v>
       </c>
       <c r="C33" t="str">
-        <f>'Point List'!L30</f>
+        <f>'Point List'!L33</f>
         <v>WordAddress</v>
       </c>
       <c r="D33" t="s">
         <v>312</v>
       </c>
       <c r="E33" t="str">
-        <f>'Point List'!J30</f>
-        <v>412571</v>
+        <f>'Point List'!J33</f>
+        <v>012309</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="0"/>
-        <v>Real RTD 3 Signal,,WordAddress,PLC1,412571,,</v>
+        <v>Debounced Water Level Low Signal,,WordAddress,PLC1,012309,,</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
-        <f>'Point List'!C31</f>
-        <v>AVAILABLE</v>
-      </c>
-      <c r="C34" t="str">
-        <f>'Point List'!L31</f>
-        <v>WordAddress</v>
+        <f>'Point List'!C34</f>
+        <v>Debounced Water Level Low Low Signal</v>
+      </c>
+      <c r="C34">
+        <f>'Point List'!L34</f>
+        <v>0</v>
       </c>
       <c r="D34" t="s">
         <v>312</v>
       </c>
       <c r="E34" t="str">
-        <f>'Point List'!J31</f>
-        <v>412573</v>
+        <f>'Point List'!J34</f>
+        <v>012310</v>
       </c>
       <c r="K34" t="str">
         <f t="shared" si="0"/>
-        <v>AVAILABLE,,WordAddress,PLC1,412573,,</v>
+        <v>Debounced Water Level Low Low Signal,,0,PLC1,012310,,</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
-        <f>'Point List'!C32</f>
-        <v xml:space="preserve">Measured Valve Position </v>
-      </c>
-      <c r="C35" t="str">
-        <f>'Point List'!L32</f>
-        <v>WordAddress</v>
+        <f>'Point List'!C35</f>
+        <v>Debounced Pressure Signal</v>
+      </c>
+      <c r="C35">
+        <f>'Point List'!L35</f>
+        <v>0</v>
       </c>
       <c r="D35" t="s">
         <v>312</v>
       </c>
       <c r="E35" t="str">
-        <f>'Point List'!J32</f>
-        <v>412575</v>
+        <f>'Point List'!J35</f>
+        <v>012311</v>
       </c>
       <c r="K35" t="str">
         <f t="shared" si="0"/>
-        <v>Measured Valve Position ,,WordAddress,PLC1,412575,,</v>
+        <v>Debounced Pressure Signal,,0,PLC1,012311,,</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
-        <f>'Point List'!C33</f>
-        <v>Debounced Water Level Low Signal</v>
-      </c>
-      <c r="C36" t="str">
-        <f>'Point List'!L33</f>
-        <v>WordAddress</v>
+        <f>'Point List'!C36</f>
+        <v>Debounced Conductivity Alarm Signal</v>
+      </c>
+      <c r="C36">
+        <f>'Point List'!L36</f>
+        <v>0</v>
       </c>
       <c r="D36" t="s">
         <v>312</v>
       </c>
       <c r="E36" t="str">
-        <f>'Point List'!J33</f>
-        <v>012309</v>
+        <f>'Point List'!J36</f>
+        <v>012312</v>
       </c>
       <c r="K36" t="str">
         <f t="shared" si="0"/>
-        <v>Debounced Water Level Low Signal,,WordAddress,PLC1,012309,,</v>
+        <v>Debounced Conductivity Alarm Signal,,0,PLC1,012312,,</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
-        <f>'Point List'!C34</f>
-        <v>Debounced Water Level Low Low Signal</v>
+        <f>'Point List'!C37</f>
+        <v>Debounced Conductivity Fault Signal</v>
       </c>
       <c r="C37">
-        <f>'Point List'!L34</f>
+        <f>'Point List'!L37</f>
         <v>0</v>
       </c>
       <c r="D37" t="s">
         <v>312</v>
       </c>
       <c r="E37" t="str">
-        <f>'Point List'!J34</f>
-        <v>012310</v>
+        <f>'Point List'!J37</f>
+        <v>012313</v>
       </c>
       <c r="K37" t="str">
         <f t="shared" si="0"/>
-        <v>Debounced Water Level Low Low Signal,,0,PLC1,012310,,</v>
+        <v>Debounced Conductivity Fault Signal,,0,PLC1,012313,,</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
-        <f>'Point List'!C35</f>
-        <v>Debounced Pressure Signal</v>
-      </c>
-      <c r="C38">
-        <f>'Point List'!L35</f>
-        <v>0</v>
+        <f>'Point List'!C38</f>
+        <v>Output Water Level Low Signal</v>
+      </c>
+      <c r="C38" t="str">
+        <f>'Point List'!L38</f>
+        <v>BitAddress</v>
       </c>
       <c r="D38" t="s">
         <v>312</v>
       </c>
       <c r="E38" t="str">
-        <f>'Point List'!J35</f>
-        <v>012311</v>
+        <f>'Point List'!J38</f>
+        <v>012314</v>
       </c>
       <c r="K38" t="str">
         <f t="shared" si="0"/>
-        <v>Debounced Pressure Signal,,0,PLC1,012311,,</v>
+        <v>Output Water Level Low Signal,,BitAddress,PLC1,012314,,</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
-        <f>'Point List'!C36</f>
-        <v>Debounced Conductivity Alarm Signal</v>
-      </c>
-      <c r="C39">
-        <f>'Point List'!L36</f>
-        <v>0</v>
+        <f>'Point List'!C39</f>
+        <v>Output Water Level Low Low Signal</v>
+      </c>
+      <c r="C39" t="str">
+        <f>'Point List'!L39</f>
+        <v>BitAddress</v>
       </c>
       <c r="D39" t="s">
         <v>312</v>
       </c>
       <c r="E39" t="str">
-        <f>'Point List'!J36</f>
-        <v>012312</v>
+        <f>'Point List'!J39</f>
+        <v>012315</v>
       </c>
       <c r="K39" t="str">
         <f t="shared" si="0"/>
-        <v>Debounced Conductivity Alarm Signal,,0,PLC1,012312,,</v>
+        <v>Output Water Level Low Low Signal,,BitAddress,PLC1,012315,,</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
-        <f>'Point List'!C37</f>
-        <v>Debounced Conductivity Fault Signal</v>
-      </c>
-      <c r="C40">
-        <f>'Point List'!L37</f>
-        <v>0</v>
+        <f>'Point List'!C40</f>
+        <v>Output Pressure Signal</v>
+      </c>
+      <c r="C40" t="str">
+        <f>'Point List'!L40</f>
+        <v>BitAddress</v>
       </c>
       <c r="D40" t="s">
         <v>312</v>
       </c>
       <c r="E40" t="str">
-        <f>'Point List'!J37</f>
-        <v>012313</v>
+        <f>'Point List'!J40</f>
+        <v>012316</v>
       </c>
       <c r="K40" t="str">
         <f t="shared" si="0"/>
-        <v>Debounced Conductivity Fault Signal,,0,PLC1,012313,,</v>
+        <v>Output Pressure Signal,,BitAddress,PLC1,012316,,</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
-        <f>'Point List'!C38</f>
-        <v>Output Water Level Low Signal</v>
+        <f>'Point List'!C41</f>
+        <v>Output Conductivity Alarm Signal</v>
       </c>
       <c r="C41" t="str">
-        <f>'Point List'!L38</f>
+        <f>'Point List'!L41</f>
         <v>BitAddress</v>
       </c>
       <c r="D41" t="s">
         <v>312</v>
       </c>
       <c r="E41" t="str">
-        <f>'Point List'!J38</f>
-        <v>012314</v>
+        <f>'Point List'!J41</f>
+        <v>012317</v>
       </c>
       <c r="K41" t="str">
         <f t="shared" si="0"/>
-        <v>Output Water Level Low Signal,,BitAddress,PLC1,012314,,</v>
+        <v>Output Conductivity Alarm Signal,,BitAddress,PLC1,012317,,</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
-        <f>'Point List'!C39</f>
-        <v>Output Water Level Low Low Signal</v>
+        <f>'Point List'!C42</f>
+        <v>Output Conductivity Fault Signal</v>
       </c>
       <c r="C42" t="str">
-        <f>'Point List'!L39</f>
+        <f>'Point List'!L42</f>
         <v>BitAddress</v>
       </c>
       <c r="D42" t="s">
         <v>312</v>
       </c>
       <c r="E42" t="str">
-        <f>'Point List'!J39</f>
-        <v>012315</v>
+        <f>'Point List'!J42</f>
+        <v>012318</v>
       </c>
       <c r="K42" t="str">
         <f t="shared" si="0"/>
-        <v>Output Water Level Low Low Signal,,BitAddress,PLC1,012315,,</v>
+        <v>Output Conductivity Fault Signal,,BitAddress,PLC1,012318,,</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
-        <f>'Point List'!C40</f>
-        <v>Output Pressure Signal</v>
-      </c>
-      <c r="C43" t="str">
-        <f>'Point List'!L40</f>
-        <v>BitAddress</v>
+        <f>'Point List'!C43</f>
+        <v>Differential Pump Hours</v>
+      </c>
+      <c r="C43">
+        <f>'Point List'!L43</f>
+        <v>0</v>
       </c>
       <c r="D43" t="s">
         <v>312</v>
       </c>
       <c r="E43" t="str">
-        <f>'Point List'!J40</f>
-        <v>012316</v>
+        <f>'Point List'!J43</f>
+        <v>012453</v>
       </c>
       <c r="K43" t="str">
         <f t="shared" si="0"/>
-        <v>Output Pressure Signal,,BitAddress,PLC1,012316,,</v>
+        <v>Differential Pump Hours,,0,PLC1,012453,,</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
-        <f>'Point List'!C41</f>
-        <v>Output Conductivity Alarm Signal</v>
-      </c>
-      <c r="C44" t="str">
-        <f>'Point List'!L41</f>
-        <v>BitAddress</v>
+        <f>'Point List'!C44</f>
+        <v>System Pulse</v>
+      </c>
+      <c r="C44">
+        <f>'Point List'!L44</f>
+        <v>0</v>
       </c>
       <c r="D44" t="s">
         <v>312</v>
       </c>
       <c r="E44" t="str">
-        <f>'Point List'!J41</f>
-        <v>012317</v>
+        <f>'Point List'!J44</f>
+        <v>012319</v>
       </c>
       <c r="K44" t="str">
         <f t="shared" si="0"/>
-        <v>Output Conductivity Alarm Signal,,BitAddress,PLC1,012317,,</v>
+        <v>System Pulse,,0,PLC1,012319,,</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
-        <f>'Point List'!C42</f>
-        <v>Output Conductivity Fault Signal</v>
+        <f>'Point List'!C45</f>
+        <v>Measured Active Pump  Voltage</v>
       </c>
       <c r="C45" t="str">
-        <f>'Point List'!L42</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L45</f>
+        <v>WordAddress</v>
       </c>
       <c r="D45" t="s">
         <v>312</v>
       </c>
       <c r="E45" t="str">
-        <f>'Point List'!J42</f>
-        <v>012318</v>
+        <f>'Point List'!J45</f>
+        <v>412577</v>
       </c>
       <c r="K45" t="str">
         <f t="shared" si="0"/>
-        <v>Output Conductivity Fault Signal,,BitAddress,PLC1,012318,,</v>
+        <v>Measured Active Pump  Voltage,,WordAddress,PLC1,412577,,</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
-        <f>'Point List'!C43</f>
-        <v>Differential Pump Hours</v>
-      </c>
-      <c r="C46">
-        <f>'Point List'!L43</f>
-        <v>0</v>
+        <f>'Point List'!C46</f>
+        <v>Measured Active Pump  Current</v>
+      </c>
+      <c r="C46" t="str">
+        <f>'Point List'!L46</f>
+        <v>WordAddress</v>
       </c>
       <c r="D46" t="s">
         <v>312</v>
       </c>
       <c r="E46" t="str">
-        <f>'Point List'!J43</f>
-        <v>012453</v>
+        <f>'Point List'!J46</f>
+        <v>412579</v>
       </c>
       <c r="K46" t="str">
         <f t="shared" si="0"/>
-        <v>Differential Pump Hours,,0,PLC1,012453,,</v>
+        <v>Measured Active Pump  Current,,WordAddress,PLC1,412579,,</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
-        <f>'Point List'!C44</f>
-        <v>System Pulse</v>
-      </c>
-      <c r="C47">
-        <f>'Point List'!L44</f>
-        <v>0</v>
+        <f>'Point List'!C49</f>
+        <v>Pump 1 Total Hours</v>
+      </c>
+      <c r="C47" t="str">
+        <f>'Point List'!L49</f>
+        <v>WordAddress</v>
       </c>
       <c r="D47" t="s">
         <v>312</v>
       </c>
       <c r="E47" t="str">
-        <f>'Point List'!J44</f>
-        <v>012319</v>
+        <f>'Point List'!J49</f>
+        <v>412455</v>
       </c>
       <c r="K47" t="str">
         <f t="shared" si="0"/>
-        <v>System Pulse,,0,PLC1,012319,,</v>
+        <v>Pump 1 Total Hours,,WordAddress,PLC1,412455,,</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
-        <f>'Point List'!C45</f>
-        <v>Measured Active Pump  Voltage</v>
+        <f>'Point List'!C50</f>
+        <v>Pump 2 Total Hours</v>
       </c>
       <c r="C48" t="str">
-        <f>'Point List'!L45</f>
+        <f>'Point List'!L50</f>
         <v>WordAddress</v>
       </c>
       <c r="D48" t="s">
         <v>312</v>
       </c>
       <c r="E48" t="str">
-        <f>'Point List'!J45</f>
-        <v>412577</v>
+        <f>'Point List'!J50</f>
+        <v>412457</v>
       </c>
       <c r="K48" t="str">
         <f t="shared" si="0"/>
-        <v>Measured Active Pump  Voltage,,WordAddress,PLC1,412577,,</v>
+        <v>Pump 2 Total Hours,,WordAddress,PLC1,412457,,</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
-        <f>'Point List'!C46</f>
-        <v>Measured Active Pump  Current</v>
+        <f>'Point List'!C51</f>
+        <v xml:space="preserve">High Coolant Temperature </v>
       </c>
       <c r="C49" t="str">
-        <f>'Point List'!L46</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L51</f>
+        <v>BitAddress</v>
       </c>
       <c r="D49" t="s">
         <v>312</v>
       </c>
       <c r="E49" t="str">
-        <f>'Point List'!J46</f>
-        <v>412579</v>
+        <f>'Point List'!J51</f>
+        <v>012320</v>
       </c>
       <c r="K49" t="str">
         <f t="shared" si="0"/>
-        <v>Measured Active Pump  Current,,WordAddress,PLC1,412579,,</v>
+        <v>High Coolant Temperature ,,BitAddress,PLC1,012320,,</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
-        <f>'Point List'!C47</f>
-        <v>AVAILABLE</v>
+        <f>'Point List'!C52</f>
+        <v>Low Coolant Level in Vessel</v>
       </c>
       <c r="C50" t="str">
-        <f>'Point List'!L47</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L52</f>
+        <v>BitAddress</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
       </c>
       <c r="E50" t="str">
-        <f>'Point List'!J47</f>
-        <v>412581</v>
+        <f>'Point List'!J52</f>
+        <v>012321</v>
       </c>
       <c r="K50" t="str">
         <f t="shared" si="0"/>
-        <v>AVAILABLE,,WordAddress,PLC1,412581,,</v>
+        <v>Low Coolant Level in Vessel,,BitAddress,PLC1,012321,,</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
-        <f>'Point List'!C48</f>
-        <v>AVAILABLE</v>
-      </c>
-      <c r="C51">
-        <f>'Point List'!L48</f>
-        <v>0</v>
+        <f>'Point List'!C53</f>
+        <v xml:space="preserve">High Coolant Conductivity </v>
+      </c>
+      <c r="C51" t="str">
+        <f>'Point List'!L53</f>
+        <v>BitAddress</v>
       </c>
       <c r="D51" t="s">
         <v>312</v>
       </c>
       <c r="E51" t="str">
-        <f>'Point List'!J48</f>
-        <v>412583</v>
+        <f>'Point List'!J53</f>
+        <v>012322</v>
       </c>
       <c r="K51" t="str">
         <f t="shared" si="0"/>
-        <v>AVAILABLE,,0,PLC1,412583,,</v>
+        <v>High Coolant Conductivity ,,BitAddress,PLC1,012322,,</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
-        <f>'Point List'!C49</f>
-        <v>Pump 1 Total Hours</v>
+        <f>'Point List'!C54</f>
+        <v>Low Hydraulic Power</v>
       </c>
       <c r="C52" t="str">
-        <f>'Point List'!L49</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L54</f>
+        <v>BitAddress</v>
       </c>
       <c r="D52" t="s">
         <v>312</v>
       </c>
       <c r="E52" t="str">
-        <f>'Point List'!J49</f>
-        <v>412455</v>
+        <f>'Point List'!J54</f>
+        <v>012323</v>
       </c>
       <c r="K52" t="str">
         <f t="shared" si="0"/>
-        <v>Pump 1 Total Hours,,WordAddress,PLC1,412455,,</v>
+        <v>Low Hydraulic Power,,BitAddress,PLC1,012323,,</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
-        <f>'Point List'!C50</f>
-        <v>Pump 2 Total Hours</v>
+        <f>'Point List'!C55</f>
+        <v>Low Hydraulic Flow</v>
       </c>
       <c r="C53" t="str">
-        <f>'Point List'!L50</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L55</f>
+        <v>BitAddress</v>
       </c>
       <c r="D53" t="s">
         <v>312</v>
       </c>
       <c r="E53" t="str">
-        <f>'Point List'!J50</f>
-        <v>412457</v>
+        <f>'Point List'!J55</f>
+        <v>012324</v>
       </c>
       <c r="K53" t="str">
         <f t="shared" si="0"/>
-        <v>Pump 2 Total Hours,,WordAddress,PLC1,412457,,</v>
+        <v>Low Hydraulic Flow,,BitAddress,PLC1,012324,,</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
-        <f>'Point List'!C51</f>
-        <v xml:space="preserve">High Coolant Temperature </v>
+        <f>'Point List'!C56</f>
+        <v>Low Hydraulic Pressure</v>
       </c>
       <c r="C54" t="str">
-        <f>'Point List'!L51</f>
+        <f>'Point List'!L56</f>
         <v>BitAddress</v>
       </c>
       <c r="D54" t="s">
         <v>312</v>
       </c>
       <c r="E54" t="str">
-        <f>'Point List'!J51</f>
-        <v>012320</v>
+        <f>'Point List'!J56</f>
+        <v>012325</v>
       </c>
       <c r="K54" t="str">
         <f t="shared" si="0"/>
-        <v>High Coolant Temperature ,,BitAddress,PLC1,012320,,</v>
+        <v>Low Hydraulic Pressure,,BitAddress,PLC1,012325,,</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
-        <f>'Point List'!C52</f>
-        <v>Low Coolant Level in Vessel</v>
+        <f>'Point List'!C57</f>
+        <v>Voltage Signal Malfunction</v>
       </c>
       <c r="C55" t="str">
-        <f>'Point List'!L52</f>
+        <f>'Point List'!L57</f>
         <v>BitAddress</v>
       </c>
       <c r="D55" t="s">
         <v>312</v>
       </c>
       <c r="E55" t="str">
-        <f>'Point List'!J52</f>
-        <v>012321</v>
+        <f>'Point List'!J57</f>
+        <v>012326</v>
       </c>
       <c r="K55" t="str">
         <f t="shared" si="0"/>
-        <v>Low Coolant Level in Vessel,,BitAddress,PLC1,012321,,</v>
+        <v>Voltage Signal Malfunction,,BitAddress,PLC1,012326,,</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
-        <f>'Point List'!C53</f>
-        <v xml:space="preserve">High Coolant Conductivity </v>
+        <f>'Point List'!C58</f>
+        <v>Current Signal Malfunction</v>
       </c>
       <c r="C56" t="str">
-        <f>'Point List'!L53</f>
+        <f>'Point List'!L58</f>
         <v>BitAddress</v>
       </c>
       <c r="D56" t="s">
         <v>312</v>
       </c>
       <c r="E56" t="str">
-        <f>'Point List'!J53</f>
-        <v>012322</v>
+        <f>'Point List'!J58</f>
+        <v>012327</v>
       </c>
       <c r="K56" t="str">
         <f t="shared" si="0"/>
-        <v>High Coolant Conductivity ,,BitAddress,PLC1,012322,,</v>
+        <v>Current Signal Malfunction,,BitAddress,PLC1,012327,,</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
-        <f>'Point List'!C54</f>
-        <v>Low Hydraulic Power</v>
+        <f>'Point List'!C59</f>
+        <v>Primary Hydraulic Failure</v>
       </c>
       <c r="C57" t="str">
-        <f>'Point List'!L54</f>
+        <f>'Point List'!L59</f>
         <v>BitAddress</v>
       </c>
       <c r="D57" t="s">
         <v>312</v>
       </c>
       <c r="E57" t="str">
-        <f>'Point List'!J54</f>
-        <v>012323</v>
+        <f>'Point List'!J59</f>
+        <v>012328</v>
       </c>
       <c r="K57" t="str">
         <f t="shared" si="0"/>
-        <v>Low Hydraulic Power,,BitAddress,PLC1,012323,,</v>
+        <v>Primary Hydraulic Failure,,BitAddress,PLC1,012328,,</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
-        <f>'Point List'!C55</f>
-        <v>Low Hydraulic Flow</v>
+        <f>'Point List'!C60</f>
+        <v>Secondary Hydraulic Failure</v>
       </c>
       <c r="C58" t="str">
-        <f>'Point List'!L55</f>
+        <f>'Point List'!L60</f>
         <v>BitAddress</v>
       </c>
       <c r="D58" t="s">
         <v>312</v>
       </c>
       <c r="E58" t="str">
-        <f>'Point List'!J55</f>
-        <v>012324</v>
+        <f>'Point List'!J60</f>
+        <v>012329</v>
       </c>
       <c r="K58" t="str">
         <f t="shared" si="0"/>
-        <v>Low Hydraulic Flow,,BitAddress,PLC1,012324,,</v>
+        <v>Secondary Hydraulic Failure,,BitAddress,PLC1,012329,,</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
-        <f>'Point List'!C56</f>
-        <v>Low Hydraulic Pressure</v>
+        <f>'Point List'!C61</f>
+        <v>Automatic Valve Control Disabled</v>
       </c>
       <c r="C59" t="str">
-        <f>'Point List'!L56</f>
+        <f>'Point List'!L61</f>
         <v>BitAddress</v>
       </c>
       <c r="D59" t="s">
         <v>312</v>
       </c>
       <c r="E59" t="str">
-        <f>'Point List'!J56</f>
-        <v>012325</v>
+        <f>'Point List'!J61</f>
+        <v>012330</v>
       </c>
       <c r="K59" t="str">
         <f t="shared" si="0"/>
-        <v>Low Hydraulic Pressure,,BitAddress,PLC1,012325,,</v>
+        <v>Automatic Valve Control Disabled,,BitAddress,PLC1,012330,,</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
-        <f>'Point List'!C57</f>
-        <v>Voltage Signal Malfunction</v>
+        <f>'Point List'!C62</f>
+        <v>Automatic Fan Control Disabled</v>
       </c>
       <c r="C60" t="str">
-        <f>'Point List'!L57</f>
+        <f>'Point List'!L62</f>
         <v>BitAddress</v>
       </c>
       <c r="D60" t="s">
         <v>312</v>
       </c>
       <c r="E60" t="str">
-        <f>'Point List'!J57</f>
-        <v>012326</v>
+        <f>'Point List'!J62</f>
+        <v>012331</v>
       </c>
       <c r="K60" t="str">
         <f t="shared" si="0"/>
-        <v>Voltage Signal Malfunction,,BitAddress,PLC1,012326,,</v>
+        <v>Automatic Fan Control Disabled,,BitAddress,PLC1,012331,,</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
-        <f>'Point List'!C58</f>
-        <v>Current Signal Malfunction</v>
+        <f>'Point List'!C63</f>
+        <v>Flow Signal Malfunction</v>
       </c>
       <c r="C61" t="str">
-        <f>'Point List'!L58</f>
+        <f>'Point List'!L63</f>
         <v>BitAddress</v>
       </c>
       <c r="D61" t="s">
         <v>312</v>
       </c>
       <c r="E61" t="str">
-        <f>'Point List'!J58</f>
-        <v>012327</v>
+        <f>'Point List'!J63</f>
+        <v>012332</v>
       </c>
       <c r="K61" t="str">
         <f t="shared" si="0"/>
-        <v>Current Signal Malfunction,,BitAddress,PLC1,012327,,</v>
+        <v>Flow Signal Malfunction,,BitAddress,PLC1,012332,,</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
-        <f>'Point List'!C59</f>
-        <v>Primary Hydraulic Failure</v>
+        <f>'Point List'!C64</f>
+        <v>Bad RTD 1 Signal</v>
       </c>
       <c r="C62" t="str">
-        <f>'Point List'!L59</f>
+        <f>'Point List'!L64</f>
         <v>BitAddress</v>
       </c>
       <c r="D62" t="s">
         <v>312</v>
       </c>
       <c r="E62" t="str">
-        <f>'Point List'!J59</f>
-        <v>012328</v>
+        <f>'Point List'!J64</f>
+        <v>012333</v>
       </c>
       <c r="K62" t="str">
         <f t="shared" si="0"/>
-        <v>Primary Hydraulic Failure,,BitAddress,PLC1,012328,,</v>
+        <v>Bad RTD 1 Signal,,BitAddress,PLC1,012333,,</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
-        <f>'Point List'!C60</f>
-        <v>Secondary Hydraulic Failure</v>
+        <f>'Point List'!C65</f>
+        <v>Bad RTD 2 Signal</v>
       </c>
       <c r="C63" t="str">
-        <f>'Point List'!L60</f>
+        <f>'Point List'!L65</f>
         <v>BitAddress</v>
       </c>
       <c r="D63" t="s">
         <v>312</v>
       </c>
       <c r="E63" t="str">
-        <f>'Point List'!J60</f>
-        <v>012329</v>
+        <f>'Point List'!J65</f>
+        <v>012334</v>
       </c>
       <c r="K63" t="str">
         <f t="shared" si="0"/>
-        <v>Secondary Hydraulic Failure,,BitAddress,PLC1,012329,,</v>
+        <v>Bad RTD 2 Signal,,BitAddress,PLC1,012334,,</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
-        <f>'Point List'!C61</f>
-        <v>Automatic Valve Control Disabled</v>
+        <f>'Point List'!C66</f>
+        <v>Bad RTD 3 Signal</v>
       </c>
       <c r="C64" t="str">
-        <f>'Point List'!L61</f>
+        <f>'Point List'!L66</f>
         <v>BitAddress</v>
       </c>
       <c r="D64" t="s">
         <v>312</v>
       </c>
       <c r="E64" t="str">
-        <f>'Point List'!J61</f>
-        <v>012330</v>
+        <f>'Point List'!J66</f>
+        <v>012335</v>
       </c>
       <c r="K64" t="str">
         <f t="shared" si="0"/>
-        <v>Automatic Valve Control Disabled,,BitAddress,PLC1,012330,,</v>
+        <v>Bad RTD 3 Signal,,BitAddress,PLC1,012335,,</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
-        <f>'Point List'!C62</f>
-        <v>Automatic Fan Control Disabled</v>
+        <f>'Point List'!C67</f>
+        <v>Pump Cycle Alarm</v>
       </c>
       <c r="C65" t="str">
-        <f>'Point List'!L62</f>
+        <f>'Point List'!L67</f>
         <v>BitAddress</v>
       </c>
       <c r="D65" t="s">
         <v>312</v>
       </c>
       <c r="E65" t="str">
-        <f>'Point List'!J62</f>
-        <v>012331</v>
+        <f>'Point List'!J67</f>
+        <v>012336</v>
       </c>
       <c r="K65" t="str">
         <f t="shared" si="0"/>
-        <v>Automatic Fan Control Disabled,,BitAddress,PLC1,012331,,</v>
+        <v>Pump Cycle Alarm,,BitAddress,PLC1,012336,,</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
-        <f>'Point List'!C63</f>
-        <v>Flow Signal Malfunction</v>
+        <f>'Point List'!C68</f>
+        <v>Critical Temperature</v>
       </c>
       <c r="C66" t="str">
-        <f>'Point List'!L63</f>
+        <f>'Point List'!L68</f>
         <v>BitAddress</v>
       </c>
       <c r="D66" t="s">
         <v>312</v>
       </c>
       <c r="E66" t="str">
-        <f>'Point List'!J63</f>
-        <v>012332</v>
+        <f>'Point List'!J68</f>
+        <v>012337</v>
       </c>
       <c r="K66" t="str">
-        <f t="shared" si="0"/>
-        <v>Flow Signal Malfunction,,BitAddress,PLC1,012332,,</v>
+        <f t="shared" ref="K66:K74" si="1">_xlfn.CONCAT(A66,",",B66,",",C66,",",D66,",",E66,",",F66,",",G66)</f>
+        <v>Critical Temperature,,BitAddress,PLC1,012337,,</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
-        <f>'Point List'!C64</f>
-        <v>Bad RTD 1 Signal</v>
+        <f>'Point List'!C69</f>
+        <v>Critical Vessel Level</v>
       </c>
       <c r="C67" t="str">
-        <f>'Point List'!L64</f>
+        <f>'Point List'!L69</f>
         <v>BitAddress</v>
       </c>
       <c r="D67" t="s">
         <v>312</v>
       </c>
       <c r="E67" t="str">
-        <f>'Point List'!J64</f>
-        <v>012333</v>
+        <f>'Point List'!J69</f>
+        <v>012338</v>
       </c>
       <c r="K67" t="str">
-        <f t="shared" si="0"/>
-        <v>Bad RTD 1 Signal,,BitAddress,PLC1,012333,,</v>
+        <f t="shared" si="1"/>
+        <v>Critical Vessel Level,,BitAddress,PLC1,012338,,</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
-        <f>'Point List'!C65</f>
-        <v>Bad RTD 2 Signal</v>
+        <f>'Point List'!C70</f>
+        <v>Critical Conductivity</v>
       </c>
       <c r="C68" t="str">
-        <f>'Point List'!L65</f>
+        <f>'Point List'!L70</f>
         <v>BitAddress</v>
       </c>
       <c r="D68" t="s">
         <v>312</v>
       </c>
       <c r="E68" t="str">
-        <f>'Point List'!J65</f>
-        <v>012334</v>
+        <f>'Point List'!J70</f>
+        <v>012339</v>
       </c>
       <c r="K68" t="str">
-        <f t="shared" si="0"/>
-        <v>Bad RTD 2 Signal,,BitAddress,PLC1,012334,,</v>
+        <f t="shared" si="1"/>
+        <v>Critical Conductivity,,BitAddress,PLC1,012339,,</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
-        <f>'Point List'!C66</f>
-        <v>Bad RTD 3 Signal</v>
+        <f>'Point List'!C71</f>
+        <v>Level Sensor Malfunction</v>
       </c>
       <c r="C69" t="str">
-        <f>'Point List'!L66</f>
+        <f>'Point List'!L71</f>
         <v>BitAddress</v>
       </c>
       <c r="D69" t="s">
         <v>312</v>
       </c>
       <c r="E69" t="str">
-        <f>'Point List'!J66</f>
-        <v>012335</v>
+        <f>'Point List'!J71</f>
+        <v>012340</v>
       </c>
       <c r="K69" t="str">
-        <f t="shared" si="0"/>
-        <v>Bad RTD 3 Signal,,BitAddress,PLC1,012335,,</v>
+        <f t="shared" si="1"/>
+        <v>Level Sensor Malfunction,,BitAddress,PLC1,012340,,</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
-        <f>'Point List'!C67</f>
-        <v>Pump Cycle Alarm</v>
+        <f>'Point List'!C72</f>
+        <v>Conductivity Sensor Malfunction</v>
       </c>
       <c r="C70" t="str">
-        <f>'Point List'!L67</f>
+        <f>'Point List'!L72</f>
         <v>BitAddress</v>
       </c>
       <c r="D70" t="s">
         <v>312</v>
       </c>
       <c r="E70" t="str">
-        <f>'Point List'!J67</f>
-        <v>012336</v>
+        <f>'Point List'!J72</f>
+        <v>012341</v>
       </c>
       <c r="K70" t="str">
-        <f t="shared" si="0"/>
-        <v>Pump Cycle Alarm,,BitAddress,PLC1,012336,,</v>
+        <f t="shared" si="1"/>
+        <v>Conductivity Sensor Malfunction,,BitAddress,PLC1,012341,,</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
-        <f>'Point List'!C68</f>
-        <v>Critical Temperature</v>
+        <f>'Point List'!C73</f>
+        <v>Bingo Pumps</v>
       </c>
       <c r="C71" t="str">
-        <f>'Point List'!L68</f>
+        <f>'Point List'!L73</f>
         <v>BitAddress</v>
       </c>
       <c r="D71" t="s">
         <v>312</v>
       </c>
       <c r="E71" t="str">
-        <f>'Point List'!J68</f>
-        <v>012337</v>
+        <f>'Point List'!J73</f>
+        <v>012342</v>
       </c>
       <c r="K71" t="str">
-        <f t="shared" ref="K71:K79" si="1">_xlfn.CONCAT(A71,",",B71,",",C71,",",D71,",",E71,",",F71,",",G71)</f>
-        <v>Critical Temperature,,BitAddress,PLC1,012337,,</v>
+        <f t="shared" si="1"/>
+        <v>Bingo Pumps,,BitAddress,PLC1,012342,,</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
-        <f>'Point List'!C69</f>
-        <v>Critical Vessel Level</v>
+        <f>'Point List'!C74</f>
+        <v>Temperature Sensor Malfunction</v>
       </c>
       <c r="C72" t="str">
-        <f>'Point List'!L69</f>
+        <f>'Point List'!L74</f>
         <v>BitAddress</v>
       </c>
       <c r="D72" t="s">
         <v>312</v>
       </c>
       <c r="E72" t="str">
-        <f>'Point List'!J69</f>
-        <v>012338</v>
+        <f>'Point List'!J74</f>
+        <v>012343</v>
       </c>
       <c r="K72" t="str">
         <f t="shared" si="1"/>
-        <v>Critical Vessel Level,,BitAddress,PLC1,012338,,</v>
+        <v>Temperature Sensor Malfunction,,BitAddress,PLC1,012343,,</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="str">
-        <f>'Point List'!C70</f>
-        <v>Critical Conductivity</v>
+        <f>'Point List'!C75</f>
+        <v>Bad Valve Pos</v>
       </c>
       <c r="C73" t="str">
-        <f>'Point List'!L70</f>
+        <f>'Point List'!L75</f>
         <v>BitAddress</v>
       </c>
       <c r="D73" t="s">
         <v>312</v>
       </c>
       <c r="E73" t="str">
-        <f>'Point List'!J70</f>
-        <v>012339</v>
+        <f>'Point List'!J75</f>
+        <v>012344</v>
       </c>
       <c r="K73" t="str">
         <f t="shared" si="1"/>
-        <v>Critical Conductivity,,BitAddress,PLC1,012339,,</v>
+        <v>Bad Valve Pos,,BitAddress,PLC1,012344,,</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
-        <f>'Point List'!C71</f>
-        <v>Level Sensor Malfunction</v>
+        <f>'Point List'!C76</f>
+        <v>Master Fault Signal</v>
       </c>
       <c r="C74" t="str">
-        <f>'Point List'!L71</f>
+        <f>'Point List'!L76</f>
         <v>BitAddress</v>
       </c>
       <c r="D74" t="s">
         <v>312</v>
       </c>
       <c r="E74" t="str">
-        <f>'Point List'!J71</f>
-        <v>012340</v>
+        <f>'Point List'!J76</f>
+        <v>012345</v>
       </c>
       <c r="K74" t="str">
         <f t="shared" si="1"/>
-        <v>Level Sensor Malfunction,,BitAddress,PLC1,012340,,</v>
+        <v>Master Fault Signal,,BitAddress,PLC1,012345,,</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
-        <f>'Point List'!C72</f>
-        <v>Conductivity Sensor Malfunction</v>
+        <f>'Point List'!C98</f>
+        <v>Primary Pump Active</v>
       </c>
       <c r="C75" t="str">
-        <f>'Point List'!L72</f>
+        <f>'Point List'!L98</f>
         <v>BitAddress</v>
       </c>
       <c r="D75" t="s">
         <v>312</v>
       </c>
       <c r="E75" t="str">
-        <f>'Point List'!J72</f>
-        <v>012341</v>
+        <f>'Point List'!J98</f>
+        <v>012346</v>
       </c>
       <c r="K75" t="str">
-        <f t="shared" si="1"/>
-        <v>Conductivity Sensor Malfunction,,BitAddress,PLC1,012341,,</v>
+        <f>_xlfn.CONCAT(A75,",",B75,",",C75,",",D75,",",E75,",",F75,",",G75)</f>
+        <v>Primary Pump Active,,BitAddress,PLC1,012346,,</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
-        <f>'Point List'!C73</f>
-        <v>Bingo Pumps</v>
+        <f>'Point List'!C99</f>
+        <v>Secondary Pump  Active</v>
       </c>
       <c r="C76" t="str">
-        <f>'Point List'!L73</f>
+        <f>'Point List'!L99</f>
         <v>BitAddress</v>
       </c>
       <c r="D76" t="s">
         <v>312</v>
       </c>
       <c r="E76" t="str">
-        <f>'Point List'!J73</f>
-        <v>012342</v>
+        <f>'Point List'!J99</f>
+        <v>012347</v>
       </c>
       <c r="K76" t="str">
-        <f t="shared" si="1"/>
-        <v>Bingo Pumps,,BitAddress,PLC1,012342,,</v>
+        <f>_xlfn.CONCAT(A76,",",B76,",",C76,",",D76,",",E76,",",F76,",",G76)</f>
+        <v>Secondary Pump  Active,,BitAddress,PLC1,012347,,</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
-        <f>'Point List'!C74</f>
-        <v>Temperature Sensor Malfunction</v>
+        <f>'Point List'!C100</f>
+        <v>Simplex Mode Active</v>
       </c>
       <c r="C77" t="str">
-        <f>'Point List'!L74</f>
+        <f>'Point List'!L100</f>
         <v>BitAddress</v>
       </c>
       <c r="D77" t="s">
         <v>312</v>
       </c>
       <c r="E77" t="str">
-        <f>'Point List'!J74</f>
-        <v>012343</v>
+        <f>'Point List'!J100</f>
+        <v>012348</v>
       </c>
       <c r="K77" t="str">
-        <f t="shared" si="1"/>
-        <v>Temperature Sensor Malfunction,,BitAddress,PLC1,012343,,</v>
+        <f>_xlfn.CONCAT(A77,",",B77,",",C77,",",D77,",",E77,",",F77,",",G77)</f>
+        <v>Simplex Mode Active,,BitAddress,PLC1,012348,,</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
-        <f>'Point List'!C75</f>
-        <v>Bad Valve Pos</v>
+        <f>'Point List'!C101</f>
+        <v>Fan 1 Active</v>
       </c>
       <c r="C78" t="str">
-        <f>'Point List'!L75</f>
+        <f>'Point List'!L101</f>
         <v>BitAddress</v>
       </c>
       <c r="D78" t="s">
         <v>312</v>
       </c>
       <c r="E78" t="str">
-        <f>'Point List'!J75</f>
-        <v>012344</v>
+        <f>'Point List'!J101</f>
+        <v>012349</v>
       </c>
       <c r="K78" t="str">
-        <f t="shared" si="1"/>
-        <v>Bad Valve Pos,,BitAddress,PLC1,012344,,</v>
+        <f>_xlfn.CONCAT(A78,",",B78,",",C78,",",D78,",",E78,",",F78,",",G78)</f>
+        <v>Fan 1 Active,,BitAddress,PLC1,012349,,</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
-        <f>'Point List'!C76</f>
-        <v>Master Fault Signal</v>
+        <f>'Point List'!C102</f>
+        <v>Fan 2 Active</v>
       </c>
       <c r="C79" t="str">
-        <f>'Point List'!L76</f>
+        <f>'Point List'!L102</f>
         <v>BitAddress</v>
       </c>
       <c r="D79" t="s">
         <v>312</v>
       </c>
       <c r="E79" t="str">
-        <f>'Point List'!J76</f>
-        <v>012345</v>
+        <f>'Point List'!J102</f>
+        <v>012350</v>
       </c>
       <c r="K79" t="str">
-        <f t="shared" si="1"/>
-        <v>Master Fault Signal,,BitAddress,PLC1,012345,,</v>
+        <f>_xlfn.CONCAT(A79,",",B79,",",C79,",",D79,",",E79,",",F79,",",G79)</f>
+        <v>Fan 2 Active,,BitAddress,PLC1,012350,,</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
-        <f>'Point List'!C98</f>
-        <v>Primary Pump Active</v>
+        <f>'Point List'!C103</f>
+        <v>Enable Pump Cycling</v>
       </c>
       <c r="C80" t="str">
-        <f>'Point List'!L98</f>
+        <f>'Point List'!L103</f>
         <v>BitAddress</v>
       </c>
       <c r="D80" t="s">
         <v>312</v>
       </c>
       <c r="E80" t="str">
-        <f>'Point List'!J98</f>
-        <v>012346</v>
+        <f>'Point List'!J103</f>
+        <v>012351</v>
       </c>
       <c r="K80" t="str">
         <f>_xlfn.CONCAT(A80,",",B80,",",C80,",",D80,",",E80,",",F80,",",G80)</f>
-        <v>Primary Pump Active,,BitAddress,PLC1,012346,,</v>
+        <v>Enable Pump Cycling,,BitAddress,PLC1,012351,,</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
-        <f>'Point List'!C99</f>
-        <v>Secondary Pump  Active</v>
+        <f>'Point List'!C104</f>
+        <v>System Diagnostics</v>
       </c>
       <c r="C81" t="str">
-        <f>'Point List'!L99</f>
+        <f>'Point List'!L104</f>
         <v>BitAddress</v>
       </c>
       <c r="D81" t="s">
         <v>312</v>
       </c>
       <c r="E81" t="str">
-        <f>'Point List'!J99</f>
-        <v>012347</v>
+        <f>'Point List'!J104</f>
+        <v>012352</v>
       </c>
       <c r="K81" t="str">
         <f>_xlfn.CONCAT(A81,",",B81,",",C81,",",D81,",",E81,",",F81,",",G81)</f>
-        <v>Secondary Pump  Active,,BitAddress,PLC1,012347,,</v>
+        <v>System Diagnostics,,BitAddress,PLC1,012352,,</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
-        <f>'Point List'!C100</f>
-        <v>Simplex Mode Active</v>
+        <f>'Point List'!C105</f>
+        <v>Status Indicator Text</v>
       </c>
       <c r="C82" t="str">
-        <f>'Point List'!L100</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L105</f>
+        <v>WordAddress</v>
       </c>
       <c r="D82" t="s">
         <v>312</v>
       </c>
       <c r="E82" t="str">
-        <f>'Point List'!J100</f>
-        <v>012348</v>
+        <f>'Point List'!J105</f>
+        <v>012683</v>
       </c>
       <c r="K82" t="str">
         <f>_xlfn.CONCAT(A82,",",B82,",",C82,",",D82,",",E82,",",F82,",",G82)</f>
-        <v>Simplex Mode Active,,BitAddress,PLC1,012348,,</v>
+        <v>Status Indicator Text,,WordAddress,PLC1,012683,,</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A83" t="str">
-        <f>'Point List'!C101</f>
-        <v>Fan 1 Active</v>
-      </c>
-      <c r="C83" t="str">
-        <f>'Point List'!L101</f>
-        <v>BitAddress</v>
+      <c r="A83">
+        <f>'Point List'!C106</f>
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <f>'Point List'!L106</f>
+        <v>0</v>
       </c>
       <c r="D83" t="s">
         <v>312</v>
       </c>
-      <c r="E83" t="str">
-        <f>'Point List'!J101</f>
-        <v>012349</v>
-      </c>
-      <c r="K83" t="str">
-        <f>_xlfn.CONCAT(A83,",",B83,",",C83,",",D83,",",E83,",",F83,",",G83)</f>
-        <v>Fan 1 Active,,BitAddress,PLC1,012349,,</v>
+      <c r="E83">
+        <f>'Point List'!J106</f>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A84" t="str">
-        <f>'Point List'!C102</f>
-        <v>Fan 2 Active</v>
-      </c>
-      <c r="C84" t="str">
-        <f>'Point List'!L102</f>
-        <v>BitAddress</v>
+      <c r="A84">
+        <f>'Point List'!C107</f>
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <f>'Point List'!L107</f>
+        <v>0</v>
       </c>
       <c r="D84" t="s">
         <v>312</v>
       </c>
-      <c r="E84" t="str">
-        <f>'Point List'!J102</f>
-        <v>012350</v>
-      </c>
-      <c r="K84" t="str">
-        <f>_xlfn.CONCAT(A84,",",B84,",",C84,",",D84,",",E84,",",F84,",",G84)</f>
-        <v>Fan 2 Active,,BitAddress,PLC1,012350,,</v>
+      <c r="E84">
+        <f>'Point List'!J107</f>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A85" t="str">
-        <f>'Point List'!C103</f>
-        <v>Enable Pump Cycling</v>
-      </c>
-      <c r="C85" t="str">
-        <f>'Point List'!L103</f>
-        <v>BitAddress</v>
+      <c r="A85">
+        <f>'Point List'!C108</f>
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <f>'Point List'!L108</f>
+        <v>0</v>
       </c>
       <c r="D85" t="s">
         <v>312</v>
       </c>
-      <c r="E85" t="str">
-        <f>'Point List'!J103</f>
-        <v>012351</v>
-      </c>
-      <c r="K85" t="str">
-        <f>_xlfn.CONCAT(A85,",",B85,",",C85,",",D85,",",E85,",",F85,",",G85)</f>
-        <v>Enable Pump Cycling,,BitAddress,PLC1,012351,,</v>
+      <c r="E85">
+        <f>'Point List'!J108</f>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A86" t="str">
-        <f>'Point List'!C104</f>
-        <v>System Diagnostics</v>
-      </c>
-      <c r="C86" t="str">
-        <f>'Point List'!L104</f>
-        <v>BitAddress</v>
+      <c r="A86">
+        <f>'Point List'!C109</f>
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <f>'Point List'!L109</f>
+        <v>0</v>
       </c>
       <c r="D86" t="s">
         <v>312</v>
       </c>
-      <c r="E86" t="str">
-        <f>'Point List'!J104</f>
-        <v>012352</v>
-      </c>
-      <c r="K86" t="str">
-        <f>_xlfn.CONCAT(A86,",",B86,",",C86,",",D86,",",E86,",",F86,",",G86)</f>
-        <v>System Diagnostics,,BitAddress,PLC1,012352,,</v>
+      <c r="E86">
+        <f>'Point List'!J109</f>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A87" t="str">
-        <f>'Point List'!C105</f>
-        <v>Status Indicator Text</v>
-      </c>
-      <c r="C87" t="str">
-        <f>'Point List'!L105</f>
-        <v>WordAddress</v>
+      <c r="A87">
+        <f>'Point List'!C110</f>
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <f>'Point List'!L110</f>
+        <v>0</v>
       </c>
       <c r="D87" t="s">
         <v>312</v>
       </c>
-      <c r="E87" t="str">
-        <f>'Point List'!J105</f>
-        <v>012683</v>
-      </c>
-      <c r="K87" t="str">
-        <f>_xlfn.CONCAT(A87,",",B87,",",C87,",",D87,",",E87,",",F87,",",G87)</f>
-        <v>Status Indicator Text,,WordAddress,PLC1,012683,,</v>
+      <c r="E87">
+        <f>'Point List'!J110</f>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
-        <f>'Point List'!C106</f>
+        <f>'Point List'!C111</f>
         <v>0</v>
       </c>
       <c r="C88">
-        <f>'Point List'!L106</f>
+        <f>'Point List'!L111</f>
         <v>0</v>
       </c>
       <c r="D88" t="s">
         <v>312</v>
       </c>
       <c r="E88">
-        <f>'Point List'!J106</f>
+        <f>'Point List'!J111</f>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
-        <f>'Point List'!C107</f>
+        <f>'Point List'!C112</f>
         <v>0</v>
       </c>
       <c r="C89">
-        <f>'Point List'!L107</f>
+        <f>'Point List'!L112</f>
         <v>0</v>
       </c>
       <c r="D89" t="s">
         <v>312</v>
       </c>
       <c r="E89">
-        <f>'Point List'!J107</f>
+        <f>'Point List'!J112</f>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
-        <f>'Point List'!C108</f>
+        <f>'Point List'!C113</f>
         <v>0</v>
       </c>
       <c r="C90">
-        <f>'Point List'!L108</f>
+        <f>'Point List'!L113</f>
         <v>0</v>
       </c>
       <c r="D90" t="s">
         <v>312</v>
       </c>
       <c r="E90">
-        <f>'Point List'!J108</f>
+        <f>'Point List'!J113</f>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
-        <f>'Point List'!C109</f>
+        <f>'Point List'!C114</f>
         <v>0</v>
       </c>
       <c r="C91">
-        <f>'Point List'!L109</f>
+        <f>'Point List'!L114</f>
         <v>0</v>
       </c>
       <c r="D91" t="s">
         <v>312</v>
       </c>
       <c r="E91">
-        <f>'Point List'!J109</f>
+        <f>'Point List'!J114</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
-        <f>'Point List'!C110</f>
+        <f>'Point List'!C115</f>
         <v>0</v>
       </c>
       <c r="C92">
-        <f>'Point List'!L110</f>
+        <f>'Point List'!L115</f>
         <v>0</v>
       </c>
       <c r="D92" t="s">
         <v>312</v>
       </c>
       <c r="E92">
-        <f>'Point List'!J110</f>
+        <f>'Point List'!J115</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
-        <f>'Point List'!C111</f>
+        <f>'Point List'!C116</f>
         <v>0</v>
       </c>
       <c r="C93">
-        <f>'Point List'!L111</f>
+        <f>'Point List'!L116</f>
         <v>0</v>
       </c>
       <c r="D93" t="s">
         <v>312</v>
       </c>
       <c r="E93">
-        <f>'Point List'!J111</f>
+        <f>'Point List'!J116</f>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
-        <f>'Point List'!C112</f>
+        <f>'Point List'!C117</f>
         <v>0</v>
       </c>
       <c r="C94">
-        <f>'Point List'!L112</f>
+        <f>'Point List'!L117</f>
         <v>0</v>
       </c>
       <c r="D94" t="s">
         <v>312</v>
       </c>
       <c r="E94">
-        <f>'Point List'!J112</f>
+        <f>'Point List'!J117</f>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
-        <f>'Point List'!C113</f>
+        <f>'Point List'!C118</f>
         <v>0</v>
       </c>
       <c r="C95">
-        <f>'Point List'!L113</f>
+        <f>'Point List'!L118</f>
         <v>0</v>
       </c>
       <c r="D95" t="s">
         <v>312</v>
       </c>
       <c r="E95">
-        <f>'Point List'!J113</f>
+        <f>'Point List'!J118</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
-        <f>'Point List'!C114</f>
+        <f>'Point List'!C119</f>
         <v>0</v>
       </c>
       <c r="C96">
-        <f>'Point List'!L114</f>
+        <f>'Point List'!L119</f>
         <v>0</v>
       </c>
       <c r="D96" t="s">
         <v>312</v>
       </c>
       <c r="E96">
-        <f>'Point List'!J114</f>
+        <f>'Point List'!J119</f>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
-        <f>'Point List'!C115</f>
+        <f>'Point List'!C120</f>
         <v>0</v>
       </c>
       <c r="C97">
-        <f>'Point List'!L115</f>
+        <f>'Point List'!L120</f>
         <v>0</v>
       </c>
       <c r="D97" t="s">
         <v>312</v>
       </c>
       <c r="E97">
-        <f>'Point List'!J115</f>
+        <f>'Point List'!J120</f>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
-        <f>'Point List'!C116</f>
+        <f>'Point List'!C121</f>
         <v>0</v>
       </c>
       <c r="C98">
-        <f>'Point List'!L116</f>
+        <f>'Point List'!L121</f>
         <v>0</v>
       </c>
       <c r="D98" t="s">
         <v>312</v>
       </c>
       <c r="E98">
-        <f>'Point List'!J116</f>
+        <f>'Point List'!J121</f>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
-        <f>'Point List'!C117</f>
+        <f>'Point List'!C122</f>
         <v>0</v>
       </c>
       <c r="C99">
-        <f>'Point List'!L117</f>
+        <f>'Point List'!L122</f>
         <v>0</v>
       </c>
       <c r="D99" t="s">
         <v>312</v>
       </c>
       <c r="E99">
-        <f>'Point List'!J117</f>
+        <f>'Point List'!J122</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
-        <f>'Point List'!C118</f>
+        <f>'Point List'!C123</f>
         <v>0</v>
       </c>
       <c r="C100">
-        <f>'Point List'!L118</f>
+        <f>'Point List'!L123</f>
         <v>0</v>
       </c>
       <c r="D100" t="s">
         <v>312</v>
       </c>
       <c r="E100">
-        <f>'Point List'!J118</f>
+        <f>'Point List'!J123</f>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
-        <f>'Point List'!C119</f>
+        <f>'Point List'!C124</f>
         <v>0</v>
       </c>
       <c r="C101">
-        <f>'Point List'!L119</f>
+        <f>'Point List'!L124</f>
         <v>0</v>
       </c>
       <c r="D101" t="s">
         <v>312</v>
       </c>
       <c r="E101">
-        <f>'Point List'!J119</f>
+        <f>'Point List'!J124</f>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
-        <f>'Point List'!C120</f>
+        <f>'Point List'!C125</f>
         <v>0</v>
       </c>
       <c r="C102">
-        <f>'Point List'!L120</f>
+        <f>'Point List'!L125</f>
         <v>0</v>
       </c>
       <c r="D102" t="s">
         <v>312</v>
       </c>
       <c r="E102">
-        <f>'Point List'!J120</f>
+        <f>'Point List'!J125</f>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
-        <f>'Point List'!C121</f>
+        <f>'Point List'!C126</f>
         <v>0</v>
       </c>
       <c r="C103">
-        <f>'Point List'!L121</f>
+        <f>'Point List'!L126</f>
         <v>0</v>
       </c>
       <c r="D103" t="s">
         <v>312</v>
       </c>
       <c r="E103">
-        <f>'Point List'!J121</f>
+        <f>'Point List'!J126</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
-        <f>'Point List'!C122</f>
+        <f>'Point List'!C127</f>
         <v>0</v>
       </c>
       <c r="C104">
-        <f>'Point List'!L122</f>
+        <f>'Point List'!L127</f>
         <v>0</v>
       </c>
       <c r="D104" t="s">
         <v>312</v>
       </c>
       <c r="E104">
-        <f>'Point List'!J122</f>
+        <f>'Point List'!J127</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
-        <f>'Point List'!C123</f>
+        <f>'Point List'!C128</f>
         <v>0</v>
       </c>
       <c r="C105">
-        <f>'Point List'!L123</f>
+        <f>'Point List'!L128</f>
         <v>0</v>
       </c>
       <c r="D105" t="s">
         <v>312</v>
       </c>
       <c r="E105">
-        <f>'Point List'!J123</f>
+        <f>'Point List'!J128</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
-        <f>'Point List'!C124</f>
+        <f>'Point List'!C129</f>
         <v>0</v>
       </c>
       <c r="C106">
-        <f>'Point List'!L124</f>
+        <f>'Point List'!L129</f>
         <v>0</v>
       </c>
       <c r="D106" t="s">
         <v>312</v>
       </c>
       <c r="E106">
-        <f>'Point List'!J124</f>
+        <f>'Point List'!J129</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
-        <f>'Point List'!C125</f>
+        <f>'Point List'!C130</f>
         <v>0</v>
       </c>
       <c r="C107">
-        <f>'Point List'!L125</f>
+        <f>'Point List'!L130</f>
         <v>0</v>
       </c>
       <c r="D107" t="s">
         <v>312</v>
       </c>
       <c r="E107">
-        <f>'Point List'!J125</f>
+        <f>'Point List'!J130</f>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
-        <f>'Point List'!C126</f>
+        <f>'Point List'!C131</f>
         <v>0</v>
       </c>
       <c r="C108">
-        <f>'Point List'!L126</f>
+        <f>'Point List'!L131</f>
         <v>0</v>
       </c>
       <c r="D108" t="s">
         <v>312</v>
       </c>
       <c r="E108">
-        <f>'Point List'!J126</f>
+        <f>'Point List'!J131</f>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
-        <f>'Point List'!C127</f>
+        <f>'Point List'!C132</f>
         <v>0</v>
       </c>
       <c r="C109">
-        <f>'Point List'!L127</f>
+        <f>'Point List'!L132</f>
         <v>0</v>
       </c>
       <c r="D109" t="s">
         <v>312</v>
       </c>
       <c r="E109">
-        <f>'Point List'!J127</f>
+        <f>'Point List'!J132</f>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
-        <f>'Point List'!C128</f>
+        <f>'Point List'!C133</f>
         <v>0</v>
       </c>
       <c r="C110">
-        <f>'Point List'!L128</f>
+        <f>'Point List'!L133</f>
         <v>0</v>
       </c>
       <c r="D110" t="s">
         <v>312</v>
       </c>
       <c r="E110">
-        <f>'Point List'!J128</f>
+        <f>'Point List'!J133</f>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
-        <f>'Point List'!C129</f>
+        <f>'Point List'!C134</f>
         <v>0</v>
       </c>
       <c r="C111">
-        <f>'Point List'!L129</f>
+        <f>'Point List'!L134</f>
         <v>0</v>
       </c>
       <c r="D111" t="s">
         <v>312</v>
       </c>
       <c r="E111">
-        <f>'Point List'!J129</f>
+        <f>'Point List'!J134</f>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
-        <f>'Point List'!C130</f>
+        <f>'Point List'!C135</f>
         <v>0</v>
       </c>
       <c r="C112">
-        <f>'Point List'!L130</f>
+        <f>'Point List'!L135</f>
         <v>0</v>
       </c>
       <c r="D112" t="s">
         <v>312</v>
       </c>
       <c r="E112">
-        <f>'Point List'!J130</f>
+        <f>'Point List'!J135</f>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
-        <f>'Point List'!C131</f>
+        <f>'Point List'!C136</f>
         <v>0</v>
       </c>
       <c r="C113">
-        <f>'Point List'!L131</f>
+        <f>'Point List'!L136</f>
         <v>0</v>
       </c>
       <c r="D113" t="s">
         <v>312</v>
       </c>
       <c r="E113">
-        <f>'Point List'!J131</f>
+        <f>'Point List'!J136</f>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
-        <f>'Point List'!C132</f>
+        <f>'Point List'!C137</f>
         <v>0</v>
       </c>
       <c r="C114">
-        <f>'Point List'!L132</f>
+        <f>'Point List'!L137</f>
         <v>0</v>
       </c>
       <c r="D114" t="s">
         <v>312</v>
       </c>
       <c r="E114">
-        <f>'Point List'!J132</f>
+        <f>'Point List'!J137</f>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
-        <f>'Point List'!C133</f>
+        <f>'Point List'!C138</f>
         <v>0</v>
       </c>
       <c r="C115">
-        <f>'Point List'!L133</f>
+        <f>'Point List'!L138</f>
         <v>0</v>
       </c>
       <c r="D115" t="s">
         <v>312</v>
       </c>
       <c r="E115">
-        <f>'Point List'!J133</f>
+        <f>'Point List'!J138</f>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
-        <f>'Point List'!C134</f>
+        <f>'Point List'!C139</f>
         <v>0</v>
       </c>
       <c r="C116">
-        <f>'Point List'!L134</f>
+        <f>'Point List'!L139</f>
         <v>0</v>
       </c>
       <c r="D116" t="s">
         <v>312</v>
       </c>
       <c r="E116">
-        <f>'Point List'!J134</f>
+        <f>'Point List'!J139</f>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
-        <f>'Point List'!C135</f>
+        <f>'Point List'!C140</f>
         <v>0</v>
       </c>
       <c r="C117">
-        <f>'Point List'!L135</f>
+        <f>'Point List'!L140</f>
         <v>0</v>
       </c>
       <c r="D117" t="s">
         <v>312</v>
       </c>
       <c r="E117">
-        <f>'Point List'!J135</f>
+        <f>'Point List'!J140</f>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
-        <f>'Point List'!C136</f>
+        <f>'Point List'!C141</f>
         <v>0</v>
       </c>
       <c r="C118">
-        <f>'Point List'!L136</f>
+        <f>'Point List'!L141</f>
         <v>0</v>
       </c>
       <c r="D118" t="s">
         <v>312</v>
       </c>
       <c r="E118">
-        <f>'Point List'!J136</f>
+        <f>'Point List'!J141</f>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
-        <f>'Point List'!C137</f>
+        <f>'Point List'!C142</f>
         <v>0</v>
       </c>
       <c r="C119">
-        <f>'Point List'!L137</f>
+        <f>'Point List'!L142</f>
         <v>0</v>
       </c>
       <c r="D119" t="s">
         <v>312</v>
       </c>
       <c r="E119">
-        <f>'Point List'!J137</f>
+        <f>'Point List'!J142</f>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
-        <f>'Point List'!C138</f>
+        <f>'Point List'!C143</f>
         <v>0</v>
       </c>
       <c r="C120">
-        <f>'Point List'!L138</f>
+        <f>'Point List'!L143</f>
         <v>0</v>
       </c>
       <c r="D120" t="s">
         <v>312</v>
       </c>
       <c r="E120">
-        <f>'Point List'!J138</f>
+        <f>'Point List'!J143</f>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
-        <f>'Point List'!C139</f>
+        <f>'Point List'!C144</f>
         <v>0</v>
       </c>
       <c r="C121">
-        <f>'Point List'!L139</f>
+        <f>'Point List'!L144</f>
         <v>0</v>
       </c>
       <c r="D121" t="s">
         <v>312</v>
       </c>
       <c r="E121">
-        <f>'Point List'!J139</f>
+        <f>'Point List'!J144</f>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
-        <f>'Point List'!C140</f>
+        <f>'Point List'!C145</f>
         <v>0</v>
       </c>
       <c r="C122">
-        <f>'Point List'!L140</f>
+        <f>'Point List'!L145</f>
         <v>0</v>
       </c>
       <c r="D122" t="s">
         <v>312</v>
       </c>
       <c r="E122">
-        <f>'Point List'!J140</f>
+        <f>'Point List'!J145</f>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
-        <f>'Point List'!C141</f>
+        <f>'Point List'!C146</f>
         <v>0</v>
       </c>
       <c r="C123">
-        <f>'Point List'!L141</f>
+        <f>'Point List'!L146</f>
         <v>0</v>
       </c>
       <c r="D123" t="s">
         <v>312</v>
       </c>
       <c r="E123">
-        <f>'Point List'!J141</f>
+        <f>'Point List'!J146</f>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
-        <f>'Point List'!C142</f>
+        <f>'Point List'!C147</f>
         <v>0</v>
       </c>
       <c r="C124">
-        <f>'Point List'!L142</f>
+        <f>'Point List'!L147</f>
         <v>0</v>
       </c>
       <c r="D124" t="s">
         <v>312</v>
       </c>
       <c r="E124">
-        <f>'Point List'!J142</f>
+        <f>'Point List'!J147</f>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
-        <f>'Point List'!C143</f>
+        <f>'Point List'!C148</f>
         <v>0</v>
       </c>
       <c r="C125">
-        <f>'Point List'!L143</f>
+        <f>'Point List'!L148</f>
         <v>0</v>
       </c>
       <c r="D125" t="s">
         <v>312</v>
       </c>
       <c r="E125">
-        <f>'Point List'!J143</f>
+        <f>'Point List'!J148</f>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
-        <f>'Point List'!C144</f>
+        <f>'Point List'!C149</f>
         <v>0</v>
       </c>
       <c r="C126">
-        <f>'Point List'!L144</f>
+        <f>'Point List'!L149</f>
         <v>0</v>
       </c>
       <c r="D126" t="s">
         <v>312</v>
       </c>
       <c r="E126">
-        <f>'Point List'!J144</f>
+        <f>'Point List'!J149</f>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
-        <f>'Point List'!C145</f>
+        <f>'Point List'!C150</f>
         <v>0</v>
       </c>
       <c r="C127">
-        <f>'Point List'!L145</f>
+        <f>'Point List'!L150</f>
         <v>0</v>
       </c>
       <c r="D127" t="s">
         <v>312</v>
       </c>
       <c r="E127">
-        <f>'Point List'!J145</f>
+        <f>'Point List'!J150</f>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
-        <f>'Point List'!C146</f>
+        <f>'Point List'!C151</f>
         <v>0</v>
       </c>
       <c r="C128">
-        <f>'Point List'!L146</f>
+        <f>'Point List'!L151</f>
         <v>0</v>
       </c>
       <c r="D128" t="s">
         <v>312</v>
       </c>
       <c r="E128">
-        <f>'Point List'!J146</f>
+        <f>'Point List'!J151</f>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
-        <f>'Point List'!C147</f>
+        <f>'Point List'!C152</f>
         <v>0</v>
       </c>
       <c r="C129">
-        <f>'Point List'!L147</f>
+        <f>'Point List'!L152</f>
         <v>0</v>
       </c>
       <c r="D129" t="s">
         <v>312</v>
       </c>
       <c r="E129">
-        <f>'Point List'!J147</f>
+        <f>'Point List'!J152</f>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
-        <f>'Point List'!C148</f>
+        <f>'Point List'!C153</f>
         <v>0</v>
       </c>
       <c r="C130">
-        <f>'Point List'!L148</f>
+        <f>'Point List'!L153</f>
         <v>0</v>
       </c>
       <c r="D130" t="s">
         <v>312</v>
       </c>
       <c r="E130">
-        <f>'Point List'!J148</f>
+        <f>'Point List'!J153</f>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
-        <f>'Point List'!C149</f>
+        <f>'Point List'!C154</f>
         <v>0</v>
       </c>
       <c r="C131">
-        <f>'Point List'!L149</f>
+        <f>'Point List'!L154</f>
         <v>0</v>
       </c>
       <c r="D131" t="s">
         <v>312</v>
       </c>
       <c r="E131">
-        <f>'Point List'!J149</f>
+        <f>'Point List'!J154</f>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
-        <f>'Point List'!C150</f>
+        <f>'Point List'!C155</f>
         <v>0</v>
       </c>
       <c r="C132">
-        <f>'Point List'!L150</f>
+        <f>'Point List'!L155</f>
         <v>0</v>
       </c>
       <c r="D132" t="s">
         <v>312</v>
       </c>
       <c r="E132">
-        <f>'Point List'!J150</f>
+        <f>'Point List'!J155</f>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
-        <f>'Point List'!C151</f>
+        <f>'Point List'!C156</f>
         <v>0</v>
       </c>
       <c r="C133">
-        <f>'Point List'!L151</f>
+        <f>'Point List'!L156</f>
         <v>0</v>
       </c>
       <c r="D133" t="s">
         <v>312</v>
       </c>
       <c r="E133">
-        <f>'Point List'!J151</f>
+        <f>'Point List'!J156</f>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
-        <f>'Point List'!C152</f>
+        <f>'Point List'!C157</f>
         <v>0</v>
       </c>
       <c r="C134">
-        <f>'Point List'!L152</f>
+        <f>'Point List'!L157</f>
         <v>0</v>
       </c>
       <c r="D134" t="s">
         <v>312</v>
       </c>
       <c r="E134">
-        <f>'Point List'!J152</f>
+        <f>'Point List'!J157</f>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
-        <f>'Point List'!C153</f>
+        <f>'Point List'!C158</f>
         <v>0</v>
       </c>
       <c r="C135">
-        <f>'Point List'!L153</f>
+        <f>'Point List'!L158</f>
         <v>0</v>
       </c>
       <c r="D135" t="s">
         <v>312</v>
       </c>
       <c r="E135">
-        <f>'Point List'!J153</f>
+        <f>'Point List'!J158</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
-        <f>'Point List'!C154</f>
+        <f>'Point List'!C159</f>
         <v>0</v>
       </c>
       <c r="C136">
-        <f>'Point List'!L154</f>
+        <f>'Point List'!L159</f>
         <v>0</v>
       </c>
       <c r="D136" t="s">
         <v>312</v>
       </c>
       <c r="E136">
-        <f>'Point List'!J154</f>
+        <f>'Point List'!J159</f>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
-        <f>'Point List'!C155</f>
+        <f>'Point List'!C160</f>
         <v>0</v>
       </c>
       <c r="C137">
-        <f>'Point List'!L155</f>
+        <f>'Point List'!L160</f>
         <v>0</v>
       </c>
       <c r="D137" t="s">
         <v>312</v>
       </c>
       <c r="E137">
-        <f>'Point List'!J155</f>
+        <f>'Point List'!J160</f>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
-        <f>'Point List'!C156</f>
+        <f>'Point List'!C161</f>
         <v>0</v>
       </c>
       <c r="C138">
-        <f>'Point List'!L156</f>
+        <f>'Point List'!L161</f>
         <v>0</v>
       </c>
       <c r="D138" t="s">
         <v>312</v>
       </c>
       <c r="E138">
-        <f>'Point List'!J156</f>
+        <f>'Point List'!J161</f>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
-        <f>'Point List'!C157</f>
+        <f>'Point List'!C162</f>
         <v>0</v>
       </c>
       <c r="C139">
-        <f>'Point List'!L157</f>
+        <f>'Point List'!L162</f>
         <v>0</v>
       </c>
       <c r="D139" t="s">
         <v>312</v>
       </c>
       <c r="E139">
-        <f>'Point List'!J157</f>
+        <f>'Point List'!J162</f>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
-        <f>'Point List'!C158</f>
+        <f>'Point List'!C163</f>
         <v>0</v>
       </c>
       <c r="C140">
-        <f>'Point List'!L158</f>
+        <f>'Point List'!L163</f>
         <v>0</v>
       </c>
       <c r="D140" t="s">
         <v>312</v>
       </c>
       <c r="E140">
-        <f>'Point List'!J158</f>
+        <f>'Point List'!J163</f>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
-        <f>'Point List'!C159</f>
+        <f>'Point List'!C164</f>
         <v>0</v>
       </c>
       <c r="C141">
-        <f>'Point List'!L159</f>
+        <f>'Point List'!L164</f>
         <v>0</v>
       </c>
       <c r="D141" t="s">
         <v>312</v>
       </c>
       <c r="E141">
-        <f>'Point List'!J159</f>
+        <f>'Point List'!J164</f>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
-        <f>'Point List'!C160</f>
+        <f>'Point List'!C165</f>
         <v>0</v>
       </c>
       <c r="C142">
-        <f>'Point List'!L160</f>
+        <f>'Point List'!L165</f>
         <v>0</v>
       </c>
       <c r="D142" t="s">
         <v>312</v>
       </c>
       <c r="E142">
-        <f>'Point List'!J160</f>
+        <f>'Point List'!J165</f>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
-        <f>'Point List'!C161</f>
+        <f>'Point List'!C166</f>
         <v>0</v>
       </c>
       <c r="C143">
-        <f>'Point List'!L161</f>
+        <f>'Point List'!L166</f>
         <v>0</v>
       </c>
       <c r="D143" t="s">
         <v>312</v>
       </c>
       <c r="E143">
-        <f>'Point List'!J161</f>
+        <f>'Point List'!J166</f>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
-        <f>'Point List'!C162</f>
+        <f>'Point List'!C167</f>
         <v>0</v>
       </c>
       <c r="C144">
-        <f>'Point List'!L162</f>
+        <f>'Point List'!L167</f>
         <v>0</v>
       </c>
       <c r="D144" t="s">
         <v>312</v>
       </c>
       <c r="E144">
-        <f>'Point List'!J162</f>
+        <f>'Point List'!J167</f>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
-        <f>'Point List'!C163</f>
+        <f>'Point List'!C168</f>
         <v>0</v>
       </c>
       <c r="C145">
-        <f>'Point List'!L163</f>
+        <f>'Point List'!L168</f>
         <v>0</v>
       </c>
       <c r="D145" t="s">
         <v>312</v>
       </c>
       <c r="E145">
-        <f>'Point List'!J163</f>
+        <f>'Point List'!J168</f>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
-        <f>'Point List'!C164</f>
+        <f>'Point List'!C169</f>
         <v>0</v>
       </c>
       <c r="C146">
-        <f>'Point List'!L164</f>
+        <f>'Point List'!L169</f>
         <v>0</v>
       </c>
       <c r="D146" t="s">
         <v>312</v>
       </c>
       <c r="E146">
-        <f>'Point List'!J164</f>
+        <f>'Point List'!J169</f>
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
-        <f>'Point List'!C165</f>
+        <f>'Point List'!C170</f>
         <v>0</v>
       </c>
       <c r="C147">
-        <f>'Point List'!L165</f>
+        <f>'Point List'!L170</f>
         <v>0</v>
       </c>
       <c r="D147" t="s">
         <v>312</v>
       </c>
       <c r="E147">
-        <f>'Point List'!J165</f>
+        <f>'Point List'!J170</f>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
-        <f>'Point List'!C166</f>
+        <f>'Point List'!C171</f>
         <v>0</v>
       </c>
       <c r="C148">
-        <f>'Point List'!L166</f>
+        <f>'Point List'!L171</f>
         <v>0</v>
       </c>
       <c r="D148" t="s">
         <v>312</v>
       </c>
       <c r="E148">
-        <f>'Point List'!J166</f>
+        <f>'Point List'!J171</f>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
-        <f>'Point List'!C167</f>
+        <f>'Point List'!C172</f>
         <v>0</v>
       </c>
       <c r="C149">
-        <f>'Point List'!L167</f>
+        <f>'Point List'!L172</f>
         <v>0</v>
       </c>
       <c r="D149" t="s">
         <v>312</v>
       </c>
       <c r="E149">
-        <f>'Point List'!J167</f>
+        <f>'Point List'!J172</f>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
-        <f>'Point List'!C168</f>
+        <f>'Point List'!C173</f>
         <v>0</v>
       </c>
       <c r="C150">
-        <f>'Point List'!L168</f>
+        <f>'Point List'!L173</f>
         <v>0</v>
       </c>
       <c r="D150" t="s">
         <v>312</v>
       </c>
       <c r="E150">
-        <f>'Point List'!J168</f>
+        <f>'Point List'!J173</f>
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
-        <f>'Point List'!C169</f>
+        <f>'Point List'!C174</f>
         <v>0</v>
       </c>
       <c r="C151">
-        <f>'Point List'!L169</f>
+        <f>'Point List'!L174</f>
         <v>0</v>
       </c>
       <c r="D151" t="s">
         <v>312</v>
       </c>
       <c r="E151">
-        <f>'Point List'!J169</f>
+        <f>'Point List'!J174</f>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
-        <f>'Point List'!C170</f>
+        <f>'Point List'!C175</f>
         <v>0</v>
       </c>
       <c r="C152">
-        <f>'Point List'!L170</f>
+        <f>'Point List'!L175</f>
         <v>0</v>
       </c>
       <c r="D152" t="s">
         <v>312</v>
       </c>
       <c r="E152">
-        <f>'Point List'!J170</f>
+        <f>'Point List'!J175</f>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
-        <f>'Point List'!C171</f>
+        <f>'Point List'!C176</f>
         <v>0</v>
       </c>
       <c r="C153">
-        <f>'Point List'!L171</f>
+        <f>'Point List'!L176</f>
         <v>0</v>
       </c>
       <c r="D153" t="s">
         <v>312</v>
       </c>
       <c r="E153">
-        <f>'Point List'!J171</f>
+        <f>'Point List'!J176</f>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
-        <f>'Point List'!C172</f>
+        <f>'Point List'!C177</f>
         <v>0</v>
       </c>
       <c r="C154">
-        <f>'Point List'!L172</f>
+        <f>'Point List'!L177</f>
         <v>0</v>
       </c>
       <c r="D154" t="s">
         <v>312</v>
       </c>
       <c r="E154">
-        <f>'Point List'!J172</f>
+        <f>'Point List'!J177</f>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
-        <f>'Point List'!C173</f>
+        <f>'Point List'!C178</f>
         <v>0</v>
       </c>
       <c r="C155">
-        <f>'Point List'!L173</f>
+        <f>'Point List'!L178</f>
         <v>0</v>
       </c>
       <c r="D155" t="s">
         <v>312</v>
       </c>
       <c r="E155">
-        <f>'Point List'!J173</f>
+        <f>'Point List'!J178</f>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
-        <f>'Point List'!C174</f>
+        <f>'Point List'!C179</f>
         <v>0</v>
       </c>
       <c r="C156">
-        <f>'Point List'!L174</f>
+        <f>'Point List'!L179</f>
         <v>0</v>
       </c>
       <c r="D156" t="s">
         <v>312</v>
       </c>
       <c r="E156">
-        <f>'Point List'!J174</f>
+        <f>'Point List'!J179</f>
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
-        <f>'Point List'!C175</f>
+        <f>'Point List'!C180</f>
         <v>0</v>
       </c>
       <c r="C157">
-        <f>'Point List'!L175</f>
+        <f>'Point List'!L180</f>
         <v>0</v>
       </c>
       <c r="D157" t="s">
         <v>312</v>
       </c>
       <c r="E157">
-        <f>'Point List'!J175</f>
+        <f>'Point List'!J180</f>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
-        <f>'Point List'!C176</f>
+        <f>'Point List'!C181</f>
         <v>0</v>
       </c>
       <c r="C158">
-        <f>'Point List'!L176</f>
+        <f>'Point List'!L181</f>
         <v>0</v>
       </c>
       <c r="D158" t="s">
         <v>312</v>
       </c>
       <c r="E158">
-        <f>'Point List'!J176</f>
+        <f>'Point List'!J181</f>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
-        <f>'Point List'!C177</f>
+        <f>'Point List'!C182</f>
         <v>0</v>
       </c>
       <c r="C159">
-        <f>'Point List'!L177</f>
+        <f>'Point List'!L182</f>
         <v>0</v>
       </c>
       <c r="D159" t="s">
         <v>312</v>
       </c>
       <c r="E159">
-        <f>'Point List'!J177</f>
+        <f>'Point List'!J182</f>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
-        <f>'Point List'!C178</f>
+        <f>'Point List'!C183</f>
         <v>0</v>
       </c>
       <c r="C160">
-        <f>'Point List'!L178</f>
+        <f>'Point List'!L183</f>
         <v>0</v>
       </c>
       <c r="D160" t="s">
         <v>312</v>
       </c>
       <c r="E160">
-        <f>'Point List'!J178</f>
+        <f>'Point List'!J183</f>
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
-        <f>'Point List'!C179</f>
+        <f>'Point List'!C184</f>
         <v>0</v>
       </c>
       <c r="C161">
-        <f>'Point List'!L179</f>
+        <f>'Point List'!L184</f>
         <v>0</v>
       </c>
       <c r="D161" t="s">
         <v>312</v>
       </c>
       <c r="E161">
-        <f>'Point List'!J179</f>
+        <f>'Point List'!J184</f>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
-        <f>'Point List'!C180</f>
+        <f>'Point List'!C185</f>
         <v>0</v>
       </c>
       <c r="C162">
-        <f>'Point List'!L180</f>
+        <f>'Point List'!L185</f>
         <v>0</v>
       </c>
       <c r="D162" t="s">
         <v>312</v>
       </c>
       <c r="E162">
-        <f>'Point List'!J180</f>
+        <f>'Point List'!J185</f>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
-        <f>'Point List'!C181</f>
+        <f>'Point List'!C186</f>
         <v>0</v>
       </c>
       <c r="C163">
-        <f>'Point List'!L181</f>
+        <f>'Point List'!L186</f>
         <v>0</v>
       </c>
       <c r="D163" t="s">
         <v>312</v>
       </c>
       <c r="E163">
-        <f>'Point List'!J181</f>
+        <f>'Point List'!J186</f>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164">
-        <f>'Point List'!C182</f>
+        <f>'Point List'!C187</f>
         <v>0</v>
       </c>
       <c r="C164">
-        <f>'Point List'!L182</f>
+        <f>'Point List'!L187</f>
         <v>0</v>
       </c>
       <c r="D164" t="s">
         <v>312</v>
       </c>
       <c r="E164">
-        <f>'Point List'!J182</f>
+        <f>'Point List'!J187</f>
         <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165">
-        <f>'Point List'!C183</f>
+        <f>'Point List'!C188</f>
         <v>0</v>
       </c>
       <c r="C165">
-        <f>'Point List'!L183</f>
+        <f>'Point List'!L188</f>
         <v>0</v>
       </c>
       <c r="D165" t="s">
         <v>312</v>
       </c>
       <c r="E165">
-        <f>'Point List'!J183</f>
+        <f>'Point List'!J188</f>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166">
-        <f>'Point List'!C184</f>
+        <f>'Point List'!C189</f>
         <v>0</v>
       </c>
       <c r="C166">
-        <f>'Point List'!L184</f>
+        <f>'Point List'!L189</f>
         <v>0</v>
       </c>
       <c r="D166" t="s">
         <v>312</v>
       </c>
       <c r="E166">
-        <f>'Point List'!J184</f>
+        <f>'Point List'!J189</f>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167">
-        <f>'Point List'!C185</f>
+        <f>'Point List'!C190</f>
         <v>0</v>
       </c>
       <c r="C167">
-        <f>'Point List'!L185</f>
+        <f>'Point List'!L190</f>
         <v>0</v>
       </c>
       <c r="D167" t="s">
         <v>312</v>
       </c>
       <c r="E167">
-        <f>'Point List'!J185</f>
+        <f>'Point List'!J190</f>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168">
-        <f>'Point List'!C186</f>
+        <f>'Point List'!C191</f>
         <v>0</v>
       </c>
       <c r="C168">
-        <f>'Point List'!L186</f>
+        <f>'Point List'!L191</f>
         <v>0</v>
       </c>
       <c r="D168" t="s">
         <v>312</v>
       </c>
       <c r="E168">
-        <f>'Point List'!J186</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169">
-        <f>'Point List'!C187</f>
-        <v>0</v>
-      </c>
-      <c r="C169">
-        <f>'Point List'!L187</f>
-        <v>0</v>
-      </c>
-      <c r="D169" t="s">
-        <v>312</v>
-      </c>
-      <c r="E169">
-        <f>'Point List'!J187</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170">
-        <f>'Point List'!C188</f>
-        <v>0</v>
-      </c>
-      <c r="C170">
-        <f>'Point List'!L188</f>
-        <v>0</v>
-      </c>
-      <c r="D170" t="s">
-        <v>312</v>
-      </c>
-      <c r="E170">
-        <f>'Point List'!J188</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171">
-        <f>'Point List'!C189</f>
-        <v>0</v>
-      </c>
-      <c r="C171">
-        <f>'Point List'!L189</f>
-        <v>0</v>
-      </c>
-      <c r="D171" t="s">
-        <v>312</v>
-      </c>
-      <c r="E171">
-        <f>'Point List'!J189</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172">
-        <f>'Point List'!C190</f>
-        <v>0</v>
-      </c>
-      <c r="C172">
-        <f>'Point List'!L190</f>
-        <v>0</v>
-      </c>
-      <c r="D172" t="s">
-        <v>312</v>
-      </c>
-      <c r="E172">
-        <f>'Point List'!J190</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173">
-        <f>'Point List'!C191</f>
-        <v>0</v>
-      </c>
-      <c r="C173">
-        <f>'Point List'!L191</f>
-        <v>0</v>
-      </c>
-      <c r="D173" t="s">
-        <v>312</v>
-      </c>
-      <c r="E173">
         <f>'Point List'!J191</f>
         <v>0</v>
       </c>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1799" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B360D68E-8D64-4908-80A8-EFD4A768C930}"/>
+  <xr:revisionPtr revIDLastSave="1804" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{072B345C-D261-42BD-86B7-64DD569AFA22}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point List" sheetId="1" r:id="rId1"/>
@@ -987,12 +987,6 @@
     <t>Enable_Manual_Fan_Control</t>
   </si>
   <si>
-    <t>Force_Fan_1_On/Off</t>
-  </si>
-  <si>
-    <t>Force_Fan_2_On/Off</t>
-  </si>
-  <si>
     <t>Primary_Hydraulic_Fault_ACK</t>
   </si>
   <si>
@@ -1023,9 +1017,6 @@
     <t>Measured_Pump_Power</t>
   </si>
   <si>
-    <t>Measured_Inlet_Coolant_Temperature</t>
-  </si>
-  <si>
     <t>Measured_Conductivity</t>
   </si>
   <si>
@@ -1048,9 +1039,6 @@
   </si>
   <si>
     <t>Debounced_Water_Level_Low_Signal</t>
-  </si>
-  <si>
-    <t>Debounced_Water_Level_Low_Low_Signal</t>
   </si>
   <si>
     <t>Debounced_Pressure_Signal</t>
@@ -1246,6 +1234,18 @@
   </si>
   <si>
     <t>Status_Indicator_Text</t>
+  </si>
+  <si>
+    <t>Force_Fan_1_On_Off</t>
+  </si>
+  <si>
+    <t>Force_Fan_2_On_Off</t>
+  </si>
+  <si>
+    <t>MICT</t>
+  </si>
+  <si>
+    <t>Debounced_Water_Level_L_L_Signal</t>
   </si>
 </sst>
 </file>
@@ -2875,7 +2875,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>308</v>
+        <v>391</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>200</v>
@@ -2951,7 +2951,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>309</v>
+        <v>392</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>200</v>
@@ -3027,7 +3027,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>206</v>
@@ -3103,7 +3103,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>206</v>
@@ -3179,7 +3179,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>199</v>
@@ -3255,7 +3255,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>199</v>
@@ -3331,7 +3331,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>197</v>
@@ -3551,7 +3551,7 @@
         <v>27</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>197</v>
@@ -3627,7 +3627,7 @@
         <v>28</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>197</v>
@@ -3703,7 +3703,7 @@
         <v>29</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>197</v>
@@ -3779,7 +3779,7 @@
         <v>30</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>197</v>
@@ -3855,7 +3855,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>199</v>
@@ -3930,8 +3930,8 @@
       <c r="B24" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>320</v>
+      <c r="C24" s="15" t="s">
+        <v>393</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>203</v>
@@ -4007,7 +4007,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>201</v>
@@ -4083,7 +4083,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>202</v>
@@ -4159,7 +4159,7 @@
         <v>36</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>198</v>
@@ -4235,7 +4235,7 @@
         <v>37</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>203</v>
@@ -4311,7 +4311,7 @@
         <v>38</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>203</v>
@@ -4387,7 +4387,7 @@
         <v>39</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>203</v>
@@ -4537,7 +4537,7 @@
         <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D32" t="s">
         <v>198</v>
@@ -4613,7 +4613,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>205</v>
@@ -4688,8 +4688,8 @@
       <c r="B34" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>329</v>
+      <c r="C34" s="15" t="s">
+        <v>394</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>205</v>
@@ -4763,7 +4763,7 @@
         <v>44</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>204</v>
@@ -4837,7 +4837,7 @@
         <v>45</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>201</v>
@@ -4911,7 +4911,7 @@
         <v>46</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>201</v>
@@ -4985,7 +4985,7 @@
         <v>47</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D38" s="14" t="s">
         <v>205</v>
@@ -5061,7 +5061,7 @@
         <v>48</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>205</v>
@@ -5137,7 +5137,7 @@
         <v>49</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>204</v>
@@ -5213,7 +5213,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>201</v>
@@ -5289,7 +5289,7 @@
         <v>51</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>201</v>
@@ -5365,7 +5365,7 @@
         <v>52</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>199</v>
@@ -5439,7 +5439,7 @@
         <v>105</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>197</v>
@@ -5513,7 +5513,7 @@
         <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D45" t="s">
         <v>199</v>
@@ -5589,7 +5589,7 @@
         <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D46" t="s">
         <v>199</v>
@@ -5809,7 +5809,7 @@
         <v>111</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>199</v>
@@ -5885,7 +5885,7 @@
         <v>112</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>199</v>
@@ -5961,7 +5961,7 @@
         <v>54</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>203</v>
@@ -6037,7 +6037,7 @@
         <v>55</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>205</v>
@@ -6113,7 +6113,7 @@
         <v>56</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>201</v>
@@ -6189,7 +6189,7 @@
         <v>57</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>199</v>
@@ -6265,7 +6265,7 @@
         <v>58</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>202</v>
@@ -6341,7 +6341,7 @@
         <v>59</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D56" s="14" t="s">
         <v>204</v>
@@ -6417,7 +6417,7 @@
         <v>60</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>199</v>
@@ -6493,7 +6493,7 @@
         <v>61</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>199</v>
@@ -6569,7 +6569,7 @@
         <v>62</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>206</v>
@@ -6645,7 +6645,7 @@
         <v>63</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>206</v>
@@ -6721,7 +6721,7 @@
         <v>64</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>198</v>
@@ -6797,7 +6797,7 @@
         <v>65</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>200</v>
@@ -6873,7 +6873,7 @@
         <v>66</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>202</v>
@@ -6949,7 +6949,7 @@
         <v>67</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>203</v>
@@ -7025,7 +7025,7 @@
         <v>68</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>203</v>
@@ -7101,7 +7101,7 @@
         <v>69</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>203</v>
@@ -7177,7 +7177,7 @@
         <v>70</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D67" s="14" t="s">
         <v>199</v>
@@ -7253,7 +7253,7 @@
         <v>72</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>203</v>
@@ -7329,7 +7329,7 @@
         <v>73</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D69" s="14" t="s">
         <v>205</v>
@@ -7405,7 +7405,7 @@
         <v>74</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>201</v>
@@ -7481,7 +7481,7 @@
         <v>75</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>205</v>
@@ -7557,7 +7557,7 @@
         <v>76</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>201</v>
@@ -7633,7 +7633,7 @@
         <v>77</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>199</v>
@@ -7709,7 +7709,7 @@
         <v>78</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>203</v>
@@ -7785,7 +7785,7 @@
         <v>79</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>198</v>
@@ -7861,7 +7861,7 @@
         <v>123</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>197</v>
@@ -7937,7 +7937,7 @@
         <v>81</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>201</v>
@@ -8006,7 +8006,7 @@
         <v>84</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D78" s="14" t="s">
         <v>203</v>
@@ -8075,7 +8075,7 @@
         <v>86</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>203</v>
@@ -8144,7 +8144,7 @@
         <v>87</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>203</v>
@@ -8317,7 +8317,7 @@
         <v>90</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>202</v>
@@ -8386,7 +8386,7 @@
         <v>91</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>201</v>
@@ -8455,7 +8455,7 @@
         <v>92</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>201</v>
@@ -8524,7 +8524,7 @@
         <v>93</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D86" s="14" t="s">
         <v>205</v>
@@ -8593,7 +8593,7 @@
         <v>94</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D87" s="14" t="s">
         <v>205</v>
@@ -8662,7 +8662,7 @@
         <v>95</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>200</v>
@@ -8731,7 +8731,7 @@
         <v>96</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>200</v>
@@ -8800,7 +8800,7 @@
         <v>97</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D90" s="14" t="s">
         <v>199</v>
@@ -8869,7 +8869,7 @@
         <v>98</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D91" s="14" t="s">
         <v>199</v>
@@ -8938,7 +8938,7 @@
         <v>99</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D92" s="14" t="s">
         <v>198</v>
@@ -9007,7 +9007,7 @@
         <v>100</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>204</v>
@@ -9076,7 +9076,7 @@
         <v>101</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>199</v>
@@ -9145,7 +9145,7 @@
         <v>102</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>199</v>
@@ -9214,7 +9214,7 @@
         <v>103</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>198</v>
@@ -9350,7 +9350,7 @@
         <v>187</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>199</v>
@@ -9422,7 +9422,7 @@
         <v>188</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>199</v>
@@ -9494,7 +9494,7 @@
         <v>189</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>199</v>
@@ -9566,7 +9566,7 @@
         <v>191</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>200</v>
@@ -9638,7 +9638,7 @@
         <v>192</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>200</v>
@@ -9710,7 +9710,7 @@
         <v>195</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>199</v>
@@ -9780,7 +9780,7 @@
         <v>196</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D104" s="14" t="s">
         <v>197</v>
@@ -9850,7 +9850,7 @@
         <v>222</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>197</v>
@@ -11082,7 +11082,7 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>'Point List'!C10</f>
-        <v>Force_Fan_1_On/Off</v>
+        <v>Force_Fan_1_On_Off</v>
       </c>
       <c r="C13" t="str">
         <f>'Point List'!L10</f>
@@ -11097,13 +11097,13 @@
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
-        <v>Force_Fan_1_On/Off,,BitAddress,PLC1,012296,,</v>
+        <v>Force_Fan_1_On_Off,,BitAddress,PLC1,012296,,</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>'Point List'!C11</f>
-        <v>Force_Fan_2_On/Off</v>
+        <v>Force_Fan_2_On_Off</v>
       </c>
       <c r="C14" t="str">
         <f>'Point List'!L11</f>
@@ -11118,7 +11118,7 @@
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
-        <v>Force_Fan_2_On/Off,,BitAddress,PLC1,012297,,</v>
+        <v>Force_Fan_2_On_Off,,BitAddress,PLC1,012297,,</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -11376,7 +11376,7 @@
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>'Point List'!C24</f>
-        <v>Measured_Inlet_Coolant_Temperature</v>
+        <v>MICT</v>
       </c>
       <c r="C27" t="str">
         <f>'Point List'!L24</f>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="K27" t="str">
         <f t="shared" si="0"/>
-        <v>Measured_Inlet_Coolant_Temperature,,WordAddress,PLC1,412559,,</v>
+        <v>MICT,,WordAddress,PLC1,412559,,</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -11586,7 +11586,7 @@
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f>'Point List'!C34</f>
-        <v>Debounced_Water_Level_Low_Low_Signal</v>
+        <v>Debounced_Water_Level_L_L_Signal</v>
       </c>
       <c r="C37">
         <f>'Point List'!L34</f>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="K37" t="str">
         <f t="shared" si="0"/>
-        <v>Debounced_Water_Level_Low_Low_Signal,,0,PLC1,012310,,</v>
+        <v>Debounced_Water_Level_L_L_Signal,,0,PLC1,012310,,</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -75080,7 +75080,7 @@
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>'Point List'!C10</f>
-        <v>Force_Fan_1_On/Off</v>
+        <v>Force_Fan_1_On_Off</v>
       </c>
       <c r="C13" t="str">
         <f>'Point List'!L10</f>
@@ -75095,7 +75095,7 @@
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
-        <v>Force_Fan_1_On/Off,,BitAddress,PLC1,012296,,</v>
+        <v>Force_Fan_1_On_Off,,BitAddress,PLC1,012296,,</v>
       </c>
       <c r="O13" t="s">
         <v>237</v>
@@ -75104,7 +75104,7 @@
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>'Point List'!C11</f>
-        <v>Force_Fan_2_On/Off</v>
+        <v>Force_Fan_2_On_Off</v>
       </c>
       <c r="C14" t="str">
         <f>'Point List'!L11</f>
@@ -75119,7 +75119,7 @@
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
-        <v>Force_Fan_2_On/Off,,BitAddress,PLC1,012297,,</v>
+        <v>Force_Fan_2_On_Off,,BitAddress,PLC1,012297,,</v>
       </c>
       <c r="O14" t="s">
         <v>238</v>
@@ -75368,7 +75368,7 @@
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>'Point List'!C24</f>
-        <v>Measured_Inlet_Coolant_Temperature</v>
+        <v>MICT</v>
       </c>
       <c r="C25" t="str">
         <f>'Point List'!L24</f>
@@ -75383,7 +75383,7 @@
       </c>
       <c r="K25" t="str">
         <f t="shared" si="0"/>
-        <v>Measured_Inlet_Coolant_Temperature,,WordAddress,PLC1,412559,,</v>
+        <v>MICT,,WordAddress,PLC1,412559,,</v>
       </c>
       <c r="O25" t="s">
         <v>249</v>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1804" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{072B345C-D261-42BD-86B7-64DD569AFA22}"/>
+  <xr:revisionPtr revIDLastSave="1807" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A593D45-0960-4144-B3B4-272349E4B6C2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point List" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="395">
   <si>
     <t>Signal Type</t>
   </si>
@@ -957,9 +957,6 @@
     <t>Fan 2 Active,,BitAddress,PLC1,012350,,</t>
   </si>
   <si>
-    <t>Enable Pump Cycling,,BitAddress,PLC1,012351,,</t>
-  </si>
-  <si>
     <t>System Diagnostics,,BitAddress,PLC1,012352,,</t>
   </si>
   <si>
@@ -1051,9 +1048,6 @@
   </si>
   <si>
     <t>Output_Water_Level_Low_Signal</t>
-  </si>
-  <si>
-    <t>Output_Water_Level_Low_Low_Signal</t>
   </si>
   <si>
     <t>Output_Pressure_Signal</t>
@@ -1246,6 +1240,12 @@
   </si>
   <si>
     <t>Debounced_Water_Level_L_L_Signal</t>
+  </si>
+  <si>
+    <t>Output_Water_Level_Low_Low</t>
+  </si>
+  <si>
+    <t>Internal/External</t>
   </si>
 </sst>
 </file>
@@ -2274,7 +2274,7 @@
         <v>113</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>197</v>
@@ -2343,7 +2343,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>197</v>
@@ -2419,7 +2419,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>197</v>
@@ -2495,7 +2495,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>199</v>
@@ -2571,7 +2571,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>199</v>
@@ -2647,7 +2647,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>198</v>
@@ -2723,7 +2723,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>200</v>
@@ -2875,7 +2875,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>200</v>
@@ -2951,7 +2951,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>200</v>
@@ -3027,7 +3027,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>206</v>
@@ -3103,7 +3103,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>206</v>
@@ -3179,7 +3179,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>199</v>
@@ -3255,7 +3255,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>199</v>
@@ -3331,7 +3331,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>197</v>
@@ -3551,7 +3551,7 @@
         <v>27</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>197</v>
@@ -3627,7 +3627,7 @@
         <v>28</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>197</v>
@@ -3703,7 +3703,7 @@
         <v>29</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>197</v>
@@ -3779,7 +3779,7 @@
         <v>30</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>197</v>
@@ -3855,7 +3855,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>199</v>
@@ -3931,7 +3931,7 @@
         <v>32</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>203</v>
@@ -4007,7 +4007,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>201</v>
@@ -4083,7 +4083,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>202</v>
@@ -4159,7 +4159,7 @@
         <v>36</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>198</v>
@@ -4235,7 +4235,7 @@
         <v>37</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>203</v>
@@ -4311,7 +4311,7 @@
         <v>38</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>203</v>
@@ -4387,7 +4387,7 @@
         <v>39</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>203</v>
@@ -4537,7 +4537,7 @@
         <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D32" t="s">
         <v>198</v>
@@ -4613,7 +4613,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>205</v>
@@ -4689,7 +4689,7 @@
         <v>43</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>205</v>
@@ -4763,7 +4763,7 @@
         <v>44</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>204</v>
@@ -4837,7 +4837,7 @@
         <v>45</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>201</v>
@@ -4911,7 +4911,7 @@
         <v>46</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>201</v>
@@ -4985,7 +4985,7 @@
         <v>47</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D38" s="14" t="s">
         <v>205</v>
@@ -5060,8 +5060,8 @@
       <c r="B39" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>330</v>
+      <c r="C39" s="15" t="s">
+        <v>393</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>205</v>
@@ -5137,7 +5137,7 @@
         <v>49</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>204</v>
@@ -5213,7 +5213,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>201</v>
@@ -5289,7 +5289,7 @@
         <v>51</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>201</v>
@@ -5365,7 +5365,7 @@
         <v>52</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>199</v>
@@ -5439,7 +5439,7 @@
         <v>105</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>197</v>
@@ -5513,7 +5513,7 @@
         <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D45" t="s">
         <v>199</v>
@@ -5589,7 +5589,7 @@
         <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D46" t="s">
         <v>199</v>
@@ -5809,7 +5809,7 @@
         <v>111</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>199</v>
@@ -5885,7 +5885,7 @@
         <v>112</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>199</v>
@@ -5961,7 +5961,7 @@
         <v>54</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>203</v>
@@ -6037,7 +6037,7 @@
         <v>55</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>205</v>
@@ -6113,7 +6113,7 @@
         <v>56</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>201</v>
@@ -6189,7 +6189,7 @@
         <v>57</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>199</v>
@@ -6265,7 +6265,7 @@
         <v>58</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>202</v>
@@ -6341,7 +6341,7 @@
         <v>59</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D56" s="14" t="s">
         <v>204</v>
@@ -6417,7 +6417,7 @@
         <v>60</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>199</v>
@@ -6493,7 +6493,7 @@
         <v>61</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>199</v>
@@ -6569,7 +6569,7 @@
         <v>62</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>206</v>
@@ -6645,7 +6645,7 @@
         <v>63</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>206</v>
@@ -6721,7 +6721,7 @@
         <v>64</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>198</v>
@@ -6797,7 +6797,7 @@
         <v>65</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>200</v>
@@ -6873,7 +6873,7 @@
         <v>66</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>202</v>
@@ -6949,7 +6949,7 @@
         <v>67</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>203</v>
@@ -7025,7 +7025,7 @@
         <v>68</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>203</v>
@@ -7101,7 +7101,7 @@
         <v>69</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>203</v>
@@ -7177,7 +7177,7 @@
         <v>70</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D67" s="14" t="s">
         <v>199</v>
@@ -7253,7 +7253,7 @@
         <v>72</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>203</v>
@@ -7329,7 +7329,7 @@
         <v>73</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D69" s="14" t="s">
         <v>205</v>
@@ -7405,7 +7405,7 @@
         <v>74</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>201</v>
@@ -7481,7 +7481,7 @@
         <v>75</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>205</v>
@@ -7557,7 +7557,7 @@
         <v>76</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>201</v>
@@ -7633,7 +7633,7 @@
         <v>77</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>199</v>
@@ -7709,7 +7709,7 @@
         <v>78</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>203</v>
@@ -7785,7 +7785,7 @@
         <v>79</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>198</v>
@@ -7861,7 +7861,7 @@
         <v>123</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>197</v>
@@ -7937,7 +7937,7 @@
         <v>81</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>201</v>
@@ -8006,7 +8006,7 @@
         <v>84</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D78" s="14" t="s">
         <v>203</v>
@@ -8075,7 +8075,7 @@
         <v>86</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>203</v>
@@ -8144,7 +8144,7 @@
         <v>87</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>203</v>
@@ -8317,7 +8317,7 @@
         <v>90</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>202</v>
@@ -8386,7 +8386,7 @@
         <v>91</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>201</v>
@@ -8455,7 +8455,7 @@
         <v>92</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>201</v>
@@ -8524,7 +8524,7 @@
         <v>93</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D86" s="14" t="s">
         <v>205</v>
@@ -8593,7 +8593,7 @@
         <v>94</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D87" s="14" t="s">
         <v>205</v>
@@ -8662,7 +8662,7 @@
         <v>95</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>200</v>
@@ -8731,7 +8731,7 @@
         <v>96</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>200</v>
@@ -8800,7 +8800,7 @@
         <v>97</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D90" s="14" t="s">
         <v>199</v>
@@ -8869,7 +8869,7 @@
         <v>98</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D91" s="14" t="s">
         <v>199</v>
@@ -8938,7 +8938,7 @@
         <v>99</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D92" s="14" t="s">
         <v>198</v>
@@ -9007,7 +9007,7 @@
         <v>100</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>204</v>
@@ -9076,7 +9076,7 @@
         <v>101</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>199</v>
@@ -9145,7 +9145,7 @@
         <v>102</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>199</v>
@@ -9214,7 +9214,7 @@
         <v>103</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>198</v>
@@ -9350,7 +9350,7 @@
         <v>187</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>199</v>
@@ -9422,7 +9422,7 @@
         <v>188</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>199</v>
@@ -9494,7 +9494,7 @@
         <v>189</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>199</v>
@@ -9566,7 +9566,7 @@
         <v>191</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>200</v>
@@ -9638,7 +9638,7 @@
         <v>192</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>200</v>
@@ -9710,7 +9710,7 @@
         <v>195</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>199</v>
@@ -9780,7 +9780,7 @@
         <v>196</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D104" s="14" t="s">
         <v>197</v>
@@ -9850,7 +9850,7 @@
         <v>222</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>197</v>
@@ -11691,7 +11691,7 @@
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f>'Point List'!C39</f>
-        <v>Output_Water_Level_Low_Low_Signal</v>
+        <v>Output_Water_Level_Low_Low</v>
       </c>
       <c r="C42" t="str">
         <f>'Point List'!L39</f>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="K42" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Water_Level_Low_Low_Signal,,BitAddress,PLC1,012315,,</v>
+        <v>Output_Water_Level_Low_Low,,BitAddress,PLC1,012315,,</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
@@ -74824,7 +74824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B9609-D38B-45A0-9E25-0F7CEDBD1FA5}">
-  <dimension ref="A1:O162"/>
+  <dimension ref="A1:O161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
@@ -74890,7 +74890,7 @@
         <v>213</v>
       </c>
       <c r="D5" t="s">
-        <v>214</v>
+        <v>394</v>
       </c>
       <c r="E5" t="s">
         <v>215</v>
@@ -74903,7 +74903,7 @@
       </c>
       <c r="K5" t="str">
         <f>_xlfn.CONCAT(""""&amp;A5&amp;"""",",",""""&amp;B5&amp;"""",",",""""&amp;C5&amp;"""",",",""""&amp;D5&amp;"""",",",""""&amp;E5&amp;"""",",",""""&amp;F5&amp;"""",",",""""&amp;G5&amp;"""")</f>
-        <v>"Name","Index","Type","External/Internal","Address","Keep","Comment"</v>
+        <v>"Name","Index","Type","Internal/External","Address","Keep","Comment"</v>
       </c>
       <c r="O5" t="s">
         <v>226</v>
@@ -75608,7 +75608,7 @@
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f>'Point List'!C39</f>
-        <v>Output_Water_Level_Low_Low_Signal</v>
+        <v>Output_Water_Level_Low_Low</v>
       </c>
       <c r="C35" t="str">
         <f>'Point List'!L39</f>
@@ -75623,7 +75623,7 @@
       </c>
       <c r="K35" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Water_Level_Low_Low_Signal,,BitAddress,PLC1,012315,,</v>
+        <v>Output_Water_Level_Low_Low,,BitAddress,PLC1,012315,,</v>
       </c>
       <c r="O35" t="s">
         <v>259</v>
@@ -76543,23 +76543,23 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
-        <f>'Point List'!C103</f>
-        <v>Enable_Pump_Cycling</v>
+        <f>'Point List'!C104</f>
+        <v>System_Diagnostics</v>
       </c>
       <c r="C74" t="str">
-        <f>'Point List'!L103</f>
+        <f>'Point List'!L104</f>
         <v>BitAddress</v>
       </c>
       <c r="D74" t="s">
         <v>220</v>
       </c>
       <c r="E74" t="str">
-        <f>'Point List'!J103</f>
-        <v>012351</v>
+        <f>'Point List'!J104</f>
+        <v>012352</v>
       </c>
       <c r="K74" t="str">
         <f>_xlfn.CONCAT(A74,",",B74,",",C74,",",D74,",",E74,",",F74,",",G74)</f>
-        <v>Enable_Pump_Cycling,,BitAddress,PLC1,012351,,</v>
+        <v>System_Diagnostics,,BitAddress,PLC1,012352,,</v>
       </c>
       <c r="O74" t="s">
         <v>298</v>
@@ -76567,1510 +76567,1486 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
-        <f>'Point List'!C104</f>
-        <v>System_Diagnostics</v>
+        <f>'Point List'!C105</f>
+        <v>Status_Indicator_Text</v>
       </c>
       <c r="C75" t="str">
-        <f>'Point List'!L104</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L105</f>
+        <v>WordAddress</v>
       </c>
       <c r="D75" t="s">
         <v>220</v>
       </c>
       <c r="E75" t="str">
-        <f>'Point List'!J104</f>
-        <v>012352</v>
+        <f>'Point List'!J105</f>
+        <v>412683</v>
       </c>
       <c r="K75" t="str">
         <f>_xlfn.CONCAT(A75,",",B75,",",C75,",",D75,",",E75,",",F75,",",G75)</f>
-        <v>System_Diagnostics,,BitAddress,PLC1,012352,,</v>
+        <v>Status_Indicator_Text,,WordAddress,PLC1,412683,,</v>
       </c>
       <c r="O75" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" t="str">
-        <f>'Point List'!C105</f>
-        <v>Status_Indicator_Text</v>
-      </c>
-      <c r="C76" t="str">
-        <f>'Point List'!L105</f>
-        <v>WordAddress</v>
+      <c r="A76">
+        <f>'Point List'!C106</f>
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <f>'Point List'!L106</f>
+        <v>0</v>
       </c>
       <c r="D76" t="s">
         <v>220</v>
       </c>
-      <c r="E76" t="str">
-        <f>'Point List'!J105</f>
-        <v>412683</v>
-      </c>
-      <c r="K76" t="str">
-        <f>_xlfn.CONCAT(A76,",",B76,",",C76,",",D76,",",E76,",",F76,",",G76)</f>
-        <v>Status_Indicator_Text,,WordAddress,PLC1,412683,,</v>
-      </c>
-      <c r="O76" t="s">
-        <v>300</v>
+      <c r="E76">
+        <f>'Point List'!J106</f>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77">
-        <f>'Point List'!C106</f>
+        <f>'Point List'!C107</f>
         <v>0</v>
       </c>
       <c r="C77">
-        <f>'Point List'!L106</f>
+        <f>'Point List'!L107</f>
         <v>0</v>
       </c>
       <c r="D77" t="s">
         <v>220</v>
       </c>
       <c r="E77">
-        <f>'Point List'!J106</f>
+        <f>'Point List'!J107</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78">
-        <f>'Point List'!C107</f>
+        <f>'Point List'!C108</f>
         <v>0</v>
       </c>
       <c r="C78">
-        <f>'Point List'!L107</f>
+        <f>'Point List'!L108</f>
         <v>0</v>
       </c>
       <c r="D78" t="s">
         <v>220</v>
       </c>
       <c r="E78">
-        <f>'Point List'!J107</f>
+        <f>'Point List'!J108</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79">
-        <f>'Point List'!C108</f>
+        <f>'Point List'!C109</f>
         <v>0</v>
       </c>
       <c r="C79">
-        <f>'Point List'!L108</f>
+        <f>'Point List'!L109</f>
         <v>0</v>
       </c>
       <c r="D79" t="s">
         <v>220</v>
       </c>
       <c r="E79">
-        <f>'Point List'!J108</f>
+        <f>'Point List'!J109</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80">
-        <f>'Point List'!C109</f>
+        <f>'Point List'!C110</f>
         <v>0</v>
       </c>
       <c r="C80">
-        <f>'Point List'!L109</f>
+        <f>'Point List'!L110</f>
         <v>0</v>
       </c>
       <c r="D80" t="s">
         <v>220</v>
       </c>
       <c r="E80">
-        <f>'Point List'!J109</f>
+        <f>'Point List'!J110</f>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
-        <f>'Point List'!C110</f>
+        <f>'Point List'!C111</f>
         <v>0</v>
       </c>
       <c r="C81">
-        <f>'Point List'!L110</f>
+        <f>'Point List'!L111</f>
         <v>0</v>
       </c>
       <c r="D81" t="s">
         <v>220</v>
       </c>
       <c r="E81">
-        <f>'Point List'!J110</f>
+        <f>'Point List'!J111</f>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
-        <f>'Point List'!C111</f>
+        <f>'Point List'!C112</f>
         <v>0</v>
       </c>
       <c r="C82">
-        <f>'Point List'!L111</f>
+        <f>'Point List'!L112</f>
         <v>0</v>
       </c>
       <c r="D82" t="s">
         <v>220</v>
       </c>
       <c r="E82">
-        <f>'Point List'!J111</f>
+        <f>'Point List'!J112</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
-        <f>'Point List'!C112</f>
+        <f>'Point List'!C113</f>
         <v>0</v>
       </c>
       <c r="C83">
-        <f>'Point List'!L112</f>
+        <f>'Point List'!L113</f>
         <v>0</v>
       </c>
       <c r="D83" t="s">
         <v>220</v>
       </c>
       <c r="E83">
-        <f>'Point List'!J112</f>
+        <f>'Point List'!J113</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
-        <f>'Point List'!C113</f>
+        <f>'Point List'!C114</f>
         <v>0</v>
       </c>
       <c r="C84">
-        <f>'Point List'!L113</f>
+        <f>'Point List'!L114</f>
         <v>0</v>
       </c>
       <c r="D84" t="s">
         <v>220</v>
       </c>
       <c r="E84">
-        <f>'Point List'!J113</f>
+        <f>'Point List'!J114</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
-        <f>'Point List'!C114</f>
+        <f>'Point List'!C115</f>
         <v>0</v>
       </c>
       <c r="C85">
-        <f>'Point List'!L114</f>
+        <f>'Point List'!L115</f>
         <v>0</v>
       </c>
       <c r="D85" t="s">
         <v>220</v>
       </c>
       <c r="E85">
-        <f>'Point List'!J114</f>
+        <f>'Point List'!J115</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
-        <f>'Point List'!C115</f>
+        <f>'Point List'!C116</f>
         <v>0</v>
       </c>
       <c r="C86">
-        <f>'Point List'!L115</f>
+        <f>'Point List'!L116</f>
         <v>0</v>
       </c>
       <c r="D86" t="s">
         <v>220</v>
       </c>
       <c r="E86">
-        <f>'Point List'!J115</f>
+        <f>'Point List'!J116</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
-        <f>'Point List'!C116</f>
+        <f>'Point List'!C117</f>
         <v>0</v>
       </c>
       <c r="C87">
-        <f>'Point List'!L116</f>
+        <f>'Point List'!L117</f>
         <v>0</v>
       </c>
       <c r="D87" t="s">
         <v>220</v>
       </c>
       <c r="E87">
-        <f>'Point List'!J116</f>
+        <f>'Point List'!J117</f>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
-        <f>'Point List'!C117</f>
+        <f>'Point List'!C118</f>
         <v>0</v>
       </c>
       <c r="C88">
-        <f>'Point List'!L117</f>
+        <f>'Point List'!L118</f>
         <v>0</v>
       </c>
       <c r="D88" t="s">
         <v>220</v>
       </c>
       <c r="E88">
-        <f>'Point List'!J117</f>
+        <f>'Point List'!J118</f>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
-        <f>'Point List'!C118</f>
+        <f>'Point List'!C119</f>
         <v>0</v>
       </c>
       <c r="C89">
-        <f>'Point List'!L118</f>
+        <f>'Point List'!L119</f>
         <v>0</v>
       </c>
       <c r="D89" t="s">
         <v>220</v>
       </c>
       <c r="E89">
-        <f>'Point List'!J118</f>
+        <f>'Point List'!J119</f>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
-        <f>'Point List'!C119</f>
+        <f>'Point List'!C120</f>
         <v>0</v>
       </c>
       <c r="C90">
-        <f>'Point List'!L119</f>
+        <f>'Point List'!L120</f>
         <v>0</v>
       </c>
       <c r="D90" t="s">
         <v>220</v>
       </c>
       <c r="E90">
-        <f>'Point List'!J119</f>
+        <f>'Point List'!J120</f>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
-        <f>'Point List'!C120</f>
+        <f>'Point List'!C121</f>
         <v>0</v>
       </c>
       <c r="C91">
-        <f>'Point List'!L120</f>
+        <f>'Point List'!L121</f>
         <v>0</v>
       </c>
       <c r="D91" t="s">
         <v>220</v>
       </c>
       <c r="E91">
-        <f>'Point List'!J120</f>
+        <f>'Point List'!J121</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
-        <f>'Point List'!C121</f>
+        <f>'Point List'!C122</f>
         <v>0</v>
       </c>
       <c r="C92">
-        <f>'Point List'!L121</f>
+        <f>'Point List'!L122</f>
         <v>0</v>
       </c>
       <c r="D92" t="s">
         <v>220</v>
       </c>
       <c r="E92">
-        <f>'Point List'!J121</f>
+        <f>'Point List'!J122</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
-        <f>'Point List'!C122</f>
+        <f>'Point List'!C123</f>
         <v>0</v>
       </c>
       <c r="C93">
-        <f>'Point List'!L122</f>
+        <f>'Point List'!L123</f>
         <v>0</v>
       </c>
       <c r="D93" t="s">
         <v>220</v>
       </c>
       <c r="E93">
-        <f>'Point List'!J122</f>
+        <f>'Point List'!J123</f>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
-        <f>'Point List'!C123</f>
+        <f>'Point List'!C124</f>
         <v>0</v>
       </c>
       <c r="C94">
-        <f>'Point List'!L123</f>
+        <f>'Point List'!L124</f>
         <v>0</v>
       </c>
       <c r="D94" t="s">
         <v>220</v>
       </c>
       <c r="E94">
-        <f>'Point List'!J123</f>
+        <f>'Point List'!J124</f>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
-        <f>'Point List'!C124</f>
+        <f>'Point List'!C125</f>
         <v>0</v>
       </c>
       <c r="C95">
-        <f>'Point List'!L124</f>
+        <f>'Point List'!L125</f>
         <v>0</v>
       </c>
       <c r="D95" t="s">
         <v>220</v>
       </c>
       <c r="E95">
-        <f>'Point List'!J124</f>
+        <f>'Point List'!J125</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
-        <f>'Point List'!C125</f>
+        <f>'Point List'!C126</f>
         <v>0</v>
       </c>
       <c r="C96">
-        <f>'Point List'!L125</f>
+        <f>'Point List'!L126</f>
         <v>0</v>
       </c>
       <c r="D96" t="s">
         <v>220</v>
       </c>
       <c r="E96">
-        <f>'Point List'!J125</f>
+        <f>'Point List'!J126</f>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
-        <f>'Point List'!C126</f>
+        <f>'Point List'!C127</f>
         <v>0</v>
       </c>
       <c r="C97">
-        <f>'Point List'!L126</f>
+        <f>'Point List'!L127</f>
         <v>0</v>
       </c>
       <c r="D97" t="s">
         <v>220</v>
       </c>
       <c r="E97">
-        <f>'Point List'!J126</f>
+        <f>'Point List'!J127</f>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
-        <f>'Point List'!C127</f>
+        <f>'Point List'!C128</f>
         <v>0</v>
       </c>
       <c r="C98">
-        <f>'Point List'!L127</f>
+        <f>'Point List'!L128</f>
         <v>0</v>
       </c>
       <c r="D98" t="s">
         <v>220</v>
       </c>
       <c r="E98">
-        <f>'Point List'!J127</f>
+        <f>'Point List'!J128</f>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
-        <f>'Point List'!C128</f>
+        <f>'Point List'!C129</f>
         <v>0</v>
       </c>
       <c r="C99">
-        <f>'Point List'!L128</f>
+        <f>'Point List'!L129</f>
         <v>0</v>
       </c>
       <c r="D99" t="s">
         <v>220</v>
       </c>
       <c r="E99">
-        <f>'Point List'!J128</f>
+        <f>'Point List'!J129</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
-        <f>'Point List'!C129</f>
+        <f>'Point List'!C130</f>
         <v>0</v>
       </c>
       <c r="C100">
-        <f>'Point List'!L129</f>
+        <f>'Point List'!L130</f>
         <v>0</v>
       </c>
       <c r="D100" t="s">
         <v>220</v>
       </c>
       <c r="E100">
-        <f>'Point List'!J129</f>
+        <f>'Point List'!J130</f>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
-        <f>'Point List'!C130</f>
+        <f>'Point List'!C131</f>
         <v>0</v>
       </c>
       <c r="C101">
-        <f>'Point List'!L130</f>
+        <f>'Point List'!L131</f>
         <v>0</v>
       </c>
       <c r="D101" t="s">
         <v>220</v>
       </c>
       <c r="E101">
-        <f>'Point List'!J130</f>
+        <f>'Point List'!J131</f>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
-        <f>'Point List'!C131</f>
+        <f>'Point List'!C132</f>
         <v>0</v>
       </c>
       <c r="C102">
-        <f>'Point List'!L131</f>
+        <f>'Point List'!L132</f>
         <v>0</v>
       </c>
       <c r="D102" t="s">
         <v>220</v>
       </c>
       <c r="E102">
-        <f>'Point List'!J131</f>
+        <f>'Point List'!J132</f>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
-        <f>'Point List'!C132</f>
+        <f>'Point List'!C133</f>
         <v>0</v>
       </c>
       <c r="C103">
-        <f>'Point List'!L132</f>
+        <f>'Point List'!L133</f>
         <v>0</v>
       </c>
       <c r="D103" t="s">
         <v>220</v>
       </c>
       <c r="E103">
-        <f>'Point List'!J132</f>
+        <f>'Point List'!J133</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
-        <f>'Point List'!C133</f>
+        <f>'Point List'!C134</f>
         <v>0</v>
       </c>
       <c r="C104">
-        <f>'Point List'!L133</f>
+        <f>'Point List'!L134</f>
         <v>0</v>
       </c>
       <c r="D104" t="s">
         <v>220</v>
       </c>
       <c r="E104">
-        <f>'Point List'!J133</f>
+        <f>'Point List'!J134</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
-        <f>'Point List'!C134</f>
+        <f>'Point List'!C135</f>
         <v>0</v>
       </c>
       <c r="C105">
-        <f>'Point List'!L134</f>
+        <f>'Point List'!L135</f>
         <v>0</v>
       </c>
       <c r="D105" t="s">
         <v>220</v>
       </c>
       <c r="E105">
-        <f>'Point List'!J134</f>
+        <f>'Point List'!J135</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
-        <f>'Point List'!C135</f>
+        <f>'Point List'!C136</f>
         <v>0</v>
       </c>
       <c r="C106">
-        <f>'Point List'!L135</f>
+        <f>'Point List'!L136</f>
         <v>0</v>
       </c>
       <c r="D106" t="s">
         <v>220</v>
       </c>
       <c r="E106">
-        <f>'Point List'!J135</f>
+        <f>'Point List'!J136</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
-        <f>'Point List'!C136</f>
+        <f>'Point List'!C137</f>
         <v>0</v>
       </c>
       <c r="C107">
-        <f>'Point List'!L136</f>
+        <f>'Point List'!L137</f>
         <v>0</v>
       </c>
       <c r="D107" t="s">
         <v>220</v>
       </c>
       <c r="E107">
-        <f>'Point List'!J136</f>
+        <f>'Point List'!J137</f>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
-        <f>'Point List'!C137</f>
+        <f>'Point List'!C138</f>
         <v>0</v>
       </c>
       <c r="C108">
-        <f>'Point List'!L137</f>
+        <f>'Point List'!L138</f>
         <v>0</v>
       </c>
       <c r="D108" t="s">
         <v>220</v>
       </c>
       <c r="E108">
-        <f>'Point List'!J137</f>
+        <f>'Point List'!J138</f>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
-        <f>'Point List'!C138</f>
+        <f>'Point List'!C139</f>
         <v>0</v>
       </c>
       <c r="C109">
-        <f>'Point List'!L138</f>
+        <f>'Point List'!L139</f>
         <v>0</v>
       </c>
       <c r="D109" t="s">
         <v>220</v>
       </c>
       <c r="E109">
-        <f>'Point List'!J138</f>
+        <f>'Point List'!J139</f>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
-        <f>'Point List'!C139</f>
+        <f>'Point List'!C140</f>
         <v>0</v>
       </c>
       <c r="C110">
-        <f>'Point List'!L139</f>
+        <f>'Point List'!L140</f>
         <v>0</v>
       </c>
       <c r="D110" t="s">
         <v>220</v>
       </c>
       <c r="E110">
-        <f>'Point List'!J139</f>
+        <f>'Point List'!J140</f>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
-        <f>'Point List'!C140</f>
+        <f>'Point List'!C141</f>
         <v>0</v>
       </c>
       <c r="C111">
-        <f>'Point List'!L140</f>
+        <f>'Point List'!L141</f>
         <v>0</v>
       </c>
       <c r="D111" t="s">
         <v>220</v>
       </c>
       <c r="E111">
-        <f>'Point List'!J140</f>
+        <f>'Point List'!J141</f>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
-        <f>'Point List'!C141</f>
+        <f>'Point List'!C142</f>
         <v>0</v>
       </c>
       <c r="C112">
-        <f>'Point List'!L141</f>
+        <f>'Point List'!L142</f>
         <v>0</v>
       </c>
       <c r="D112" t="s">
         <v>220</v>
       </c>
       <c r="E112">
-        <f>'Point List'!J141</f>
+        <f>'Point List'!J142</f>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
-        <f>'Point List'!C142</f>
+        <f>'Point List'!C143</f>
         <v>0</v>
       </c>
       <c r="C113">
-        <f>'Point List'!L142</f>
+        <f>'Point List'!L143</f>
         <v>0</v>
       </c>
       <c r="D113" t="s">
         <v>220</v>
       </c>
       <c r="E113">
-        <f>'Point List'!J142</f>
+        <f>'Point List'!J143</f>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
-        <f>'Point List'!C143</f>
+        <f>'Point List'!C144</f>
         <v>0</v>
       </c>
       <c r="C114">
-        <f>'Point List'!L143</f>
+        <f>'Point List'!L144</f>
         <v>0</v>
       </c>
       <c r="D114" t="s">
         <v>220</v>
       </c>
       <c r="E114">
-        <f>'Point List'!J143</f>
+        <f>'Point List'!J144</f>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
-        <f>'Point List'!C144</f>
+        <f>'Point List'!C145</f>
         <v>0</v>
       </c>
       <c r="C115">
-        <f>'Point List'!L144</f>
+        <f>'Point List'!L145</f>
         <v>0</v>
       </c>
       <c r="D115" t="s">
         <v>220</v>
       </c>
       <c r="E115">
-        <f>'Point List'!J144</f>
+        <f>'Point List'!J145</f>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
-        <f>'Point List'!C145</f>
+        <f>'Point List'!C146</f>
         <v>0</v>
       </c>
       <c r="C116">
-        <f>'Point List'!L145</f>
+        <f>'Point List'!L146</f>
         <v>0</v>
       </c>
       <c r="D116" t="s">
         <v>220</v>
       </c>
       <c r="E116">
-        <f>'Point List'!J145</f>
+        <f>'Point List'!J146</f>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
-        <f>'Point List'!C146</f>
+        <f>'Point List'!C147</f>
         <v>0</v>
       </c>
       <c r="C117">
-        <f>'Point List'!L146</f>
+        <f>'Point List'!L147</f>
         <v>0</v>
       </c>
       <c r="D117" t="s">
         <v>220</v>
       </c>
       <c r="E117">
-        <f>'Point List'!J146</f>
+        <f>'Point List'!J147</f>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
-        <f>'Point List'!C147</f>
+        <f>'Point List'!C148</f>
         <v>0</v>
       </c>
       <c r="C118">
-        <f>'Point List'!L147</f>
+        <f>'Point List'!L148</f>
         <v>0</v>
       </c>
       <c r="D118" t="s">
         <v>220</v>
       </c>
       <c r="E118">
-        <f>'Point List'!J147</f>
+        <f>'Point List'!J148</f>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
-        <f>'Point List'!C148</f>
+        <f>'Point List'!C149</f>
         <v>0</v>
       </c>
       <c r="C119">
-        <f>'Point List'!L148</f>
+        <f>'Point List'!L149</f>
         <v>0</v>
       </c>
       <c r="D119" t="s">
         <v>220</v>
       </c>
       <c r="E119">
-        <f>'Point List'!J148</f>
+        <f>'Point List'!J149</f>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
-        <f>'Point List'!C149</f>
+        <f>'Point List'!C150</f>
         <v>0</v>
       </c>
       <c r="C120">
-        <f>'Point List'!L149</f>
+        <f>'Point List'!L150</f>
         <v>0</v>
       </c>
       <c r="D120" t="s">
         <v>220</v>
       </c>
       <c r="E120">
-        <f>'Point List'!J149</f>
+        <f>'Point List'!J150</f>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
-        <f>'Point List'!C150</f>
+        <f>'Point List'!C151</f>
         <v>0</v>
       </c>
       <c r="C121">
-        <f>'Point List'!L150</f>
+        <f>'Point List'!L151</f>
         <v>0</v>
       </c>
       <c r="D121" t="s">
         <v>220</v>
       </c>
       <c r="E121">
-        <f>'Point List'!J150</f>
+        <f>'Point List'!J151</f>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
-        <f>'Point List'!C151</f>
+        <f>'Point List'!C152</f>
         <v>0</v>
       </c>
       <c r="C122">
-        <f>'Point List'!L151</f>
+        <f>'Point List'!L152</f>
         <v>0</v>
       </c>
       <c r="D122" t="s">
         <v>220</v>
       </c>
       <c r="E122">
-        <f>'Point List'!J151</f>
+        <f>'Point List'!J152</f>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
-        <f>'Point List'!C152</f>
+        <f>'Point List'!C153</f>
         <v>0</v>
       </c>
       <c r="C123">
-        <f>'Point List'!L152</f>
+        <f>'Point List'!L153</f>
         <v>0</v>
       </c>
       <c r="D123" t="s">
         <v>220</v>
       </c>
       <c r="E123">
-        <f>'Point List'!J152</f>
+        <f>'Point List'!J153</f>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
-        <f>'Point List'!C153</f>
+        <f>'Point List'!C154</f>
         <v>0</v>
       </c>
       <c r="C124">
-        <f>'Point List'!L153</f>
+        <f>'Point List'!L154</f>
         <v>0</v>
       </c>
       <c r="D124" t="s">
         <v>220</v>
       </c>
       <c r="E124">
-        <f>'Point List'!J153</f>
+        <f>'Point List'!J154</f>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
-        <f>'Point List'!C154</f>
+        <f>'Point List'!C155</f>
         <v>0</v>
       </c>
       <c r="C125">
-        <f>'Point List'!L154</f>
+        <f>'Point List'!L155</f>
         <v>0</v>
       </c>
       <c r="D125" t="s">
         <v>220</v>
       </c>
       <c r="E125">
-        <f>'Point List'!J154</f>
+        <f>'Point List'!J155</f>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
-        <f>'Point List'!C155</f>
+        <f>'Point List'!C156</f>
         <v>0</v>
       </c>
       <c r="C126">
-        <f>'Point List'!L155</f>
+        <f>'Point List'!L156</f>
         <v>0</v>
       </c>
       <c r="D126" t="s">
         <v>220</v>
       </c>
       <c r="E126">
-        <f>'Point List'!J155</f>
+        <f>'Point List'!J156</f>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
-        <f>'Point List'!C156</f>
+        <f>'Point List'!C157</f>
         <v>0</v>
       </c>
       <c r="C127">
-        <f>'Point List'!L156</f>
+        <f>'Point List'!L157</f>
         <v>0</v>
       </c>
       <c r="D127" t="s">
         <v>220</v>
       </c>
       <c r="E127">
-        <f>'Point List'!J156</f>
+        <f>'Point List'!J157</f>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
-        <f>'Point List'!C157</f>
+        <f>'Point List'!C158</f>
         <v>0</v>
       </c>
       <c r="C128">
-        <f>'Point List'!L157</f>
+        <f>'Point List'!L158</f>
         <v>0</v>
       </c>
       <c r="D128" t="s">
         <v>220</v>
       </c>
       <c r="E128">
-        <f>'Point List'!J157</f>
+        <f>'Point List'!J158</f>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
-        <f>'Point List'!C158</f>
+        <f>'Point List'!C159</f>
         <v>0</v>
       </c>
       <c r="C129">
-        <f>'Point List'!L158</f>
+        <f>'Point List'!L159</f>
         <v>0</v>
       </c>
       <c r="D129" t="s">
         <v>220</v>
       </c>
       <c r="E129">
-        <f>'Point List'!J158</f>
+        <f>'Point List'!J159</f>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
-        <f>'Point List'!C159</f>
+        <f>'Point List'!C160</f>
         <v>0</v>
       </c>
       <c r="C130">
-        <f>'Point List'!L159</f>
+        <f>'Point List'!L160</f>
         <v>0</v>
       </c>
       <c r="D130" t="s">
         <v>220</v>
       </c>
       <c r="E130">
-        <f>'Point List'!J159</f>
+        <f>'Point List'!J160</f>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
-        <f>'Point List'!C160</f>
+        <f>'Point List'!C161</f>
         <v>0</v>
       </c>
       <c r="C131">
-        <f>'Point List'!L160</f>
+        <f>'Point List'!L161</f>
         <v>0</v>
       </c>
       <c r="D131" t="s">
         <v>220</v>
       </c>
       <c r="E131">
-        <f>'Point List'!J160</f>
+        <f>'Point List'!J161</f>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
-        <f>'Point List'!C161</f>
+        <f>'Point List'!C162</f>
         <v>0</v>
       </c>
       <c r="C132">
-        <f>'Point List'!L161</f>
+        <f>'Point List'!L162</f>
         <v>0</v>
       </c>
       <c r="D132" t="s">
         <v>220</v>
       </c>
       <c r="E132">
-        <f>'Point List'!J161</f>
+        <f>'Point List'!J162</f>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
-        <f>'Point List'!C162</f>
+        <f>'Point List'!C163</f>
         <v>0</v>
       </c>
       <c r="C133">
-        <f>'Point List'!L162</f>
+        <f>'Point List'!L163</f>
         <v>0</v>
       </c>
       <c r="D133" t="s">
         <v>220</v>
       </c>
       <c r="E133">
-        <f>'Point List'!J162</f>
+        <f>'Point List'!J163</f>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
-        <f>'Point List'!C163</f>
+        <f>'Point List'!C164</f>
         <v>0</v>
       </c>
       <c r="C134">
-        <f>'Point List'!L163</f>
+        <f>'Point List'!L164</f>
         <v>0</v>
       </c>
       <c r="D134" t="s">
         <v>220</v>
       </c>
       <c r="E134">
-        <f>'Point List'!J163</f>
+        <f>'Point List'!J164</f>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
-        <f>'Point List'!C164</f>
+        <f>'Point List'!C165</f>
         <v>0</v>
       </c>
       <c r="C135">
-        <f>'Point List'!L164</f>
+        <f>'Point List'!L165</f>
         <v>0</v>
       </c>
       <c r="D135" t="s">
         <v>220</v>
       </c>
       <c r="E135">
-        <f>'Point List'!J164</f>
+        <f>'Point List'!J165</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
-        <f>'Point List'!C165</f>
+        <f>'Point List'!C166</f>
         <v>0</v>
       </c>
       <c r="C136">
-        <f>'Point List'!L165</f>
+        <f>'Point List'!L166</f>
         <v>0</v>
       </c>
       <c r="D136" t="s">
         <v>220</v>
       </c>
       <c r="E136">
-        <f>'Point List'!J165</f>
+        <f>'Point List'!J166</f>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
-        <f>'Point List'!C166</f>
+        <f>'Point List'!C167</f>
         <v>0</v>
       </c>
       <c r="C137">
-        <f>'Point List'!L166</f>
+        <f>'Point List'!L167</f>
         <v>0</v>
       </c>
       <c r="D137" t="s">
         <v>220</v>
       </c>
       <c r="E137">
-        <f>'Point List'!J166</f>
+        <f>'Point List'!J167</f>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
-        <f>'Point List'!C167</f>
+        <f>'Point List'!C168</f>
         <v>0</v>
       </c>
       <c r="C138">
-        <f>'Point List'!L167</f>
+        <f>'Point List'!L168</f>
         <v>0</v>
       </c>
       <c r="D138" t="s">
         <v>220</v>
       </c>
       <c r="E138">
-        <f>'Point List'!J167</f>
+        <f>'Point List'!J168</f>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
-        <f>'Point List'!C168</f>
+        <f>'Point List'!C169</f>
         <v>0</v>
       </c>
       <c r="C139">
-        <f>'Point List'!L168</f>
+        <f>'Point List'!L169</f>
         <v>0</v>
       </c>
       <c r="D139" t="s">
         <v>220</v>
       </c>
       <c r="E139">
-        <f>'Point List'!J168</f>
+        <f>'Point List'!J169</f>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
-        <f>'Point List'!C169</f>
+        <f>'Point List'!C170</f>
         <v>0</v>
       </c>
       <c r="C140">
-        <f>'Point List'!L169</f>
+        <f>'Point List'!L170</f>
         <v>0</v>
       </c>
       <c r="D140" t="s">
         <v>220</v>
       </c>
       <c r="E140">
-        <f>'Point List'!J169</f>
+        <f>'Point List'!J170</f>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
-        <f>'Point List'!C170</f>
+        <f>'Point List'!C171</f>
         <v>0</v>
       </c>
       <c r="C141">
-        <f>'Point List'!L170</f>
+        <f>'Point List'!L171</f>
         <v>0</v>
       </c>
       <c r="D141" t="s">
         <v>220</v>
       </c>
       <c r="E141">
-        <f>'Point List'!J170</f>
+        <f>'Point List'!J171</f>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
-        <f>'Point List'!C171</f>
+        <f>'Point List'!C172</f>
         <v>0</v>
       </c>
       <c r="C142">
-        <f>'Point List'!L171</f>
+        <f>'Point List'!L172</f>
         <v>0</v>
       </c>
       <c r="D142" t="s">
         <v>220</v>
       </c>
       <c r="E142">
-        <f>'Point List'!J171</f>
+        <f>'Point List'!J172</f>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
-        <f>'Point List'!C172</f>
+        <f>'Point List'!C173</f>
         <v>0</v>
       </c>
       <c r="C143">
-        <f>'Point List'!L172</f>
+        <f>'Point List'!L173</f>
         <v>0</v>
       </c>
       <c r="D143" t="s">
         <v>220</v>
       </c>
       <c r="E143">
-        <f>'Point List'!J172</f>
+        <f>'Point List'!J173</f>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
-        <f>'Point List'!C173</f>
+        <f>'Point List'!C174</f>
         <v>0</v>
       </c>
       <c r="C144">
-        <f>'Point List'!L173</f>
+        <f>'Point List'!L174</f>
         <v>0</v>
       </c>
       <c r="D144" t="s">
         <v>220</v>
       </c>
       <c r="E144">
-        <f>'Point List'!J173</f>
+        <f>'Point List'!J174</f>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
-        <f>'Point List'!C174</f>
+        <f>'Point List'!C175</f>
         <v>0</v>
       </c>
       <c r="C145">
-        <f>'Point List'!L174</f>
+        <f>'Point List'!L175</f>
         <v>0</v>
       </c>
       <c r="D145" t="s">
         <v>220</v>
       </c>
       <c r="E145">
-        <f>'Point List'!J174</f>
+        <f>'Point List'!J175</f>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
-        <f>'Point List'!C175</f>
+        <f>'Point List'!C176</f>
         <v>0</v>
       </c>
       <c r="C146">
-        <f>'Point List'!L175</f>
+        <f>'Point List'!L176</f>
         <v>0</v>
       </c>
       <c r="D146" t="s">
         <v>220</v>
       </c>
       <c r="E146">
-        <f>'Point List'!J175</f>
+        <f>'Point List'!J176</f>
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
-        <f>'Point List'!C176</f>
+        <f>'Point List'!C177</f>
         <v>0</v>
       </c>
       <c r="C147">
-        <f>'Point List'!L176</f>
+        <f>'Point List'!L177</f>
         <v>0</v>
       </c>
       <c r="D147" t="s">
         <v>220</v>
       </c>
       <c r="E147">
-        <f>'Point List'!J176</f>
+        <f>'Point List'!J177</f>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
-        <f>'Point List'!C177</f>
+        <f>'Point List'!C178</f>
         <v>0</v>
       </c>
       <c r="C148">
-        <f>'Point List'!L177</f>
+        <f>'Point List'!L178</f>
         <v>0</v>
       </c>
       <c r="D148" t="s">
         <v>220</v>
       </c>
       <c r="E148">
-        <f>'Point List'!J177</f>
+        <f>'Point List'!J178</f>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
-        <f>'Point List'!C178</f>
+        <f>'Point List'!C179</f>
         <v>0</v>
       </c>
       <c r="C149">
-        <f>'Point List'!L178</f>
+        <f>'Point List'!L179</f>
         <v>0</v>
       </c>
       <c r="D149" t="s">
         <v>220</v>
       </c>
       <c r="E149">
-        <f>'Point List'!J178</f>
+        <f>'Point List'!J179</f>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
-        <f>'Point List'!C179</f>
+        <f>'Point List'!C180</f>
         <v>0</v>
       </c>
       <c r="C150">
-        <f>'Point List'!L179</f>
+        <f>'Point List'!L180</f>
         <v>0</v>
       </c>
       <c r="D150" t="s">
         <v>220</v>
       </c>
       <c r="E150">
-        <f>'Point List'!J179</f>
+        <f>'Point List'!J180</f>
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
-        <f>'Point List'!C180</f>
+        <f>'Point List'!C181</f>
         <v>0</v>
       </c>
       <c r="C151">
-        <f>'Point List'!L180</f>
+        <f>'Point List'!L181</f>
         <v>0</v>
       </c>
       <c r="D151" t="s">
         <v>220</v>
       </c>
       <c r="E151">
-        <f>'Point List'!J180</f>
+        <f>'Point List'!J181</f>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
-        <f>'Point List'!C181</f>
+        <f>'Point List'!C182</f>
         <v>0</v>
       </c>
       <c r="C152">
-        <f>'Point List'!L181</f>
+        <f>'Point List'!L182</f>
         <v>0</v>
       </c>
       <c r="D152" t="s">
         <v>220</v>
       </c>
       <c r="E152">
-        <f>'Point List'!J181</f>
+        <f>'Point List'!J182</f>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
-        <f>'Point List'!C182</f>
+        <f>'Point List'!C183</f>
         <v>0</v>
       </c>
       <c r="C153">
-        <f>'Point List'!L182</f>
+        <f>'Point List'!L183</f>
         <v>0</v>
       </c>
       <c r="D153" t="s">
         <v>220</v>
       </c>
       <c r="E153">
-        <f>'Point List'!J182</f>
+        <f>'Point List'!J183</f>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
-        <f>'Point List'!C183</f>
+        <f>'Point List'!C184</f>
         <v>0</v>
       </c>
       <c r="C154">
-        <f>'Point List'!L183</f>
+        <f>'Point List'!L184</f>
         <v>0</v>
       </c>
       <c r="D154" t="s">
         <v>220</v>
       </c>
       <c r="E154">
-        <f>'Point List'!J183</f>
+        <f>'Point List'!J184</f>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
-        <f>'Point List'!C184</f>
+        <f>'Point List'!C185</f>
         <v>0</v>
       </c>
       <c r="C155">
-        <f>'Point List'!L184</f>
+        <f>'Point List'!L185</f>
         <v>0</v>
       </c>
       <c r="D155" t="s">
         <v>220</v>
       </c>
       <c r="E155">
-        <f>'Point List'!J184</f>
+        <f>'Point List'!J185</f>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
-        <f>'Point List'!C185</f>
+        <f>'Point List'!C186</f>
         <v>0</v>
       </c>
       <c r="C156">
-        <f>'Point List'!L185</f>
+        <f>'Point List'!L186</f>
         <v>0</v>
       </c>
       <c r="D156" t="s">
         <v>220</v>
       </c>
       <c r="E156">
-        <f>'Point List'!J185</f>
+        <f>'Point List'!J186</f>
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
-        <f>'Point List'!C186</f>
+        <f>'Point List'!C187</f>
         <v>0</v>
       </c>
       <c r="C157">
-        <f>'Point List'!L186</f>
+        <f>'Point List'!L187</f>
         <v>0</v>
       </c>
       <c r="D157" t="s">
         <v>220</v>
       </c>
       <c r="E157">
-        <f>'Point List'!J186</f>
+        <f>'Point List'!J187</f>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
-        <f>'Point List'!C187</f>
+        <f>'Point List'!C188</f>
         <v>0</v>
       </c>
       <c r="C158">
-        <f>'Point List'!L187</f>
+        <f>'Point List'!L188</f>
         <v>0</v>
       </c>
       <c r="D158" t="s">
         <v>220</v>
       </c>
       <c r="E158">
-        <f>'Point List'!J187</f>
+        <f>'Point List'!J188</f>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
-        <f>'Point List'!C188</f>
+        <f>'Point List'!C189</f>
         <v>0</v>
       </c>
       <c r="C159">
-        <f>'Point List'!L188</f>
+        <f>'Point List'!L189</f>
         <v>0</v>
       </c>
       <c r="D159" t="s">
         <v>220</v>
       </c>
       <c r="E159">
-        <f>'Point List'!J188</f>
+        <f>'Point List'!J189</f>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
-        <f>'Point List'!C189</f>
+        <f>'Point List'!C190</f>
         <v>0</v>
       </c>
       <c r="C160">
-        <f>'Point List'!L189</f>
+        <f>'Point List'!L190</f>
         <v>0</v>
       </c>
       <c r="D160" t="s">
         <v>220</v>
       </c>
       <c r="E160">
-        <f>'Point List'!J189</f>
+        <f>'Point List'!J190</f>
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
-        <f>'Point List'!C190</f>
+        <f>'Point List'!C191</f>
         <v>0</v>
       </c>
       <c r="C161">
-        <f>'Point List'!L190</f>
+        <f>'Point List'!L191</f>
         <v>0</v>
       </c>
       <c r="D161" t="s">
         <v>220</v>
       </c>
       <c r="E161">
-        <f>'Point List'!J190</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162">
-        <f>'Point List'!C191</f>
-        <v>0</v>
-      </c>
-      <c r="C162">
-        <f>'Point List'!L191</f>
-        <v>0</v>
-      </c>
-      <c r="D162" t="s">
-        <v>220</v>
-      </c>
-      <c r="E162">
         <f>'Point List'!J191</f>
         <v>0</v>
       </c>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1807" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A593D45-0960-4144-B3B4-272349E4B6C2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point List" sheetId="1" r:id="rId1"/>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1807" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A593D45-0960-4144-B3B4-272349E4B6C2}"/>
+  <xr:revisionPtr revIDLastSave="1814" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{713ED015-D111-4AC9-A855-4B9B41B1833B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1252,11 +1252,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1392,19 +1399,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
@@ -1418,13 +1425,10 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1940,7 +1944,21 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}" name="Table1" displayName="Table1" ref="A1:W106" totalsRowShown="0" headerRowDxfId="23">
-  <autoFilter ref="A1:W106" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}"/>
+  <autoFilter ref="A1:W106" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="412557"/>
+        <filter val="412561"/>
+        <filter val="412563"/>
+        <filter val="412565"/>
+        <filter val="412567"/>
+        <filter val="412569"/>
+        <filter val="412571"/>
+        <filter val="412577"/>
+        <filter val="412579"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{423FA6DC-9142-4672-A14E-553234A081EF}" name="Signal Type" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{56D9DA24-EF6A-4F6A-8733-677B62E46902}" name="Tag No" dataDxfId="21"/>
@@ -2266,7 +2284,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -2335,7 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -2411,7 +2429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -2487,7 +2505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2563,7 +2581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -2639,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -2715,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2791,7 +2809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -2867,7 +2885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -2943,7 +2961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -3019,7 +3037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -3095,7 +3113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -3171,7 +3189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>8</v>
       </c>
@@ -3247,7 +3265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -3323,7 +3341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>8</v>
       </c>
@@ -3399,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -3471,7 +3489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
@@ -3543,7 +3561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
@@ -3619,7 +3637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>26</v>
       </c>
@@ -3695,7 +3713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>26</v>
       </c>
@@ -3771,7 +3789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>26</v>
       </c>
@@ -3923,7 +3941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -4006,7 +4024,7 @@
       <c r="B25" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="16" t="s">
         <v>317</v>
       </c>
       <c r="D25" s="14" t="s">
@@ -4455,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>26</v>
       </c>
@@ -4529,7 +4547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>26</v>
       </c>
@@ -4605,7 +4623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>26</v>
       </c>
@@ -4681,7 +4699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>26</v>
       </c>
@@ -4755,7 +4773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>26</v>
       </c>
@@ -4829,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>26</v>
       </c>
@@ -4903,7 +4921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>26</v>
       </c>
@@ -4977,7 +4995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>26</v>
       </c>
@@ -5053,7 +5071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>26</v>
       </c>
@@ -5129,7 +5147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>26</v>
       </c>
@@ -5205,7 +5223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>26</v>
       </c>
@@ -5281,7 +5299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>26</v>
       </c>
@@ -5357,7 +5375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>26</v>
       </c>
@@ -5431,7 +5449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>26</v>
       </c>
@@ -5657,7 +5675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>26</v>
       </c>
@@ -5730,7 +5748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>26</v>
       </c>
@@ -5801,7 +5819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>26</v>
       </c>
@@ -5877,7 +5895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>26</v>
       </c>
@@ -5953,7 +5971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>53</v>
       </c>
@@ -6029,7 +6047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>53</v>
       </c>
@@ -6105,7 +6123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -6181,7 +6199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>53</v>
       </c>
@@ -6257,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>53</v>
       </c>
@@ -6333,7 +6351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>53</v>
       </c>
@@ -6409,7 +6427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>53</v>
       </c>
@@ -6485,7 +6503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>53</v>
       </c>
@@ -6561,7 +6579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>53</v>
       </c>
@@ -6637,7 +6655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>53</v>
       </c>
@@ -6713,7 +6731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>53</v>
       </c>
@@ -6789,7 +6807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>53</v>
       </c>
@@ -6865,7 +6883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>53</v>
       </c>
@@ -6941,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>53</v>
       </c>
@@ -7017,7 +7035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>53</v>
       </c>
@@ -7093,7 +7111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>53</v>
       </c>
@@ -7169,7 +7187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>53</v>
       </c>
@@ -7245,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>71</v>
       </c>
@@ -7321,7 +7339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>71</v>
       </c>
@@ -7397,7 +7415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>71</v>
       </c>
@@ -7473,7 +7491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -7549,7 +7567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>71</v>
       </c>
@@ -7625,7 +7643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>71</v>
       </c>
@@ -7701,7 +7719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>71</v>
       </c>
@@ -7777,7 +7795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>71</v>
       </c>
@@ -7853,7 +7871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>71</v>
       </c>
@@ -7929,7 +7947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>80</v>
       </c>
@@ -7998,7 +8016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>80</v>
       </c>
@@ -8067,7 +8085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>80</v>
       </c>
@@ -8136,7 +8154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:23" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>80</v>
       </c>
@@ -8205,7 +8223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:23" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>80</v>
       </c>
@@ -8257,7 +8275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>80</v>
       </c>
@@ -8309,7 +8327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>80</v>
       </c>
@@ -8378,7 +8396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>80</v>
       </c>
@@ -8447,7 +8465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>80</v>
       </c>
@@ -8516,7 +8534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>80</v>
       </c>
@@ -8585,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>80</v>
       </c>
@@ -8654,7 +8672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>80</v>
       </c>
@@ -8723,7 +8741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>80</v>
       </c>
@@ -8792,7 +8810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>80</v>
       </c>
@@ -8861,7 +8879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>80</v>
       </c>
@@ -8930,7 +8948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>80</v>
       </c>
@@ -8999,7 +9017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>80</v>
       </c>
@@ -9068,7 +9086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>80</v>
       </c>
@@ -9137,7 +9155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>80</v>
       </c>
@@ -9206,7 +9224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>80</v>
       </c>
@@ -9275,7 +9293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>80</v>
       </c>
@@ -9342,7 +9360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
         <v>26</v>
       </c>
@@ -9373,7 +9391,7 @@
         <v>12345</v>
       </c>
       <c r="J98" s="6" t="str">
-        <f t="shared" ref="J98:J105" si="18">_xlfn.CONCAT(0,I98+1)</f>
+        <f t="shared" ref="J98:J104" si="18">_xlfn.CONCAT(0,I98+1)</f>
         <v>012346</v>
       </c>
       <c r="K98" s="9" t="s">
@@ -9414,7 +9432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
         <v>26</v>
       </c>
@@ -9486,7 +9504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>26</v>
       </c>
@@ -9558,7 +9576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
         <v>26</v>
       </c>
@@ -9630,7 +9648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
         <v>26</v>
       </c>
@@ -9702,7 +9720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
         <v>26</v>
       </c>
@@ -9772,7 +9790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
         <v>26</v>
       </c>
@@ -9842,33 +9860,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="16" t="s">
+    <row r="105" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B105" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C105" s="16" t="s">
+      <c r="C105" s="15" t="s">
         <v>388</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="E105" s="17" t="s">
+      <c r="E105" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F105" s="16" t="s">
+      <c r="F105" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="G105" s="16" t="s">
+      <c r="G105" s="15" t="s">
         <v>124</v>
       </c>
       <c r="H105" s="5" t="str">
         <f t="shared" si="17"/>
         <v>0x318A</v>
       </c>
-      <c r="I105" s="16">
+      <c r="I105" s="15">
         <f>I48+100</f>
         <v>12682</v>
       </c>
@@ -9885,7 +9903,7 @@
       <c r="M105" s="15">
         <v>32</v>
       </c>
-      <c r="N105" s="16" t="str">
+      <c r="N105" s="15" t="str">
         <f>_xlfn.CONCAT("%MD",INDEX('Mapping Sheet'!G:G,Table1[[#This Row],[Modbus Address]]-12287,1))</f>
         <v>%MD197</v>
       </c>
@@ -9904,40 +9922,35 @@
       <c r="S105" t="s">
         <v>12</v>
       </c>
-      <c r="T105" s="18" t="s">
+      <c r="T105" t="s">
         <v>224</v>
       </c>
-      <c r="U105" s="18" t="s">
+      <c r="U105" t="s">
         <v>83</v>
       </c>
-      <c r="V105" s="16"/>
+      <c r="V105" s="15"/>
       <c r="W105" s="12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="16"/>
-      <c r="B106" s="16"/>
-      <c r="C106" s="16"/>
+    <row r="106" spans="1:23" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="15"/>
+      <c r="B106" s="15"/>
+      <c r="C106" s="15"/>
       <c r="D106" s="15"/>
-      <c r="E106" s="17"/>
-      <c r="F106" s="16"/>
-      <c r="G106" s="16"/>
-      <c r="H106" s="16"/>
-      <c r="I106" s="16"/>
-      <c r="J106" s="16"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="15"/>
+      <c r="G106" s="15"/>
+      <c r="H106" s="15"/>
+      <c r="I106" s="15"/>
+      <c r="J106" s="15"/>
       <c r="K106" s="15"/>
       <c r="L106" s="15"/>
       <c r="M106" s="15"/>
-      <c r="N106" s="16"/>
-      <c r="O106" s="18"/>
-      <c r="P106" s="16"/>
-      <c r="Q106" s="18"/>
-      <c r="R106" s="16"/>
-      <c r="S106" s="19"/>
-      <c r="T106" s="18"/>
-      <c r="U106" s="18"/>
-      <c r="V106" s="16"/>
+      <c r="N106" s="15"/>
+      <c r="P106" s="15"/>
+      <c r="R106" s="15"/>
+      <c r="V106" s="15"/>
       <c r="W106" s="12" t="b">
         <v>0</v>
       </c>
@@ -10848,7 +10861,7 @@
     <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1011" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="32" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
@@ -14554,7 +14567,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -76438,7 +76451,7 @@
         <v>012346</v>
       </c>
       <c r="K69" t="str">
-        <f>_xlfn.CONCAT(A69,",",B69,",",C69,",",D69,",",E69,",",F69,",",G69)</f>
+        <f t="shared" ref="K69:K75" si="2">_xlfn.CONCAT(A69,",",B69,",",C69,",",D69,",",E69,",",F69,",",G69)</f>
         <v>Primary_Pump_Active,,BitAddress,PLC1,012346,,</v>
       </c>
       <c r="O69" t="s">
@@ -76462,7 +76475,7 @@
         <v>012347</v>
       </c>
       <c r="K70" t="str">
-        <f>_xlfn.CONCAT(A70,",",B70,",",C70,",",D70,",",E70,",",F70,",",G70)</f>
+        <f t="shared" si="2"/>
         <v>Secondary_Pump__Active,,BitAddress,PLC1,012347,,</v>
       </c>
       <c r="O70" t="s">
@@ -76486,7 +76499,7 @@
         <v>012348</v>
       </c>
       <c r="K71" t="str">
-        <f>_xlfn.CONCAT(A71,",",B71,",",C71,",",D71,",",E71,",",F71,",",G71)</f>
+        <f t="shared" si="2"/>
         <v>Simplex_Mode_Active,,BitAddress,PLC1,012348,,</v>
       </c>
       <c r="O71" t="s">
@@ -76510,7 +76523,7 @@
         <v>012349</v>
       </c>
       <c r="K72" t="str">
-        <f>_xlfn.CONCAT(A72,",",B72,",",C72,",",D72,",",E72,",",F72,",",G72)</f>
+        <f t="shared" si="2"/>
         <v>Fan_1_Active,,BitAddress,PLC1,012349,,</v>
       </c>
       <c r="O72" t="s">
@@ -76534,7 +76547,7 @@
         <v>012350</v>
       </c>
       <c r="K73" t="str">
-        <f>_xlfn.CONCAT(A73,",",B73,",",C73,",",D73,",",E73,",",F73,",",G73)</f>
+        <f t="shared" si="2"/>
         <v>Fan_2_Active,,BitAddress,PLC1,012350,,</v>
       </c>
       <c r="O73" t="s">
@@ -76558,7 +76571,7 @@
         <v>012352</v>
       </c>
       <c r="K74" t="str">
-        <f>_xlfn.CONCAT(A74,",",B74,",",C74,",",D74,",",E74,",",F74,",",G74)</f>
+        <f t="shared" si="2"/>
         <v>System_Diagnostics,,BitAddress,PLC1,012352,,</v>
       </c>
       <c r="O74" t="s">
@@ -76582,7 +76595,7 @@
         <v>412683</v>
       </c>
       <c r="K75" t="str">
-        <f>_xlfn.CONCAT(A75,",",B75,",",C75,",",D75,",",E75,",",F75,",",G75)</f>
+        <f t="shared" si="2"/>
         <v>Status_Indicator_Text,,WordAddress,PLC1,412683,,</v>
       </c>
       <c r="O75" t="s">

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2041" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FDFF281-3939-497D-AC0C-BE4B2C87DBDC}"/>
+  <xr:revisionPtr revIDLastSave="2046" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88DB539D-1C08-4058-90BA-464C26EB554C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,9 +690,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>External/Internal</t>
-  </si>
-  <si>
     <t>Address</t>
   </si>
   <si>
@@ -1138,6 +1135,9 @@
   </si>
   <si>
     <t>Output_Water_Level_Low_Low</t>
+  </si>
+  <si>
+    <t>Internal/External</t>
   </si>
   <si>
     <t>Pump_Cycle_Enabled</t>
@@ -2173,7 +2173,7 @@
         <v>178</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>182</v>
@@ -2220,7 +2220,7 @@
         <v>113</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>192</v>
@@ -2291,7 +2291,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>192</v>
@@ -2321,7 +2321,7 @@
         <v>177</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M3" s="6">
         <v>1</v>
@@ -2370,7 +2370,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>192</v>
@@ -2400,7 +2400,7 @@
         <v>177</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M4" s="6">
         <v>1</v>
@@ -2449,7 +2449,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>194</v>
@@ -2479,7 +2479,7 @@
         <v>177</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M5" s="6">
         <v>1</v>
@@ -2528,7 +2528,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>194</v>
@@ -2558,7 +2558,7 @@
         <v>177</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M6" s="6">
         <v>1</v>
@@ -2607,7 +2607,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>193</v>
@@ -2637,7 +2637,7 @@
         <v>179</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M7" s="6">
         <v>1</v>
@@ -2686,7 +2686,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>195</v>
@@ -2716,7 +2716,7 @@
         <v>179</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M8" s="6">
         <v>1</v>
@@ -2844,7 +2844,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>195</v>
@@ -2874,7 +2874,7 @@
         <v>179</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M10" s="6">
         <v>1</v>
@@ -2923,7 +2923,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>195</v>
@@ -2953,7 +2953,7 @@
         <v>179</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M11" s="6">
         <v>1</v>
@@ -3002,7 +3002,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>201</v>
@@ -3032,7 +3032,7 @@
         <v>177</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M12" s="6">
         <v>1</v>
@@ -3081,7 +3081,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>201</v>
@@ -3111,7 +3111,7 @@
         <v>177</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M13" s="6">
         <v>1</v>
@@ -3160,7 +3160,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>194</v>
@@ -3190,7 +3190,7 @@
         <v>177</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M14" s="6">
         <v>1</v>
@@ -3239,7 +3239,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>194</v>
@@ -3269,7 +3269,7 @@
         <v>177</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M15" s="6">
         <v>1</v>
@@ -3348,7 +3348,7 @@
         <v>177</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M16" s="6">
         <v>1</v>
@@ -3551,7 +3551,7 @@
         <v>27</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>192</v>
@@ -3581,7 +3581,7 @@
         <v>180</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M19" s="6">
         <v>1</v>
@@ -3630,7 +3630,7 @@
         <v>28</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>192</v>
@@ -3660,7 +3660,7 @@
         <v>180</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M20" s="6">
         <v>1</v>
@@ -3709,7 +3709,7 @@
         <v>29</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>192</v>
@@ -3739,7 +3739,7 @@
         <v>180</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M21" s="6">
         <v>1</v>
@@ -3788,7 +3788,7 @@
         <v>30</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>192</v>
@@ -3818,7 +3818,7 @@
         <v>180</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M22" s="6">
         <v>1</v>
@@ -3867,7 +3867,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>194</v>
@@ -3897,7 +3897,7 @@
         <v>181</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M23" s="6">
         <v>32</v>
@@ -3976,7 +3976,7 @@
         <v>181</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M24" s="6">
         <v>32</v>
@@ -4025,7 +4025,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>196</v>
@@ -4055,7 +4055,7 @@
         <v>181</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M25" s="6">
         <v>32</v>
@@ -4104,7 +4104,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>197</v>
@@ -4134,7 +4134,7 @@
         <v>181</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M26" s="6">
         <v>32</v>
@@ -4213,7 +4213,7 @@
         <v>181</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M27" s="6">
         <v>32</v>
@@ -4262,7 +4262,7 @@
         <v>37</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>198</v>
@@ -4292,7 +4292,7 @@
         <v>181</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M28" s="6">
         <v>32</v>
@@ -4341,7 +4341,7 @@
         <v>38</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>198</v>
@@ -4371,7 +4371,7 @@
         <v>181</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M29" s="6">
         <v>32</v>
@@ -4420,7 +4420,7 @@
         <v>39</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>198</v>
@@ -4450,7 +4450,7 @@
         <v>181</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M30" s="6">
         <v>32</v>
@@ -4606,7 +4606,7 @@
         <v>181</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M32" s="6">
         <v>32</v>
@@ -4655,7 +4655,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>200</v>
@@ -4685,7 +4685,7 @@
         <v>11</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M33" s="6">
         <v>1</v>
@@ -4734,7 +4734,7 @@
         <v>43</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>200</v>
@@ -4813,7 +4813,7 @@
         <v>44</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>199</v>
@@ -4892,7 +4892,7 @@
         <v>45</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>196</v>
@@ -4971,7 +4971,7 @@
         <v>46</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>196</v>
@@ -5050,7 +5050,7 @@
         <v>47</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D38" s="14" t="s">
         <v>200</v>
@@ -5080,7 +5080,7 @@
         <v>180</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M38" s="6">
         <v>1</v>
@@ -5129,7 +5129,7 @@
         <v>48</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>200</v>
@@ -5159,7 +5159,7 @@
         <v>180</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M39" s="6">
         <v>1</v>
@@ -5208,7 +5208,7 @@
         <v>49</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>199</v>
@@ -5238,7 +5238,7 @@
         <v>180</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M40" s="6">
         <v>1</v>
@@ -5287,7 +5287,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>196</v>
@@ -5317,7 +5317,7 @@
         <v>180</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M41" s="6">
         <v>1</v>
@@ -5366,7 +5366,7 @@
         <v>51</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>196</v>
@@ -5396,7 +5396,7 @@
         <v>180</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M42" s="6">
         <v>1</v>
@@ -5445,7 +5445,7 @@
         <v>52</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>194</v>
@@ -5524,7 +5524,7 @@
         <v>105</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>192</v>
@@ -5603,7 +5603,7 @@
         <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D45" t="s">
         <v>194</v>
@@ -5633,7 +5633,7 @@
         <v>181</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M45" s="6">
         <v>32</v>
@@ -5682,7 +5682,7 @@
         <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D46" t="s">
         <v>194</v>
@@ -5712,7 +5712,7 @@
         <v>181</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M46" s="6">
         <v>32</v>
@@ -5913,7 +5913,7 @@
         <v>111</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>194</v>
@@ -5943,7 +5943,7 @@
         <v>181</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M49" s="6">
         <v>32</v>
@@ -5992,7 +5992,7 @@
         <v>112</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>194</v>
@@ -6022,7 +6022,7 @@
         <v>181</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M50" s="6">
         <v>32</v>
@@ -6071,7 +6071,7 @@
         <v>54</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>198</v>
@@ -6101,7 +6101,7 @@
         <v>180</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M51" s="6">
         <v>1</v>
@@ -6150,7 +6150,7 @@
         <v>55</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>200</v>
@@ -6180,7 +6180,7 @@
         <v>180</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M52" s="6">
         <v>1</v>
@@ -6229,7 +6229,7 @@
         <v>56</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>196</v>
@@ -6259,7 +6259,7 @@
         <v>180</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M53" s="6">
         <v>1</v>
@@ -6308,7 +6308,7 @@
         <v>57</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>194</v>
@@ -6338,7 +6338,7 @@
         <v>180</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M54" s="6">
         <v>1</v>
@@ -6387,7 +6387,7 @@
         <v>58</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>197</v>
@@ -6417,7 +6417,7 @@
         <v>180</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M55" s="6">
         <v>1</v>
@@ -6466,7 +6466,7 @@
         <v>59</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D56" s="14" t="s">
         <v>199</v>
@@ -6496,7 +6496,7 @@
         <v>180</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M56" s="6">
         <v>1</v>
@@ -6545,7 +6545,7 @@
         <v>60</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>194</v>
@@ -6575,7 +6575,7 @@
         <v>180</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M57" s="6">
         <v>1</v>
@@ -6624,7 +6624,7 @@
         <v>61</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>194</v>
@@ -6654,7 +6654,7 @@
         <v>180</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M58" s="6">
         <v>1</v>
@@ -6703,7 +6703,7 @@
         <v>62</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>201</v>
@@ -6733,7 +6733,7 @@
         <v>180</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M59" s="6">
         <v>1</v>
@@ -6782,7 +6782,7 @@
         <v>63</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>201</v>
@@ -6812,7 +6812,7 @@
         <v>180</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M60" s="6">
         <v>1</v>
@@ -6861,7 +6861,7 @@
         <v>64</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>193</v>
@@ -6891,7 +6891,7 @@
         <v>180</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M61" s="6">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         <v>65</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>195</v>
@@ -6970,7 +6970,7 @@
         <v>180</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M62" s="6">
         <v>1</v>
@@ -7019,7 +7019,7 @@
         <v>66</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>197</v>
@@ -7049,7 +7049,7 @@
         <v>180</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M63" s="6">
         <v>1</v>
@@ -7098,7 +7098,7 @@
         <v>67</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>198</v>
@@ -7128,7 +7128,7 @@
         <v>180</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M64" s="6">
         <v>1</v>
@@ -7177,7 +7177,7 @@
         <v>68</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>198</v>
@@ -7207,7 +7207,7 @@
         <v>180</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M65" s="6">
         <v>1</v>
@@ -7256,7 +7256,7 @@
         <v>69</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>198</v>
@@ -7286,7 +7286,7 @@
         <v>180</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M66" s="6">
         <v>1</v>
@@ -7335,7 +7335,7 @@
         <v>70</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D67" s="14" t="s">
         <v>194</v>
@@ -7365,7 +7365,7 @@
         <v>180</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M67" s="6">
         <v>1</v>
@@ -7414,7 +7414,7 @@
         <v>72</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>198</v>
@@ -7444,7 +7444,7 @@
         <v>180</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M68" s="6">
         <v>1</v>
@@ -7493,7 +7493,7 @@
         <v>73</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D69" s="14" t="s">
         <v>200</v>
@@ -7523,7 +7523,7 @@
         <v>180</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M69" s="6">
         <v>1</v>
@@ -7572,7 +7572,7 @@
         <v>74</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>196</v>
@@ -7602,7 +7602,7 @@
         <v>180</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M70" s="6">
         <v>1</v>
@@ -7651,7 +7651,7 @@
         <v>75</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>200</v>
@@ -7681,7 +7681,7 @@
         <v>180</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M71" s="6">
         <v>1</v>
@@ -7730,7 +7730,7 @@
         <v>76</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>196</v>
@@ -7760,7 +7760,7 @@
         <v>180</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M72" s="6">
         <v>1</v>
@@ -7809,7 +7809,7 @@
         <v>77</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>194</v>
@@ -7839,7 +7839,7 @@
         <v>180</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M73" s="6">
         <v>1</v>
@@ -7888,7 +7888,7 @@
         <v>78</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>198</v>
@@ -7918,7 +7918,7 @@
         <v>180</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M74" s="6">
         <v>1</v>
@@ -7967,7 +7967,7 @@
         <v>79</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>193</v>
@@ -7997,7 +7997,7 @@
         <v>180</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M75" s="6">
         <v>1</v>
@@ -8046,7 +8046,7 @@
         <v>123</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>192</v>
@@ -8076,7 +8076,7 @@
         <v>180</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M76" s="6">
         <v>1</v>
@@ -8125,7 +8125,7 @@
         <v>81</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>196</v>
@@ -8199,7 +8199,7 @@
         <v>84</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D78" s="14" t="s">
         <v>198</v>
@@ -8273,7 +8273,7 @@
         <v>86</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>198</v>
@@ -8347,7 +8347,7 @@
         <v>87</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>198</v>
@@ -8535,7 +8535,7 @@
         <v>90</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>197</v>
@@ -8609,7 +8609,7 @@
         <v>91</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>196</v>
@@ -8683,7 +8683,7 @@
         <v>92</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>196</v>
@@ -8757,7 +8757,7 @@
         <v>93</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D86" s="14" t="s">
         <v>200</v>
@@ -8831,7 +8831,7 @@
         <v>94</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D87" s="14" t="s">
         <v>200</v>
@@ -8905,7 +8905,7 @@
         <v>95</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>195</v>
@@ -8979,7 +8979,7 @@
         <v>96</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>195</v>
@@ -9053,7 +9053,7 @@
         <v>97</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D90" s="14" t="s">
         <v>194</v>
@@ -9127,7 +9127,7 @@
         <v>98</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D91" s="14" t="s">
         <v>194</v>
@@ -9201,7 +9201,7 @@
         <v>99</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D92" s="14" t="s">
         <v>193</v>
@@ -9275,7 +9275,7 @@
         <v>100</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>199</v>
@@ -9349,7 +9349,7 @@
         <v>101</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>194</v>
@@ -9423,7 +9423,7 @@
         <v>102</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>194</v>
@@ -9497,7 +9497,7 @@
         <v>103</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>193</v>
@@ -9641,7 +9641,7 @@
         <v>183</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>194</v>
@@ -9671,7 +9671,7 @@
         <v>180</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M98" s="9">
         <v>1</v>
@@ -9716,7 +9716,7 @@
         <v>184</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>194</v>
@@ -9746,7 +9746,7 @@
         <v>180</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M99" s="9">
         <v>1</v>
@@ -9791,7 +9791,7 @@
         <v>185</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>194</v>
@@ -9821,7 +9821,7 @@
         <v>180</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M100" s="9">
         <v>1</v>
@@ -9866,7 +9866,7 @@
         <v>187</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>195</v>
@@ -9896,7 +9896,7 @@
         <v>180</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M101" s="9">
         <v>1</v>
@@ -9941,7 +9941,7 @@
         <v>188</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>195</v>
@@ -9971,7 +9971,7 @@
         <v>180</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M102" s="9">
         <v>1</v>
@@ -10046,7 +10046,7 @@
         <v>180</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M103" s="9">
         <v>1</v>
@@ -10089,7 +10089,7 @@
         <v>191</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D104" s="14" t="s">
         <v>192</v>
@@ -10119,7 +10119,7 @@
         <v>180</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M104" s="9">
         <v>1</v>
@@ -10159,10 +10159,10 @@
         <v>26</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>192</v>
@@ -10171,7 +10171,7 @@
         <v>140</v>
       </c>
       <c r="F105" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G105" s="15" t="s">
         <v>124</v>
@@ -10189,10 +10189,10 @@
         <v>412683</v>
       </c>
       <c r="K105" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L105" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M105" s="15">
         <v>32</v>
@@ -10217,7 +10217,7 @@
         <v>12</v>
       </c>
       <c r="T105" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="U105" t="s">
         <v>83</v>
@@ -11176,7 +11176,7 @@
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="59.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -11184,8 +11184,8 @@
         <v>203</v>
       </c>
       <c r="K1" t="str">
-        <f>A1</f>
-        <v>GP-Pro EX</v>
+        <f>""""&amp;A1&amp;""""</f>
+        <v>"GP-Pro EX"</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -11196,8 +11196,8 @@
         <v>206</v>
       </c>
       <c r="K2" t="str">
-        <f>_xlfn.CONCAT(A2,",",B2)</f>
-        <v>File Type,SymbolVariable</v>
+        <f>_xlfn.CONCAT(""""&amp;A2&amp;"""",",",""""&amp;B2&amp;"""")</f>
+        <v>"File Type","SymbolVariable"</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -11211,8 +11211,8 @@
         <v>0</v>
       </c>
       <c r="K3" t="str">
-        <f>_xlfn.CONCAT(A3,",",B3,",",C3)</f>
-        <v>File Version,3,0</v>
+        <f>_xlfn.CONCAT(""""&amp;A3&amp;"""",",",""""&amp;B3&amp;"""",",",""""&amp;C3&amp;"""")</f>
+        <v>"File Version","3","0"</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -11226,20 +11226,20 @@
         <v>208</v>
       </c>
       <c r="D5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E5" t="s">
         <v>209</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>210</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>211</v>
       </c>
-      <c r="G5" t="s">
-        <v>212</v>
-      </c>
       <c r="K5" t="str">
-        <f>_xlfn.CONCAT(A5,",",B5,",",C5,",",D5,",",E5,",",F5,",",G5)</f>
-        <v>Name,Index,Type,External/Internal,Address,Keep,Comment</v>
+        <f>_xlfn.CONCAT(""""&amp;A5&amp;"""",",",""""&amp;B5&amp;"""",",",""""&amp;C5&amp;"""",",",""""&amp;D5&amp;"""",",",""""&amp;E5&amp;"""",",",""""&amp;F5&amp;"""",",",""""&amp;G5&amp;"""")</f>
+        <v>"Name","Index","Type","Internal/External","Address","Keep","Comment"</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -11252,7 +11252,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E6" t="str">
         <f>'Point List'!J3</f>
@@ -11273,7 +11273,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E7" t="str">
         <f>'Point List'!J4</f>
@@ -11294,7 +11294,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E8" t="str">
         <f>'Point List'!J5</f>
@@ -11315,7 +11315,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E9" t="str">
         <f>'Point List'!J6</f>
@@ -11336,7 +11336,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E10" t="str">
         <f>'Point List'!J7</f>
@@ -11357,7 +11357,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E11" t="str">
         <f>'Point List'!J8</f>
@@ -11378,7 +11378,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E12" t="str">
         <f>'Point List'!J9</f>
@@ -11399,7 +11399,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E13" t="str">
         <f>'Point List'!J10</f>
@@ -11420,7 +11420,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E14" t="str">
         <f>'Point List'!J11</f>
@@ -11441,7 +11441,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E15" t="str">
         <f>'Point List'!J12</f>
@@ -11462,7 +11462,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E16" t="str">
         <f>'Point List'!J13</f>
@@ -11483,7 +11483,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E17" t="str">
         <f>'Point List'!J14</f>
@@ -11504,7 +11504,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E18" t="str">
         <f>'Point List'!J15</f>
@@ -11525,7 +11525,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E19" t="str">
         <f>'Point List'!J16</f>
@@ -11546,7 +11546,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E20" t="str">
         <f>'Point List'!J17</f>
@@ -11567,7 +11567,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E21" t="str">
         <f>'Point List'!J18</f>
@@ -11588,7 +11588,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E22" t="str">
         <f>'Point List'!J19</f>
@@ -11609,7 +11609,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E23" t="str">
         <f>'Point List'!J20</f>
@@ -11630,7 +11630,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E24" t="str">
         <f>'Point List'!J21</f>
@@ -11651,7 +11651,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E25" t="str">
         <f>'Point List'!J22</f>
@@ -11672,7 +11672,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E26" t="str">
         <f>'Point List'!J23</f>
@@ -11693,7 +11693,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E27" t="str">
         <f>'Point List'!J24</f>
@@ -11714,7 +11714,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E28" t="str">
         <f>'Point List'!J25</f>
@@ -11735,7 +11735,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E29" t="str">
         <f>'Point List'!J26</f>
@@ -11756,7 +11756,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E30" t="str">
         <f>'Point List'!J27</f>
@@ -11777,7 +11777,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E31" t="str">
         <f>'Point List'!J28</f>
@@ -11798,7 +11798,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E32" t="str">
         <f>'Point List'!J29</f>
@@ -11819,7 +11819,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E33" t="str">
         <f>'Point List'!J30</f>
@@ -11840,7 +11840,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E34" t="str">
         <f>'Point List'!J31</f>
@@ -11861,7 +11861,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E35" t="str">
         <f>'Point List'!J32</f>
@@ -11882,7 +11882,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E36" t="str">
         <f>'Point List'!J33</f>
@@ -11903,7 +11903,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E37" t="str">
         <f>'Point List'!J34</f>
@@ -11924,7 +11924,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E38" t="str">
         <f>'Point List'!J35</f>
@@ -11945,7 +11945,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E39" t="str">
         <f>'Point List'!J36</f>
@@ -11966,7 +11966,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E40" t="str">
         <f>'Point List'!J37</f>
@@ -11987,7 +11987,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E41" t="str">
         <f>'Point List'!J38</f>
@@ -12008,7 +12008,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E42" t="str">
         <f>'Point List'!J39</f>
@@ -12029,7 +12029,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E43" t="str">
         <f>'Point List'!J40</f>
@@ -12050,7 +12050,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E44" t="str">
         <f>'Point List'!J41</f>
@@ -12071,7 +12071,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E45" t="str">
         <f>'Point List'!J42</f>
@@ -12092,7 +12092,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D46" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E46" t="str">
         <f>'Point List'!J43</f>
@@ -12113,7 +12113,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D47" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E47" t="str">
         <f>'Point List'!J44</f>
@@ -12134,7 +12134,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E48" t="str">
         <f>'Point List'!J45</f>
@@ -12155,7 +12155,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D49" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E49" t="str">
         <f>'Point List'!J46</f>
@@ -12176,7 +12176,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E50" t="str">
         <f>'Point List'!J47</f>
@@ -12197,7 +12197,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E51" t="str">
         <f>'Point List'!J48</f>
@@ -12218,7 +12218,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E52" t="str">
         <f>'Point List'!J49</f>
@@ -12239,7 +12239,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D53" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E53" t="str">
         <f>'Point List'!J50</f>
@@ -12260,7 +12260,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E54" t="str">
         <f>'Point List'!J51</f>
@@ -12281,7 +12281,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D55" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E55" t="str">
         <f>'Point List'!J52</f>
@@ -12302,7 +12302,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E56" t="str">
         <f>'Point List'!J53</f>
@@ -12323,7 +12323,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E57" t="str">
         <f>'Point List'!J54</f>
@@ -12344,7 +12344,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E58" t="str">
         <f>'Point List'!J55</f>
@@ -12365,7 +12365,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D59" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E59" t="str">
         <f>'Point List'!J56</f>
@@ -12386,7 +12386,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D60" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E60" t="str">
         <f>'Point List'!J57</f>
@@ -12407,7 +12407,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D61" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E61" t="str">
         <f>'Point List'!J58</f>
@@ -12428,7 +12428,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D62" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E62" t="str">
         <f>'Point List'!J59</f>
@@ -12449,7 +12449,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D63" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E63" t="str">
         <f>'Point List'!J60</f>
@@ -12470,7 +12470,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E64" t="str">
         <f>'Point List'!J61</f>
@@ -12491,7 +12491,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D65" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E65" t="str">
         <f>'Point List'!J62</f>
@@ -12512,7 +12512,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D66" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E66" t="str">
         <f>'Point List'!J63</f>
@@ -12533,7 +12533,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D67" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E67" t="str">
         <f>'Point List'!J64</f>
@@ -12554,7 +12554,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E68" t="str">
         <f>'Point List'!J65</f>
@@ -12575,7 +12575,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D69" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E69" t="str">
         <f>'Point List'!J66</f>
@@ -12596,7 +12596,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D70" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E70" t="str">
         <f>'Point List'!J67</f>
@@ -12617,7 +12617,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D71" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E71" t="str">
         <f>'Point List'!J68</f>
@@ -12638,7 +12638,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D72" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E72" t="str">
         <f>'Point List'!J69</f>
@@ -12659,7 +12659,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D73" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E73" t="str">
         <f>'Point List'!J70</f>
@@ -12680,7 +12680,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E74" t="str">
         <f>'Point List'!J71</f>
@@ -12701,7 +12701,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D75" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E75" t="str">
         <f>'Point List'!J72</f>
@@ -12722,7 +12722,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D76" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E76" t="str">
         <f>'Point List'!J73</f>
@@ -12743,7 +12743,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D77" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E77" t="str">
         <f>'Point List'!J74</f>
@@ -12764,7 +12764,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D78" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E78" t="str">
         <f>'Point List'!J75</f>
@@ -12785,7 +12785,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E79" t="str">
         <f>'Point List'!J76</f>
@@ -12806,7 +12806,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D80" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E80" t="str">
         <f>'Point List'!J77</f>
@@ -12827,7 +12827,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D81" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E81" t="str">
         <f>'Point List'!J78</f>
@@ -12848,7 +12848,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D82" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E82" t="str">
         <f>'Point List'!J79</f>
@@ -12869,7 +12869,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D83" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E83" t="str">
         <f>'Point List'!J80</f>
@@ -12890,7 +12890,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E84" t="str">
         <f>'Point List'!J81</f>
@@ -12911,7 +12911,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D85" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E85" t="str">
         <f>'Point List'!J82</f>
@@ -12932,7 +12932,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D86" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E86" t="str">
         <f>'Point List'!J83</f>
@@ -12953,7 +12953,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D87" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E87" t="str">
         <f>'Point List'!J84</f>
@@ -12974,7 +12974,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E88" t="str">
         <f>'Point List'!J85</f>
@@ -12995,7 +12995,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E89" t="str">
         <f>'Point List'!J86</f>
@@ -13016,7 +13016,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E90" t="str">
         <f>'Point List'!J87</f>
@@ -13037,7 +13037,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E91" t="str">
         <f>'Point List'!J88</f>
@@ -13058,7 +13058,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D92" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E92" t="str">
         <f>'Point List'!J89</f>
@@ -13079,7 +13079,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D93" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E93" t="str">
         <f>'Point List'!J90</f>
@@ -13100,7 +13100,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D94" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E94" t="str">
         <f>'Point List'!J91</f>
@@ -13121,7 +13121,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E95" t="str">
         <f>'Point List'!J92</f>
@@ -13142,7 +13142,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D96" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E96" t="str">
         <f>'Point List'!J93</f>
@@ -13163,7 +13163,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D97" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E97" t="str">
         <f>'Point List'!J94</f>
@@ -13184,7 +13184,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D98" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E98" t="str">
         <f>'Point List'!J95</f>
@@ -13205,7 +13205,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D99" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E99" t="str">
         <f>'Point List'!J96</f>
@@ -13226,7 +13226,7 @@
         <v>REMOVE</v>
       </c>
       <c r="D100" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E100" t="str">
         <f>'Point List'!J97</f>
@@ -13247,7 +13247,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D101" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E101" t="str">
         <f>'Point List'!J98</f>
@@ -13268,7 +13268,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E102" t="str">
         <f>'Point List'!J99</f>
@@ -13289,7 +13289,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D103" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E103" t="str">
         <f>'Point List'!J100</f>
@@ -13310,7 +13310,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D104" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E104" t="str">
         <f>'Point List'!J101</f>
@@ -13331,7 +13331,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D105" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E105" t="str">
         <f>'Point List'!J102</f>
@@ -13352,7 +13352,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D106" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E106" t="str">
         <f>'Point List'!J103</f>
@@ -13373,7 +13373,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D107" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E107" t="str">
         <f>'Point List'!J104</f>
@@ -13394,7 +13394,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D108" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E108" t="str">
         <f>'Point List'!J105</f>
@@ -13415,7 +13415,7 @@
         <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E109">
         <f>'Point List'!J106</f>
@@ -13432,7 +13432,7 @@
         <v>0</v>
       </c>
       <c r="D110" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E110">
         <f>'Point List'!J107</f>
@@ -13449,7 +13449,7 @@
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E111">
         <f>'Point List'!J108</f>
@@ -13466,7 +13466,7 @@
         <v>0</v>
       </c>
       <c r="D112" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E112">
         <f>'Point List'!J109</f>
@@ -13483,7 +13483,7 @@
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E113">
         <f>'Point List'!J110</f>
@@ -13500,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E114">
         <f>'Point List'!J111</f>
@@ -13517,7 +13517,7 @@
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E115">
         <f>'Point List'!J112</f>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E116">
         <f>'Point List'!J113</f>
@@ -13551,7 +13551,7 @@
         <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E117">
         <f>'Point List'!J114</f>
@@ -13568,7 +13568,7 @@
         <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E118">
         <f>'Point List'!J115</f>
@@ -13585,7 +13585,7 @@
         <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E119">
         <f>'Point List'!J116</f>
@@ -13602,7 +13602,7 @@
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E120">
         <f>'Point List'!J117</f>
@@ -13619,7 +13619,7 @@
         <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E121">
         <f>'Point List'!J118</f>
@@ -13636,7 +13636,7 @@
         <v>0</v>
       </c>
       <c r="D122" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E122">
         <f>'Point List'!J119</f>
@@ -13653,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E123">
         <f>'Point List'!J120</f>
@@ -13670,7 +13670,7 @@
         <v>0</v>
       </c>
       <c r="D124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E124">
         <f>'Point List'!J121</f>
@@ -13687,7 +13687,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E125">
         <f>'Point List'!J122</f>
@@ -13704,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E126">
         <f>'Point List'!J123</f>
@@ -13721,7 +13721,7 @@
         <v>0</v>
       </c>
       <c r="D127" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E127">
         <f>'Point List'!J124</f>
@@ -13738,7 +13738,7 @@
         <v>0</v>
       </c>
       <c r="D128" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E128">
         <f>'Point List'!J125</f>
@@ -13755,7 +13755,7 @@
         <v>0</v>
       </c>
       <c r="D129" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E129">
         <f>'Point List'!J126</f>
@@ -13772,7 +13772,7 @@
         <v>0</v>
       </c>
       <c r="D130" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E130">
         <f>'Point List'!J127</f>
@@ -13789,7 +13789,7 @@
         <v>0</v>
       </c>
       <c r="D131" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E131">
         <f>'Point List'!J128</f>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="D132" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E132">
         <f>'Point List'!J129</f>
@@ -13823,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E133">
         <f>'Point List'!J130</f>
@@ -13840,7 +13840,7 @@
         <v>0</v>
       </c>
       <c r="D134" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E134">
         <f>'Point List'!J131</f>
@@ -13857,7 +13857,7 @@
         <v>0</v>
       </c>
       <c r="D135" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E135">
         <f>'Point List'!J132</f>
@@ -13874,7 +13874,7 @@
         <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E136">
         <f>'Point List'!J133</f>
@@ -13891,7 +13891,7 @@
         <v>0</v>
       </c>
       <c r="D137" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E137">
         <f>'Point List'!J134</f>
@@ -13908,7 +13908,7 @@
         <v>0</v>
       </c>
       <c r="D138" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E138">
         <f>'Point List'!J135</f>
@@ -13925,7 +13925,7 @@
         <v>0</v>
       </c>
       <c r="D139" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E139">
         <f>'Point List'!J136</f>
@@ -13942,7 +13942,7 @@
         <v>0</v>
       </c>
       <c r="D140" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E140">
         <f>'Point List'!J137</f>
@@ -13959,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E141">
         <f>'Point List'!J138</f>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E142">
         <f>'Point List'!J139</f>
@@ -13993,7 +13993,7 @@
         <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E143">
         <f>'Point List'!J140</f>
@@ -14010,7 +14010,7 @@
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E144">
         <f>'Point List'!J141</f>
@@ -14027,7 +14027,7 @@
         <v>0</v>
       </c>
       <c r="D145" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E145">
         <f>'Point List'!J142</f>
@@ -14044,7 +14044,7 @@
         <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E146">
         <f>'Point List'!J143</f>
@@ -14061,7 +14061,7 @@
         <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E147">
         <f>'Point List'!J144</f>
@@ -14078,7 +14078,7 @@
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E148">
         <f>'Point List'!J145</f>
@@ -14095,7 +14095,7 @@
         <v>0</v>
       </c>
       <c r="D149" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E149">
         <f>'Point List'!J146</f>
@@ -14112,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="D150" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E150">
         <f>'Point List'!J147</f>
@@ -14129,7 +14129,7 @@
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E151">
         <f>'Point List'!J148</f>
@@ -14146,7 +14146,7 @@
         <v>0</v>
       </c>
       <c r="D152" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E152">
         <f>'Point List'!J149</f>
@@ -14163,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E153">
         <f>'Point List'!J150</f>
@@ -14180,7 +14180,7 @@
         <v>0</v>
       </c>
       <c r="D154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E154">
         <f>'Point List'!J151</f>
@@ -14197,7 +14197,7 @@
         <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E155">
         <f>'Point List'!J152</f>
@@ -14214,7 +14214,7 @@
         <v>0</v>
       </c>
       <c r="D156" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E156">
         <f>'Point List'!J153</f>
@@ -14231,7 +14231,7 @@
         <v>0</v>
       </c>
       <c r="D157" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E157">
         <f>'Point List'!J154</f>
@@ -14248,7 +14248,7 @@
         <v>0</v>
       </c>
       <c r="D158" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E158">
         <f>'Point List'!J155</f>
@@ -14265,7 +14265,7 @@
         <v>0</v>
       </c>
       <c r="D159" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E159">
         <f>'Point List'!J156</f>
@@ -14282,7 +14282,7 @@
         <v>0</v>
       </c>
       <c r="D160" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E160">
         <f>'Point List'!J157</f>
@@ -14299,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="D161" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E161">
         <f>'Point List'!J158</f>
@@ -14316,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="D162" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E162">
         <f>'Point List'!J159</f>
@@ -14333,7 +14333,7 @@
         <v>0</v>
       </c>
       <c r="D163" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E163">
         <f>'Point List'!J160</f>
@@ -14350,7 +14350,7 @@
         <v>0</v>
       </c>
       <c r="D164" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E164">
         <f>'Point List'!J161</f>
@@ -14367,7 +14367,7 @@
         <v>0</v>
       </c>
       <c r="D165" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E165">
         <f>'Point List'!J162</f>
@@ -14384,7 +14384,7 @@
         <v>0</v>
       </c>
       <c r="D166" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E166">
         <f>'Point List'!J163</f>
@@ -14401,7 +14401,7 @@
         <v>0</v>
       </c>
       <c r="D167" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E167">
         <f>'Point List'!J164</f>
@@ -14418,7 +14418,7 @@
         <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E168">
         <f>'Point List'!J165</f>
@@ -14435,7 +14435,7 @@
         <v>0</v>
       </c>
       <c r="D169" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E169">
         <f>'Point List'!J166</f>
@@ -14452,7 +14452,7 @@
         <v>0</v>
       </c>
       <c r="D170" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E170">
         <f>'Point List'!J167</f>
@@ -14469,7 +14469,7 @@
         <v>0</v>
       </c>
       <c r="D171" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E171">
         <f>'Point List'!J168</f>
@@ -14486,7 +14486,7 @@
         <v>0</v>
       </c>
       <c r="D172" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E172">
         <f>'Point List'!J169</f>
@@ -14503,7 +14503,7 @@
         <v>0</v>
       </c>
       <c r="D173" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E173">
         <f>'Point List'!J170</f>
@@ -14520,7 +14520,7 @@
         <v>0</v>
       </c>
       <c r="D174" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E174">
         <f>'Point List'!J171</f>
@@ -14537,7 +14537,7 @@
         <v>0</v>
       </c>
       <c r="D175" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E175">
         <f>'Point List'!J172</f>
@@ -14554,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="D176" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E176">
         <f>'Point List'!J173</f>
@@ -14571,7 +14571,7 @@
         <v>0</v>
       </c>
       <c r="D177" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E177">
         <f>'Point List'!J174</f>
@@ -14588,7 +14588,7 @@
         <v>0</v>
       </c>
       <c r="D178" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E178">
         <f>'Point List'!J175</f>
@@ -14605,7 +14605,7 @@
         <v>0</v>
       </c>
       <c r="D179" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E179">
         <f>'Point List'!J176</f>
@@ -14622,7 +14622,7 @@
         <v>0</v>
       </c>
       <c r="D180" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E180">
         <f>'Point List'!J177</f>
@@ -14639,7 +14639,7 @@
         <v>0</v>
       </c>
       <c r="D181" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E181">
         <f>'Point List'!J178</f>
@@ -14656,7 +14656,7 @@
         <v>0</v>
       </c>
       <c r="D182" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E182">
         <f>'Point List'!J179</f>
@@ -14673,7 +14673,7 @@
         <v>0</v>
       </c>
       <c r="D183" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E183">
         <f>'Point List'!J180</f>
@@ -14690,7 +14690,7 @@
         <v>0</v>
       </c>
       <c r="D184" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E184">
         <f>'Point List'!J181</f>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="D185" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E185">
         <f>'Point List'!J182</f>
@@ -14724,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="D186" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E186">
         <f>'Point List'!J183</f>
@@ -14741,7 +14741,7 @@
         <v>0</v>
       </c>
       <c r="D187" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E187">
         <f>'Point List'!J184</f>
@@ -14758,7 +14758,7 @@
         <v>0</v>
       </c>
       <c r="D188" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E188">
         <f>'Point List'!J185</f>
@@ -14775,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="D189" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E189">
         <f>'Point List'!J186</f>
@@ -14792,7 +14792,7 @@
         <v>0</v>
       </c>
       <c r="D190" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E190">
         <f>'Point List'!J187</f>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="D191" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E191">
         <f>'Point List'!J188</f>
@@ -14826,7 +14826,7 @@
         <v>0</v>
       </c>
       <c r="D192" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E192">
         <f>'Point List'!J189</f>
@@ -14843,7 +14843,7 @@
         <v>0</v>
       </c>
       <c r="D193" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E193">
         <f>'Point List'!J190</f>
@@ -14860,7 +14860,7 @@
         <v>0</v>
       </c>
       <c r="D194" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E194">
         <f>'Point List'!J191</f>
@@ -75157,7 +75157,7 @@
         <v>"GP-Pro EX"</v>
       </c>
       <c r="O1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -75172,7 +75172,7 @@
         <v>"File Type","SymbolVariable"</v>
       </c>
       <c r="O2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -75190,7 +75190,7 @@
         <v>"File Version","3","0"</v>
       </c>
       <c r="O3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -75204,23 +75204,23 @@
         <v>208</v>
       </c>
       <c r="D5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E5" t="s">
         <v>209</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>210</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>211</v>
-      </c>
-      <c r="G5" t="s">
-        <v>212</v>
       </c>
       <c r="K5" t="str">
         <f>_xlfn.CONCAT(""""&amp;A5&amp;"""",",",""""&amp;B5&amp;"""",",",""""&amp;C5&amp;"""",",",""""&amp;D5&amp;"""",",",""""&amp;E5&amp;"""",",",""""&amp;F5&amp;"""",",",""""&amp;G5&amp;"""")</f>
-        <v>"Name","Index","Type","External/Internal","Address","Keep","Comment"</v>
+        <v>"Name","Index","Type","Internal/External","Address","Keep","Comment"</v>
       </c>
       <c r="O5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -75233,7 +75233,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E6" t="str">
         <f>'Point List'!J3</f>
@@ -75244,7 +75244,7 @@
         <v>System_Start,,BitAddress,PLC1,012289,,</v>
       </c>
       <c r="O6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -75257,7 +75257,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E7" t="str">
         <f>'Point List'!J4</f>
@@ -75268,7 +75268,7 @@
         <v>System_Shutdown,,BitAddress,PLC1,012290,,</v>
       </c>
       <c r="O7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -75281,7 +75281,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E8" t="str">
         <f>'Point List'!J5</f>
@@ -75292,7 +75292,7 @@
         <v>Simplex_Mode,,BitAddress,PLC1,012291,,</v>
       </c>
       <c r="O8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -75305,7 +75305,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E9" t="str">
         <f>'Point List'!J6</f>
@@ -75316,7 +75316,7 @@
         <v>Manual_Turnover,,BitAddress,PLC1,012292,,</v>
       </c>
       <c r="O9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -75329,7 +75329,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E10" t="str">
         <f>'Point List'!J7</f>
@@ -75340,7 +75340,7 @@
         <v>Enable_Manual_Valve_Control,,BitAddress,PLC1,012293,,</v>
       </c>
       <c r="O10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -75353,7 +75353,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E11" t="str">
         <f>'Point List'!J8</f>
@@ -75364,7 +75364,7 @@
         <v>Enable_Manual_Fan_Control,,BitAddress,PLC1,012294,,</v>
       </c>
       <c r="O11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -75377,7 +75377,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E12" t="str">
         <f>'Point List'!J10</f>
@@ -75388,7 +75388,7 @@
         <v>Force_Fan_1_On_Off,,BitAddress,PLC1,012296,,</v>
       </c>
       <c r="O12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -75401,7 +75401,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E13" t="str">
         <f>'Point List'!J11</f>
@@ -75412,7 +75412,7 @@
         <v>Force_Fan_2_On_Off,,BitAddress,PLC1,012297,,</v>
       </c>
       <c r="O13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -75425,7 +75425,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E14" t="str">
         <f>'Point List'!J12</f>
@@ -75436,7 +75436,7 @@
         <v>Primary_Hydraulic_Fault_ACK,,BitAddress,PLC1,012298,,</v>
       </c>
       <c r="O14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -75449,7 +75449,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E15" t="str">
         <f>'Point List'!J13</f>
@@ -75460,7 +75460,7 @@
         <v>Secondary_Hydraulic_Fault_ACK,,BitAddress,PLC1,012299,,</v>
       </c>
       <c r="O15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -75473,7 +75473,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E16" t="str">
         <f>'Point List'!J14</f>
@@ -75484,7 +75484,7 @@
         <v>Enable_Pump_Cycling,,BitAddress,PLC1,012300,,</v>
       </c>
       <c r="O16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -75497,7 +75497,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E17" t="str">
         <f>'Point List'!J15</f>
@@ -75508,7 +75508,7 @@
         <v>Reset_Pump_Differential_Signal,,BitAddress,PLC1,012301,,</v>
       </c>
       <c r="O17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -75521,7 +75521,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E18" t="str">
         <f>'Point List'!J16</f>
@@ -75532,7 +75532,7 @@
         <v>Fault_Override,,BitAddress,PLC1,012302,,</v>
       </c>
       <c r="O18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -75545,7 +75545,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E19" t="str">
         <f>'Point List'!J19</f>
@@ -75556,7 +75556,7 @@
         <v>System_On,,BitAddress,PLC1,012305,,</v>
       </c>
       <c r="O19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -75569,7 +75569,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E20" t="str">
         <f>'Point List'!J20</f>
@@ -75580,7 +75580,7 @@
         <v>System_Shutting_Down,,BitAddress,PLC1,012306,,</v>
       </c>
       <c r="O20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -75593,7 +75593,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E21" t="str">
         <f>'Point List'!J21</f>
@@ -75604,7 +75604,7 @@
         <v>System_Initializing,,BitAddress,PLC1,012307,,</v>
       </c>
       <c r="O21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -75617,7 +75617,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E22" t="str">
         <f>'Point List'!J22</f>
@@ -75628,7 +75628,7 @@
         <v>System_Calibrating,,BitAddress,PLC1,012308,,</v>
       </c>
       <c r="O22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -75641,7 +75641,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E23" t="str">
         <f>'Point List'!J23</f>
@@ -75652,7 +75652,7 @@
         <v>Measured_Pump_Power,,WordAddress,PLC1,412557,,</v>
       </c>
       <c r="O23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -75665,7 +75665,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E24" t="str">
         <f>'Point List'!J24</f>
@@ -75676,7 +75676,7 @@
         <v>Meas_Av_Temp,,WordAddress,PLC1,412559,,</v>
       </c>
       <c r="O24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -75689,7 +75689,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E25" t="str">
         <f>'Point List'!J25</f>
@@ -75700,7 +75700,7 @@
         <v>Measured_Conductivity,,WordAddress,PLC1,412561,,</v>
       </c>
       <c r="O25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -75713,7 +75713,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E26" t="str">
         <f>'Point List'!J26</f>
@@ -75724,7 +75724,7 @@
         <v>Measured_Flow,,WordAddress,PLC1,412563,,</v>
       </c>
       <c r="O26" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
@@ -75737,7 +75737,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E27" t="str">
         <f>'Point List'!J27</f>
@@ -75748,7 +75748,7 @@
         <v>Valve_Position_Input,,WordAddress,PLC1,412565,,</v>
       </c>
       <c r="O27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -75761,7 +75761,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E28" t="str">
         <f>'Point List'!J28</f>
@@ -75772,7 +75772,7 @@
         <v>Real_RTD_1_Signal,,WordAddress,PLC1,412567,,</v>
       </c>
       <c r="O28" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -75785,7 +75785,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E29" t="str">
         <f>'Point List'!J29</f>
@@ -75796,7 +75796,7 @@
         <v>Real_RTD_2_Signal,,WordAddress,PLC1,412569,,</v>
       </c>
       <c r="O29" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -75809,7 +75809,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E30" t="str">
         <f>'Point List'!J30</f>
@@ -75820,7 +75820,7 @@
         <v>Real_RTD_3_Signal,,WordAddress,PLC1,412571,,</v>
       </c>
       <c r="O30" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -75833,7 +75833,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E31" t="str">
         <f>'Point List'!J32</f>
@@ -75844,7 +75844,7 @@
         <v>Feedback_Valve_Position,,WordAddress,PLC1,412575,,</v>
       </c>
       <c r="O31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -75857,7 +75857,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E32" t="str">
         <f>'Point List'!J33</f>
@@ -75868,7 +75868,7 @@
         <v>Debounced_Water_Level_Low_Signal,,WordAddress,PLC1,012309,,</v>
       </c>
       <c r="O32" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
@@ -75881,7 +75881,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E33" t="str">
         <f>'Point List'!J38</f>
@@ -75892,7 +75892,7 @@
         <v>Output_Water_Level_Low_Signal,,BitAddress,PLC1,012314,,</v>
       </c>
       <c r="O33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
@@ -75905,7 +75905,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E34" t="str">
         <f>'Point List'!J39</f>
@@ -75916,7 +75916,7 @@
         <v>Output_Water_Level_Low_Low,,BitAddress,PLC1,012315,,</v>
       </c>
       <c r="O34" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
@@ -75929,7 +75929,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E35" t="str">
         <f>'Point List'!J40</f>
@@ -75940,7 +75940,7 @@
         <v>Output_Pressure_Signal,,BitAddress,PLC1,012316,,</v>
       </c>
       <c r="O35" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -75953,7 +75953,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E36" t="str">
         <f>'Point List'!J41</f>
@@ -75964,7 +75964,7 @@
         <v>Output_Conductivity_Alarm_Signal,,BitAddress,PLC1,012317,,</v>
       </c>
       <c r="O36" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
@@ -75977,7 +75977,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E37" t="str">
         <f>'Point List'!J42</f>
@@ -75988,7 +75988,7 @@
         <v>Output_Conductivity_Fault_Signal,,BitAddress,PLC1,012318,,</v>
       </c>
       <c r="O37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -76001,7 +76001,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E38" t="str">
         <f>'Point List'!J45</f>
@@ -76012,7 +76012,7 @@
         <v>Measured_Active_Pump__Voltage,,WordAddress,PLC1,412577,,</v>
       </c>
       <c r="O38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
@@ -76025,7 +76025,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E39" t="str">
         <f>'Point List'!J46</f>
@@ -76036,7 +76036,7 @@
         <v>Measured_Active_Pump__Current,,WordAddress,PLC1,412579,,</v>
       </c>
       <c r="O39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
@@ -76049,7 +76049,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E40" t="str">
         <f>'Point List'!J49</f>
@@ -76060,7 +76060,7 @@
         <v>Pump_1_Total_Hours,,WordAddress,PLC1,412455,,</v>
       </c>
       <c r="O40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
@@ -76073,7 +76073,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E41" t="str">
         <f>'Point List'!J50</f>
@@ -76084,7 +76084,7 @@
         <v>Pump_2_Total_Hours,,WordAddress,PLC1,412457,,</v>
       </c>
       <c r="O41" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
@@ -76097,7 +76097,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E42" t="str">
         <f>'Point List'!J51</f>
@@ -76108,7 +76108,7 @@
         <v>High_Coolant_Temperature_,,BitAddress,PLC1,012320,,</v>
       </c>
       <c r="O42" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
@@ -76121,7 +76121,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E43" t="str">
         <f>'Point List'!J52</f>
@@ -76132,7 +76132,7 @@
         <v>Low_Coolant_Level_in_Vessel,,BitAddress,PLC1,012321,,</v>
       </c>
       <c r="O43" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
@@ -76145,7 +76145,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E44" t="str">
         <f>'Point List'!J53</f>
@@ -76156,7 +76156,7 @@
         <v>High_Coolant_Conductivity_,,BitAddress,PLC1,012322,,</v>
       </c>
       <c r="O44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
@@ -76169,7 +76169,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E45" t="str">
         <f>'Point List'!J54</f>
@@ -76180,7 +76180,7 @@
         <v>Low_Hydraulic_Power,,BitAddress,PLC1,012323,,</v>
       </c>
       <c r="O45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
@@ -76193,7 +76193,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D46" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E46" t="str">
         <f>'Point List'!J55</f>
@@ -76204,7 +76204,7 @@
         <v>Low_Hydraulic_Flow,,BitAddress,PLC1,012324,,</v>
       </c>
       <c r="O46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
@@ -76217,7 +76217,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D47" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E47" t="str">
         <f>'Point List'!J56</f>
@@ -76228,7 +76228,7 @@
         <v>Low_Hydraulic_Pressure,,BitAddress,PLC1,012325,,</v>
       </c>
       <c r="O47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
@@ -76241,7 +76241,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E48" t="str">
         <f>'Point List'!J57</f>
@@ -76252,7 +76252,7 @@
         <v>Voltage_Signal_Malfunction,,BitAddress,PLC1,012326,,</v>
       </c>
       <c r="O48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
@@ -76265,7 +76265,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D49" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E49" t="str">
         <f>'Point List'!J58</f>
@@ -76276,7 +76276,7 @@
         <v>Current_Signal_Malfunction,,BitAddress,PLC1,012327,,</v>
       </c>
       <c r="O49" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
@@ -76289,7 +76289,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E50" t="str">
         <f>'Point List'!J59</f>
@@ -76310,7 +76310,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E51" t="str">
         <f>'Point List'!J60</f>
@@ -76331,7 +76331,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E52" t="str">
         <f>'Point List'!J61</f>
@@ -76352,7 +76352,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D53" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E53" t="str">
         <f>'Point List'!J62</f>
@@ -76373,7 +76373,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E54" t="str">
         <f>'Point List'!J63</f>
@@ -76394,7 +76394,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D55" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E55" t="str">
         <f>'Point List'!J64</f>
@@ -76415,7 +76415,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E56" t="str">
         <f>'Point List'!J65</f>
@@ -76436,7 +76436,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E57" t="str">
         <f>'Point List'!J66</f>
@@ -76457,7 +76457,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E58" t="str">
         <f>'Point List'!J67</f>
@@ -76478,7 +76478,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D59" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E59" t="str">
         <f>'Point List'!J68</f>
@@ -76499,7 +76499,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D60" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E60" t="str">
         <f>'Point List'!J69</f>
@@ -76520,7 +76520,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D61" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E61" t="str">
         <f>'Point List'!J70</f>
@@ -76541,7 +76541,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D62" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E62" t="str">
         <f>'Point List'!J71</f>
@@ -76562,7 +76562,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D63" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E63" t="str">
         <f>'Point List'!J72</f>
@@ -76583,7 +76583,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E64" t="str">
         <f>'Point List'!J73</f>
@@ -76604,7 +76604,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D65" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E65" t="str">
         <f>'Point List'!J74</f>
@@ -76625,7 +76625,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D66" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E66" t="str">
         <f>'Point List'!J75</f>
@@ -76646,7 +76646,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D67" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E67" t="str">
         <f>'Point List'!J76</f>
@@ -76667,7 +76667,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E68" t="str">
         <f>'Point List'!J98</f>
@@ -76688,7 +76688,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D69" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E69" t="str">
         <f>'Point List'!J99</f>
@@ -76709,7 +76709,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D70" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E70" t="str">
         <f>'Point List'!J100</f>
@@ -76730,7 +76730,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D71" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E71" t="str">
         <f>'Point List'!J101</f>
@@ -76751,7 +76751,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D72" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E72" t="str">
         <f>'Point List'!J102</f>
@@ -76772,7 +76772,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D73" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E73" t="str">
         <f>'Point List'!J103</f>
@@ -76793,7 +76793,7 @@
         <v>BitAddress</v>
       </c>
       <c r="D74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E74" t="str">
         <f>'Point List'!J104</f>
@@ -76814,7 +76814,7 @@
         <v>WordAddress</v>
       </c>
       <c r="D75" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E75" t="str">
         <f>'Point List'!J105</f>
@@ -76835,7 +76835,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E76">
         <f>'Point List'!J174</f>
@@ -76852,7 +76852,7 @@
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E77">
         <f>'Point List'!J175</f>
@@ -76869,7 +76869,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E78">
         <f>'Point List'!J176</f>
@@ -76886,7 +76886,7 @@
         <v>0</v>
       </c>
       <c r="D79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E79">
         <f>'Point List'!J177</f>
@@ -76903,7 +76903,7 @@
         <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E80">
         <f>'Point List'!J178</f>
@@ -76920,7 +76920,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E81">
         <f>'Point List'!J179</f>
@@ -76937,7 +76937,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E82">
         <f>'Point List'!J180</f>
@@ -76954,7 +76954,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E83">
         <f>'Point List'!J181</f>
@@ -76971,7 +76971,7 @@
         <v>0</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E84">
         <f>'Point List'!J182</f>
@@ -76988,7 +76988,7 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E85">
         <f>'Point List'!J183</f>
@@ -77005,7 +77005,7 @@
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E86">
         <f>'Point List'!J184</f>
@@ -77022,7 +77022,7 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E87">
         <f>'Point List'!J185</f>
@@ -77039,7 +77039,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E88">
         <f>'Point List'!J186</f>
@@ -77056,7 +77056,7 @@
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E89">
         <f>'Point List'!J187</f>
@@ -77073,7 +77073,7 @@
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E90">
         <f>'Point List'!J188</f>
@@ -77090,7 +77090,7 @@
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E91">
         <f>'Point List'!J189</f>
@@ -77107,7 +77107,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E92">
         <f>'Point List'!J190</f>
@@ -77124,7 +77124,7 @@
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E93">
         <f>'Point List'!J191</f>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2046" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88DB539D-1C08-4058-90BA-464C26EB554C}"/>
+  <xr:revisionPtr revIDLastSave="2071" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B7649CE-CF59-45F1-B9E0-04BF781030D4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="348">
   <si>
     <t>Signal Type</t>
   </si>
@@ -753,19 +753,10 @@
     <t>Enable Manual Fan Control,,BitAddress,PLC1,012294,,</t>
   </si>
   <si>
-    <t>Force Fan 2 On/Off,,BitAddress,PLC1,012297,,</t>
-  </si>
-  <si>
     <t>Primary Hydraulic Fault ACK,,BitAddress,PLC1,012298,,</t>
   </si>
   <si>
     <t>Secondary Hydraulic Fault ACK,,BitAddress,PLC1,012299,,</t>
-  </si>
-  <si>
-    <t>Enable Pump Cycling,,BitAddress,PLC1,012300,,</t>
-  </si>
-  <si>
-    <t>Reset Pump Differential Signal,,BitAddress,PLC1,012301,,</t>
   </si>
   <si>
     <t>Fault ACK,,BitAddress,PLC1,012302,,</t>
@@ -777,28 +768,7 @@
     <t>Measured Flow,,WordAddress,PLC1,412563,,</t>
   </si>
   <si>
-    <t>Valve Open Percentage,,WordAddress,PLC1,412565,,</t>
-  </si>
-  <si>
-    <t>Real RTD 1 Signal,,WordAddress,PLC1,412567,,</t>
-  </si>
-  <si>
-    <t>Real RTD 2 Signal,,WordAddress,PLC1,412569,,</t>
-  </si>
-  <si>
-    <t>Real RTD 3 Signal,,WordAddress,PLC1,412571,,</t>
-  </si>
-  <si>
-    <t>Measured Valve Position ,,WordAddress,PLC1,412575,,</t>
-  </si>
-  <si>
-    <t>Debounced Water Level Low Signal,,WordAddress,PLC1,012309,,</t>
-  </si>
-  <si>
     <t>Output Water Level Low Low Signal,,BitAddress,PLC1,012315,,</t>
-  </si>
-  <si>
-    <t>Output Pressure Signal,,BitAddress,PLC1,012316,,</t>
   </si>
   <si>
     <t>Output Conductivity Alarm Signal,,BitAddress,PLC1,012317,,</t>
@@ -819,46 +789,7 @@
     <t>Flow Signal Malfunction,,BitAddress,PLC1,012332,,</t>
   </si>
   <si>
-    <t>Bad RTD 1 Signal,,BitAddress,PLC1,012333,,</t>
-  </si>
-  <si>
     <t>Bad RTD 2 Signal,,BitAddress,PLC1,012334,,</t>
-  </si>
-  <si>
-    <t>Bad RTD 3 Signal,,BitAddress,PLC1,012335,,</t>
-  </si>
-  <si>
-    <t>Pump Cycle Alarm,,BitAddress,PLC1,012336,,</t>
-  </si>
-  <si>
-    <t>Critical Conductivity,,BitAddress,PLC1,012339,,</t>
-  </si>
-  <si>
-    <t>Level Sensor Malfunction,,BitAddress,PLC1,012340,,</t>
-  </si>
-  <si>
-    <t>Temperature Sensor Malfunction,,BitAddress,PLC1,012343,,</t>
-  </si>
-  <si>
-    <t>Bad Valve Pos,,BitAddress,PLC1,012344,,</t>
-  </si>
-  <si>
-    <t>Master Fault Signal,,BitAddress,PLC1,012345,,</t>
-  </si>
-  <si>
-    <t>Primary Pump Active,,BitAddress,PLC1,012346,,</t>
-  </si>
-  <si>
-    <t>Secondary Pump  Active,,BitAddress,PLC1,012347,,</t>
-  </si>
-  <si>
-    <t>Simplex Mode Active,,BitAddress,PLC1,012348,,</t>
-  </si>
-  <si>
-    <t>Fan 1 Active,,BitAddress,PLC1,012349,,</t>
-  </si>
-  <si>
-    <t>Fan 2 Active,,BitAddress,PLC1,012350,,</t>
   </si>
   <si>
     <t>System Diagnostics,,BitAddress,PLC1,012352,,</t>
@@ -1874,9 +1805,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}" name="Table1" displayName="Table1" ref="A1:X106" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="A1:X106" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}">
-    <filterColumn colId="2">
+    <filterColumn colId="4">
       <filters>
-        <filter val="AVAILABLE"/>
+        <filter val="RESERVED"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2206,10 +2137,10 @@
         <v>106</v>
       </c>
       <c r="W1" s="11" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="X1" s="17" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -2220,7 +2151,7 @@
         <v>113</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>192</v>
@@ -2247,7 +2178,7 @@
         <v>11</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>11</v>
@@ -2291,7 +2222,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>192</v>
@@ -2370,7 +2301,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>192</v>
@@ -2449,7 +2380,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>194</v>
@@ -2528,7 +2459,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>194</v>
@@ -2607,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>193</v>
@@ -2686,7 +2617,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>195</v>
@@ -2757,7 +2688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -2795,7 +2726,7 @@
         <v>11</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M9" s="6">
         <v>1</v>
@@ -2844,7 +2775,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>195</v>
@@ -2923,7 +2854,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>195</v>
@@ -3002,7 +2933,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>201</v>
@@ -3032,7 +2963,7 @@
         <v>177</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M12" s="6">
         <v>1</v>
@@ -3081,7 +3012,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>201</v>
@@ -3111,7 +3042,7 @@
         <v>177</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M13" s="6">
         <v>1</v>
@@ -3160,7 +3091,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>194</v>
@@ -3239,7 +3170,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>194</v>
@@ -3318,7 +3249,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>192</v>
@@ -3389,7 +3320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -3425,7 +3356,7 @@
         <v>11</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M17" s="6">
         <v>1</v>
@@ -3466,7 +3397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
@@ -3502,7 +3433,7 @@
         <v>11</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M18" s="6">
         <v>1</v>
@@ -3551,7 +3482,7 @@
         <v>27</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>192</v>
@@ -3581,7 +3512,7 @@
         <v>180</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M19" s="6">
         <v>1</v>
@@ -3630,7 +3561,7 @@
         <v>28</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>192</v>
@@ -3660,7 +3591,7 @@
         <v>180</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M20" s="6">
         <v>1</v>
@@ -3709,7 +3640,7 @@
         <v>29</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>192</v>
@@ -3739,7 +3670,7 @@
         <v>180</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M21" s="6">
         <v>1</v>
@@ -3788,7 +3719,7 @@
         <v>30</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>192</v>
@@ -3818,7 +3749,7 @@
         <v>180</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M22" s="6">
         <v>1</v>
@@ -3867,7 +3798,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>194</v>
@@ -3946,7 +3877,7 @@
         <v>32</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>198</v>
@@ -3976,7 +3907,7 @@
         <v>181</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>213</v>
+        <v>347</v>
       </c>
       <c r="M24" s="6">
         <v>32</v>
@@ -4025,7 +3956,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>196</v>
@@ -4104,7 +4035,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>197</v>
@@ -4183,7 +4114,7 @@
         <v>36</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>193</v>
@@ -4262,7 +4193,7 @@
         <v>37</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>198</v>
@@ -4341,7 +4272,7 @@
         <v>38</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>198</v>
@@ -4420,7 +4351,7 @@
         <v>39</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>198</v>
@@ -4491,7 +4422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>26</v>
       </c>
@@ -4527,7 +4458,7 @@
         <v>181</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M31" s="6">
         <v>32</v>
@@ -4576,7 +4507,7 @@
         <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D32" t="s">
         <v>193</v>
@@ -4647,7 +4578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>26</v>
       </c>
@@ -4655,7 +4586,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>200</v>
@@ -4685,7 +4616,7 @@
         <v>11</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>213</v>
+        <v>347</v>
       </c>
       <c r="M33" s="6">
         <v>1</v>
@@ -4726,7 +4657,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>26</v>
       </c>
@@ -4734,7 +4665,7 @@
         <v>43</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>200</v>
@@ -4764,7 +4695,7 @@
         <v>11</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M34" s="6">
         <v>1</v>
@@ -4805,7 +4736,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>26</v>
       </c>
@@ -4813,7 +4744,7 @@
         <v>44</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>199</v>
@@ -4843,7 +4774,7 @@
         <v>11</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M35" s="6">
         <v>1</v>
@@ -4884,7 +4815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>26</v>
       </c>
@@ -4892,7 +4823,7 @@
         <v>45</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>196</v>
@@ -4922,7 +4853,7 @@
         <v>11</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M36" s="6">
         <v>1</v>
@@ -4963,7 +4894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>26</v>
       </c>
@@ -4971,7 +4902,7 @@
         <v>46</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>196</v>
@@ -5001,7 +4932,7 @@
         <v>11</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M37" s="6">
         <v>1</v>
@@ -5042,7 +4973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>26</v>
       </c>
@@ -5050,7 +4981,7 @@
         <v>47</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="D38" s="14" t="s">
         <v>200</v>
@@ -5080,7 +5011,7 @@
         <v>180</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M38" s="6">
         <v>1</v>
@@ -5121,7 +5052,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>26</v>
       </c>
@@ -5129,7 +5060,7 @@
         <v>48</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>200</v>
@@ -5159,7 +5090,7 @@
         <v>180</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M39" s="6">
         <v>1</v>
@@ -5200,7 +5131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>26</v>
       </c>
@@ -5208,7 +5139,7 @@
         <v>49</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>199</v>
@@ -5238,7 +5169,7 @@
         <v>180</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M40" s="6">
         <v>1</v>
@@ -5279,7 +5210,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>26</v>
       </c>
@@ -5287,7 +5218,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>196</v>
@@ -5317,7 +5248,7 @@
         <v>180</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M41" s="6">
         <v>1</v>
@@ -5358,7 +5289,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>26</v>
       </c>
@@ -5366,7 +5297,7 @@
         <v>51</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>196</v>
@@ -5396,7 +5327,7 @@
         <v>180</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="M42" s="6">
         <v>1</v>
@@ -5437,7 +5368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>26</v>
       </c>
@@ -5445,7 +5376,7 @@
         <v>52</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>194</v>
@@ -5475,7 +5406,7 @@
         <v>11</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M43" s="6">
         <v>32</v>
@@ -5516,7 +5447,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>26</v>
       </c>
@@ -5524,7 +5455,7 @@
         <v>105</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>192</v>
@@ -5554,7 +5485,7 @@
         <v>11</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M44" s="6">
         <v>1</v>
@@ -5603,7 +5534,7 @@
         <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="D45" t="s">
         <v>194</v>
@@ -5682,7 +5613,7 @@
         <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="D46" t="s">
         <v>194</v>
@@ -5753,7 +5684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>26</v>
       </c>
@@ -5788,7 +5719,7 @@
         <v>181</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M47" s="6">
         <v>32</v>
@@ -5829,7 +5760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>26</v>
       </c>
@@ -5864,7 +5795,7 @@
         <v>11</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M48" s="6">
         <v>32</v>
@@ -5902,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="X48" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5913,7 +5844,7 @@
         <v>111</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>194</v>
@@ -5992,7 +5923,7 @@
         <v>112</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>194</v>
@@ -6071,7 +6002,7 @@
         <v>54</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>198</v>
@@ -6150,7 +6081,7 @@
         <v>55</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>200</v>
@@ -6229,7 +6160,7 @@
         <v>56</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>196</v>
@@ -6308,7 +6239,7 @@
         <v>57</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>194</v>
@@ -6387,7 +6318,7 @@
         <v>58</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>197</v>
@@ -6466,7 +6397,7 @@
         <v>59</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="D56" s="14" t="s">
         <v>199</v>
@@ -6545,7 +6476,7 @@
         <v>60</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>194</v>
@@ -6624,7 +6555,7 @@
         <v>61</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>194</v>
@@ -6703,7 +6634,7 @@
         <v>62</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>201</v>
@@ -6782,7 +6713,7 @@
         <v>63</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>201</v>
@@ -6861,7 +6792,7 @@
         <v>64</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>193</v>
@@ -6940,7 +6871,7 @@
         <v>65</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>195</v>
@@ -7019,7 +6950,7 @@
         <v>66</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>197</v>
@@ -7098,7 +7029,7 @@
         <v>67</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>198</v>
@@ -7177,7 +7108,7 @@
         <v>68</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>198</v>
@@ -7256,7 +7187,7 @@
         <v>69</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>198</v>
@@ -7335,7 +7266,7 @@
         <v>70</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="D67" s="14" t="s">
         <v>194</v>
@@ -7414,7 +7345,7 @@
         <v>72</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>198</v>
@@ -7493,7 +7424,7 @@
         <v>73</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="D69" s="14" t="s">
         <v>200</v>
@@ -7572,7 +7503,7 @@
         <v>74</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>196</v>
@@ -7651,7 +7582,7 @@
         <v>75</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>200</v>
@@ -7730,7 +7661,7 @@
         <v>76</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>196</v>
@@ -7809,7 +7740,7 @@
         <v>77</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>194</v>
@@ -7888,7 +7819,7 @@
         <v>78</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>198</v>
@@ -7967,7 +7898,7 @@
         <v>79</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>193</v>
@@ -8046,7 +7977,7 @@
         <v>123</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>192</v>
@@ -8125,7 +8056,7 @@
         <v>81</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>196</v>
@@ -8152,7 +8083,7 @@
         <v>11</v>
       </c>
       <c r="L77" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M77" s="5">
         <v>16</v>
@@ -8199,7 +8130,7 @@
         <v>84</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="D78" s="14" t="s">
         <v>198</v>
@@ -8226,7 +8157,7 @@
         <v>11</v>
       </c>
       <c r="L78" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M78" s="5">
         <v>16</v>
@@ -8273,7 +8204,7 @@
         <v>86</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>198</v>
@@ -8300,7 +8231,7 @@
         <v>11</v>
       </c>
       <c r="L79" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M79" s="5">
         <v>16</v>
@@ -8347,7 +8278,7 @@
         <v>87</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>198</v>
@@ -8374,7 +8305,7 @@
         <v>11</v>
       </c>
       <c r="L80" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M80" s="5">
         <v>16</v>
@@ -8413,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>80</v>
       </c>
@@ -8446,7 +8377,7 @@
         <v>11</v>
       </c>
       <c r="L81" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M81" s="5">
         <v>16</v>
@@ -8470,7 +8401,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>80</v>
       </c>
@@ -8503,7 +8434,7 @@
         <v>11</v>
       </c>
       <c r="L82" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M82" s="5">
         <v>16</v>
@@ -8535,7 +8466,7 @@
         <v>90</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>197</v>
@@ -8562,7 +8493,7 @@
         <v>11</v>
       </c>
       <c r="L83" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M83" s="5">
         <v>16</v>
@@ -8609,7 +8540,7 @@
         <v>91</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>196</v>
@@ -8636,7 +8567,7 @@
         <v>11</v>
       </c>
       <c r="L84" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M84" s="6">
         <v>1</v>
@@ -8683,7 +8614,7 @@
         <v>92</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>196</v>
@@ -8710,7 +8641,7 @@
         <v>11</v>
       </c>
       <c r="L85" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M85" s="6">
         <v>1</v>
@@ -8757,7 +8688,7 @@
         <v>93</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="D86" s="14" t="s">
         <v>200</v>
@@ -8784,7 +8715,7 @@
         <v>11</v>
       </c>
       <c r="L86" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M86" s="6">
         <v>1</v>
@@ -8831,7 +8762,7 @@
         <v>94</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="D87" s="14" t="s">
         <v>200</v>
@@ -8858,7 +8789,7 @@
         <v>11</v>
       </c>
       <c r="L87" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M87" s="6">
         <v>1</v>
@@ -8905,7 +8836,7 @@
         <v>95</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>195</v>
@@ -8932,7 +8863,7 @@
         <v>11</v>
       </c>
       <c r="L88" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M88" s="6">
         <v>1</v>
@@ -8979,7 +8910,7 @@
         <v>96</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>195</v>
@@ -9006,7 +8937,7 @@
         <v>11</v>
       </c>
       <c r="L89" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M89" s="6">
         <v>1</v>
@@ -9053,7 +8984,7 @@
         <v>97</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="D90" s="14" t="s">
         <v>194</v>
@@ -9080,7 +9011,7 @@
         <v>11</v>
       </c>
       <c r="L90" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M90" s="6">
         <v>1</v>
@@ -9127,7 +9058,7 @@
         <v>98</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="D91" s="14" t="s">
         <v>194</v>
@@ -9154,7 +9085,7 @@
         <v>11</v>
       </c>
       <c r="L91" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M91" s="6">
         <v>1</v>
@@ -9201,7 +9132,7 @@
         <v>99</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="D92" s="14" t="s">
         <v>193</v>
@@ -9228,7 +9159,7 @@
         <v>11</v>
       </c>
       <c r="L92" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M92" s="5">
         <v>16</v>
@@ -9275,7 +9206,7 @@
         <v>100</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>199</v>
@@ -9302,7 +9233,7 @@
         <v>11</v>
       </c>
       <c r="L93" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M93" s="6">
         <v>1</v>
@@ -9349,7 +9280,7 @@
         <v>101</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>194</v>
@@ -9376,7 +9307,7 @@
         <v>11</v>
       </c>
       <c r="L94" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M94" s="5">
         <v>16</v>
@@ -9400,7 +9331,7 @@
         <v>83</v>
       </c>
       <c r="T94" s="16" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="U94" s="5" t="s">
         <v>12</v>
@@ -9423,7 +9354,7 @@
         <v>102</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>194</v>
@@ -9450,7 +9381,7 @@
         <v>11</v>
       </c>
       <c r="L95" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M95" s="5">
         <v>16</v>
@@ -9474,7 +9405,7 @@
         <v>83</v>
       </c>
       <c r="T95" s="16" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="U95" s="5" t="s">
         <v>12</v>
@@ -9497,7 +9428,7 @@
         <v>103</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>193</v>
@@ -9524,7 +9455,7 @@
         <v>11</v>
       </c>
       <c r="L96" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M96" s="5">
         <v>16</v>
@@ -9548,7 +9479,7 @@
         <v>83</v>
       </c>
       <c r="T96" s="16" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="U96" s="5" t="s">
         <v>12</v>
@@ -9563,7 +9494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>80</v>
       </c>
@@ -9596,7 +9527,7 @@
         <v>11</v>
       </c>
       <c r="L97" s="16" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M97" s="5">
         <v>16</v>
@@ -9641,7 +9572,7 @@
         <v>183</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>194</v>
@@ -9716,7 +9647,7 @@
         <v>184</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>194</v>
@@ -9791,7 +9722,7 @@
         <v>185</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>194</v>
@@ -9866,7 +9797,7 @@
         <v>187</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>195</v>
@@ -9941,7 +9872,7 @@
         <v>188</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>195</v>
@@ -10016,7 +9947,7 @@
         <v>190</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>194</v>
@@ -10089,7 +10020,7 @@
         <v>191</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="D104" s="14" t="s">
         <v>192</v>
@@ -10162,7 +10093,7 @@
         <v>216</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>192</v>
@@ -11226,7 +11157,7 @@
         <v>208</v>
       </c>
       <c r="D5" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="E5" t="s">
         <v>209</v>
@@ -11438,7 +11369,7 @@
       </c>
       <c r="C15" t="str">
         <f>'Point List'!L12</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D15" t="s">
         <v>214</v>
@@ -11449,7 +11380,7 @@
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
-        <v>Primary_Hydraulic_Fault_ACK,,BitAddress,PLC1,012298,,</v>
+        <v>Primary_Hydraulic_Fault_ACK,,REMOVE,PLC1,012298,,</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -11459,7 +11390,7 @@
       </c>
       <c r="C16" t="str">
         <f>'Point List'!L13</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D16" t="s">
         <v>214</v>
@@ -11470,7 +11401,7 @@
       </c>
       <c r="K16" t="str">
         <f t="shared" si="0"/>
-        <v>Secondary_Hydraulic_Fault_ACK,,BitAddress,PLC1,012299,,</v>
+        <v>Secondary_Hydraulic_Fault_ACK,,REMOVE,PLC1,012299,,</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -11585,7 +11516,7 @@
       </c>
       <c r="C22" t="str">
         <f>'Point List'!L19</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D22" t="s">
         <v>214</v>
@@ -11596,7 +11527,7 @@
       </c>
       <c r="K22" t="str">
         <f t="shared" si="0"/>
-        <v>System_On,,BitAddress,PLC1,012305,,</v>
+        <v>System_On,,REMOVE,PLC1,012305,,</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -11606,7 +11537,7 @@
       </c>
       <c r="C23" t="str">
         <f>'Point List'!L20</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D23" t="s">
         <v>214</v>
@@ -11617,7 +11548,7 @@
       </c>
       <c r="K23" t="str">
         <f t="shared" si="0"/>
-        <v>System_Shutting_Down,,BitAddress,PLC1,012306,,</v>
+        <v>System_Shutting_Down,,REMOVE,PLC1,012306,,</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -11627,7 +11558,7 @@
       </c>
       <c r="C24" t="str">
         <f>'Point List'!L21</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D24" t="s">
         <v>214</v>
@@ -11638,7 +11569,7 @@
       </c>
       <c r="K24" t="str">
         <f t="shared" si="0"/>
-        <v>System_Initializing,,BitAddress,PLC1,012307,,</v>
+        <v>System_Initializing,,REMOVE,PLC1,012307,,</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -11648,7 +11579,7 @@
       </c>
       <c r="C25" t="str">
         <f>'Point List'!L22</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D25" t="s">
         <v>214</v>
@@ -11659,7 +11590,7 @@
       </c>
       <c r="K25" t="str">
         <f t="shared" si="0"/>
-        <v>System_Calibrating,,BitAddress,PLC1,012308,,</v>
+        <v>System_Calibrating,,REMOVE,PLC1,012308,,</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -11690,7 +11621,7 @@
       </c>
       <c r="C27" t="str">
         <f>'Point List'!L24</f>
-        <v>WordAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D27" t="s">
         <v>214</v>
@@ -11701,7 +11632,7 @@
       </c>
       <c r="K27" t="str">
         <f t="shared" si="0"/>
-        <v>Meas_Av_Temp,,WordAddress,PLC1,412559,,</v>
+        <v>Meas_Av_Temp,,REMOVE,PLC1,412559,,</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -11879,7 +11810,7 @@
       </c>
       <c r="C36" t="str">
         <f>'Point List'!L33</f>
-        <v>WordAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D36" t="s">
         <v>214</v>
@@ -11890,7 +11821,7 @@
       </c>
       <c r="K36" t="str">
         <f t="shared" si="0"/>
-        <v>Debounced_Water_Level_Low_Signal,,WordAddress,PLC1,012309,,</v>
+        <v>Debounced_Water_Level_Low_Signal,,REMOVE,PLC1,012309,,</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
@@ -11984,7 +11915,7 @@
       </c>
       <c r="C41" t="str">
         <f>'Point List'!L38</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D41" t="s">
         <v>214</v>
@@ -11995,7 +11926,7 @@
       </c>
       <c r="K41" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Water_Level_Low_Signal,,BitAddress,PLC1,012314,,</v>
+        <v>Output_Water_Level_Low_Signal,,REMOVE,PLC1,012314,,</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -12005,7 +11936,7 @@
       </c>
       <c r="C42" t="str">
         <f>'Point List'!L39</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D42" t="s">
         <v>214</v>
@@ -12016,7 +11947,7 @@
       </c>
       <c r="K42" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Water_Level_Low_Low,,BitAddress,PLC1,012315,,</v>
+        <v>Output_Water_Level_Low_Low,,REMOVE,PLC1,012315,,</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
@@ -12026,7 +11957,7 @@
       </c>
       <c r="C43" t="str">
         <f>'Point List'!L40</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D43" t="s">
         <v>214</v>
@@ -12037,7 +11968,7 @@
       </c>
       <c r="K43" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Pressure_Signal,,BitAddress,PLC1,012316,,</v>
+        <v>Output_Pressure_Signal,,REMOVE,PLC1,012316,,</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
@@ -12047,7 +11978,7 @@
       </c>
       <c r="C44" t="str">
         <f>'Point List'!L41</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D44" t="s">
         <v>214</v>
@@ -12058,7 +11989,7 @@
       </c>
       <c r="K44" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Conductivity_Alarm_Signal,,BitAddress,PLC1,012317,,</v>
+        <v>Output_Conductivity_Alarm_Signal,,REMOVE,PLC1,012317,,</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
@@ -12068,7 +11999,7 @@
       </c>
       <c r="C45" t="str">
         <f>'Point List'!L42</f>
-        <v>BitAddress</v>
+        <v>REMOVE</v>
       </c>
       <c r="D45" t="s">
         <v>214</v>
@@ -12079,7 +12010,7 @@
       </c>
       <c r="K45" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Conductivity_Fault_Signal,,BitAddress,PLC1,012318,,</v>
+        <v>Output_Conductivity_Fault_Signal,,REMOVE,PLC1,012318,,</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
@@ -75138,7 +75069,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B9609-D38B-45A0-9E25-0F7CEDBD1FA5}">
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
@@ -75204,7 +75135,7 @@
         <v>208</v>
       </c>
       <c r="D5" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="E5" t="s">
         <v>209</v>
@@ -75264,7 +75195,7 @@
         <v>012290</v>
       </c>
       <c r="K7" t="str">
-        <f t="shared" ref="K7:K58" si="0">_xlfn.CONCAT(A7,",",B7,",",C7,",",D7,",",E7,",",F7,",",G7)</f>
+        <f t="shared" ref="K7:K45" si="0">_xlfn.CONCAT(A7,",",B7,",",C7,",",D7,",",E7,",",F7,",",G7)</f>
         <v>System_Shutdown,,BitAddress,PLC1,012290,,</v>
       </c>
       <c r="O7" t="s">
@@ -75417,23 +75348,23 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
-        <f>'Point List'!C12</f>
-        <v>Primary_Hydraulic_Fault_ACK</v>
+        <f>'Point List'!C14</f>
+        <v>Enable_Pump_Cycling</v>
       </c>
       <c r="C14" t="str">
-        <f>'Point List'!L12</f>
+        <f>'Point List'!L14</f>
         <v>BitAddress</v>
       </c>
       <c r="D14" t="s">
         <v>214</v>
       </c>
       <c r="E14" t="str">
-        <f>'Point List'!J12</f>
-        <v>012298</v>
+        <f>'Point List'!J14</f>
+        <v>012300</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
-        <v>Primary_Hydraulic_Fault_ACK,,BitAddress,PLC1,012298,,</v>
+        <v>Enable_Pump_Cycling,,BitAddress,PLC1,012300,,</v>
       </c>
       <c r="O14" t="s">
         <v>232</v>
@@ -75441,23 +75372,23 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
-        <f>'Point List'!C13</f>
-        <v>Secondary_Hydraulic_Fault_ACK</v>
+        <f>'Point List'!C15</f>
+        <v>Reset_Pump_Differential_Signal</v>
       </c>
       <c r="C15" t="str">
-        <f>'Point List'!L13</f>
+        <f>'Point List'!L15</f>
         <v>BitAddress</v>
       </c>
       <c r="D15" t="s">
         <v>214</v>
       </c>
       <c r="E15" t="str">
-        <f>'Point List'!J13</f>
-        <v>012299</v>
+        <f>'Point List'!J15</f>
+        <v>012301</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
-        <v>Secondary_Hydraulic_Fault_ACK,,BitAddress,PLC1,012299,,</v>
+        <v>Reset_Pump_Differential_Signal,,BitAddress,PLC1,012301,,</v>
       </c>
       <c r="O15" t="s">
         <v>233</v>
@@ -75465,23 +75396,23 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
-        <f>'Point List'!C14</f>
-        <v>Enable_Pump_Cycling</v>
+        <f>'Point List'!C16</f>
+        <v>Fault_Override</v>
       </c>
       <c r="C16" t="str">
-        <f>'Point List'!L14</f>
+        <f>'Point List'!L16</f>
         <v>BitAddress</v>
       </c>
       <c r="D16" t="s">
         <v>214</v>
       </c>
       <c r="E16" t="str">
-        <f>'Point List'!J14</f>
-        <v>012300</v>
+        <f>'Point List'!J16</f>
+        <v>012302</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="0"/>
-        <v>Enable_Pump_Cycling,,BitAddress,PLC1,012300,,</v>
+        <v>Fault_Override,,BitAddress,PLC1,012302,,</v>
       </c>
       <c r="O16" t="s">
         <v>234</v>
@@ -75489,23 +75420,23 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
-        <f>'Point List'!C15</f>
-        <v>Reset_Pump_Differential_Signal</v>
+        <f>'Point List'!C23</f>
+        <v>Measured_Pump_Power</v>
       </c>
       <c r="C17" t="str">
-        <f>'Point List'!L15</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L23</f>
+        <v>WordAddress</v>
       </c>
       <c r="D17" t="s">
         <v>214</v>
       </c>
       <c r="E17" t="str">
-        <f>'Point List'!J15</f>
-        <v>012301</v>
+        <f>'Point List'!J23</f>
+        <v>412557</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="0"/>
-        <v>Reset_Pump_Differential_Signal,,BitAddress,PLC1,012301,,</v>
+        <v>Measured_Pump_Power,,WordAddress,PLC1,412557,,</v>
       </c>
       <c r="O17" t="s">
         <v>235</v>
@@ -75513,23 +75444,23 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
-        <f>'Point List'!C16</f>
-        <v>Fault_Override</v>
+        <f>'Point List'!C25</f>
+        <v>Measured_Conductivity</v>
       </c>
       <c r="C18" t="str">
-        <f>'Point List'!L16</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L25</f>
+        <v>WordAddress</v>
       </c>
       <c r="D18" t="s">
         <v>214</v>
       </c>
       <c r="E18" t="str">
-        <f>'Point List'!J16</f>
-        <v>012302</v>
+        <f>'Point List'!J25</f>
+        <v>412561</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="0"/>
-        <v>Fault_Override,,BitAddress,PLC1,012302,,</v>
+        <v>Measured_Conductivity,,WordAddress,PLC1,412561,,</v>
       </c>
       <c r="O18" t="s">
         <v>236</v>
@@ -75537,23 +75468,23 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
-        <f>'Point List'!C19</f>
-        <v>System_On</v>
+        <f>'Point List'!C26</f>
+        <v>Measured_Flow</v>
       </c>
       <c r="C19" t="str">
-        <f>'Point List'!L19</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L26</f>
+        <v>WordAddress</v>
       </c>
       <c r="D19" t="s">
         <v>214</v>
       </c>
       <c r="E19" t="str">
-        <f>'Point List'!J19</f>
-        <v>012305</v>
+        <f>'Point List'!J26</f>
+        <v>412563</v>
       </c>
       <c r="K19" t="str">
         <f t="shared" si="0"/>
-        <v>System_On,,BitAddress,PLC1,012305,,</v>
+        <v>Measured_Flow,,WordAddress,PLC1,412563,,</v>
       </c>
       <c r="O19" t="s">
         <v>237</v>
@@ -75561,23 +75492,23 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f>'Point List'!C20</f>
-        <v>System_Shutting_Down</v>
+        <f>'Point List'!C27</f>
+        <v>Valve_Position_Input</v>
       </c>
       <c r="C20" t="str">
-        <f>'Point List'!L20</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L27</f>
+        <v>WordAddress</v>
       </c>
       <c r="D20" t="s">
         <v>214</v>
       </c>
       <c r="E20" t="str">
-        <f>'Point List'!J20</f>
-        <v>012306</v>
+        <f>'Point List'!J27</f>
+        <v>412565</v>
       </c>
       <c r="K20" t="str">
         <f t="shared" si="0"/>
-        <v>System_Shutting_Down,,BitAddress,PLC1,012306,,</v>
+        <v>Valve_Position_Input,,WordAddress,PLC1,412565,,</v>
       </c>
       <c r="O20" t="s">
         <v>238</v>
@@ -75585,23 +75516,23 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
-        <f>'Point List'!C21</f>
-        <v>System_Initializing</v>
+        <f>'Point List'!C28</f>
+        <v>Real_RTD_1_Signal</v>
       </c>
       <c r="C21" t="str">
-        <f>'Point List'!L21</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L28</f>
+        <v>WordAddress</v>
       </c>
       <c r="D21" t="s">
         <v>214</v>
       </c>
       <c r="E21" t="str">
-        <f>'Point List'!J21</f>
-        <v>012307</v>
+        <f>'Point List'!J28</f>
+        <v>412567</v>
       </c>
       <c r="K21" t="str">
         <f t="shared" si="0"/>
-        <v>System_Initializing,,BitAddress,PLC1,012307,,</v>
+        <v>Real_RTD_1_Signal,,WordAddress,PLC1,412567,,</v>
       </c>
       <c r="O21" t="s">
         <v>239</v>
@@ -75609,23 +75540,23 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
-        <f>'Point List'!C22</f>
-        <v>System_Calibrating</v>
+        <f>'Point List'!C29</f>
+        <v>Real_RTD_2_Signal</v>
       </c>
       <c r="C22" t="str">
-        <f>'Point List'!L22</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L29</f>
+        <v>WordAddress</v>
       </c>
       <c r="D22" t="s">
         <v>214</v>
       </c>
       <c r="E22" t="str">
-        <f>'Point List'!J22</f>
-        <v>012308</v>
+        <f>'Point List'!J29</f>
+        <v>412569</v>
       </c>
       <c r="K22" t="str">
         <f t="shared" si="0"/>
-        <v>System_Calibrating,,BitAddress,PLC1,012308,,</v>
+        <v>Real_RTD_2_Signal,,WordAddress,PLC1,412569,,</v>
       </c>
       <c r="O22" t="s">
         <v>240</v>
@@ -75633,23 +75564,23 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
-        <f>'Point List'!C23</f>
-        <v>Measured_Pump_Power</v>
+        <f>'Point List'!C30</f>
+        <v>Real_RTD_3_Signal</v>
       </c>
       <c r="C23" t="str">
-        <f>'Point List'!L23</f>
+        <f>'Point List'!L30</f>
         <v>WordAddress</v>
       </c>
       <c r="D23" t="s">
         <v>214</v>
       </c>
       <c r="E23" t="str">
-        <f>'Point List'!J23</f>
-        <v>412557</v>
+        <f>'Point List'!J30</f>
+        <v>412571</v>
       </c>
       <c r="K23" t="str">
         <f t="shared" si="0"/>
-        <v>Measured_Pump_Power,,WordAddress,PLC1,412557,,</v>
+        <v>Real_RTD_3_Signal,,WordAddress,PLC1,412571,,</v>
       </c>
       <c r="O23" t="s">
         <v>241</v>
@@ -75657,23 +75588,23 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
-        <f>'Point List'!C24</f>
-        <v>Meas_Av_Temp</v>
+        <f>'Point List'!C32</f>
+        <v>Feedback_Valve_Position</v>
       </c>
       <c r="C24" t="str">
-        <f>'Point List'!L24</f>
+        <f>'Point List'!L32</f>
         <v>WordAddress</v>
       </c>
       <c r="D24" t="s">
         <v>214</v>
       </c>
       <c r="E24" t="str">
-        <f>'Point List'!J24</f>
-        <v>412559</v>
+        <f>'Point List'!J32</f>
+        <v>412575</v>
       </c>
       <c r="K24" t="str">
         <f t="shared" si="0"/>
-        <v>Meas_Av_Temp,,WordAddress,PLC1,412559,,</v>
+        <v>Feedback_Valve_Position,,WordAddress,PLC1,412575,,</v>
       </c>
       <c r="O24" t="s">
         <v>242</v>
@@ -75681,23 +75612,23 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
-        <f>'Point List'!C25</f>
-        <v>Measured_Conductivity</v>
+        <f>'Point List'!C45</f>
+        <v>Measured_Active_Pump__Voltage</v>
       </c>
       <c r="C25" t="str">
-        <f>'Point List'!L25</f>
+        <f>'Point List'!L45</f>
         <v>WordAddress</v>
       </c>
       <c r="D25" t="s">
         <v>214</v>
       </c>
       <c r="E25" t="str">
-        <f>'Point List'!J25</f>
-        <v>412561</v>
+        <f>'Point List'!J45</f>
+        <v>412577</v>
       </c>
       <c r="K25" t="str">
         <f t="shared" si="0"/>
-        <v>Measured_Conductivity,,WordAddress,PLC1,412561,,</v>
+        <v>Measured_Active_Pump__Voltage,,WordAddress,PLC1,412577,,</v>
       </c>
       <c r="O25" t="s">
         <v>243</v>
@@ -75705,23 +75636,23 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
-        <f>'Point List'!C26</f>
-        <v>Measured_Flow</v>
+        <f>'Point List'!C46</f>
+        <v>Measured_Active_Pump__Current</v>
       </c>
       <c r="C26" t="str">
-        <f>'Point List'!L26</f>
+        <f>'Point List'!L46</f>
         <v>WordAddress</v>
       </c>
       <c r="D26" t="s">
         <v>214</v>
       </c>
       <c r="E26" t="str">
-        <f>'Point List'!J26</f>
-        <v>412563</v>
+        <f>'Point List'!J46</f>
+        <v>412579</v>
       </c>
       <c r="K26" t="str">
         <f t="shared" si="0"/>
-        <v>Measured_Flow,,WordAddress,PLC1,412563,,</v>
+        <v>Measured_Active_Pump__Current,,WordAddress,PLC1,412579,,</v>
       </c>
       <c r="O26" t="s">
         <v>244</v>
@@ -75729,1406 +75660,758 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
-        <f>'Point List'!C27</f>
-        <v>Valve_Position_Input</v>
+        <f>'Point List'!C49</f>
+        <v>Pump_1_Total_Hours</v>
       </c>
       <c r="C27" t="str">
-        <f>'Point List'!L27</f>
+        <f>'Point List'!L49</f>
         <v>WordAddress</v>
       </c>
       <c r="D27" t="s">
         <v>214</v>
       </c>
       <c r="E27" t="str">
-        <f>'Point List'!J27</f>
-        <v>412565</v>
+        <f>'Point List'!J49</f>
+        <v>412455</v>
       </c>
       <c r="K27" t="str">
         <f t="shared" si="0"/>
-        <v>Valve_Position_Input,,WordAddress,PLC1,412565,,</v>
-      </c>
-      <c r="O27" t="s">
-        <v>245</v>
+        <v>Pump_1_Total_Hours,,WordAddress,PLC1,412455,,</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
-        <f>'Point List'!C28</f>
-        <v>Real_RTD_1_Signal</v>
+        <f>'Point List'!C50</f>
+        <v>Pump_2_Total_Hours</v>
       </c>
       <c r="C28" t="str">
-        <f>'Point List'!L28</f>
+        <f>'Point List'!L50</f>
         <v>WordAddress</v>
       </c>
       <c r="D28" t="s">
         <v>214</v>
       </c>
       <c r="E28" t="str">
-        <f>'Point List'!J28</f>
-        <v>412567</v>
+        <f>'Point List'!J50</f>
+        <v>412457</v>
       </c>
       <c r="K28" t="str">
         <f t="shared" si="0"/>
-        <v>Real_RTD_1_Signal,,WordAddress,PLC1,412567,,</v>
-      </c>
-      <c r="O28" t="s">
-        <v>246</v>
+        <v>Pump_2_Total_Hours,,WordAddress,PLC1,412457,,</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
-        <f>'Point List'!C29</f>
-        <v>Real_RTD_2_Signal</v>
+        <f>'Point List'!C51</f>
+        <v>High_Coolant_Temperature_</v>
       </c>
       <c r="C29" t="str">
-        <f>'Point List'!L29</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L51</f>
+        <v>BitAddress</v>
       </c>
       <c r="D29" t="s">
         <v>214</v>
       </c>
       <c r="E29" t="str">
-        <f>'Point List'!J29</f>
-        <v>412569</v>
+        <f>'Point List'!J51</f>
+        <v>012320</v>
       </c>
       <c r="K29" t="str">
         <f t="shared" si="0"/>
-        <v>Real_RTD_2_Signal,,WordAddress,PLC1,412569,,</v>
-      </c>
-      <c r="O29" t="s">
-        <v>247</v>
+        <v>High_Coolant_Temperature_,,BitAddress,PLC1,012320,,</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
-        <f>'Point List'!C30</f>
-        <v>Real_RTD_3_Signal</v>
+        <f>'Point List'!C52</f>
+        <v>Low_Coolant_Level_in_Vessel</v>
       </c>
       <c r="C30" t="str">
-        <f>'Point List'!L30</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L52</f>
+        <v>BitAddress</v>
       </c>
       <c r="D30" t="s">
         <v>214</v>
       </c>
       <c r="E30" t="str">
-        <f>'Point List'!J30</f>
-        <v>412571</v>
+        <f>'Point List'!J52</f>
+        <v>012321</v>
       </c>
       <c r="K30" t="str">
         <f t="shared" si="0"/>
-        <v>Real_RTD_3_Signal,,WordAddress,PLC1,412571,,</v>
-      </c>
-      <c r="O30" t="s">
-        <v>248</v>
+        <v>Low_Coolant_Level_in_Vessel,,BitAddress,PLC1,012321,,</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
-        <f>'Point List'!C32</f>
-        <v>Feedback_Valve_Position</v>
+        <f>'Point List'!C53</f>
+        <v>High_Coolant_Conductivity_</v>
       </c>
       <c r="C31" t="str">
-        <f>'Point List'!L32</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L53</f>
+        <v>BitAddress</v>
       </c>
       <c r="D31" t="s">
         <v>214</v>
       </c>
       <c r="E31" t="str">
-        <f>'Point List'!J32</f>
-        <v>412575</v>
+        <f>'Point List'!J53</f>
+        <v>012322</v>
       </c>
       <c r="K31" t="str">
         <f t="shared" si="0"/>
-        <v>Feedback_Valve_Position,,WordAddress,PLC1,412575,,</v>
-      </c>
-      <c r="O31" t="s">
-        <v>249</v>
+        <v>High_Coolant_Conductivity_,,BitAddress,PLC1,012322,,</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
-        <f>'Point List'!C33</f>
-        <v>Debounced_Water_Level_Low_Signal</v>
+        <f>'Point List'!C54</f>
+        <v>Low_Hydraulic_Power</v>
       </c>
       <c r="C32" t="str">
-        <f>'Point List'!L33</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L54</f>
+        <v>BitAddress</v>
       </c>
       <c r="D32" t="s">
         <v>214</v>
       </c>
       <c r="E32" t="str">
-        <f>'Point List'!J33</f>
-        <v>012309</v>
+        <f>'Point List'!J54</f>
+        <v>012323</v>
       </c>
       <c r="K32" t="str">
         <f t="shared" si="0"/>
-        <v>Debounced_Water_Level_Low_Signal,,WordAddress,PLC1,012309,,</v>
-      </c>
-      <c r="O32" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Low_Hydraulic_Power,,BitAddress,PLC1,012323,,</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
-        <f>'Point List'!C38</f>
-        <v>Output_Water_Level_Low_Signal</v>
+        <f>'Point List'!C55</f>
+        <v>Low_Hydraulic_Flow</v>
       </c>
       <c r="C33" t="str">
-        <f>'Point List'!L38</f>
+        <f>'Point List'!L55</f>
         <v>BitAddress</v>
       </c>
       <c r="D33" t="s">
         <v>214</v>
       </c>
       <c r="E33" t="str">
-        <f>'Point List'!J38</f>
-        <v>012314</v>
+        <f>'Point List'!J55</f>
+        <v>012324</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Water_Level_Low_Signal,,BitAddress,PLC1,012314,,</v>
-      </c>
-      <c r="O33" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Low_Hydraulic_Flow,,BitAddress,PLC1,012324,,</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
-        <f>'Point List'!C39</f>
-        <v>Output_Water_Level_Low_Low</v>
+        <f>'Point List'!C56</f>
+        <v>Low_Hydraulic_Pressure</v>
       </c>
       <c r="C34" t="str">
-        <f>'Point List'!L39</f>
+        <f>'Point List'!L56</f>
         <v>BitAddress</v>
       </c>
       <c r="D34" t="s">
         <v>214</v>
       </c>
       <c r="E34" t="str">
-        <f>'Point List'!J39</f>
-        <v>012315</v>
+        <f>'Point List'!J56</f>
+        <v>012325</v>
       </c>
       <c r="K34" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Water_Level_Low_Low,,BitAddress,PLC1,012315,,</v>
-      </c>
-      <c r="O34" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Low_Hydraulic_Pressure,,BitAddress,PLC1,012325,,</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
-        <f>'Point List'!C40</f>
-        <v>Output_Pressure_Signal</v>
+        <f>'Point List'!C57</f>
+        <v>Voltage_Signal_Malfunction</v>
       </c>
       <c r="C35" t="str">
-        <f>'Point List'!L40</f>
+        <f>'Point List'!L57</f>
         <v>BitAddress</v>
       </c>
       <c r="D35" t="s">
         <v>214</v>
       </c>
       <c r="E35" t="str">
-        <f>'Point List'!J40</f>
-        <v>012316</v>
+        <f>'Point List'!J57</f>
+        <v>012326</v>
       </c>
       <c r="K35" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Pressure_Signal,,BitAddress,PLC1,012316,,</v>
-      </c>
-      <c r="O35" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Voltage_Signal_Malfunction,,BitAddress,PLC1,012326,,</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
-        <f>'Point List'!C41</f>
-        <v>Output_Conductivity_Alarm_Signal</v>
+        <f>'Point List'!C58</f>
+        <v>Current_Signal_Malfunction</v>
       </c>
       <c r="C36" t="str">
-        <f>'Point List'!L41</f>
+        <f>'Point List'!L58</f>
         <v>BitAddress</v>
       </c>
       <c r="D36" t="s">
         <v>214</v>
       </c>
       <c r="E36" t="str">
-        <f>'Point List'!J41</f>
-        <v>012317</v>
+        <f>'Point List'!J58</f>
+        <v>012327</v>
       </c>
       <c r="K36" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Conductivity_Alarm_Signal,,BitAddress,PLC1,012317,,</v>
-      </c>
-      <c r="O36" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Current_Signal_Malfunction,,BitAddress,PLC1,012327,,</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
-        <f>'Point List'!C42</f>
-        <v>Output_Conductivity_Fault_Signal</v>
+        <f>'Point List'!C59</f>
+        <v>Primary_Hydraulic_Failure</v>
       </c>
       <c r="C37" t="str">
-        <f>'Point List'!L42</f>
+        <f>'Point List'!L59</f>
         <v>BitAddress</v>
       </c>
       <c r="D37" t="s">
         <v>214</v>
       </c>
       <c r="E37" t="str">
-        <f>'Point List'!J42</f>
-        <v>012318</v>
+        <f>'Point List'!J59</f>
+        <v>012328</v>
       </c>
       <c r="K37" t="str">
         <f t="shared" si="0"/>
-        <v>Output_Conductivity_Fault_Signal,,BitAddress,PLC1,012318,,</v>
-      </c>
-      <c r="O37" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Primary_Hydraulic_Failure,,BitAddress,PLC1,012328,,</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
-        <f>'Point List'!C45</f>
-        <v>Measured_Active_Pump__Voltage</v>
+        <f>'Point List'!C60</f>
+        <v>Secondary_Hydraulic_Failure</v>
       </c>
       <c r="C38" t="str">
-        <f>'Point List'!L45</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L60</f>
+        <v>BitAddress</v>
       </c>
       <c r="D38" t="s">
         <v>214</v>
       </c>
       <c r="E38" t="str">
-        <f>'Point List'!J45</f>
-        <v>412577</v>
+        <f>'Point List'!J60</f>
+        <v>012329</v>
       </c>
       <c r="K38" t="str">
         <f t="shared" si="0"/>
-        <v>Measured_Active_Pump__Voltage,,WordAddress,PLC1,412577,,</v>
-      </c>
-      <c r="O38" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Secondary_Hydraulic_Failure,,BitAddress,PLC1,012329,,</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
-        <f>'Point List'!C46</f>
-        <v>Measured_Active_Pump__Current</v>
+        <f>'Point List'!C61</f>
+        <v>Automatic_Valve_Control_Disabled</v>
       </c>
       <c r="C39" t="str">
-        <f>'Point List'!L46</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L61</f>
+        <v>BitAddress</v>
       </c>
       <c r="D39" t="s">
         <v>214</v>
       </c>
       <c r="E39" t="str">
-        <f>'Point List'!J46</f>
-        <v>412579</v>
+        <f>'Point List'!J61</f>
+        <v>012330</v>
       </c>
       <c r="K39" t="str">
         <f t="shared" si="0"/>
-        <v>Measured_Active_Pump__Current,,WordAddress,PLC1,412579,,</v>
-      </c>
-      <c r="O39" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Automatic_Valve_Control_Disabled,,BitAddress,PLC1,012330,,</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
-        <f>'Point List'!C49</f>
-        <v>Pump_1_Total_Hours</v>
+        <f>'Point List'!C62</f>
+        <v>Automatic_Fan_Control_Disabled</v>
       </c>
       <c r="C40" t="str">
-        <f>'Point List'!L49</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L62</f>
+        <v>BitAddress</v>
       </c>
       <c r="D40" t="s">
         <v>214</v>
       </c>
       <c r="E40" t="str">
-        <f>'Point List'!J49</f>
-        <v>412455</v>
+        <f>'Point List'!J62</f>
+        <v>012331</v>
       </c>
       <c r="K40" t="str">
         <f t="shared" si="0"/>
-        <v>Pump_1_Total_Hours,,WordAddress,PLC1,412455,,</v>
-      </c>
-      <c r="O40" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Automatic_Fan_Control_Disabled,,BitAddress,PLC1,012331,,</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
-        <f>'Point List'!C50</f>
-        <v>Pump_2_Total_Hours</v>
+        <f>'Point List'!C63</f>
+        <v>Flow_Signal_Malfunction</v>
       </c>
       <c r="C41" t="str">
-        <f>'Point List'!L50</f>
-        <v>WordAddress</v>
+        <f>'Point List'!L63</f>
+        <v>BitAddress</v>
       </c>
       <c r="D41" t="s">
         <v>214</v>
       </c>
       <c r="E41" t="str">
-        <f>'Point List'!J50</f>
-        <v>412457</v>
+        <f>'Point List'!J63</f>
+        <v>012332</v>
       </c>
       <c r="K41" t="str">
         <f t="shared" si="0"/>
-        <v>Pump_2_Total_Hours,,WordAddress,PLC1,412457,,</v>
-      </c>
-      <c r="O41" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Flow_Signal_Malfunction,,BitAddress,PLC1,012332,,</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
-        <f>'Point List'!C51</f>
-        <v>High_Coolant_Temperature_</v>
+        <f>'Point List'!C64</f>
+        <v>Bad_RTD_1_Signal</v>
       </c>
       <c r="C42" t="str">
-        <f>'Point List'!L51</f>
+        <f>'Point List'!L64</f>
         <v>BitAddress</v>
       </c>
       <c r="D42" t="s">
         <v>214</v>
       </c>
       <c r="E42" t="str">
-        <f>'Point List'!J51</f>
-        <v>012320</v>
+        <f>'Point List'!J64</f>
+        <v>012333</v>
       </c>
       <c r="K42" t="str">
         <f t="shared" si="0"/>
-        <v>High_Coolant_Temperature_,,BitAddress,PLC1,012320,,</v>
-      </c>
-      <c r="O42" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Bad_RTD_1_Signal,,BitAddress,PLC1,012333,,</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
-        <f>'Point List'!C52</f>
-        <v>Low_Coolant_Level_in_Vessel</v>
+        <f>'Point List'!C65</f>
+        <v>Bad_RTD_2_Signal</v>
       </c>
       <c r="C43" t="str">
-        <f>'Point List'!L52</f>
+        <f>'Point List'!L65</f>
         <v>BitAddress</v>
       </c>
       <c r="D43" t="s">
         <v>214</v>
       </c>
       <c r="E43" t="str">
-        <f>'Point List'!J52</f>
-        <v>012321</v>
+        <f>'Point List'!J65</f>
+        <v>012334</v>
       </c>
       <c r="K43" t="str">
         <f t="shared" si="0"/>
-        <v>Low_Coolant_Level_in_Vessel,,BitAddress,PLC1,012321,,</v>
-      </c>
-      <c r="O43" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Bad_RTD_2_Signal,,BitAddress,PLC1,012334,,</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
-        <f>'Point List'!C53</f>
-        <v>High_Coolant_Conductivity_</v>
+        <f>'Point List'!C66</f>
+        <v>Bad_RTD_3_Signal</v>
       </c>
       <c r="C44" t="str">
-        <f>'Point List'!L53</f>
+        <f>'Point List'!L66</f>
         <v>BitAddress</v>
       </c>
       <c r="D44" t="s">
         <v>214</v>
       </c>
       <c r="E44" t="str">
-        <f>'Point List'!J53</f>
-        <v>012322</v>
+        <f>'Point List'!J66</f>
+        <v>012335</v>
       </c>
       <c r="K44" t="str">
         <f t="shared" si="0"/>
-        <v>High_Coolant_Conductivity_,,BitAddress,PLC1,012322,,</v>
-      </c>
-      <c r="O44" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Bad_RTD_3_Signal,,BitAddress,PLC1,012335,,</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
-        <f>'Point List'!C54</f>
-        <v>Low_Hydraulic_Power</v>
+        <f>'Point List'!C67</f>
+        <v>Pump_Cycle_Alarm</v>
       </c>
       <c r="C45" t="str">
-        <f>'Point List'!L54</f>
+        <f>'Point List'!L67</f>
         <v>BitAddress</v>
       </c>
       <c r="D45" t="s">
         <v>214</v>
       </c>
       <c r="E45" t="str">
-        <f>'Point List'!J54</f>
-        <v>012323</v>
+        <f>'Point List'!J67</f>
+        <v>012336</v>
       </c>
       <c r="K45" t="str">
         <f t="shared" si="0"/>
-        <v>Low_Hydraulic_Power,,BitAddress,PLC1,012323,,</v>
-      </c>
-      <c r="O45" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Pump_Cycle_Alarm,,BitAddress,PLC1,012336,,</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
-        <f>'Point List'!C55</f>
-        <v>Low_Hydraulic_Flow</v>
+        <f>'Point List'!C68</f>
+        <v>Critical_Temperature</v>
       </c>
       <c r="C46" t="str">
-        <f>'Point List'!L55</f>
+        <f>'Point List'!L68</f>
         <v>BitAddress</v>
       </c>
       <c r="D46" t="s">
         <v>214</v>
       </c>
       <c r="E46" t="str">
-        <f>'Point List'!J55</f>
-        <v>012324</v>
+        <f>'Point List'!J68</f>
+        <v>012337</v>
       </c>
       <c r="K46" t="str">
-        <f t="shared" si="0"/>
-        <v>Low_Hydraulic_Flow,,BitAddress,PLC1,012324,,</v>
-      </c>
-      <c r="O46" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" ref="K46:K62" si="1">_xlfn.CONCAT(A46,",",B46,",",C46,",",D46,",",E46,",",F46,",",G46)</f>
+        <v>Critical_Temperature,,BitAddress,PLC1,012337,,</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
-        <f>'Point List'!C56</f>
-        <v>Low_Hydraulic_Pressure</v>
+        <f>'Point List'!C69</f>
+        <v>Critical_Vessel_Level</v>
       </c>
       <c r="C47" t="str">
-        <f>'Point List'!L56</f>
+        <f>'Point List'!L69</f>
         <v>BitAddress</v>
       </c>
       <c r="D47" t="s">
         <v>214</v>
       </c>
       <c r="E47" t="str">
-        <f>'Point List'!J56</f>
-        <v>012325</v>
+        <f>'Point List'!J69</f>
+        <v>012338</v>
       </c>
       <c r="K47" t="str">
-        <f t="shared" si="0"/>
-        <v>Low_Hydraulic_Pressure,,BitAddress,PLC1,012325,,</v>
-      </c>
-      <c r="O47" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Critical_Vessel_Level,,BitAddress,PLC1,012338,,</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
-        <f>'Point List'!C57</f>
-        <v>Voltage_Signal_Malfunction</v>
+        <f>'Point List'!C70</f>
+        <v>Critical_Conductivity</v>
       </c>
       <c r="C48" t="str">
-        <f>'Point List'!L57</f>
+        <f>'Point List'!L70</f>
         <v>BitAddress</v>
       </c>
       <c r="D48" t="s">
         <v>214</v>
       </c>
       <c r="E48" t="str">
-        <f>'Point List'!J57</f>
-        <v>012326</v>
+        <f>'Point List'!J70</f>
+        <v>012339</v>
       </c>
       <c r="K48" t="str">
-        <f t="shared" si="0"/>
-        <v>Voltage_Signal_Malfunction,,BitAddress,PLC1,012326,,</v>
-      </c>
-      <c r="O48" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Critical_Conductivity,,BitAddress,PLC1,012339,,</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
-        <f>'Point List'!C58</f>
-        <v>Current_Signal_Malfunction</v>
+        <f>'Point List'!C71</f>
+        <v>Level_Sensor_Malfunction</v>
       </c>
       <c r="C49" t="str">
-        <f>'Point List'!L58</f>
+        <f>'Point List'!L71</f>
         <v>BitAddress</v>
       </c>
       <c r="D49" t="s">
         <v>214</v>
       </c>
       <c r="E49" t="str">
-        <f>'Point List'!J58</f>
-        <v>012327</v>
+        <f>'Point List'!J71</f>
+        <v>012340</v>
       </c>
       <c r="K49" t="str">
-        <f t="shared" si="0"/>
-        <v>Current_Signal_Malfunction,,BitAddress,PLC1,012327,,</v>
-      </c>
-      <c r="O49" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Level_Sensor_Malfunction,,BitAddress,PLC1,012340,,</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
-        <f>'Point List'!C59</f>
-        <v>Primary_Hydraulic_Failure</v>
+        <f>'Point List'!C72</f>
+        <v>Conductivity_Sensor_Malfunction</v>
       </c>
       <c r="C50" t="str">
-        <f>'Point List'!L59</f>
+        <f>'Point List'!L72</f>
         <v>BitAddress</v>
       </c>
       <c r="D50" t="s">
         <v>214</v>
       </c>
       <c r="E50" t="str">
-        <f>'Point List'!J59</f>
-        <v>012328</v>
+        <f>'Point List'!J72</f>
+        <v>012341</v>
       </c>
       <c r="K50" t="str">
-        <f t="shared" si="0"/>
-        <v>Primary_Hydraulic_Failure,,BitAddress,PLC1,012328,,</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Conductivity_Sensor_Malfunction,,BitAddress,PLC1,012341,,</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
-        <f>'Point List'!C60</f>
-        <v>Secondary_Hydraulic_Failure</v>
+        <f>'Point List'!C73</f>
+        <v>Bingo_Pumps</v>
       </c>
       <c r="C51" t="str">
-        <f>'Point List'!L60</f>
+        <f>'Point List'!L73</f>
         <v>BitAddress</v>
       </c>
       <c r="D51" t="s">
         <v>214</v>
       </c>
       <c r="E51" t="str">
-        <f>'Point List'!J60</f>
-        <v>012329</v>
+        <f>'Point List'!J73</f>
+        <v>012342</v>
       </c>
       <c r="K51" t="str">
-        <f t="shared" si="0"/>
-        <v>Secondary_Hydraulic_Failure,,BitAddress,PLC1,012329,,</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Bingo_Pumps,,BitAddress,PLC1,012342,,</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
-        <f>'Point List'!C61</f>
-        <v>Automatic_Valve_Control_Disabled</v>
+        <f>'Point List'!C74</f>
+        <v>Temperature_Sensor_Malfunction</v>
       </c>
       <c r="C52" t="str">
-        <f>'Point List'!L61</f>
+        <f>'Point List'!L74</f>
         <v>BitAddress</v>
       </c>
       <c r="D52" t="s">
         <v>214</v>
       </c>
       <c r="E52" t="str">
-        <f>'Point List'!J61</f>
-        <v>012330</v>
+        <f>'Point List'!J74</f>
+        <v>012343</v>
       </c>
       <c r="K52" t="str">
-        <f t="shared" si="0"/>
-        <v>Automatic_Valve_Control_Disabled,,BitAddress,PLC1,012330,,</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Temperature_Sensor_Malfunction,,BitAddress,PLC1,012343,,</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
-        <f>'Point List'!C62</f>
-        <v>Automatic_Fan_Control_Disabled</v>
+        <f>'Point List'!C75</f>
+        <v>Bad_Valve_Pos</v>
       </c>
       <c r="C53" t="str">
-        <f>'Point List'!L62</f>
+        <f>'Point List'!L75</f>
         <v>BitAddress</v>
       </c>
       <c r="D53" t="s">
         <v>214</v>
       </c>
       <c r="E53" t="str">
-        <f>'Point List'!J62</f>
-        <v>012331</v>
+        <f>'Point List'!J75</f>
+        <v>012344</v>
       </c>
       <c r="K53" t="str">
-        <f t="shared" si="0"/>
-        <v>Automatic_Fan_Control_Disabled,,BitAddress,PLC1,012331,,</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Bad_Valve_Pos,,BitAddress,PLC1,012344,,</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
-        <f>'Point List'!C63</f>
-        <v>Flow_Signal_Malfunction</v>
+        <f>'Point List'!C76</f>
+        <v>Master_Fault_Signal</v>
       </c>
       <c r="C54" t="str">
-        <f>'Point List'!L63</f>
+        <f>'Point List'!L76</f>
         <v>BitAddress</v>
       </c>
       <c r="D54" t="s">
         <v>214</v>
       </c>
       <c r="E54" t="str">
-        <f>'Point List'!J63</f>
-        <v>012332</v>
+        <f>'Point List'!J76</f>
+        <v>012345</v>
       </c>
       <c r="K54" t="str">
-        <f t="shared" si="0"/>
-        <v>Flow_Signal_Malfunction,,BitAddress,PLC1,012332,,</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Master_Fault_Signal,,BitAddress,PLC1,012345,,</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
-        <f>'Point List'!C64</f>
-        <v>Bad_RTD_1_Signal</v>
+        <f>'Point List'!C98</f>
+        <v>Primary_Pump_Active</v>
       </c>
       <c r="C55" t="str">
-        <f>'Point List'!L64</f>
+        <f>'Point List'!L98</f>
         <v>BitAddress</v>
       </c>
       <c r="D55" t="s">
         <v>214</v>
       </c>
       <c r="E55" t="str">
-        <f>'Point List'!J64</f>
-        <v>012333</v>
+        <f>'Point List'!J98</f>
+        <v>012346</v>
       </c>
       <c r="K55" t="str">
-        <f t="shared" si="0"/>
-        <v>Bad_RTD_1_Signal,,BitAddress,PLC1,012333,,</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Primary_Pump_Active,,BitAddress,PLC1,012346,,</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
-        <f>'Point List'!C65</f>
-        <v>Bad_RTD_2_Signal</v>
+        <f>'Point List'!C99</f>
+        <v>Secondary_Pump__Active</v>
       </c>
       <c r="C56" t="str">
-        <f>'Point List'!L65</f>
+        <f>'Point List'!L99</f>
         <v>BitAddress</v>
       </c>
       <c r="D56" t="s">
         <v>214</v>
       </c>
       <c r="E56" t="str">
-        <f>'Point List'!J65</f>
-        <v>012334</v>
+        <f>'Point List'!J99</f>
+        <v>012347</v>
       </c>
       <c r="K56" t="str">
-        <f t="shared" si="0"/>
-        <v>Bad_RTD_2_Signal,,BitAddress,PLC1,012334,,</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Secondary_Pump__Active,,BitAddress,PLC1,012347,,</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
-        <f>'Point List'!C66</f>
-        <v>Bad_RTD_3_Signal</v>
+        <f>'Point List'!C100</f>
+        <v>Simplex_Mode_Active</v>
       </c>
       <c r="C57" t="str">
-        <f>'Point List'!L66</f>
+        <f>'Point List'!L100</f>
         <v>BitAddress</v>
       </c>
       <c r="D57" t="s">
         <v>214</v>
       </c>
       <c r="E57" t="str">
-        <f>'Point List'!J66</f>
-        <v>012335</v>
+        <f>'Point List'!J100</f>
+        <v>012348</v>
       </c>
       <c r="K57" t="str">
-        <f t="shared" si="0"/>
-        <v>Bad_RTD_3_Signal,,BitAddress,PLC1,012335,,</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Simplex_Mode_Active,,BitAddress,PLC1,012348,,</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
-        <f>'Point List'!C67</f>
-        <v>Pump_Cycle_Alarm</v>
+        <f>'Point List'!C101</f>
+        <v>Fan_1_Active</v>
       </c>
       <c r="C58" t="str">
-        <f>'Point List'!L67</f>
+        <f>'Point List'!L101</f>
         <v>BitAddress</v>
       </c>
       <c r="D58" t="s">
         <v>214</v>
       </c>
       <c r="E58" t="str">
-        <f>'Point List'!J67</f>
-        <v>012336</v>
+        <f>'Point List'!J101</f>
+        <v>012349</v>
       </c>
       <c r="K58" t="str">
-        <f t="shared" si="0"/>
-        <v>Pump_Cycle_Alarm,,BitAddress,PLC1,012336,,</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Fan_1_Active,,BitAddress,PLC1,012349,,</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
-        <f>'Point List'!C68</f>
-        <v>Critical_Temperature</v>
+        <f>'Point List'!C102</f>
+        <v>Fan_2_Active</v>
       </c>
       <c r="C59" t="str">
-        <f>'Point List'!L68</f>
+        <f>'Point List'!L102</f>
         <v>BitAddress</v>
       </c>
       <c r="D59" t="s">
         <v>214</v>
       </c>
       <c r="E59" t="str">
-        <f>'Point List'!J68</f>
-        <v>012337</v>
+        <f>'Point List'!J102</f>
+        <v>012350</v>
       </c>
       <c r="K59" t="str">
-        <f t="shared" ref="K59:K75" si="1">_xlfn.CONCAT(A59,",",B59,",",C59,",",D59,",",E59,",",F59,",",G59)</f>
-        <v>Critical_Temperature,,BitAddress,PLC1,012337,,</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>Fan_2_Active,,BitAddress,PLC1,012350,,</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
-        <f>'Point List'!C69</f>
-        <v>Critical_Vessel_Level</v>
+        <f>'Point List'!C103</f>
+        <v>Pump_Cycle_Enabled</v>
       </c>
       <c r="C60" t="str">
-        <f>'Point List'!L69</f>
+        <f>'Point List'!L103</f>
         <v>BitAddress</v>
       </c>
       <c r="D60" t="s">
         <v>214</v>
       </c>
       <c r="E60" t="str">
-        <f>'Point List'!J69</f>
-        <v>012338</v>
+        <f>'Point List'!J103</f>
+        <v>012351</v>
       </c>
       <c r="K60" t="str">
         <f t="shared" si="1"/>
-        <v>Critical_Vessel_Level,,BitAddress,PLC1,012338,,</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+        <v>Pump_Cycle_Enabled,,BitAddress,PLC1,012351,,</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
-        <f>'Point List'!C70</f>
-        <v>Critical_Conductivity</v>
+        <f>'Point List'!C104</f>
+        <v>System_Diagnostics</v>
       </c>
       <c r="C61" t="str">
-        <f>'Point List'!L70</f>
+        <f>'Point List'!L104</f>
         <v>BitAddress</v>
       </c>
       <c r="D61" t="s">
         <v>214</v>
       </c>
       <c r="E61" t="str">
-        <f>'Point List'!J70</f>
-        <v>012339</v>
+        <f>'Point List'!J104</f>
+        <v>012352</v>
       </c>
       <c r="K61" t="str">
         <f t="shared" si="1"/>
-        <v>Critical_Conductivity,,BitAddress,PLC1,012339,,</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+        <v>System_Diagnostics,,BitAddress,PLC1,012352,,</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
-        <f>'Point List'!C71</f>
-        <v>Level_Sensor_Malfunction</v>
+        <f>'Point List'!C105</f>
+        <v>Status_Indicator_Text</v>
       </c>
       <c r="C62" t="str">
-        <f>'Point List'!L71</f>
-        <v>BitAddress</v>
+        <f>'Point List'!L105</f>
+        <v>WordAddress</v>
       </c>
       <c r="D62" t="s">
         <v>214</v>
       </c>
       <c r="E62" t="str">
-        <f>'Point List'!J71</f>
-        <v>012340</v>
+        <f>'Point List'!J105</f>
+        <v>412683</v>
       </c>
       <c r="K62" t="str">
         <f t="shared" si="1"/>
-        <v>Level_Sensor_Malfunction,,BitAddress,PLC1,012340,,</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" t="str">
-        <f>'Point List'!C72</f>
-        <v>Conductivity_Sensor_Malfunction</v>
-      </c>
-      <c r="C63" t="str">
-        <f>'Point List'!L72</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D63" t="s">
-        <v>214</v>
-      </c>
-      <c r="E63" t="str">
-        <f>'Point List'!J72</f>
-        <v>012341</v>
-      </c>
-      <c r="K63" t="str">
-        <f t="shared" si="1"/>
-        <v>Conductivity_Sensor_Malfunction,,BitAddress,PLC1,012341,,</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" t="str">
-        <f>'Point List'!C73</f>
-        <v>Bingo_Pumps</v>
-      </c>
-      <c r="C64" t="str">
-        <f>'Point List'!L73</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D64" t="s">
-        <v>214</v>
-      </c>
-      <c r="E64" t="str">
-        <f>'Point List'!J73</f>
-        <v>012342</v>
-      </c>
-      <c r="K64" t="str">
-        <f t="shared" si="1"/>
-        <v>Bingo_Pumps,,BitAddress,PLC1,012342,,</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" t="str">
-        <f>'Point List'!C74</f>
-        <v>Temperature_Sensor_Malfunction</v>
-      </c>
-      <c r="C65" t="str">
-        <f>'Point List'!L74</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D65" t="s">
-        <v>214</v>
-      </c>
-      <c r="E65" t="str">
-        <f>'Point List'!J74</f>
-        <v>012343</v>
-      </c>
-      <c r="K65" t="str">
-        <f t="shared" si="1"/>
-        <v>Temperature_Sensor_Malfunction,,BitAddress,PLC1,012343,,</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" t="str">
-        <f>'Point List'!C75</f>
-        <v>Bad_Valve_Pos</v>
-      </c>
-      <c r="C66" t="str">
-        <f>'Point List'!L75</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D66" t="s">
-        <v>214</v>
-      </c>
-      <c r="E66" t="str">
-        <f>'Point List'!J75</f>
-        <v>012344</v>
-      </c>
-      <c r="K66" t="str">
-        <f t="shared" si="1"/>
-        <v>Bad_Valve_Pos,,BitAddress,PLC1,012344,,</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" t="str">
-        <f>'Point List'!C76</f>
-        <v>Master_Fault_Signal</v>
-      </c>
-      <c r="C67" t="str">
-        <f>'Point List'!L76</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D67" t="s">
-        <v>214</v>
-      </c>
-      <c r="E67" t="str">
-        <f>'Point List'!J76</f>
-        <v>012345</v>
-      </c>
-      <c r="K67" t="str">
-        <f t="shared" si="1"/>
-        <v>Master_Fault_Signal,,BitAddress,PLC1,012345,,</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" t="str">
-        <f>'Point List'!C98</f>
-        <v>Primary_Pump_Active</v>
-      </c>
-      <c r="C68" t="str">
-        <f>'Point List'!L98</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D68" t="s">
-        <v>214</v>
-      </c>
-      <c r="E68" t="str">
-        <f>'Point List'!J98</f>
-        <v>012346</v>
-      </c>
-      <c r="K68" t="str">
-        <f t="shared" si="1"/>
-        <v>Primary_Pump_Active,,BitAddress,PLC1,012346,,</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" t="str">
-        <f>'Point List'!C99</f>
-        <v>Secondary_Pump__Active</v>
-      </c>
-      <c r="C69" t="str">
-        <f>'Point List'!L99</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D69" t="s">
-        <v>214</v>
-      </c>
-      <c r="E69" t="str">
-        <f>'Point List'!J99</f>
-        <v>012347</v>
-      </c>
-      <c r="K69" t="str">
-        <f t="shared" si="1"/>
-        <v>Secondary_Pump__Active,,BitAddress,PLC1,012347,,</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" t="str">
-        <f>'Point List'!C100</f>
-        <v>Simplex_Mode_Active</v>
-      </c>
-      <c r="C70" t="str">
-        <f>'Point List'!L100</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D70" t="s">
-        <v>214</v>
-      </c>
-      <c r="E70" t="str">
-        <f>'Point List'!J100</f>
-        <v>012348</v>
-      </c>
-      <c r="K70" t="str">
-        <f t="shared" si="1"/>
-        <v>Simplex_Mode_Active,,BitAddress,PLC1,012348,,</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" t="str">
-        <f>'Point List'!C101</f>
-        <v>Fan_1_Active</v>
-      </c>
-      <c r="C71" t="str">
-        <f>'Point List'!L101</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D71" t="s">
-        <v>214</v>
-      </c>
-      <c r="E71" t="str">
-        <f>'Point List'!J101</f>
-        <v>012349</v>
-      </c>
-      <c r="K71" t="str">
-        <f t="shared" si="1"/>
-        <v>Fan_1_Active,,BitAddress,PLC1,012349,,</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" t="str">
-        <f>'Point List'!C102</f>
-        <v>Fan_2_Active</v>
-      </c>
-      <c r="C72" t="str">
-        <f>'Point List'!L102</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D72" t="s">
-        <v>214</v>
-      </c>
-      <c r="E72" t="str">
-        <f>'Point List'!J102</f>
-        <v>012350</v>
-      </c>
-      <c r="K72" t="str">
-        <f t="shared" si="1"/>
-        <v>Fan_2_Active,,BitAddress,PLC1,012350,,</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" t="str">
-        <f>'Point List'!C103</f>
-        <v>Pump_Cycle_Enabled</v>
-      </c>
-      <c r="C73" t="str">
-        <f>'Point List'!L103</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D73" t="s">
-        <v>214</v>
-      </c>
-      <c r="E73" t="str">
-        <f>'Point List'!J103</f>
-        <v>012351</v>
-      </c>
-      <c r="K73" t="str">
-        <f t="shared" si="1"/>
-        <v>Pump_Cycle_Enabled,,BitAddress,PLC1,012351,,</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" t="str">
-        <f>'Point List'!C104</f>
-        <v>System_Diagnostics</v>
-      </c>
-      <c r="C74" t="str">
-        <f>'Point List'!L104</f>
-        <v>BitAddress</v>
-      </c>
-      <c r="D74" t="s">
-        <v>214</v>
-      </c>
-      <c r="E74" t="str">
-        <f>'Point List'!J104</f>
-        <v>012352</v>
-      </c>
-      <c r="K74" t="str">
-        <f t="shared" si="1"/>
-        <v>System_Diagnostics,,BitAddress,PLC1,012352,,</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" t="str">
-        <f>'Point List'!C105</f>
-        <v>Status_Indicator_Text</v>
-      </c>
-      <c r="C75" t="str">
-        <f>'Point List'!L105</f>
-        <v>WordAddress</v>
-      </c>
-      <c r="D75" t="s">
-        <v>214</v>
-      </c>
-      <c r="E75" t="str">
-        <f>'Point List'!J105</f>
-        <v>412683</v>
-      </c>
-      <c r="K75" t="str">
-        <f t="shared" si="1"/>
         <v>Status_Indicator_Text,,WordAddress,PLC1,412683,,</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <f>'Point List'!C174</f>
-        <v>0</v>
-      </c>
-      <c r="C76">
-        <f>'Point List'!L174</f>
-        <v>0</v>
-      </c>
-      <c r="D76" t="s">
-        <v>214</v>
-      </c>
-      <c r="E76">
-        <f>'Point List'!J174</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <f>'Point List'!C175</f>
-        <v>0</v>
-      </c>
-      <c r="C77">
-        <f>'Point List'!L175</f>
-        <v>0</v>
-      </c>
-      <c r="D77" t="s">
-        <v>214</v>
-      </c>
-      <c r="E77">
-        <f>'Point List'!J175</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <f>'Point List'!C176</f>
-        <v>0</v>
-      </c>
-      <c r="C78">
-        <f>'Point List'!L176</f>
-        <v>0</v>
-      </c>
-      <c r="D78" t="s">
-        <v>214</v>
-      </c>
-      <c r="E78">
-        <f>'Point List'!J176</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <f>'Point List'!C177</f>
-        <v>0</v>
-      </c>
-      <c r="C79">
-        <f>'Point List'!L177</f>
-        <v>0</v>
-      </c>
-      <c r="D79" t="s">
-        <v>214</v>
-      </c>
-      <c r="E79">
-        <f>'Point List'!J177</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <f>'Point List'!C178</f>
-        <v>0</v>
-      </c>
-      <c r="C80">
-        <f>'Point List'!L178</f>
-        <v>0</v>
-      </c>
-      <c r="D80" t="s">
-        <v>214</v>
-      </c>
-      <c r="E80">
-        <f>'Point List'!J178</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <f>'Point List'!C179</f>
-        <v>0</v>
-      </c>
-      <c r="C81">
-        <f>'Point List'!L179</f>
-        <v>0</v>
-      </c>
-      <c r="D81" t="s">
-        <v>214</v>
-      </c>
-      <c r="E81">
-        <f>'Point List'!J179</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <f>'Point List'!C180</f>
-        <v>0</v>
-      </c>
-      <c r="C82">
-        <f>'Point List'!L180</f>
-        <v>0</v>
-      </c>
-      <c r="D82" t="s">
-        <v>214</v>
-      </c>
-      <c r="E82">
-        <f>'Point List'!J180</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <f>'Point List'!C181</f>
-        <v>0</v>
-      </c>
-      <c r="C83">
-        <f>'Point List'!L181</f>
-        <v>0</v>
-      </c>
-      <c r="D83" t="s">
-        <v>214</v>
-      </c>
-      <c r="E83">
-        <f>'Point List'!J181</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <f>'Point List'!C182</f>
-        <v>0</v>
-      </c>
-      <c r="C84">
-        <f>'Point List'!L182</f>
-        <v>0</v>
-      </c>
-      <c r="D84" t="s">
-        <v>214</v>
-      </c>
-      <c r="E84">
-        <f>'Point List'!J182</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <f>'Point List'!C183</f>
-        <v>0</v>
-      </c>
-      <c r="C85">
-        <f>'Point List'!L183</f>
-        <v>0</v>
-      </c>
-      <c r="D85" t="s">
-        <v>214</v>
-      </c>
-      <c r="E85">
-        <f>'Point List'!J183</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <f>'Point List'!C184</f>
-        <v>0</v>
-      </c>
-      <c r="C86">
-        <f>'Point List'!L184</f>
-        <v>0</v>
-      </c>
-      <c r="D86" t="s">
-        <v>214</v>
-      </c>
-      <c r="E86">
-        <f>'Point List'!J184</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <f>'Point List'!C185</f>
-        <v>0</v>
-      </c>
-      <c r="C87">
-        <f>'Point List'!L185</f>
-        <v>0</v>
-      </c>
-      <c r="D87" t="s">
-        <v>214</v>
-      </c>
-      <c r="E87">
-        <f>'Point List'!J185</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <f>'Point List'!C186</f>
-        <v>0</v>
-      </c>
-      <c r="C88">
-        <f>'Point List'!L186</f>
-        <v>0</v>
-      </c>
-      <c r="D88" t="s">
-        <v>214</v>
-      </c>
-      <c r="E88">
-        <f>'Point List'!J186</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <f>'Point List'!C187</f>
-        <v>0</v>
-      </c>
-      <c r="C89">
-        <f>'Point List'!L187</f>
-        <v>0</v>
-      </c>
-      <c r="D89" t="s">
-        <v>214</v>
-      </c>
-      <c r="E89">
-        <f>'Point List'!J187</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <f>'Point List'!C188</f>
-        <v>0</v>
-      </c>
-      <c r="C90">
-        <f>'Point List'!L188</f>
-        <v>0</v>
-      </c>
-      <c r="D90" t="s">
-        <v>214</v>
-      </c>
-      <c r="E90">
-        <f>'Point List'!J188</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <f>'Point List'!C189</f>
-        <v>0</v>
-      </c>
-      <c r="C91">
-        <f>'Point List'!L189</f>
-        <v>0</v>
-      </c>
-      <c r="D91" t="s">
-        <v>214</v>
-      </c>
-      <c r="E91">
-        <f>'Point List'!J189</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <f>'Point List'!C190</f>
-        <v>0</v>
-      </c>
-      <c r="C92">
-        <f>'Point List'!L190</f>
-        <v>0</v>
-      </c>
-      <c r="D92" t="s">
-        <v>214</v>
-      </c>
-      <c r="E92">
-        <f>'Point List'!J190</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <f>'Point List'!C191</f>
-        <v>0</v>
-      </c>
-      <c r="C93">
-        <f>'Point List'!L191</f>
-        <v>0</v>
-      </c>
-      <c r="D93" t="s">
-        <v>214</v>
-      </c>
-      <c r="E93">
-        <f>'Point List'!J191</f>
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2071" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B7649CE-CF59-45F1-B9E0-04BF781030D4}"/>
+  <xr:revisionPtr revIDLastSave="2082" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42753FDD-5063-47D6-8E99-AF95DFBA2975}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point List" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="347">
   <si>
     <t>Signal Type</t>
   </si>
@@ -1095,9 +1095,6 @@
     <t>wrValvePos</t>
   </si>
   <si>
-    <t>FALS</t>
-  </si>
-  <si>
     <t>Linked</t>
   </si>
   <si>
@@ -1804,13 +1801,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}" name="Table1" displayName="Table1" ref="A1:X106" totalsRowShown="0" headerRowDxfId="23">
-  <autoFilter ref="A1:X106" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="RESERVED"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:X106" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{423FA6DC-9142-4672-A14E-553234A081EF}" name="Signal Type" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{56D9DA24-EF6A-4F6A-8733-677B62E46902}" name="Tag No" dataDxfId="21"/>
@@ -2137,13 +2128,13 @@
         <v>106</v>
       </c>
       <c r="W1" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="X1" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="X1" s="17" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -2178,7 +2169,7 @@
         <v>11</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>11</v>
@@ -2214,7 +2205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -2293,7 +2284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -2372,7 +2363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2451,7 +2442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -2530,7 +2521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -2609,7 +2600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2688,7 +2679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -2726,7 +2717,7 @@
         <v>11</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M9" s="6">
         <v>1</v>
@@ -2767,7 +2758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -2846,7 +2837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -2925,7 +2916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -2963,7 +2954,7 @@
         <v>177</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M12" s="6">
         <v>1</v>
@@ -3004,7 +2995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -3042,7 +3033,7 @@
         <v>177</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M13" s="6">
         <v>1</v>
@@ -3083,7 +3074,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>8</v>
       </c>
@@ -3162,7 +3153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -3241,7 +3232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>8</v>
       </c>
@@ -3276,7 +3267,7 @@
         <v>012302</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>215</v>
@@ -3317,10 +3308,10 @@
         <v>1</v>
       </c>
       <c r="X16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -3356,7 +3347,7 @@
         <v>11</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M17" s="6">
         <v>1</v>
@@ -3397,7 +3388,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
@@ -3433,7 +3424,7 @@
         <v>11</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M18" s="6">
         <v>1</v>
@@ -3474,7 +3465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
@@ -3512,7 +3503,7 @@
         <v>180</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M19" s="6">
         <v>1</v>
@@ -3553,7 +3544,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>26</v>
       </c>
@@ -3591,7 +3582,7 @@
         <v>180</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M20" s="6">
         <v>1</v>
@@ -3632,7 +3623,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>26</v>
       </c>
@@ -3670,7 +3661,7 @@
         <v>180</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M21" s="6">
         <v>1</v>
@@ -3711,7 +3702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>26</v>
       </c>
@@ -3749,7 +3740,7 @@
         <v>180</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M22" s="6">
         <v>1</v>
@@ -3790,7 +3781,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>26</v>
       </c>
@@ -3869,7 +3860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -3907,7 +3898,7 @@
         <v>181</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M24" s="6">
         <v>32</v>
@@ -3948,7 +3939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>26</v>
       </c>
@@ -4027,7 +4018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
@@ -4106,7 +4097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>26</v>
       </c>
@@ -4185,7 +4176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>26</v>
       </c>
@@ -4264,7 +4255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>26</v>
       </c>
@@ -4343,7 +4334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>26</v>
       </c>
@@ -4422,7 +4413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>26</v>
       </c>
@@ -4458,7 +4449,7 @@
         <v>181</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M31" s="6">
         <v>32</v>
@@ -4499,7 +4490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>26</v>
       </c>
@@ -4616,7 +4607,7 @@
         <v>11</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M33" s="6">
         <v>1</v>
@@ -4695,7 +4686,7 @@
         <v>11</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M34" s="6">
         <v>1</v>
@@ -4774,7 +4765,7 @@
         <v>11</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M35" s="6">
         <v>1</v>
@@ -4853,7 +4844,7 @@
         <v>11</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M36" s="6">
         <v>1</v>
@@ -4932,7 +4923,7 @@
         <v>11</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M37" s="6">
         <v>1</v>
@@ -5011,7 +5002,7 @@
         <v>180</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M38" s="6">
         <v>1</v>
@@ -5090,7 +5081,7 @@
         <v>180</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M39" s="6">
         <v>1</v>
@@ -5169,7 +5160,7 @@
         <v>180</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M40" s="6">
         <v>1</v>
@@ -5248,7 +5239,7 @@
         <v>180</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M41" s="6">
         <v>1</v>
@@ -5327,7 +5318,7 @@
         <v>180</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M42" s="6">
         <v>1</v>
@@ -5406,7 +5397,7 @@
         <v>11</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M43" s="6">
         <v>32</v>
@@ -5485,7 +5476,7 @@
         <v>11</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M44" s="6">
         <v>1</v>
@@ -5526,7 +5517,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>26</v>
       </c>
@@ -5605,7 +5596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>26</v>
       </c>
@@ -5684,7 +5675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>26</v>
       </c>
@@ -5719,7 +5710,7 @@
         <v>181</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M47" s="6">
         <v>32</v>
@@ -5756,11 +5747,11 @@
       <c r="W47" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="X47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>26</v>
       </c>
@@ -5795,7 +5786,7 @@
         <v>11</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M48" s="6">
         <v>32</v>
@@ -5833,10 +5824,10 @@
         <v>1</v>
       </c>
       <c r="X48" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>26</v>
       </c>
@@ -5912,10 +5903,10 @@
         <v>1</v>
       </c>
       <c r="X49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>26</v>
       </c>
@@ -5991,10 +5982,10 @@
         <v>1</v>
       </c>
       <c r="X50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>53</v>
       </c>
@@ -6070,10 +6061,10 @@
         <v>1</v>
       </c>
       <c r="X51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>53</v>
       </c>
@@ -6149,10 +6140,10 @@
         <v>1</v>
       </c>
       <c r="X52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -6228,10 +6219,10 @@
         <v>1</v>
       </c>
       <c r="X53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>53</v>
       </c>
@@ -6307,10 +6298,10 @@
         <v>1</v>
       </c>
       <c r="X54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>53</v>
       </c>
@@ -6386,10 +6377,10 @@
         <v>1</v>
       </c>
       <c r="X55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>53</v>
       </c>
@@ -6465,10 +6456,10 @@
         <v>1</v>
       </c>
       <c r="X56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>53</v>
       </c>
@@ -6544,10 +6535,10 @@
         <v>1</v>
       </c>
       <c r="X57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>53</v>
       </c>
@@ -6623,10 +6614,10 @@
         <v>1</v>
       </c>
       <c r="X58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>53</v>
       </c>
@@ -6702,10 +6693,10 @@
         <v>1</v>
       </c>
       <c r="X59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>53</v>
       </c>
@@ -6781,10 +6772,10 @@
         <v>1</v>
       </c>
       <c r="X60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>53</v>
       </c>
@@ -6860,10 +6851,10 @@
         <v>1</v>
       </c>
       <c r="X61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>53</v>
       </c>
@@ -6939,10 +6930,10 @@
         <v>1</v>
       </c>
       <c r="X62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>53</v>
       </c>
@@ -7018,10 +7009,10 @@
         <v>1</v>
       </c>
       <c r="X63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>53</v>
       </c>
@@ -7097,10 +7088,10 @@
         <v>1</v>
       </c>
       <c r="X64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>53</v>
       </c>
@@ -7176,10 +7167,10 @@
         <v>1</v>
       </c>
       <c r="X65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>53</v>
       </c>
@@ -7255,10 +7246,10 @@
         <v>1</v>
       </c>
       <c r="X66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>53</v>
       </c>
@@ -7334,10 +7325,10 @@
         <v>1</v>
       </c>
       <c r="X67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>71</v>
       </c>
@@ -7413,10 +7404,10 @@
         <v>1</v>
       </c>
       <c r="X68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>71</v>
       </c>
@@ -7492,10 +7483,10 @@
         <v>1</v>
       </c>
       <c r="X69" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>71</v>
       </c>
@@ -7571,10 +7562,10 @@
         <v>1</v>
       </c>
       <c r="X70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -7650,10 +7641,10 @@
         <v>1</v>
       </c>
       <c r="X71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>71</v>
       </c>
@@ -7729,10 +7720,10 @@
         <v>1</v>
       </c>
       <c r="X72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>71</v>
       </c>
@@ -7808,10 +7799,10 @@
         <v>1</v>
       </c>
       <c r="X73" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>71</v>
       </c>
@@ -7887,10 +7878,10 @@
         <v>1</v>
       </c>
       <c r="X74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>71</v>
       </c>
@@ -7966,10 +7957,10 @@
         <v>1</v>
       </c>
       <c r="X75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>71</v>
       </c>
@@ -8045,10 +8036,10 @@
         <v>1</v>
       </c>
       <c r="X76" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>80</v>
       </c>
@@ -8083,7 +8074,7 @@
         <v>11</v>
       </c>
       <c r="L77" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M77" s="5">
         <v>16</v>
@@ -8122,7 +8113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>80</v>
       </c>
@@ -8157,7 +8148,7 @@
         <v>11</v>
       </c>
       <c r="L78" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M78" s="5">
         <v>16</v>
@@ -8196,7 +8187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>80</v>
       </c>
@@ -8231,7 +8222,7 @@
         <v>11</v>
       </c>
       <c r="L79" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M79" s="5">
         <v>16</v>
@@ -8270,7 +8261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:24" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:24" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>80</v>
       </c>
@@ -8305,7 +8296,7 @@
         <v>11</v>
       </c>
       <c r="L80" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M80" s="5">
         <v>16</v>
@@ -8344,7 +8335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>80</v>
       </c>
@@ -8377,7 +8368,7 @@
         <v>11</v>
       </c>
       <c r="L81" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M81" s="5">
         <v>16</v>
@@ -8401,7 +8392,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>80</v>
       </c>
@@ -8434,7 +8425,7 @@
         <v>11</v>
       </c>
       <c r="L82" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M82" s="5">
         <v>16</v>
@@ -8458,7 +8449,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>80</v>
       </c>
@@ -8493,7 +8484,7 @@
         <v>11</v>
       </c>
       <c r="L83" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M83" s="5">
         <v>16</v>
@@ -8532,7 +8523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>80</v>
       </c>
@@ -8567,7 +8558,7 @@
         <v>11</v>
       </c>
       <c r="L84" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M84" s="6">
         <v>1</v>
@@ -8606,7 +8597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>80</v>
       </c>
@@ -8641,7 +8632,7 @@
         <v>11</v>
       </c>
       <c r="L85" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M85" s="6">
         <v>1</v>
@@ -8680,7 +8671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>80</v>
       </c>
@@ -8715,7 +8706,7 @@
         <v>11</v>
       </c>
       <c r="L86" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M86" s="6">
         <v>1</v>
@@ -8754,7 +8745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>80</v>
       </c>
@@ -8789,7 +8780,7 @@
         <v>11</v>
       </c>
       <c r="L87" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M87" s="6">
         <v>1</v>
@@ -8828,7 +8819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>80</v>
       </c>
@@ -8863,7 +8854,7 @@
         <v>11</v>
       </c>
       <c r="L88" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M88" s="6">
         <v>1</v>
@@ -8902,7 +8893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>80</v>
       </c>
@@ -8937,7 +8928,7 @@
         <v>11</v>
       </c>
       <c r="L89" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M89" s="6">
         <v>1</v>
@@ -8976,7 +8967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>80</v>
       </c>
@@ -9011,7 +9002,7 @@
         <v>11</v>
       </c>
       <c r="L90" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M90" s="6">
         <v>1</v>
@@ -9050,7 +9041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>80</v>
       </c>
@@ -9085,7 +9076,7 @@
         <v>11</v>
       </c>
       <c r="L91" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M91" s="6">
         <v>1</v>
@@ -9124,7 +9115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>80</v>
       </c>
@@ -9159,7 +9150,7 @@
         <v>11</v>
       </c>
       <c r="L92" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M92" s="5">
         <v>16</v>
@@ -9198,7 +9189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>80</v>
       </c>
@@ -9233,7 +9224,7 @@
         <v>11</v>
       </c>
       <c r="L93" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M93" s="6">
         <v>1</v>
@@ -9272,7 +9263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>80</v>
       </c>
@@ -9307,7 +9298,7 @@
         <v>11</v>
       </c>
       <c r="L94" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M94" s="5">
         <v>16</v>
@@ -9346,7 +9337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>80</v>
       </c>
@@ -9381,7 +9372,7 @@
         <v>11</v>
       </c>
       <c r="L95" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M95" s="5">
         <v>16</v>
@@ -9420,7 +9411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>80</v>
       </c>
@@ -9455,7 +9446,7 @@
         <v>11</v>
       </c>
       <c r="L96" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M96" s="5">
         <v>16</v>
@@ -9494,7 +9485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>80</v>
       </c>
@@ -9527,7 +9518,7 @@
         <v>11</v>
       </c>
       <c r="L97" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M97" s="5">
         <v>16</v>
@@ -9564,7 +9555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
         <v>26</v>
       </c>
@@ -9639,7 +9630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
         <v>26</v>
       </c>
@@ -9714,7 +9705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>26</v>
       </c>
@@ -9789,7 +9780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
         <v>26</v>
       </c>
@@ -9864,7 +9855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
         <v>26</v>
       </c>
@@ -9939,7 +9930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
         <v>26</v>
       </c>
@@ -10012,7 +10003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
         <v>26</v>
       </c>
@@ -10085,7 +10076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="15" t="s">
         <v>26</v>
       </c>
@@ -10161,7 +10152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>

--- a/Documentation/PLC Point List.xlsx
+++ b/Documentation/PLC Point List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2082" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42753FDD-5063-47D6-8E99-AF95DFBA2975}"/>
+  <xr:revisionPtr revIDLastSave="2089" documentId="11_796C421E84FB48855BB0FC3EBB1F0B72633B0612" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F47B2A94-1441-43B0-85FD-706685891B02}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Point List" sheetId="1" r:id="rId1"/>
@@ -1801,7 +1801,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}" name="Table1" displayName="Table1" ref="A1:X106" totalsRowShown="0" headerRowDxfId="23">
-  <autoFilter ref="A1:X106" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}"/>
+  <autoFilter ref="A1:X106" xr:uid="{B28E4E13-ED9D-48D1-8FE5-08F11708F130}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="IN-USE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{423FA6DC-9142-4672-A14E-553234A081EF}" name="Signal Type" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{56D9DA24-EF6A-4F6A-8733-677B62E46902}" name="Tag No" dataDxfId="21"/>
@@ -2679,7 +2685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -2916,7 +2922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -2995,7 +3001,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
@@ -3311,7 +3317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -3388,7 +3394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
@@ -3465,7 +3471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
@@ -3544,7 +3550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>26</v>
       </c>
@@ -3623,7 +3629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>26</v>
       </c>
@@ -3702,7 +3708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>26</v>
       </c>
@@ -3860,7 +3866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -4413,7 +4419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>26</v>
       </c>
@@ -4569,7 +4575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>26</v>
       </c>
@@ -4648,7 +4654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>26</v>
       </c>
@@ -4727,7 +4733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>26</v>
       </c>
@@ -4806,7 +4812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>26</v>
       </c>
@@ -4885,7 +4891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>26</v>
       </c>
@@ -4964,7 +4970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>26</v>
       </c>
@@ -5043,7 +5049,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>26</v>
       </c>
@@ -5122,7 +5128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>26</v>
       </c>
@@ -5201,7 +5207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>26</v>
       </c>
@@ -5280,7 +5286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>26</v>
       </c>
@@ -5359,7 +5365,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>26</v>
       </c>
@@ -5438,7 +5444,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>26</v>
       </c>
@@ -5675,7 +5681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>26</v>
       </c>
@@ -5751,7 +5757,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>26</v>
       </c>
@@ -8335,7 +8341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24" ht="13.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>80</v>
       </c>
@@ -8392,7 +8398,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>80</v>
       </c>
@@ -9485,7 +9491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>80</v>
       </c>
@@ -10152,7 +10158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
